--- a/Auto Finan/420财务050823.xlsx
+++ b/Auto Finan/420财务050823.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FH\source\repos\Auto Finan\Auto Finan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE67D96-22D2-448C-A0D7-419242C70F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248F7D63-EE9B-4C9F-9993-6A5FDA515DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2618" uniqueCount="1513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2677" uniqueCount="1517">
   <si>
     <t>教研室内部项目序号</t>
   </si>
@@ -4955,150 +4955,157 @@
     <t>登录按钮</t>
   </si>
   <si>
+    <t>网上预约报账按钮</t>
+  </si>
+  <si>
+    <t>已阅读并同意按钮</t>
+  </si>
+  <si>
+    <t>申请报销单按钮</t>
+  </si>
+  <si>
+    <t>业务大类</t>
+  </si>
+  <si>
+    <t>报销项目号</t>
+  </si>
+  <si>
+    <t>附件张数</t>
+  </si>
+  <si>
+    <t>支付方式</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>特殊事项说明</t>
+  </si>
+  <si>
+    <t>下一步按钮1</t>
+  </si>
+  <si>
+    <t>科目</t>
+  </si>
+  <si>
+    <t>金额</t>
+  </si>
+  <si>
+    <t>下一步按钮2</t>
+  </si>
+  <si>
+    <t>子序列开始</t>
+  </si>
+  <si>
+    <t>转卡信息工号</t>
+  </si>
+  <si>
+    <t>卡号尾号</t>
+  </si>
+  <si>
+    <t>个人金额</t>
+  </si>
+  <si>
+    <t>提交按钮</t>
+  </si>
+  <si>
+    <t>子序列结束</t>
+  </si>
+  <si>
+    <t>下一步按钮3</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>校区</t>
+  </si>
+  <si>
+    <t>预约按钮</t>
+  </si>
+  <si>
+    <t>打印确认单按钮</t>
+  </si>
+  <si>
+    <t>返回主页按钮</t>
+  </si>
+  <si>
+    <t>?PDF路径</t>
+  </si>
+  <si>
+    <t>?预约号</t>
+  </si>
+  <si>
+    <t>?涉及金额</t>
+  </si>
+  <si>
+    <t>?预约单状态</t>
+  </si>
+  <si>
+    <t>Kp5070016</t>
+  </si>
+  <si>
+    <t>$点击</t>
+  </si>
+  <si>
+    <t>$$报销业务</t>
+  </si>
+  <si>
+    <t>个人转卡</t>
+  </si>
+  <si>
+    <t>#H专用材料费</t>
+  </si>
+  <si>
+    <t>*2818</t>
+  </si>
+  <si>
+    <t>*5054</t>
+  </si>
+  <si>
+    <t>2025-09-14</t>
+  </si>
+  <si>
+    <t>$$清水河校区</t>
+  </si>
+  <si>
+    <t>$预约</t>
+  </si>
+  <si>
+    <t>#M专用材料费</t>
+  </si>
+  <si>
+    <t>*2231</t>
+  </si>
+  <si>
     <t>等待</t>
   </si>
   <si>
-    <t>网上预约报账按钮</t>
-  </si>
-  <si>
-    <t>申请报销单按钮</t>
-  </si>
-  <si>
-    <t>已阅读并同意按钮</t>
-  </si>
-  <si>
-    <t>业务大类</t>
-  </si>
-  <si>
-    <t>报销项目号</t>
-  </si>
-  <si>
-    <t>附件张数</t>
-  </si>
-  <si>
-    <t>支付方式</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>特殊事项说明</t>
-  </si>
-  <si>
-    <t>下一步按钮1</t>
-  </si>
-  <si>
-    <t>科目</t>
-  </si>
-  <si>
-    <t>金额</t>
-  </si>
-  <si>
-    <t>下一步按钮2</t>
-  </si>
-  <si>
-    <t>子序列开始</t>
-  </si>
-  <si>
-    <t>转卡信息工号</t>
-  </si>
-  <si>
-    <t>卡号尾号</t>
-  </si>
-  <si>
-    <t>个人金额</t>
-  </si>
-  <si>
-    <t>提交按钮</t>
-  </si>
-  <si>
-    <t>子序列结束</t>
-  </si>
-  <si>
-    <t>下一步按钮3</t>
-  </si>
-  <si>
-    <t>日期</t>
-  </si>
-  <si>
-    <t>校区</t>
-  </si>
-  <si>
-    <t>预约按钮</t>
-  </si>
-  <si>
-    <t>打印确认单按钮</t>
+    <t>选择业务大类</t>
   </si>
   <si>
     <t>返回按钮</t>
   </si>
   <si>
-    <t>?PDF路径</t>
-  </si>
-  <si>
-    <t>?预约号</t>
-  </si>
-  <si>
-    <t>?涉及金额</t>
-  </si>
-  <si>
-    <t>?预约单状态</t>
-  </si>
-  <si>
-    <t>Kp5070016</t>
+    <t>Uestc418</t>
+  </si>
+  <si>
+    <t>我是一条备注</t>
+  </si>
+  <si>
+    <t>我是特殊事项</t>
+  </si>
+  <si>
+    <t>#M电费</t>
+  </si>
+  <si>
+    <t>*1142</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
   </si>
   <si>
     <t>$点击</t>
-  </si>
-  <si>
-    <t>$$报销业务</t>
-  </si>
-  <si>
-    <t>个人转卡</t>
-  </si>
-  <si>
-    <t>#H专用材料费</t>
-  </si>
-  <si>
-    <t>*2818</t>
-  </si>
-  <si>
-    <t>2025-09-14</t>
-  </si>
-  <si>
-    <t>$$清水河校区</t>
-  </si>
-  <si>
-    <t>$预约</t>
-  </si>
-  <si>
-    <t>#M专用材料费</t>
-  </si>
-  <si>
-    <t>*2231</t>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>202422090507</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>$点击</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>等待</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>*5054</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>已预约</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -5106,7 +5113,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5229,6 +5236,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -5273,7 +5287,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -5348,12 +5362,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5583,6 +5608,16 @@
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5877,8 +5912,8 @@
     <col min="13" max="13" width="35.33203125" style="47" customWidth="1"/>
     <col min="14" max="15" width="14.25" style="47" customWidth="1"/>
     <col min="16" max="16" width="27" style="47" customWidth="1"/>
-    <col min="17" max="27" width="8.75" style="47" customWidth="1"/>
-    <col min="28" max="16384" width="8.75" style="47"/>
+    <col min="17" max="28" width="8.75" style="47" customWidth="1"/>
+    <col min="29" max="16384" width="8.75" style="47"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="46" customFormat="1" ht="32.5" customHeight="1">
@@ -17862,7 +17897,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AT4"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
@@ -17870,28 +17905,27 @@
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="14.58203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="11" width="9" customWidth="1"/>
-    <col min="12" max="12" width="18.25" customWidth="1"/>
-    <col min="13" max="13" width="5.33203125" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="9" customWidth="1"/>
-    <col min="16" max="17" width="18.25" customWidth="1"/>
-    <col min="18" max="18" width="11.08203125" customWidth="1"/>
-    <col min="19" max="19" width="18" customWidth="1"/>
-    <col min="22" max="22" width="13.25" customWidth="1"/>
-    <col min="23" max="23" width="8" customWidth="1"/>
-    <col min="26" max="26" width="13.83203125" customWidth="1"/>
-    <col min="30" max="30" width="13.4140625" style="84" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.33203125" customWidth="1"/>
-    <col min="37" max="37" width="11.5" customWidth="1"/>
-    <col min="39" max="40" width="9.33203125" customWidth="1"/>
-    <col min="41" max="41" width="16" customWidth="1"/>
-    <col min="42" max="42" width="14.33203125" customWidth="1"/>
-    <col min="43" max="43" width="73.6640625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="11" max="11" width="18.25" customWidth="1"/>
+    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="18.25" customWidth="1"/>
+    <col min="15" max="15" width="11.08203125" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="19" max="19" width="13.25" customWidth="1"/>
+    <col min="20" max="20" width="8" customWidth="1"/>
+    <col min="22" max="22" width="13.83203125" customWidth="1"/>
+    <col min="26" max="26" width="13.4140625" style="84" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.33203125" customWidth="1"/>
+    <col min="32" max="32" width="11.5" customWidth="1"/>
+    <col min="34" max="34" width="9.33203125" customWidth="1"/>
+    <col min="35" max="35" width="16" customWidth="1"/>
+    <col min="36" max="36" width="14.33203125" customWidth="1"/>
+    <col min="37" max="37" width="73.6640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" s="1" customFormat="1" ht="42">
+    <row r="1" spans="1:40" s="1" customFormat="1" ht="42">
       <c r="A1" s="2" t="s">
         <v>1457</v>
       </c>
@@ -17929,115 +17963,95 @@
         <v>1467</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>1468</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>1466</v>
-      </c>
-      <c r="P1" s="4" t="s">
+        <v>1467</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>1469</v>
       </c>
+      <c r="P1" s="5" t="s">
+        <v>1470</v>
+      </c>
       <c r="Q1" s="5" t="s">
-        <v>1466</v>
+        <v>1471</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="Y1" s="5" t="s">
-        <v>1466</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>1477</v>
+        <v>1479</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>1480</v>
       </c>
       <c r="AA1" s="5" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="AB1" s="5" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="AC1" s="5" t="s">
-        <v>1480</v>
-      </c>
-      <c r="AD1" s="6" t="s">
-        <v>1481</v>
+        <v>1483</v>
+      </c>
+      <c r="AD1" s="5" t="s">
+        <v>1484</v>
       </c>
       <c r="AE1" s="5" t="s">
-        <v>1482</v>
-      </c>
-      <c r="AF1" s="5" t="s">
-        <v>1483</v>
+        <v>1485</v>
+      </c>
+      <c r="AF1" s="6" t="s">
+        <v>1486</v>
       </c>
       <c r="AG1" s="5" t="s">
-        <v>1484</v>
+        <v>1487</v>
       </c>
       <c r="AH1" s="5" t="s">
-        <v>1510</v>
+        <v>1488</v>
       </c>
       <c r="AI1" s="5" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="AJ1" s="5" t="s">
-        <v>1486</v>
-      </c>
-      <c r="AK1" s="6" t="s">
-        <v>1487</v>
-      </c>
-      <c r="AL1" s="5" t="s">
-        <v>1488</v>
-      </c>
-      <c r="AM1" s="5" t="s">
-        <v>1489</v>
-      </c>
-      <c r="AN1" s="5" t="s">
-        <v>1466</v>
-      </c>
-      <c r="AO1" s="5" t="s">
         <v>1490</v>
       </c>
-      <c r="AP1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>1491</v>
       </c>
-      <c r="AQ1" s="5" t="s">
+      <c r="AL1" s="79" t="s">
         <v>1492</v>
       </c>
-      <c r="AR1" s="79" t="s">
+      <c r="AM1" s="79" t="s">
         <v>1493</v>
       </c>
-      <c r="AS1" s="79" t="s">
+      <c r="AN1" s="79" t="s">
         <v>1494</v>
       </c>
-      <c r="AT1" s="79" t="s">
-        <v>1495</v>
-      </c>
-    </row>
-    <row r="2" spans="1:46">
+    </row>
+    <row r="2" spans="1:40">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
-        <v>1512</v>
-      </c>
+      <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3">
@@ -18047,82 +18061,67 @@
         <v>5070016</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>1497</v>
       </c>
-      <c r="K2" s="3">
-        <v>5</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="M2" s="3">
-        <v>6</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="O2" s="3">
-        <v>3</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>5</v>
+      <c r="P2" s="78" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q2" s="78">
+        <v>2</v>
       </c>
       <c r="R2" s="3" t="s">
         <v>1498</v>
       </c>
-      <c r="S2" s="78" t="s">
-        <v>361</v>
-      </c>
-      <c r="T2" s="78">
-        <v>2</v>
-      </c>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
       <c r="U2" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="V2" s="3" t="s">
         <v>1499</v>
       </c>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
+      <c r="W2" s="3">
+        <v>3600</v>
+      </c>
       <c r="X2" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z2" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" s="7">
+        <v>5070016</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>1500</v>
       </c>
-      <c r="AA2" s="3">
-        <v>3600</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>1497</v>
+      <c r="AB2" s="3">
+        <v>3500</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD2" s="7">
-        <v>5070016</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>1501</v>
-      </c>
-      <c r="AF2" s="3">
-        <v>3500</v>
-      </c>
-      <c r="AG2" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="AH2" s="3">
-        <v>3</v>
-      </c>
-      <c r="AI2" s="3"/>
-    </row>
-    <row r="3" spans="1:46">
+        <v>1496</v>
+      </c>
+      <c r="AD2" s="3"/>
+    </row>
+    <row r="3" spans="1:40">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -18140,61 +18139,51 @@
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
       <c r="R3" s="3"/>
-      <c r="S3" s="78"/>
-      <c r="T3" s="78"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="7" t="s">
-        <v>1508</v>
+      <c r="Z3" s="7" t="s">
+        <v>993</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>1501</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="AE3" s="3" t="s">
-        <v>1511</v>
-      </c>
-      <c r="AF3" s="3">
-        <v>100</v>
+        <v>1496</v>
+      </c>
+      <c r="AF3" s="7" t="s">
+        <v>1502</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>1509</v>
-      </c>
-      <c r="AH3" s="3">
-        <v>3</v>
+        <v>1503</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>1504</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>1507</v>
+        <v>1496</v>
       </c>
       <c r="AJ3" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="AK3" s="7" t="s">
-        <v>1502</v>
-      </c>
-      <c r="AL3" s="3" t="s">
-        <v>1503</v>
-      </c>
-      <c r="AM3" s="3" t="s">
-        <v>1504</v>
-      </c>
-      <c r="AN3" s="3">
-        <v>5</v>
-      </c>
-      <c r="AO3" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="AP3" s="3" t="s">
-        <v>1497</v>
-      </c>
-    </row>
-    <row r="4" spans="1:46">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -18208,102 +18197,84 @@
         <v>5070016</v>
       </c>
       <c r="I4" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>1497</v>
       </c>
-      <c r="K4" s="3">
-        <v>5</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="M4" s="3">
-        <v>6</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="O4" s="3">
-        <v>3</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="Q4" s="3">
+      <c r="P4" s="78" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q4" s="78">
         <v>5</v>
       </c>
       <c r="R4" s="3" t="s">
         <v>1498</v>
       </c>
-      <c r="S4" s="78" t="s">
-        <v>386</v>
-      </c>
-      <c r="T4" s="78">
-        <v>5</v>
-      </c>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>1499</v>
-      </c>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
+        <v>1496</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="W4" s="3">
+        <v>560</v>
+      </c>
       <c r="X4" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="Y4" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z4" s="3" t="s">
-        <v>1505</v>
-      </c>
-      <c r="AA4" s="3">
+        <v>1496</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z4" s="83">
+        <v>5110016</v>
+      </c>
+      <c r="AA4" s="78" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB4" s="3">
         <v>560</v>
       </c>
-      <c r="AB4" s="3" t="s">
-        <v>1497</v>
-      </c>
       <c r="AC4" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AD4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AD4" s="83">
-        <v>5110016</v>
-      </c>
-      <c r="AE4" s="78" t="s">
-        <v>1506</v>
-      </c>
-      <c r="AF4" s="3">
-        <v>560</v>
+      <c r="AE4" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AF4" s="7" t="s">
+        <v>1502</v>
       </c>
       <c r="AG4" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="AH4" s="3">
-        <v>3</v>
+        <v>1503</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>1504</v>
       </c>
       <c r="AI4" s="3" t="s">
-        <v>22</v>
+        <v>1496</v>
       </c>
       <c r="AJ4" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="AK4" s="7" t="s">
-        <v>1502</v>
-      </c>
-      <c r="AL4" s="3" t="s">
-        <v>1503</v>
-      </c>
-      <c r="AM4" s="3" t="s">
-        <v>1504</v>
-      </c>
-      <c r="AN4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AO4" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="AP4" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
   </sheetData>
@@ -18314,9 +18285,263 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
+  <cols>
+    <col min="28" max="28" width="13.4140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:40" ht="42">
+      <c r="A1" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G1" s="85" t="s">
+        <v>403</v>
+      </c>
+      <c r="H1" s="85" t="s">
+        <v>1463</v>
+      </c>
+      <c r="I1" s="85" t="s">
+        <v>1464</v>
+      </c>
+      <c r="J1" s="85" t="s">
+        <v>1465</v>
+      </c>
+      <c r="K1" s="85" t="s">
+        <v>1507</v>
+      </c>
+      <c r="L1" s="85" t="s">
+        <v>1466</v>
+      </c>
+      <c r="M1" s="85" t="s">
+        <v>1507</v>
+      </c>
+      <c r="N1" s="85" t="s">
+        <v>1468</v>
+      </c>
+      <c r="O1" s="85" t="s">
+        <v>1467</v>
+      </c>
+      <c r="P1" s="86" t="s">
+        <v>1507</v>
+      </c>
+      <c r="Q1" s="86" t="s">
+        <v>1508</v>
+      </c>
+      <c r="R1" s="86" t="s">
+        <v>1470</v>
+      </c>
+      <c r="S1" s="86" t="s">
+        <v>1471</v>
+      </c>
+      <c r="T1" s="86" t="s">
+        <v>1472</v>
+      </c>
+      <c r="U1" s="86" t="s">
+        <v>1473</v>
+      </c>
+      <c r="V1" s="86" t="s">
+        <v>1474</v>
+      </c>
+      <c r="W1" s="86" t="s">
+        <v>1475</v>
+      </c>
+      <c r="X1" s="86" t="s">
+        <v>1476</v>
+      </c>
+      <c r="Y1" s="86" t="s">
+        <v>1477</v>
+      </c>
+      <c r="Z1" s="86" t="s">
+        <v>1478</v>
+      </c>
+      <c r="AA1" s="86" t="s">
+        <v>1479</v>
+      </c>
+      <c r="AB1" s="86" t="s">
+        <v>1480</v>
+      </c>
+      <c r="AC1" s="86" t="s">
+        <v>1507</v>
+      </c>
+      <c r="AD1" s="86" t="s">
+        <v>1481</v>
+      </c>
+      <c r="AE1" s="86" t="s">
+        <v>1482</v>
+      </c>
+      <c r="AF1" s="86" t="s">
+        <v>1483</v>
+      </c>
+      <c r="AG1" s="86" t="s">
+        <v>1507</v>
+      </c>
+      <c r="AH1" s="86" t="s">
+        <v>1484</v>
+      </c>
+      <c r="AI1" s="86" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AJ1" s="87" t="s">
+        <v>1486</v>
+      </c>
+      <c r="AK1" s="86" t="s">
+        <v>1487</v>
+      </c>
+      <c r="AL1" s="86" t="s">
+        <v>1488</v>
+      </c>
+      <c r="AM1" s="86" t="s">
+        <v>1507</v>
+      </c>
+      <c r="AN1" s="86" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>5130008</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="R2" t="s">
+        <v>250</v>
+      </c>
+      <c r="S2">
+        <v>2</v>
+      </c>
+      <c r="T2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="U2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="V2" t="s">
+        <v>1512</v>
+      </c>
+      <c r="W2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="X2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="Y2">
+        <v>100</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB2" s="88">
+        <v>5130008</v>
+      </c>
+      <c r="AC2" s="88">
+        <v>3</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="AE2">
+        <v>50</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AG2">
+        <v>3</v>
+      </c>
+      <c r="AJ2" s="84"/>
+    </row>
+    <row r="3" spans="1:40">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="88">
+        <v>202422090507</v>
+      </c>
+      <c r="AC3" s="88">
+        <v>3</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>1501</v>
+      </c>
+      <c r="AE3">
+        <v>50</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AG3">
+        <v>3</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AJ3" s="84" t="s">
+        <v>1515</v>
+      </c>
+      <c r="AK3" s="20" t="s">
+        <v>1503</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AM3">
+        <v>5</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -18350,6 +18575,6 @@
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Auto Finan/420财务050823.xlsx
+++ b/Auto Finan/420财务050823.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FH\source\repos\Auto Finan\Auto Finan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248F7D63-EE9B-4C9F-9993-6A5FDA515DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D11B1A-1325-498A-8B1B-14616A8068DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <sheet name="2-助研" sheetId="8" r:id="rId8"/>
     <sheet name="2-工资" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2677" uniqueCount="1517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="1516">
   <si>
     <t>教研室内部项目序号</t>
   </si>
@@ -147,7 +147,7 @@
     <t>是</t>
   </si>
   <si>
-    <t>项目余额: 10.151726; 
+    <t xml:space="preserve">项目余额: 10.151726; 
 收入: 450; 
 支出: 10.151726; 
 （一）直接费用: 10.151726; 
@@ -202,7 +202,7 @@
     <t>省-成果转化</t>
   </si>
   <si>
-    <t>项目余额: 0.0017; 
+    <t xml:space="preserve">项目余额: 0.0017; 
 收入: 45; 
 支出: 0.0017; 
 （一）直接费用: 0.0017; 
@@ -252,7 +252,7 @@
     <t>科瑞</t>
   </si>
   <si>
-    <t>项目余额: 1.650842; 
+    <t xml:space="preserve">项目余额: 1.650842; 
 收入: 110; 
 支出: 1.650842; 
 （一）直接费用: 1.650842; 
@@ -275,7 +275,7 @@
     <t>省-重大专项</t>
   </si>
   <si>
-    <t>项目余额: 2.669907; 
+    <t xml:space="preserve">项目余额: 2.669907; 
 收入: 300; 
 支出: 2.669907; 
 （一）直接费用: 2.669907; 
@@ -323,7 +323,7 @@
     <t>九州</t>
   </si>
   <si>
-    <t>项目余额: 1.106867; 
+    <t xml:space="preserve">项目余额: 1.106867; 
 收入: 30; 
 支出: 1.106867; 
 （一）直接费用: 1.106867; 
@@ -350,7 +350,7 @@
     <t>云智</t>
   </si>
   <si>
-    <t>项目余额: 0.01; 
+    <t xml:space="preserve">项目余额: 0.01; 
 收入: 20; 
 支出: 0.01; 
 （一）直接费用: 0.01; 
@@ -370,7 +370,7 @@
     <t>客如云</t>
   </si>
   <si>
-    <t>收入: 100; 
+    <t xml:space="preserve">收入: 100; 
 2.材料费: -1.328864; 
 3.测试化验加工费: 0.2; 
 5.差旅费: -0.147726; 
@@ -418,7 +418,7 @@
     <t>万维图新</t>
   </si>
   <si>
-    <t>项目余额: 2.361425; 
+    <t xml:space="preserve">项目余额: 2.361425; 
 收入: 60; 
 支出: 2.361425; 
 （一）直接费用: 2.361425; 
@@ -459,7 +459,7 @@
     <t>文轩教育</t>
   </si>
   <si>
-    <t>项目余额: 6.774598; 
+    <t xml:space="preserve">项目余额: 6.774598; 
 收入: 100; 
 支出: 6.774598; 
 （一）直接费用: 6.774598; 
@@ -499,7 +499,7 @@
     <t>教育融媒体统一内容生成服务平台成果转化及示范</t>
   </si>
   <si>
-    <t>项目余额: 0.823078; 
+    <t xml:space="preserve">项目余额: 0.823078; 
 收入: 50; 
 支出: 0.823078; 
 （一）直接费用: 0.823078; 
@@ -521,7 +521,7 @@
     <t>苗子工程</t>
   </si>
   <si>
-    <t>项目余额: 0.009808; 
+    <t xml:space="preserve">项目余额: 0.009808; 
 收入: 10; 
 支出: 0.009808; 
 （一）直接费用: 0.009808; 
@@ -556,7 +556,7 @@
     <t>省-科普类</t>
   </si>
   <si>
-    <t>项目余额: 0.002458; 
+    <t xml:space="preserve">项目余额: 0.002458; 
 收入: 20; 
 支出: 0.002458; 
 （一）直接费用: 0.002458; 
@@ -574,7 +574,7 @@
     <t>面向可穿戴设备的神经网络优实现及优化</t>
   </si>
   <si>
-    <t>项目余额: 1.052523; 
+    <t xml:space="preserve">项目余额: 1.052523; 
 收入: 8; 
 支出: 1.052523; 
 （一）直接费用: 1.052523; 
@@ -603,7 +603,7 @@
     <t>咪咕音乐</t>
   </si>
   <si>
-    <t>项目余额: 5.654086; 
+    <t xml:space="preserve">项目余额: 5.654086; 
 收入: 80; 
 支出: 5.654086; 
 （一）直接费用: 5.654086; 
@@ -626,7 +626,7 @@
     <t>新华文轩</t>
   </si>
   <si>
-    <t>项目余额: 8.706049; 
+    <t xml:space="preserve">项目余额: 8.706049; 
 收入: 100; 
 支出: 8.706049; 
 （一）直接费用: 8.706049; 
@@ -720,7 +720,7 @@
     <t>智能协同下轨道交通运维检修系统研发及其在供电设备运检中的实践</t>
   </si>
   <si>
-    <t>项目余额: 4.768043; 
+    <t xml:space="preserve">项目余额: 4.768043; 
 收入: 50; 
 支出: 4.768043; 
 （一）直接费用: 4.768043; 
@@ -763,7 +763,7 @@
     <t>横向</t>
   </si>
   <si>
-    <t>项目余额: 5.975; 
+    <t xml:space="preserve">项目余额: 5.975; 
 收入: 25; 
 支出: 5.975; 
 材料费: 3.375; 
@@ -781,7 +781,7 @@
     <t>四川省博物院</t>
   </si>
   <si>
-    <t>项目余额: 0.01001; 
+    <t xml:space="preserve">项目余额: 0.01001; 
 收入: 13; 
 支出: 0.01001; 
 1.项目业务费: 0.10951; 
@@ -799,7 +799,7 @@
     <t>完美时空</t>
   </si>
   <si>
-    <t>项目余额: 3.235642; 
+    <t xml:space="preserve">项目余额: 3.235642; 
 收入: 48; 
 支出: 3.235642; 
 1.项目业务费: 0.030642; 
@@ -819,7 +819,7 @@
     <t>东方电气</t>
   </si>
   <si>
-    <t>项目余额: 10.767764; 
+    <t xml:space="preserve">项目余额: 10.767764; 
 收入: 19.223301; 
 支出: 11.344463; 
 1.项目业务费: 10.869607; 
@@ -839,7 +839,7 @@
     <t>航天三院</t>
   </si>
   <si>
-    <t>项目余额: 31.490104; 
+    <t xml:space="preserve">项目余额: 31.490104; 
 收入: 39; 
 支出: 122.490104; 
 1.项目业务费: 33.135657; 
@@ -858,7 +858,7 @@
     <t>质量缺陷分析关键技术研究与工具开发服务</t>
   </si>
   <si>
-    <t>项目余额: 8.329888; 
+    <t xml:space="preserve">项目余额: 8.329888; 
 收入: 28.15534; 
 支出: 9.174548; 
 1.项目业务费: 8.644598; 
@@ -875,7 +875,7 @@
     <t>战术决策自动执行与反馈技术研究</t>
   </si>
   <si>
-    <t>项目余额: 13.410537; 
+    <t xml:space="preserve">项目余额: 13.410537; 
 收入: 101.941748; 
 支出: 16.468789; 
 1.项目业务费: 1.2642; 
@@ -902,7 +902,7 @@
     <t>面向虚拟战场的全局态势生成与PVI设计</t>
   </si>
   <si>
-    <t>项目余额: 75.68481; 
+    <t xml:space="preserve">项目余额: 75.68481; 
 收入: 91.262136; 
 支出: 78.422674; 
 1.项目业务费: 35.656396; 
@@ -920,7 +920,7 @@
     <t>基于任务互操作的分布式封控作战空基指控集成仿真验证环境</t>
   </si>
   <si>
-    <t>项目余额: 0.711514; 
+    <t xml:space="preserve">项目余额: 0.711514; 
 收入: 187.378641; 
 支出: 6.332873; 
 3.人员费: 6.332873; 
@@ -937,7 +937,7 @@
     <t>成都九洲电子信息系统股份有限公司</t>
   </si>
   <si>
-    <t>项目余额: 15.420918; 
+    <t xml:space="preserve">项目余额: 15.420918; 
 收入: 20.38835; 
 支出: 16.032568; 
 1.项目业务费: 7.062267; 
@@ -1107,7 +1107,7 @@
     <t>东方电气集团科学技术研究院</t>
   </si>
   <si>
-    <t>项目余额: 5.856465; 
+    <t xml:space="preserve">项目余额: 5.856465; 
 收入: 35; 
 支出: 5.856465; 
 一、直接费用: 5.856465; 
@@ -1140,7 +1140,7 @@
     <t>省-中央引导发展专项</t>
   </si>
   <si>
-    <t>项目余额: 17.183228; 
+    <t xml:space="preserve">项目余额: 17.183228; 
 收入: 30; 
 支出: 17.183228; 
 一、直接费用: 17.183228; 
@@ -1174,7 +1174,7 @@
     <t>四川省人民政府国防动员办公室</t>
   </si>
   <si>
-    <t>项目余额: 6.906731; 
+    <t xml:space="preserve">项目余额: 6.906731; 
 收入: 7.23301; 
 支出: 7.123721; 
 1.项目业务费: 7.152; 
@@ -1211,7 +1211,7 @@
     <t>军口-课题二</t>
   </si>
   <si>
-    <t>项目余额: 0.154824; 
+    <t xml:space="preserve">项目余额: 0.154824; 
 收入: 46; 
 支出: 4.154824; 
 （一）直接费用: 3.264424; 
@@ -1249,7 +1249,7 @@
     <t>面向虚拟场景的图像自动标注技术研究</t>
   </si>
   <si>
-    <t>项目余额: 0.034168; 
+    <t xml:space="preserve">项目余额: 0.034168; 
 收入: 3; 
 支出: 0.034168; 
 一、直接费用: 0.034168; 
@@ -1268,7 +1268,7 @@
     <t>中国船舶集团有限公司系统工程研究院</t>
   </si>
   <si>
-    <t>项目余额: 8.312066; 
+    <t xml:space="preserve">项目余额: 8.312066; 
 收入: 183.495146; 
 支出: 13.81692; 
 1.项目业务费: 4.713955; 
@@ -1298,7 +1298,7 @@
     <t>军口</t>
   </si>
   <si>
-    <t>项目余额: 13.905458; 
+    <t xml:space="preserve">项目余额: 13.905458; 
 收入: 25.242718; 
 支出: 54.38274; 
 外协费: 24; 
@@ -1372,7 +1372,7 @@
     <t>****飞机快速座舱工效评估POP驱动模型开发</t>
   </si>
   <si>
-    <t>项目余额: 80.748593; 
+    <t xml:space="preserve">项目余额: 80.748593; 
 收入: 91.262136; 
 支出: 83.486457; 
 1.项目业务费: 54; 
@@ -1392,7 +1392,7 @@
     <t>中铁二院工程集团有限责任公司</t>
   </si>
   <si>
-    <t>收入: 7; 
+    <t xml:space="preserve">收入: 7; 
 其中：1.绩效支出: 1.5; 
 2.其他: -1.5; 
 收入(不计项目余额): 5.5; 
@@ -1408,7 +1408,7 @@
     <t>四川科瑞软件有限责任公司</t>
   </si>
   <si>
-    <t>项目余额: 8.170787; 
+    <t xml:space="preserve">项目余额: 8.170787; 
 收入: 9.708738; 
 支出: 8.462049; 
 1.项目业务费: 6.8; 
@@ -1479,7 +1479,7 @@
     <t>中国航发四川燃气涡轮研究院</t>
   </si>
   <si>
-    <t>项目余额: 11.725266; 
+    <t xml:space="preserve">项目余额: 11.725266; 
 收入: 14.271845; 
 支出: 46.453421; 
 1.项目业务费: 17.3984; 
@@ -1503,7 +1503,7 @@
     <t>动态测试数字化管理技术研究</t>
   </si>
   <si>
-    <t>项目余额: 4.714275; 
+    <t xml:space="preserve">项目余额: 4.714275; 
 收入: 6.116505; 
 支出: 19.59777; 
 1.项目业务费: 11.6; 
@@ -1533,7 +1533,7 @@
     <t>市-重点研发支撑计划</t>
   </si>
   <si>
-    <t>项目余额: 1.9341; 
+    <t xml:space="preserve">项目余额: 1.9341; 
 收入: 10; 
 支出: 1.9341; 
 （一）直接费用: 1.9341; 
@@ -1558,7 +1558,7 @@
     <t>省-科技计划“揭榜挂帅”</t>
   </si>
   <si>
-    <t>项目余额: 31.64416; 
+    <t xml:space="preserve">项目余额: 31.64416; 
 收入: 40; 
 支出: 91.64416; 
 一、直接费用: 45.64416; 
@@ -1591,7 +1591,7 @@
     <t>省-经信后补助</t>
   </si>
   <si>
-    <t>项目余额: 62.475728; 
+    <t xml:space="preserve">项目余额: 62.475728; 
 收入: 77.475728; 
 支出: 64.8; 
 （一）直接费用: 64.8; 
@@ -1622,7 +1622,7 @@
     <t>四川百嘉数字科技有限公司</t>
   </si>
   <si>
-    <t>项目余额: 21.986144; 
+    <t xml:space="preserve">项目余额: 21.986144; 
 收入: 60; 
 支出: 21.986144; 
 一、直接费用: 21.986144; 
@@ -1650,7 +1650,7 @@
     <t>舆情态势感知智能分析算法技术服务采购项目</t>
   </si>
   <si>
-    <t>项目余额: 19.849231; 
+    <t xml:space="preserve">项目余额: 19.849231; 
 收入: 22.23301; 
 支出: 43.416221; 
 1.项目业务费: 21.02; 
@@ -4788,35 +4788,35 @@
     <t>侯超凡</t>
   </si>
   <si>
-    <t>一、
+    <t xml:space="preserve">一、
 教研室内部报销编号</t>
   </si>
   <si>
-    <t>二、
+    <t xml:space="preserve">二、
 提出时间</t>
   </si>
   <si>
-    <t>二、
+    <t xml:space="preserve">二、
 新事由？</t>
   </si>
   <si>
-    <t>二、
+    <t xml:space="preserve">二、
 历史报销编号</t>
   </si>
   <si>
-    <t>二、
+    <t xml:space="preserve">二、
 报销事由</t>
   </si>
   <si>
-    <t>二、
+    <t xml:space="preserve">二、
 涉及人/单位</t>
   </si>
   <si>
-    <t>二、
+    <t xml:space="preserve">二、
 涉及总金额</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <b/>
         <sz val="18"/>
@@ -4829,7 +4829,7 @@
       <t>三、
 报销审查意见</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -4843,11 +4843,11 @@
     </r>
   </si>
   <si>
-    <t>三、
+    <t xml:space="preserve">三、
 具体意见</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <b/>
         <sz val="18"/>
@@ -4861,7 +4861,7 @@
 执行反馈
 </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
@@ -4874,7 +4874,7 @@
     </r>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <b/>
         <sz val="18"/>
@@ -4888,7 +4888,7 @@
 执行情况说明
 </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
@@ -4901,30 +4901,30 @@
     </r>
   </si>
   <si>
-    <t>四、内部所需-
+    <t xml:space="preserve">四、内部所需-
 教研室内部项目序号</t>
   </si>
   <si>
-    <t>四、内部所需-
+    <t xml:space="preserve">四、内部所需-
 项目编号</t>
   </si>
   <si>
     <t>四、内部所需-项目名称</t>
   </si>
   <si>
-    <t>四、
+    <t xml:space="preserve">四、
 收/支</t>
   </si>
   <si>
-    <t>四、
+    <t xml:space="preserve">四、
 实际支出科目</t>
   </si>
   <si>
-    <t>四、
+    <t xml:space="preserve">四、
 人/单位</t>
   </si>
   <si>
-    <t>四、
+    <t xml:space="preserve">四、
 金额</t>
   </si>
   <si>
@@ -4958,12 +4958,12 @@
     <t>网上预约报账按钮</t>
   </si>
   <si>
+    <t>申请报销单按钮</t>
+  </si>
+  <si>
     <t>已阅读并同意按钮</t>
   </si>
   <si>
-    <t>申请报销单按钮</t>
-  </si>
-  <si>
     <t>业务大类</t>
   </si>
   <si>
@@ -5054,7 +5054,7 @@
     <t>个人转卡</t>
   </si>
   <si>
-    <t>#H专用材料费</t>
+    <t>#G专用材料费</t>
   </si>
   <si>
     <t>*2818</t>
@@ -5103,17 +5103,14 @@
   </si>
   <si>
     <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>$点击</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <numFmts count="0"/>
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5241,19 +5238,6 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -5376,50 +5360,50 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" applyFont="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" applyFill="1" borderId="3" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="3" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" applyFont="1" fillId="4" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" applyNumberFormat="1" fontId="0" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="4" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -5428,57 +5412,57 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -5490,73 +5474,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="12" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="5" applyFill="1" borderId="3" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="5" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="4" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="5" applyFill="1" borderId="4" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="3" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="5" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
@@ -5569,55 +5553,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" applyFont="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" applyFont="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="14" applyFont="1" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="0" borderId="6" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="16" applyFont="1" fillId="0" borderId="6" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5897,26 +5881,26 @@
   <dimension ref="A1:P119"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.58203125" style="47" customWidth="1"/>
-    <col min="2" max="2" width="29.25" style="47" customWidth="1"/>
-    <col min="3" max="3" width="42.5" style="47" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" style="47" customWidth="1"/>
-    <col min="5" max="5" width="16.25" style="47" customWidth="1"/>
-    <col min="6" max="6" width="16.5" style="47" customWidth="1"/>
-    <col min="7" max="7" width="16" style="47" customWidth="1"/>
-    <col min="8" max="8" width="16.58203125" style="47" customWidth="1"/>
-    <col min="9" max="9" width="23.83203125" style="47" customWidth="1"/>
-    <col min="10" max="10" width="20.75" style="47" customWidth="1"/>
-    <col min="11" max="11" width="27.08203125" style="47" customWidth="1"/>
-    <col min="12" max="12" width="17.9140625" style="47" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="35.33203125" style="47" customWidth="1"/>
-    <col min="14" max="15" width="14.25" style="47" customWidth="1"/>
-    <col min="16" max="16" width="27" style="47" customWidth="1"/>
-    <col min="17" max="28" width="8.75" style="47" customWidth="1"/>
-    <col min="29" max="16384" width="8.75" style="47"/>
+    <col min="1" max="1" width="13.58203125" customWidth="1" style="47"/>
+    <col min="2" max="2" width="29.25" customWidth="1" style="47"/>
+    <col min="3" max="3" width="42.5" customWidth="1" style="47"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1" style="47"/>
+    <col min="5" max="5" width="16.25" customWidth="1" style="47"/>
+    <col min="6" max="6" width="16.5" customWidth="1" style="47"/>
+    <col min="7" max="7" width="16" customWidth="1" style="47"/>
+    <col min="8" max="8" width="16.58203125" customWidth="1" style="47"/>
+    <col min="9" max="9" width="23.83203125" customWidth="1" style="47"/>
+    <col min="10" max="10" width="20.75" customWidth="1" style="47"/>
+    <col min="11" max="11" width="27.08203125" customWidth="1" style="47"/>
+    <col min="12" max="12" bestFit="1" width="17.9140625" customWidth="1" style="47"/>
+    <col min="13" max="13" width="35.33203125" customWidth="1" style="47"/>
+    <col min="14" max="15" width="14.25" customWidth="1" style="47"/>
+    <col min="16" max="16" width="27" customWidth="1" style="47"/>
+    <col min="17" max="28" width="8.75" customWidth="1" style="47"/>
+    <col min="29" max="16384" width="8.75" customWidth="1" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="46" customFormat="1" ht="32.5" customHeight="1">
+    <row r="1" ht="32.5" customHeight="1" s="46" customFormat="1">
       <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
@@ -5966,7 +5950,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="252.5">
+    <row r="2" ht="252.5">
       <c r="A2" s="50">
         <v>2025001</v>
       </c>
@@ -6010,7 +5994,7 @@
         <v>10.151726</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="31">
+    <row r="3" ht="31">
       <c r="A3" s="50">
         <v>2025002</v>
       </c>
@@ -6048,7 +6032,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.5">
+    <row r="4" ht="15.5">
       <c r="A4" s="54">
         <v>2025003</v>
       </c>
@@ -6086,7 +6070,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="98.5">
+    <row r="5" ht="98.5">
       <c r="A5" s="54">
         <v>2025004</v>
       </c>
@@ -6127,10 +6111,10 @@
         <v>36</v>
       </c>
       <c r="N5" s="47">
-        <v>1.6999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="15.5">
+        <v>0.0017</v>
+      </c>
+    </row>
+    <row r="6" ht="15.5">
       <c r="A6" s="54">
         <v>2025005</v>
       </c>
@@ -6168,7 +6152,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="28.5">
+    <row r="7" ht="28.5">
       <c r="A7" s="54">
         <v>2025006</v>
       </c>
@@ -6206,7 +6190,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="28.5">
+    <row r="8" ht="28.5">
       <c r="A8" s="54">
         <v>2025007</v>
       </c>
@@ -6244,7 +6228,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="168.5">
+    <row r="9" ht="168.5">
       <c r="A9" s="54">
         <v>2025008</v>
       </c>
@@ -6285,10 +6269,10 @@
         <v>51</v>
       </c>
       <c r="N9" s="47">
-        <v>1.6508419999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="238.5">
+        <v>1.650842</v>
+      </c>
+    </row>
+    <row r="10" ht="238.5">
       <c r="A10" s="54">
         <v>2025009</v>
       </c>
@@ -6329,10 +6313,10 @@
         <v>55</v>
       </c>
       <c r="N10" s="47">
-        <v>2.6699069999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="15.5">
+        <v>2.669907</v>
+      </c>
+    </row>
+    <row r="11" ht="15.5">
       <c r="A11" s="54">
         <v>2025010</v>
       </c>
@@ -6370,7 +6354,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.5">
+    <row r="12" ht="15.5">
       <c r="A12" s="54">
         <v>2025011</v>
       </c>
@@ -6408,7 +6392,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="154.5">
+    <row r="13" ht="154.5">
       <c r="A13" s="54">
         <v>2025012</v>
       </c>
@@ -6452,7 +6436,7 @@
         <v>1.106867</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="28.5">
+    <row r="14" ht="28.5">
       <c r="A14" s="54">
         <v>2025013</v>
       </c>
@@ -6490,7 +6474,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="126.5">
+    <row r="15" ht="126.5">
       <c r="A15" s="54">
         <v>2025014</v>
       </c>
@@ -6534,7 +6518,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="140.5">
+    <row r="16" ht="140.5">
       <c r="A16" s="54">
         <v>2025015</v>
       </c>
@@ -6578,7 +6562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="15.5">
+    <row r="17" ht="15.5">
       <c r="A17" s="54">
         <v>2025016</v>
       </c>
@@ -6616,7 +6600,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15.5">
+    <row r="18" ht="15.5">
       <c r="A18" s="54">
         <v>2025017</v>
       </c>
@@ -6654,7 +6638,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15.5">
+    <row r="19" ht="15.5">
       <c r="A19" s="54">
         <v>2025018</v>
       </c>
@@ -6692,7 +6676,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="182.5">
+    <row r="20" ht="182.5">
       <c r="A20" s="54">
         <v>2025019</v>
       </c>
@@ -6733,10 +6717,10 @@
         <v>89</v>
       </c>
       <c r="N20" s="47">
-        <v>2.3614250000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="15.5">
+        <v>2.361425</v>
+      </c>
+    </row>
+    <row r="21" ht="15.5">
       <c r="A21" s="54">
         <v>2025020</v>
       </c>
@@ -6774,7 +6758,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15.5">
+    <row r="22" ht="15.5">
       <c r="A22" s="54">
         <v>2025021</v>
       </c>
@@ -6812,7 +6796,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="196.5">
+    <row r="23" ht="196.5">
       <c r="A23" s="54">
         <v>2025022</v>
       </c>
@@ -6853,10 +6837,10 @@
         <v>99</v>
       </c>
       <c r="N23" s="47">
-        <v>6.7745980000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="15.5">
+        <v>6.774598</v>
+      </c>
+    </row>
+    <row r="24" ht="15.5">
       <c r="A24" s="54">
         <v>2025023</v>
       </c>
@@ -6894,7 +6878,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="28.5">
+    <row r="25" ht="28.5">
       <c r="A25" s="54">
         <v>2025024</v>
       </c>
@@ -6932,7 +6916,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="154.5">
+    <row r="26" ht="154.5">
       <c r="A26" s="54">
         <v>2025025</v>
       </c>
@@ -6973,10 +6957,10 @@
         <v>108</v>
       </c>
       <c r="N26" s="47">
-        <v>0.82307799999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="182.5">
+        <v>0.823078</v>
+      </c>
+    </row>
+    <row r="27" ht="182.5">
       <c r="A27" s="54">
         <v>2025026</v>
       </c>
@@ -7017,10 +7001,10 @@
         <v>112</v>
       </c>
       <c r="N27" s="47">
-        <v>9.8080000000000007E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="15.5">
+        <v>0.009808</v>
+      </c>
+    </row>
+    <row r="28" ht="15.5">
       <c r="A28" s="54">
         <v>2025027</v>
       </c>
@@ -7058,7 +7042,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="140.5">
+    <row r="29" ht="140.5">
       <c r="A29" s="54">
         <v>2025028</v>
       </c>
@@ -7099,10 +7083,10 @@
         <v>120</v>
       </c>
       <c r="N29" s="47">
-        <v>2.4580000000000001E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="126.5">
+        <v>0.002458</v>
+      </c>
+    </row>
+    <row r="30" ht="126.5">
       <c r="A30" s="54">
         <v>2025029</v>
       </c>
@@ -7143,10 +7127,10 @@
         <v>123</v>
       </c>
       <c r="N30" s="47">
-        <v>1.0525230000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="15.5">
+        <v>1.052523</v>
+      </c>
+    </row>
+    <row r="31" ht="15.5">
       <c r="A31" s="54">
         <v>2025030</v>
       </c>
@@ -7184,7 +7168,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="168.5">
+    <row r="32" ht="168.5">
       <c r="A32" s="54">
         <v>2025031</v>
       </c>
@@ -7225,10 +7209,10 @@
         <v>130</v>
       </c>
       <c r="N32" s="47">
-        <v>5.6540860000000004</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="154.5">
+        <v>5.654086</v>
+      </c>
+    </row>
+    <row r="33" ht="154.5">
       <c r="A33" s="54">
         <v>2025032</v>
       </c>
@@ -7269,10 +7253,10 @@
         <v>134</v>
       </c>
       <c r="N33" s="47">
-        <v>8.7060490000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="15.5">
+        <v>8.706049</v>
+      </c>
+    </row>
+    <row r="34" ht="15.5">
       <c r="A34" s="54">
         <v>2025033</v>
       </c>
@@ -7310,7 +7294,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="15.5">
+    <row r="35" ht="15.5">
       <c r="A35" s="54">
         <v>2025034</v>
       </c>
@@ -7348,7 +7332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="15.5">
+    <row r="36" ht="15.5">
       <c r="A36" s="54">
         <v>2025035</v>
       </c>
@@ -7386,7 +7370,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="15.5">
+    <row r="37" ht="15.5">
       <c r="A37" s="54">
         <v>2025036</v>
       </c>
@@ -7424,7 +7408,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="15.5">
+    <row r="38" ht="15.5">
       <c r="A38" s="54">
         <v>2025037</v>
       </c>
@@ -7462,7 +7446,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="15.5">
+    <row r="39" ht="15.5">
       <c r="A39" s="54">
         <v>2025038</v>
       </c>
@@ -7500,7 +7484,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="15.5">
+    <row r="40" ht="15.5">
       <c r="A40" s="54">
         <v>2025039</v>
       </c>
@@ -7538,7 +7522,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="15.5">
+    <row r="41" ht="15.5">
       <c r="A41" s="54">
         <v>2025040</v>
       </c>
@@ -7576,7 +7560,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="252.5">
+    <row r="42" ht="252.5">
       <c r="A42" s="54">
         <v>2025041</v>
       </c>
@@ -7617,10 +7601,10 @@
         <v>162</v>
       </c>
       <c r="N42" s="47">
-        <v>4.7680429999999996</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="15.5">
+        <v>4.768043</v>
+      </c>
+    </row>
+    <row r="43" ht="15.5">
       <c r="A43" s="54">
         <v>2025042</v>
       </c>
@@ -7658,7 +7642,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="15.5">
+    <row r="44" ht="15.5">
       <c r="A44" s="54">
         <v>2025043</v>
       </c>
@@ -7696,7 +7680,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="51" customHeight="1">
+    <row r="45" ht="51" customHeight="1">
       <c r="A45" s="54">
         <v>2025044</v>
       </c>
@@ -7737,10 +7721,10 @@
         <v>171</v>
       </c>
       <c r="N45" s="47">
-        <v>5.9749999999999996</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="98.5">
+        <v>5.975</v>
+      </c>
+    </row>
+    <row r="46" ht="98.5">
       <c r="A46" s="54">
         <v>2025045</v>
       </c>
@@ -7781,10 +7765,10 @@
         <v>175</v>
       </c>
       <c r="N46" s="47">
-        <v>1.001E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" ht="126.5">
+        <v>0.01001</v>
+      </c>
+    </row>
+    <row r="47" ht="126.5">
       <c r="A47" s="54">
         <v>2025046</v>
       </c>
@@ -7825,10 +7809,10 @@
         <v>179</v>
       </c>
       <c r="N47" s="47">
-        <v>3.2356419999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="126.5">
+        <v>3.235642</v>
+      </c>
+    </row>
+    <row r="48" ht="126.5">
       <c r="A48" s="54">
         <v>2025047</v>
       </c>
@@ -7872,7 +7856,7 @@
         <v>10.767764</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="154.5">
+    <row r="49" ht="154.5">
       <c r="A49" s="54">
         <v>2025048</v>
       </c>
@@ -7913,10 +7897,10 @@
         <v>187</v>
       </c>
       <c r="N49" s="47">
-        <v>31.490103999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="126.5">
+        <v>31.490104</v>
+      </c>
+    </row>
+    <row r="50" ht="126.5">
       <c r="A50" s="54">
         <v>2025049</v>
       </c>
@@ -7957,10 +7941,10 @@
         <v>190</v>
       </c>
       <c r="N50" s="47">
-        <v>8.3298880000000004</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" ht="140.5">
+        <v>8.329888</v>
+      </c>
+    </row>
+    <row r="51" ht="140.5">
       <c r="A51" s="54">
         <v>2025050</v>
       </c>
@@ -8004,7 +7988,7 @@
         <v>13.410537</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="28.5">
+    <row r="52" ht="28.5">
       <c r="A52" s="54">
         <v>2025051</v>
       </c>
@@ -8042,7 +8026,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="140.5">
+    <row r="53" ht="140.5">
       <c r="A53" s="54">
         <v>2025052</v>
       </c>
@@ -8083,10 +8067,10 @@
         <v>199</v>
       </c>
       <c r="N53" s="47">
-        <v>75.684809999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="84.5">
+        <v>75.68481</v>
+      </c>
+    </row>
+    <row r="54" ht="84.5">
       <c r="A54" s="54">
         <v>2025053</v>
       </c>
@@ -8127,10 +8111,10 @@
         <v>202</v>
       </c>
       <c r="N54" s="47">
-        <v>0.71151399999999998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" ht="126.5">
+        <v>0.711514</v>
+      </c>
+    </row>
+    <row r="55" ht="126.5">
       <c r="A55" s="54">
         <v>2025054</v>
       </c>
@@ -8174,7 +8158,7 @@
         <v>15.420918</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="28.5">
+    <row r="56" ht="28.5">
       <c r="A56" s="54">
         <v>2025055</v>
       </c>
@@ -8212,7 +8196,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="15.5">
+    <row r="57" ht="15.5">
       <c r="A57" s="54">
         <v>2025056</v>
       </c>
@@ -8242,7 +8226,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="15.5">
+    <row r="58" ht="15.5">
       <c r="A58" s="54">
         <v>2025057</v>
       </c>
@@ -8272,7 +8256,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="15.5">
+    <row r="59" ht="15.5">
       <c r="A59" s="54">
         <v>2025058</v>
       </c>
@@ -8302,7 +8286,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="15.5">
+    <row r="60" ht="15.5">
       <c r="A60" s="54">
         <v>2025059</v>
       </c>
@@ -8332,7 +8316,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="15.5">
+    <row r="61" ht="15.5">
       <c r="A61" s="54">
         <v>2025060</v>
       </c>
@@ -8362,7 +8346,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="15.5">
+    <row r="62" ht="15.5">
       <c r="A62" s="54">
         <v>2025061</v>
       </c>
@@ -8392,7 +8376,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="28.5">
+    <row r="63" ht="28.5">
       <c r="A63" s="54">
         <v>2025062</v>
       </c>
@@ -8430,7 +8414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="15.5">
+    <row r="64" ht="15.5">
       <c r="A64" s="54">
         <v>2025063</v>
       </c>
@@ -8464,7 +8448,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="15.5">
+    <row r="65" ht="15.5">
       <c r="A65" s="54">
         <v>2025064</v>
       </c>
@@ -8494,7 +8478,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="15.5">
+    <row r="66" ht="15.5">
       <c r="A66" s="54">
         <v>2025065</v>
       </c>
@@ -8528,7 +8512,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="68.5" customHeight="1">
+    <row r="67" ht="68.5" customHeight="1">
       <c r="A67" s="54">
         <v>2025066</v>
       </c>
@@ -8562,7 +8546,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="28.5">
+    <row r="68" ht="28.5">
       <c r="A68" s="54">
         <v>2025067</v>
       </c>
@@ -8600,7 +8584,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="16">
+    <row r="69" ht="16">
       <c r="A69" s="54">
         <v>2025068</v>
       </c>
@@ -8638,7 +8622,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="28.5">
+    <row r="70" ht="28.5">
       <c r="A70" s="54">
         <v>2025069</v>
       </c>
@@ -8676,7 +8660,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="28.5">
+    <row r="71" ht="28.5">
       <c r="A71" s="54">
         <v>2025070</v>
       </c>
@@ -8714,7 +8698,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="15.5">
+    <row r="72" ht="15.5">
       <c r="A72" s="54">
         <v>2025071</v>
       </c>
@@ -8744,7 +8728,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="28.5">
+    <row r="73" ht="28.5">
       <c r="A73" s="54">
         <v>2025072</v>
       </c>
@@ -8782,7 +8766,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="140.5">
+    <row r="74" ht="140.5">
       <c r="A74" s="54">
         <v>2025073</v>
       </c>
@@ -8826,7 +8810,7 @@
         <v>5.856465</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="28.5">
+    <row r="75" ht="28.5">
       <c r="A75" s="54">
         <v>2025074</v>
       </c>
@@ -8864,7 +8848,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="112.5">
+    <row r="76" ht="112.5">
       <c r="A76" s="54">
         <v>2025075</v>
       </c>
@@ -8908,7 +8892,7 @@
         <v>17.183228</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="28">
+    <row r="77" ht="28">
       <c r="A77" s="54">
         <v>2025076</v>
       </c>
@@ -8946,7 +8930,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="15.5">
+    <row r="78" ht="15.5">
       <c r="A78" s="54">
         <v>2025077</v>
       </c>
@@ -8984,7 +8968,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="112.5">
+    <row r="79" ht="112.5">
       <c r="A79" s="54">
         <v>2025078</v>
       </c>
@@ -9025,10 +9009,10 @@
         <v>277</v>
       </c>
       <c r="N79" s="47">
-        <v>6.9067309999999997</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" ht="28.5">
+        <v>6.906731</v>
+      </c>
+    </row>
+    <row r="80" ht="28.5">
       <c r="A80" s="54">
         <v>2025079</v>
       </c>
@@ -9054,10 +9038,10 @@
         <v>280</v>
       </c>
       <c r="I80" s="65">
-        <v>9.8000000000000007</v>
+        <v>9.8</v>
       </c>
       <c r="J80" s="65">
-        <v>9.8000000000000007</v>
+        <v>9.8</v>
       </c>
       <c r="K80" s="56" t="s">
         <v>170</v>
@@ -9066,7 +9050,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="28.5">
+    <row r="81" ht="28.5">
       <c r="A81" s="54">
         <v>2025080</v>
       </c>
@@ -9094,7 +9078,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="168.5">
+    <row r="82" ht="168.5">
       <c r="A82" s="54">
         <v>2025081</v>
       </c>
@@ -9131,10 +9115,10 @@
         <v>287</v>
       </c>
       <c r="N82" s="47">
-        <v>0.15482399999999999</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" ht="168.5">
+        <v>0.154824</v>
+      </c>
+    </row>
+    <row r="83" ht="168.5">
       <c r="A83" s="54">
         <v>2025082</v>
       </c>
@@ -9171,10 +9155,10 @@
         <v>287</v>
       </c>
       <c r="N83" s="47">
-        <v>0.15482399999999999</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" ht="15.5">
+        <v>0.154824</v>
+      </c>
+    </row>
+    <row r="84" ht="15.5">
       <c r="A84" s="54">
         <v>2025083</v>
       </c>
@@ -9210,7 +9194,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="126.5">
+    <row r="85" ht="126.5">
       <c r="A85" s="54">
         <v>2025084</v>
       </c>
@@ -9249,10 +9233,10 @@
         <v>296</v>
       </c>
       <c r="N85" s="47">
-        <v>3.4167999999999997E-2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" ht="140.5">
+        <v>0.034168</v>
+      </c>
+    </row>
+    <row r="86" ht="140.5">
       <c r="A86" s="54">
         <v>2025085</v>
       </c>
@@ -9289,10 +9273,10 @@
         <v>300</v>
       </c>
       <c r="N86" s="47">
-        <v>8.3120659999999997</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" ht="15.5">
+        <v>8.312066</v>
+      </c>
+    </row>
+    <row r="87" ht="15.5">
       <c r="A87" s="54">
         <v>2025086</v>
       </c>
@@ -9320,7 +9304,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="126.5">
+    <row r="88" ht="126.5">
       <c r="A88" s="54">
         <v>2025087</v>
       </c>
@@ -9357,10 +9341,10 @@
         <v>307</v>
       </c>
       <c r="N88" s="47">
-        <v>13.905457999999999</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" ht="42.5">
+        <v>13.905458</v>
+      </c>
+    </row>
+    <row r="89" ht="42.5">
       <c r="A89" s="54">
         <v>2025088</v>
       </c>
@@ -9398,7 +9382,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="39.65" customHeight="1">
+    <row r="90" ht="39.65" customHeight="1">
       <c r="A90" s="54">
         <v>2025089</v>
       </c>
@@ -9420,10 +9404,10 @@
         <v>313</v>
       </c>
       <c r="I90" s="52">
-        <v>26.993476999999999</v>
+        <v>26.993477</v>
       </c>
       <c r="J90" s="52">
-        <v>26.993476999999999</v>
+        <v>26.993477</v>
       </c>
       <c r="K90" s="52" t="s">
         <v>170</v>
@@ -9432,7 +9416,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:14" ht="28.5">
+    <row r="91" ht="28.5">
       <c r="A91" s="54">
         <v>2025090</v>
       </c>
@@ -9472,7 +9456,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="92" spans="1:14" ht="28.5">
+    <row r="92" ht="28.5">
       <c r="A92" s="54">
         <v>2025091</v>
       </c>
@@ -9511,7 +9495,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="93" spans="1:14" ht="28.5">
+    <row r="93" ht="28.5">
       <c r="A93" s="54">
         <v>2025092</v>
       </c>
@@ -9550,7 +9534,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="94" spans="1:14" ht="15.5">
+    <row r="94" ht="15.5">
       <c r="A94" s="54">
         <v>2025093</v>
       </c>
@@ -9576,7 +9560,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="15.5">
+    <row r="95" ht="15.5">
       <c r="A95" s="54">
         <v>2025094</v>
       </c>
@@ -9606,7 +9590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="96" spans="1:14" ht="126.5">
+    <row r="96" ht="126.5">
       <c r="A96" s="54">
         <v>2025095</v>
       </c>
@@ -9650,7 +9634,7 @@
         <v>80.748593</v>
       </c>
     </row>
-    <row r="97" spans="1:14" ht="70.5">
+    <row r="97" ht="70.5">
       <c r="A97" s="54">
         <v>2025096</v>
       </c>
@@ -9692,7 +9676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:14" ht="126.5">
+    <row r="98" ht="126.5">
       <c r="A98" s="54">
         <v>2025097</v>
       </c>
@@ -9733,10 +9717,10 @@
         <v>337</v>
       </c>
       <c r="N98" s="47">
-        <v>8.1707870000000007</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" ht="28.5">
+        <v>8.170787</v>
+      </c>
+    </row>
+    <row r="99" ht="28.5">
       <c r="A99" s="54">
         <v>2025098</v>
       </c>
@@ -9766,7 +9750,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="100" spans="1:14" ht="28.5">
+    <row r="100" ht="28.5">
       <c r="A100" s="54">
         <v>2025099</v>
       </c>
@@ -9796,7 +9780,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="101" spans="1:14" ht="28.5">
+    <row r="101" ht="28.5">
       <c r="A101" s="54">
         <v>2025100</v>
       </c>
@@ -9826,7 +9810,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:14" ht="57.65" customHeight="1">
+    <row r="102" ht="57.65" customHeight="1">
       <c r="A102" s="54">
         <v>2025101</v>
       </c>
@@ -9856,7 +9840,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="103" spans="1:14" ht="15.5">
+    <row r="103" ht="15.5">
       <c r="A103" s="54">
         <v>2025102</v>
       </c>
@@ -9874,10 +9858,10 @@
         <v>350</v>
       </c>
       <c r="I103" s="52">
-        <v>9.4600000000000009</v>
+        <v>9.46</v>
       </c>
       <c r="J103" s="52">
-        <v>9.4600000000000009</v>
+        <v>9.46</v>
       </c>
       <c r="K103" s="52" t="s">
         <v>234</v>
@@ -9886,7 +9870,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="104" spans="1:14" ht="15.5">
+    <row r="104" ht="15.5">
       <c r="A104" s="54">
         <v>2025103</v>
       </c>
@@ -9916,7 +9900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="105" spans="1:14" ht="140.5">
+    <row r="105" ht="140.5">
       <c r="A105" s="54">
         <v>2025104</v>
       </c>
@@ -9960,7 +9944,7 @@
         <v>11.725266</v>
       </c>
     </row>
-    <row r="106" spans="1:14" ht="42.5">
+    <row r="106" ht="42.5">
       <c r="A106" s="54">
         <v>2025105</v>
       </c>
@@ -9986,7 +9970,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="140.5">
+    <row r="107" ht="140.5">
       <c r="A107" s="54">
         <v>2025106</v>
       </c>
@@ -10027,10 +10011,10 @@
         <v>363</v>
       </c>
       <c r="N107" s="47">
-        <v>4.7142749999999998</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14" ht="28.5">
+        <v>4.714275</v>
+      </c>
+    </row>
+    <row r="108" ht="28.5">
       <c r="A108" s="54">
         <v>2025107</v>
       </c>
@@ -10056,7 +10040,7 @@
         <v>366</v>
       </c>
       <c r="I108" s="52">
-        <v>70.400000000000006</v>
+        <v>70.4</v>
       </c>
       <c r="J108" s="52"/>
       <c r="K108" s="52" t="s">
@@ -10066,7 +10050,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="1:14" ht="210.5">
+    <row r="109" ht="210.5">
       <c r="A109" s="54">
         <v>2025108</v>
       </c>
@@ -10105,10 +10089,10 @@
         <v>370</v>
       </c>
       <c r="N109" s="47">
-        <v>1.9340999999999999</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14" ht="140.5">
+        <v>1.9341</v>
+      </c>
+    </row>
+    <row r="110" ht="140.5">
       <c r="A110" s="54">
         <v>2025109</v>
       </c>
@@ -10149,10 +10133,10 @@
         <v>374</v>
       </c>
       <c r="N110" s="47">
-        <v>31.644159999999999</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14" ht="15.5">
+        <v>31.64416</v>
+      </c>
+    </row>
+    <row r="111" ht="15.5">
       <c r="A111" s="54">
         <v>2025110</v>
       </c>
@@ -10188,7 +10172,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="112" spans="1:14" ht="154.5">
+    <row r="112" ht="154.5">
       <c r="A112" s="54">
         <v>2025111</v>
       </c>
@@ -10229,10 +10213,10 @@
         <v>382</v>
       </c>
       <c r="N112" s="47">
-        <v>62.475727999999997</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14" ht="28.5">
+        <v>62.475728</v>
+      </c>
+    </row>
+    <row r="113" ht="28.5">
       <c r="A113" s="54">
         <v>2025112</v>
       </c>
@@ -10268,7 +10252,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="114" spans="1:14" ht="112.5">
+    <row r="114" ht="112.5">
       <c r="A114" s="54">
         <v>2025113</v>
       </c>
@@ -10309,10 +10293,10 @@
         <v>389</v>
       </c>
       <c r="N114" s="47">
-        <v>21.986143999999999</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14" ht="31">
+        <v>21.986144</v>
+      </c>
+    </row>
+    <row r="115" ht="31">
       <c r="A115" s="54">
         <v>2025114</v>
       </c>
@@ -10348,7 +10332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="116" spans="1:14" ht="140.5">
+    <row r="116" ht="140.5">
       <c r="A116" s="54">
         <v>2025115</v>
       </c>
@@ -10392,7 +10376,7 @@
         <v>19.849231</v>
       </c>
     </row>
-    <row r="117" spans="1:14" ht="15.5">
+    <row r="117" ht="15.5">
       <c r="A117" s="54">
         <v>2025116</v>
       </c>
@@ -10422,7 +10406,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" spans="1:14" ht="15.5">
+    <row r="118" ht="15.5">
       <c r="A118" s="54">
         <v>2025117</v>
       </c>
@@ -10460,13 +10444,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="119" spans="1:14" ht="15.5">
+    <row r="119" ht="15.5">
       <c r="A119" s="62"/>
       <c r="C119" s="62"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -10477,18 +10462,18 @@
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="32.08203125" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="23.83203125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" customWidth="1" style="20"/>
+    <col min="4" max="4" width="23.83203125" customWidth="1" style="20"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="24.25" customWidth="1"/>
     <col min="7" max="7" width="44.33203125" customWidth="1"/>
-    <col min="8" max="8" width="14.08203125" style="20" customWidth="1"/>
-    <col min="11" max="11" width="21.25" style="20" customWidth="1"/>
-    <col min="12" max="12" width="18.5" style="20" customWidth="1"/>
+    <col min="8" max="8" width="14.08203125" customWidth="1" style="20"/>
+    <col min="11" max="11" width="21.25" customWidth="1" style="20"/>
+    <col min="12" max="12" width="18.5" customWidth="1" style="20"/>
     <col min="13" max="13" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.5">
+    <row r="1" ht="15.5">
       <c r="A1" s="21" t="s">
         <v>403</v>
       </c>
@@ -10520,7 +10505,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="19" customFormat="1">
+    <row r="2" s="19" customFormat="1">
       <c r="A2" s="19">
         <v>1</v>
       </c>
@@ -10546,7 +10531,7 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:12" s="19" customFormat="1">
+    <row r="3" s="19" customFormat="1">
       <c r="A3" s="19">
         <v>2</v>
       </c>
@@ -10572,7 +10557,7 @@
       <c r="K3" s="20"/>
       <c r="L3" s="20"/>
     </row>
-    <row r="4" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="4" ht="15.5" s="19" customFormat="1">
       <c r="A4" s="19">
         <v>3</v>
       </c>
@@ -10598,7 +10583,7 @@
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
     </row>
-    <row r="5" spans="1:12" s="19" customFormat="1">
+    <row r="5" s="19" customFormat="1">
       <c r="A5" s="19">
         <v>4</v>
       </c>
@@ -10624,7 +10609,7 @@
       <c r="K5" s="20"/>
       <c r="L5" s="20"/>
     </row>
-    <row r="6" spans="1:12" s="19" customFormat="1">
+    <row r="6" s="19" customFormat="1">
       <c r="A6" s="19">
         <v>5</v>
       </c>
@@ -10650,7 +10635,7 @@
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
     </row>
-    <row r="7" spans="1:12" s="19" customFormat="1">
+    <row r="7" s="19" customFormat="1">
       <c r="A7" s="19">
         <v>6</v>
       </c>
@@ -10676,7 +10661,7 @@
       </c>
       <c r="L7" s="20"/>
     </row>
-    <row r="8" spans="1:12" s="19" customFormat="1">
+    <row r="8" s="19" customFormat="1">
       <c r="A8" s="19">
         <v>7</v>
       </c>
@@ -10702,7 +10687,7 @@
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
     </row>
-    <row r="9" spans="1:12" s="19" customFormat="1">
+    <row r="9" s="19" customFormat="1">
       <c r="A9" s="19">
         <v>8</v>
       </c>
@@ -10728,7 +10713,7 @@
       </c>
       <c r="L9" s="20"/>
     </row>
-    <row r="10" spans="1:12" s="19" customFormat="1">
+    <row r="10" s="19" customFormat="1">
       <c r="A10" s="19">
         <v>9</v>
       </c>
@@ -10754,7 +10739,7 @@
       </c>
       <c r="L10" s="20"/>
     </row>
-    <row r="11" spans="1:12" s="19" customFormat="1">
+    <row r="11" s="19" customFormat="1">
       <c r="A11" s="19">
         <v>10</v>
       </c>
@@ -10780,7 +10765,7 @@
       </c>
       <c r="L11" s="20"/>
     </row>
-    <row r="12" spans="1:12" s="19" customFormat="1">
+    <row r="12" s="19" customFormat="1">
       <c r="A12" s="19">
         <v>11</v>
       </c>
@@ -10806,7 +10791,7 @@
       </c>
       <c r="L12" s="20"/>
     </row>
-    <row r="13" spans="1:12" s="19" customFormat="1">
+    <row r="13" s="19" customFormat="1">
       <c r="A13" s="19">
         <v>12</v>
       </c>
@@ -10832,7 +10817,7 @@
       </c>
       <c r="L13" s="20"/>
     </row>
-    <row r="14" spans="1:12" s="19" customFormat="1">
+    <row r="14" s="19" customFormat="1">
       <c r="A14" s="19">
         <v>13</v>
       </c>
@@ -10854,11 +10839,11 @@
       </c>
       <c r="L14" s="20"/>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15">
       <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="0" t="s">
         <v>46</v>
       </c>
       <c r="C15" s="26" t="s">
@@ -10871,11 +10856,11 @@
         <v>5110016</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.5">
+    <row r="16" ht="15.5">
       <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="0" t="s">
         <v>209</v>
       </c>
       <c r="C16" s="26" t="s">
@@ -10887,7 +10872,7 @@
       <c r="F16" s="67" t="s">
         <v>457</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="0" t="s">
         <v>446</v>
       </c>
       <c r="H16" s="68" t="s">
@@ -10900,11 +10885,11 @@
         <v>15828154009</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17">
       <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="0" t="s">
         <v>459</v>
       </c>
       <c r="C17" s="26" t="s">
@@ -10917,7 +10902,7 @@
         <v>5090235</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="19" customFormat="1">
+    <row r="18" s="19" customFormat="1">
       <c r="A18" s="19">
         <v>17</v>
       </c>
@@ -10936,7 +10921,7 @@
       </c>
       <c r="L18" s="20"/>
     </row>
-    <row r="19" spans="1:12" s="19" customFormat="1">
+    <row r="19" s="19" customFormat="1">
       <c r="A19" s="19">
         <v>18</v>
       </c>
@@ -10955,7 +10940,7 @@
       </c>
       <c r="L19" s="20"/>
     </row>
-    <row r="20" spans="1:12" s="19" customFormat="1">
+    <row r="20" s="19" customFormat="1">
       <c r="A20" s="19">
         <v>19</v>
       </c>
@@ -10983,7 +10968,7 @@
       </c>
       <c r="L20" s="20"/>
     </row>
-    <row r="21" spans="1:12" s="19" customFormat="1">
+    <row r="21" s="19" customFormat="1">
       <c r="A21" s="19">
         <v>20</v>
       </c>
@@ -11010,7 +10995,7 @@
         <v>15828085356</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="19" customFormat="1">
+    <row r="22" s="19" customFormat="1">
       <c r="A22" s="19">
         <v>21</v>
       </c>
@@ -11034,11 +11019,11 @@
       <c r="K22" s="20"/>
       <c r="L22" s="20"/>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23">
       <c r="A23" s="19">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="0" t="s">
         <v>474</v>
       </c>
       <c r="C23" s="20" t="s">
@@ -11050,18 +11035,18 @@
       <c r="F23" s="67" t="s">
         <v>476</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="0" t="s">
         <v>477</v>
       </c>
       <c r="K23" s="20">
         <v>4230032</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24">
       <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="0" t="s">
         <v>478</v>
       </c>
       <c r="C24" s="20" t="s">
@@ -11076,18 +11061,18 @@
       <c r="F24" s="67" t="s">
         <v>480</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="0" t="s">
         <v>467</v>
       </c>
       <c r="K24" s="20">
         <v>4230036</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25">
       <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="0" t="s">
         <v>481</v>
       </c>
       <c r="C25" s="20" t="s">
@@ -11106,11 +11091,11 @@
         <v>15828139278</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26">
       <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="0" t="s">
         <v>484</v>
       </c>
       <c r="C26" s="20" t="s">
@@ -11126,7 +11111,7 @@
         <v>4230437</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="27" ht="15.5" s="19" customFormat="1">
       <c r="A27" s="19">
         <v>26</v>
       </c>
@@ -11152,7 +11137,7 @@
       </c>
       <c r="L27" s="20"/>
     </row>
-    <row r="28" spans="1:12" s="19" customFormat="1">
+    <row r="28" s="19" customFormat="1">
       <c r="A28" s="19">
         <v>27</v>
       </c>
@@ -11178,7 +11163,7 @@
       </c>
       <c r="L28" s="20"/>
     </row>
-    <row r="29" spans="1:12" s="19" customFormat="1">
+    <row r="29" s="19" customFormat="1">
       <c r="A29" s="19">
         <v>28</v>
       </c>
@@ -11204,7 +11189,7 @@
       </c>
       <c r="L29" s="20"/>
     </row>
-    <row r="30" spans="1:12" s="19" customFormat="1">
+    <row r="30" s="19" customFormat="1">
       <c r="A30" s="19">
         <v>29</v>
       </c>
@@ -11230,7 +11215,7 @@
       </c>
       <c r="L30" s="20"/>
     </row>
-    <row r="31" spans="1:12" s="19" customFormat="1">
+    <row r="31" s="19" customFormat="1">
       <c r="A31" s="19">
         <v>30</v>
       </c>
@@ -11256,7 +11241,7 @@
       </c>
       <c r="L31" s="20"/>
     </row>
-    <row r="32" spans="1:12" s="19" customFormat="1">
+    <row r="32" s="19" customFormat="1">
       <c r="A32" s="19">
         <v>31</v>
       </c>
@@ -11282,7 +11267,7 @@
       </c>
       <c r="L32" s="20"/>
     </row>
-    <row r="33" spans="1:12" s="19" customFormat="1">
+    <row r="33" s="19" customFormat="1">
       <c r="A33" s="19">
         <v>32</v>
       </c>
@@ -11308,7 +11293,7 @@
       </c>
       <c r="L33" s="20"/>
     </row>
-    <row r="34" spans="1:12" s="19" customFormat="1">
+    <row r="34" s="19" customFormat="1">
       <c r="A34" s="19">
         <v>33</v>
       </c>
@@ -11334,7 +11319,7 @@
       </c>
       <c r="L34" s="20"/>
     </row>
-    <row r="35" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="35" ht="15.5" s="19" customFormat="1">
       <c r="A35" s="19">
         <v>34</v>
       </c>
@@ -11360,7 +11345,7 @@
       </c>
       <c r="L35" s="20"/>
     </row>
-    <row r="36" spans="1:12" s="19" customFormat="1">
+    <row r="36" s="19" customFormat="1">
       <c r="A36" s="19">
         <v>35</v>
       </c>
@@ -11386,7 +11371,7 @@
       </c>
       <c r="L36" s="20"/>
     </row>
-    <row r="37" spans="1:12" s="19" customFormat="1">
+    <row r="37" s="19" customFormat="1">
       <c r="A37" s="19">
         <v>36</v>
       </c>
@@ -11412,7 +11397,7 @@
       </c>
       <c r="L37" s="20"/>
     </row>
-    <row r="38" spans="1:12" s="19" customFormat="1">
+    <row r="38" s="19" customFormat="1">
       <c r="A38" s="19">
         <v>37</v>
       </c>
@@ -11438,7 +11423,7 @@
       </c>
       <c r="L38" s="20"/>
     </row>
-    <row r="39" spans="1:12" s="19" customFormat="1">
+    <row r="39" s="19" customFormat="1">
       <c r="A39" s="19">
         <v>38</v>
       </c>
@@ -11464,7 +11449,7 @@
       </c>
       <c r="L39" s="20"/>
     </row>
-    <row r="40" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="40" ht="15.5" s="19" customFormat="1">
       <c r="A40" s="19">
         <v>39</v>
       </c>
@@ -11490,7 +11475,7 @@
       </c>
       <c r="L40" s="20"/>
     </row>
-    <row r="41" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="41" ht="15.5" s="19" customFormat="1">
       <c r="A41" s="19">
         <v>40</v>
       </c>
@@ -11516,7 +11501,7 @@
       </c>
       <c r="L41" s="20"/>
     </row>
-    <row r="42" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="42" ht="15.5" s="19" customFormat="1">
       <c r="A42" s="19">
         <v>41</v>
       </c>
@@ -11542,7 +11527,7 @@
       </c>
       <c r="L42" s="20"/>
     </row>
-    <row r="43" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="43" ht="15.5" s="19" customFormat="1">
       <c r="A43" s="19">
         <v>42</v>
       </c>
@@ -11568,7 +11553,7 @@
       </c>
       <c r="L43" s="20"/>
     </row>
-    <row r="44" spans="1:12" s="19" customFormat="1">
+    <row r="44" s="19" customFormat="1">
       <c r="A44" s="19">
         <v>43</v>
       </c>
@@ -11594,7 +11579,7 @@
       </c>
       <c r="L44" s="20"/>
     </row>
-    <row r="45" spans="1:12" s="19" customFormat="1">
+    <row r="45" s="19" customFormat="1">
       <c r="A45" s="19">
         <v>44</v>
       </c>
@@ -11620,7 +11605,7 @@
       </c>
       <c r="L45" s="20"/>
     </row>
-    <row r="46" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="46" ht="15.5" s="19" customFormat="1">
       <c r="A46" s="19">
         <v>45</v>
       </c>
@@ -11646,7 +11631,7 @@
       </c>
       <c r="L46" s="20"/>
     </row>
-    <row r="47" spans="1:12" s="19" customFormat="1">
+    <row r="47" s="19" customFormat="1">
       <c r="A47" s="19">
         <v>46</v>
       </c>
@@ -11672,7 +11657,7 @@
       </c>
       <c r="L47" s="20"/>
     </row>
-    <row r="48" spans="1:12" s="19" customFormat="1">
+    <row r="48" s="19" customFormat="1">
       <c r="A48" s="19">
         <v>47</v>
       </c>
@@ -11698,7 +11683,7 @@
       <c r="K48" s="20"/>
       <c r="L48" s="20"/>
     </row>
-    <row r="49" spans="1:15" s="19" customFormat="1">
+    <row r="49" s="19" customFormat="1">
       <c r="A49" s="19">
         <v>48</v>
       </c>
@@ -11725,7 +11710,7 @@
         <v>13880828042</v>
       </c>
     </row>
-    <row r="50" spans="1:15" s="19" customFormat="1">
+    <row r="50" s="19" customFormat="1">
       <c r="A50" s="19">
         <v>49</v>
       </c>
@@ -11760,7 +11745,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="51" spans="1:15" s="19" customFormat="1">
+    <row r="51" s="19" customFormat="1">
       <c r="A51" s="19">
         <v>50</v>
       </c>
@@ -11795,7 +11780,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="52" spans="1:15" s="19" customFormat="1">
+    <row r="52" s="19" customFormat="1">
       <c r="A52" s="19">
         <v>51</v>
       </c>
@@ -11830,7 +11815,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="53" spans="1:15" s="19" customFormat="1">
+    <row r="53" s="19" customFormat="1">
       <c r="A53" s="19">
         <v>52</v>
       </c>
@@ -11865,7 +11850,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="54" spans="1:15" s="19" customFormat="1">
+    <row r="54" s="19" customFormat="1">
       <c r="A54" s="19">
         <v>53</v>
       </c>
@@ -11900,7 +11885,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="55" spans="1:15" s="19" customFormat="1">
+    <row r="55" s="19" customFormat="1">
       <c r="A55" s="19">
         <v>54</v>
       </c>
@@ -11935,7 +11920,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="56" spans="1:15" s="19" customFormat="1">
+    <row r="56" s="19" customFormat="1">
       <c r="A56" s="19">
         <v>55</v>
       </c>
@@ -11961,7 +11946,7 @@
       <c r="K56" s="24"/>
       <c r="L56" s="24"/>
     </row>
-    <row r="57" spans="1:15" s="19" customFormat="1">
+    <row r="57" s="19" customFormat="1">
       <c r="A57" s="19">
         <v>56</v>
       </c>
@@ -11987,7 +11972,7 @@
       <c r="K57" s="24"/>
       <c r="L57" s="24"/>
     </row>
-    <row r="58" spans="1:15" s="19" customFormat="1">
+    <row r="58" s="19" customFormat="1">
       <c r="A58" s="19">
         <v>57</v>
       </c>
@@ -12013,7 +11998,7 @@
       <c r="K58" s="24"/>
       <c r="L58" s="24"/>
     </row>
-    <row r="59" spans="1:15" s="19" customFormat="1">
+    <row r="59" s="19" customFormat="1">
       <c r="A59" s="19">
         <v>58</v>
       </c>
@@ -12038,7 +12023,7 @@
       </c>
       <c r="L59" s="20"/>
     </row>
-    <row r="60" spans="1:15" s="19" customFormat="1">
+    <row r="60" s="19" customFormat="1">
       <c r="A60" s="19">
         <v>59</v>
       </c>
@@ -12069,7 +12054,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="61" spans="1:15" s="19" customFormat="1" ht="17.149999999999999" customHeight="1">
+    <row r="61" ht="17.15" customHeight="1" s="19" customFormat="1">
       <c r="A61" s="19">
         <v>60</v>
       </c>
@@ -12104,7 +12089,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="62" spans="1:15" s="19" customFormat="1" ht="28">
+    <row r="62" ht="28" s="19" customFormat="1">
       <c r="A62" s="19">
         <v>61</v>
       </c>
@@ -12130,7 +12115,7 @@
       <c r="K62" s="20"/>
       <c r="L62" s="20"/>
     </row>
-    <row r="63" spans="1:15" s="19" customFormat="1">
+    <row r="63" s="19" customFormat="1">
       <c r="A63" s="19">
         <v>62</v>
       </c>
@@ -12156,7 +12141,7 @@
       <c r="K63" s="26"/>
       <c r="L63" s="20"/>
     </row>
-    <row r="64" spans="1:15" s="19" customFormat="1" ht="15.5">
+    <row r="64" ht="15.5" s="19" customFormat="1">
       <c r="A64" s="19">
         <v>63</v>
       </c>
@@ -12181,7 +12166,7 @@
       </c>
       <c r="L64" s="20"/>
     </row>
-    <row r="65" spans="1:12" s="19" customFormat="1">
+    <row r="65" s="19" customFormat="1">
       <c r="A65" s="19">
         <v>64</v>
       </c>
@@ -12209,7 +12194,7 @@
       </c>
       <c r="L65" s="20"/>
     </row>
-    <row r="66" spans="1:12" s="19" customFormat="1">
+    <row r="66" s="19" customFormat="1">
       <c r="A66" s="19">
         <v>65</v>
       </c>
@@ -12228,7 +12213,7 @@
       </c>
       <c r="L66" s="20"/>
     </row>
-    <row r="67" spans="1:12" s="19" customFormat="1">
+    <row r="67" s="19" customFormat="1">
       <c r="A67" s="19">
         <v>66</v>
       </c>
@@ -12253,7 +12238,7 @@
       </c>
       <c r="L67" s="20"/>
     </row>
-    <row r="68" spans="1:12" s="19" customFormat="1">
+    <row r="68" s="19" customFormat="1">
       <c r="A68" s="19">
         <v>67</v>
       </c>
@@ -12272,7 +12257,7 @@
       </c>
       <c r="L68" s="20"/>
     </row>
-    <row r="69" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="69" ht="15.5" s="19" customFormat="1">
       <c r="A69" s="19">
         <v>68</v>
       </c>
@@ -12291,7 +12276,7 @@
       </c>
       <c r="L69" s="20"/>
     </row>
-    <row r="70" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="70" ht="15.5" s="19" customFormat="1">
       <c r="A70" s="19">
         <v>69</v>
       </c>
@@ -12316,7 +12301,7 @@
       </c>
       <c r="L70" s="20"/>
     </row>
-    <row r="71" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="71" ht="15.5" s="19" customFormat="1">
       <c r="A71" s="19">
         <v>70</v>
       </c>
@@ -12335,7 +12320,7 @@
       </c>
       <c r="L71" s="20"/>
     </row>
-    <row r="72" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="72" ht="15.5" s="19" customFormat="1">
       <c r="A72" s="19">
         <v>71</v>
       </c>
@@ -12360,7 +12345,7 @@
       </c>
       <c r="L72" s="20"/>
     </row>
-    <row r="73" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="73" ht="15.5" s="19" customFormat="1">
       <c r="A73" s="19">
         <v>72</v>
       </c>
@@ -12388,7 +12373,7 @@
       </c>
       <c r="L73" s="20"/>
     </row>
-    <row r="74" spans="1:12" s="19" customFormat="1">
+    <row r="74" s="19" customFormat="1">
       <c r="A74" s="19">
         <v>73</v>
       </c>
@@ -12414,7 +12399,7 @@
       <c r="K74" s="20"/>
       <c r="L74" s="20"/>
     </row>
-    <row r="75" spans="1:12" s="19" customFormat="1">
+    <row r="75" s="19" customFormat="1">
       <c r="A75" s="19">
         <v>74</v>
       </c>
@@ -12440,7 +12425,7 @@
       <c r="K75" s="20"/>
       <c r="L75" s="20"/>
     </row>
-    <row r="76" spans="1:12" s="19" customFormat="1">
+    <row r="76" s="19" customFormat="1">
       <c r="A76" s="19">
         <v>75</v>
       </c>
@@ -12466,7 +12451,7 @@
       <c r="K76" s="20"/>
       <c r="L76" s="20"/>
     </row>
-    <row r="77" spans="1:12" s="19" customFormat="1">
+    <row r="77" s="19" customFormat="1">
       <c r="A77" s="19">
         <v>76</v>
       </c>
@@ -12492,7 +12477,7 @@
       <c r="K77" s="20"/>
       <c r="L77" s="20"/>
     </row>
-    <row r="78" spans="1:12" s="19" customFormat="1">
+    <row r="78" s="19" customFormat="1">
       <c r="A78" s="19">
         <v>77</v>
       </c>
@@ -12518,7 +12503,7 @@
       <c r="K78" s="20"/>
       <c r="L78" s="20"/>
     </row>
-    <row r="79" spans="1:12" s="19" customFormat="1">
+    <row r="79" s="19" customFormat="1">
       <c r="A79" s="19">
         <v>78</v>
       </c>
@@ -12533,7 +12518,7 @@
       <c r="K79" s="20"/>
       <c r="L79" s="20"/>
     </row>
-    <row r="80" spans="1:12" s="19" customFormat="1">
+    <row r="80" s="19" customFormat="1">
       <c r="A80" s="19">
         <v>79</v>
       </c>
@@ -12561,7 +12546,7 @@
         <v>13550296530</v>
       </c>
     </row>
-    <row r="81" spans="1:12" s="19" customFormat="1">
+    <row r="81" s="19" customFormat="1">
       <c r="A81" s="19">
         <v>80</v>
       </c>
@@ -12589,7 +12574,7 @@
         <v>18380557907</v>
       </c>
     </row>
-    <row r="82" spans="1:12" s="19" customFormat="1">
+    <row r="82" s="19" customFormat="1">
       <c r="A82" s="19">
         <v>81</v>
       </c>
@@ -12617,7 +12602,7 @@
         <v>18980596322</v>
       </c>
     </row>
-    <row r="83" spans="1:12" s="19" customFormat="1">
+    <row r="83" s="19" customFormat="1">
       <c r="A83" s="19">
         <v>82</v>
       </c>
@@ -12645,7 +12630,7 @@
       </c>
       <c r="L83" s="20"/>
     </row>
-    <row r="84" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="84" ht="15.5" s="19" customFormat="1">
       <c r="A84" s="19">
         <v>83</v>
       </c>
@@ -12671,7 +12656,7 @@
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
     </row>
-    <row r="85" spans="1:12" s="19" customFormat="1">
+    <row r="85" s="19" customFormat="1">
       <c r="A85" s="19">
         <v>84</v>
       </c>
@@ -12699,7 +12684,7 @@
         <v>13980664852</v>
       </c>
     </row>
-    <row r="86" spans="1:12" s="19" customFormat="1">
+    <row r="86" s="19" customFormat="1">
       <c r="A86" s="19">
         <v>85</v>
       </c>
@@ -12727,7 +12712,7 @@
         <v>13808086286</v>
       </c>
     </row>
-    <row r="87" spans="1:12" s="19" customFormat="1">
+    <row r="87" s="19" customFormat="1">
       <c r="A87" s="19">
         <v>86</v>
       </c>
@@ -12755,7 +12740,7 @@
         <v>13608196859</v>
       </c>
     </row>
-    <row r="88" spans="1:12" s="19" customFormat="1">
+    <row r="88" s="19" customFormat="1">
       <c r="A88" s="19">
         <v>87</v>
       </c>
@@ -12783,7 +12768,7 @@
         <v>13658013287</v>
       </c>
     </row>
-    <row r="89" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="89" ht="15.5" s="19" customFormat="1">
       <c r="A89" s="19">
         <v>88</v>
       </c>
@@ -12811,7 +12796,7 @@
         <v>13648032216</v>
       </c>
     </row>
-    <row r="90" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="90" ht="15.5" s="19" customFormat="1">
       <c r="A90" s="19">
         <v>89</v>
       </c>
@@ -12839,7 +12824,7 @@
         <v>18108257155</v>
       </c>
     </row>
-    <row r="91" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="91" ht="15.5" s="19" customFormat="1">
       <c r="A91" s="19">
         <v>90</v>
       </c>
@@ -12867,7 +12852,7 @@
         <v>13908237000</v>
       </c>
     </row>
-    <row r="92" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="92" ht="15.5" s="19" customFormat="1">
       <c r="A92" s="19">
         <v>91</v>
       </c>
@@ -12895,7 +12880,7 @@
         <v>13801116402</v>
       </c>
     </row>
-    <row r="93" spans="1:12" s="19" customFormat="1">
+    <row r="93" s="19" customFormat="1">
       <c r="A93" s="19">
         <v>92</v>
       </c>
@@ -12921,7 +12906,7 @@
       <c r="K93" s="20"/>
       <c r="L93" s="20"/>
     </row>
-    <row r="94" spans="1:12" s="19" customFormat="1">
+    <row r="94" s="19" customFormat="1">
       <c r="A94" s="19">
         <v>93</v>
       </c>
@@ -12947,7 +12932,7 @@
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
     </row>
-    <row r="95" spans="1:12" s="19" customFormat="1">
+    <row r="95" s="19" customFormat="1">
       <c r="A95" s="19">
         <v>94</v>
       </c>
@@ -12973,7 +12958,7 @@
       <c r="K95" s="20"/>
       <c r="L95" s="20"/>
     </row>
-    <row r="96" spans="1:12" s="19" customFormat="1">
+    <row r="96" s="19" customFormat="1">
       <c r="A96" s="19">
         <v>95</v>
       </c>
@@ -12999,7 +12984,7 @@
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
     </row>
-    <row r="97" spans="1:12" s="19" customFormat="1">
+    <row r="97" s="19" customFormat="1">
       <c r="A97" s="19">
         <v>96</v>
       </c>
@@ -13025,7 +13010,7 @@
       <c r="K97" s="20"/>
       <c r="L97" s="20"/>
     </row>
-    <row r="98" spans="1:12" s="19" customFormat="1">
+    <row r="98" s="19" customFormat="1">
       <c r="A98" s="19">
         <v>97</v>
       </c>
@@ -13051,11 +13036,11 @@
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99">
       <c r="A99" s="19">
         <v>98</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="0" t="s">
         <v>760</v>
       </c>
       <c r="C99" s="20" t="s">
@@ -13064,24 +13049,24 @@
       <c r="D99" s="20">
         <v>4230116</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99" s="0" t="s">
         <v>761</v>
       </c>
       <c r="F99" s="67" t="s">
         <v>762</v>
       </c>
-      <c r="G99" t="s">
+      <c r="G99" s="0" t="s">
         <v>467</v>
       </c>
       <c r="K99" s="20">
         <v>4230116</v>
       </c>
     </row>
-    <row r="100" spans="1:12">
+    <row r="100">
       <c r="A100" s="19">
         <v>99</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="0" t="s">
         <v>763</v>
       </c>
       <c r="C100" s="20" t="s">
@@ -13096,7 +13081,7 @@
       <c r="F100" s="67" t="s">
         <v>765</v>
       </c>
-      <c r="G100" t="s">
+      <c r="G100" s="0" t="s">
         <v>467</v>
       </c>
       <c r="K100" s="20">
@@ -13106,11 +13091,11 @@
         <v>18980092808</v>
       </c>
     </row>
-    <row r="101" spans="1:12">
+    <row r="101">
       <c r="A101" s="19">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="0" t="s">
         <v>766</v>
       </c>
       <c r="C101" s="20" t="s">
@@ -13122,26 +13107,26 @@
       <c r="F101" s="67" t="s">
         <v>767</v>
       </c>
-      <c r="G101" t="s">
+      <c r="G101" s="0" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="15.5">
+    <row r="102" ht="15.5">
       <c r="A102" s="19">
         <v>101</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="0" t="s">
         <v>769</v>
       </c>
       <c r="C102" s="38" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="103" spans="1:12">
+    <row r="103">
       <c r="A103" s="19">
         <v>102</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="0" t="s">
         <v>771</v>
       </c>
       <c r="C103" s="20" t="s">
@@ -13150,21 +13135,21 @@
       <c r="D103" s="19">
         <v>638391245</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="0" t="s">
         <v>772</v>
       </c>
       <c r="F103" s="19">
         <v>638391245</v>
       </c>
-      <c r="G103" t="s">
+      <c r="G103" s="0" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="104" spans="1:12">
+    <row r="104">
       <c r="A104" s="19">
         <v>103</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="0" t="s">
         <v>774</v>
       </c>
       <c r="C104" s="20" t="s">
@@ -13173,24 +13158,24 @@
       <c r="D104" s="20" t="s">
         <v>775</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E104" s="0" t="s">
         <v>775</v>
       </c>
       <c r="F104" s="67" t="s">
         <v>776</v>
       </c>
-      <c r="G104" t="s">
+      <c r="G104" s="0" t="s">
         <v>777</v>
       </c>
       <c r="L104" s="20">
         <v>18328325926</v>
       </c>
     </row>
-    <row r="105" spans="1:12">
+    <row r="105">
       <c r="A105" s="19">
         <v>104</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="0" t="s">
         <v>778</v>
       </c>
       <c r="C105" s="20" t="s">
@@ -13205,15 +13190,15 @@
       <c r="F105" s="67" t="s">
         <v>780</v>
       </c>
-      <c r="G105" t="s">
+      <c r="G105" s="0" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="106" spans="1:12">
+    <row r="106">
       <c r="A106" s="19">
         <v>105</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="0" t="s">
         <v>782</v>
       </c>
       <c r="C106" s="20" t="s">
@@ -13228,15 +13213,15 @@
       <c r="F106" s="67" t="s">
         <v>784</v>
       </c>
-      <c r="G106" t="s">
+      <c r="G106" s="0" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="107" spans="1:12">
+    <row r="107">
       <c r="A107" s="19">
         <v>106</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="0" t="s">
         <v>785</v>
       </c>
       <c r="C107" s="20" t="s">
@@ -13251,15 +13236,15 @@
       <c r="F107" s="67" t="s">
         <v>787</v>
       </c>
-      <c r="G107" t="s">
+      <c r="G107" s="0" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="108" spans="1:12">
+    <row r="108">
       <c r="A108" s="19">
         <v>107</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="0" t="s">
         <v>788</v>
       </c>
       <c r="C108" s="20" t="s">
@@ -13274,15 +13259,15 @@
       <c r="F108" s="67" t="s">
         <v>790</v>
       </c>
-      <c r="G108" t="s">
+      <c r="G108" s="0" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="109" spans="1:12">
+    <row r="109">
       <c r="A109" s="19">
         <v>108</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="0" t="s">
         <v>791</v>
       </c>
       <c r="C109" s="20" t="s">
@@ -13297,11 +13282,11 @@
       <c r="F109" s="67" t="s">
         <v>793</v>
       </c>
-      <c r="G109" t="s">
+      <c r="G109" s="0" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="110" spans="1:12" s="19" customFormat="1" ht="15.5">
+    <row r="110" ht="15.5" s="19" customFormat="1">
       <c r="A110" s="19">
         <v>109</v>
       </c>
@@ -13327,11 +13312,11 @@
       </c>
       <c r="L110" s="20"/>
     </row>
-    <row r="111" spans="1:12">
+    <row r="111">
       <c r="A111" s="19">
         <v>110</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="0" t="s">
         <v>797</v>
       </c>
       <c r="C111" s="20" t="s">
@@ -13343,18 +13328,18 @@
       <c r="F111" s="67" t="s">
         <v>798</v>
       </c>
-      <c r="G111" t="s">
+      <c r="G111" s="0" t="s">
         <v>799</v>
       </c>
       <c r="H111" s="68" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="112" spans="1:12">
+    <row r="112">
       <c r="A112" s="19">
         <v>111</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="0" t="s">
         <v>801</v>
       </c>
       <c r="C112" s="20" t="s">
@@ -13366,15 +13351,15 @@
       <c r="F112" s="67" t="s">
         <v>802</v>
       </c>
-      <c r="G112" t="s">
+      <c r="G112" s="0" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="113" spans="1:12">
+    <row r="113">
       <c r="A113" s="19">
         <v>112</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="0" t="s">
         <v>804</v>
       </c>
       <c r="C113" s="26" t="s">
@@ -13389,7 +13374,7 @@
       <c r="F113" s="67" t="s">
         <v>807</v>
       </c>
-      <c r="G113" t="s">
+      <c r="G113" s="0" t="s">
         <v>808</v>
       </c>
       <c r="K113" s="68" t="s">
@@ -13399,11 +13384,11 @@
         <v>17852935846</v>
       </c>
     </row>
-    <row r="114" spans="1:12">
+    <row r="114">
       <c r="A114" s="19">
         <v>113</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="0" t="s">
         <v>809</v>
       </c>
       <c r="C114" s="26" t="s">
@@ -13418,18 +13403,18 @@
       <c r="F114" s="67" t="s">
         <v>812</v>
       </c>
-      <c r="G114" t="s">
+      <c r="G114" s="0" t="s">
         <v>813</v>
       </c>
       <c r="K114" s="68" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="115" spans="1:12">
+    <row r="115">
       <c r="A115" s="19">
         <v>114</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="0" t="s">
         <v>814</v>
       </c>
       <c r="C115" s="26" t="s">
@@ -13444,7 +13429,7 @@
       <c r="F115" s="67" t="s">
         <v>817</v>
       </c>
-      <c r="G115" t="s">
+      <c r="G115" s="0" t="s">
         <v>537</v>
       </c>
       <c r="K115" s="68" t="s">
@@ -13454,11 +13439,11 @@
         <v>18380269853</v>
       </c>
     </row>
-    <row r="116" spans="1:12">
+    <row r="116">
       <c r="A116" s="19">
         <v>115</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="0" t="s">
         <v>818</v>
       </c>
       <c r="C116" s="20" t="s">
@@ -13473,15 +13458,15 @@
       <c r="F116" s="67" t="s">
         <v>820</v>
       </c>
-      <c r="G116" t="s">
+      <c r="G116" s="0" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="15.5">
+    <row r="117" ht="15.5">
       <c r="A117" s="19">
         <v>116</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="0" t="s">
         <v>822</v>
       </c>
       <c r="C117" s="26" t="s">
@@ -13493,18 +13478,18 @@
       <c r="F117" s="67" t="s">
         <v>824</v>
       </c>
-      <c r="G117" t="s">
+      <c r="G117" s="0" t="s">
         <v>825</v>
       </c>
       <c r="K117" s="28" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="118" spans="1:12">
+    <row r="118">
       <c r="A118" s="19">
         <v>117</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="0" t="s">
         <v>826</v>
       </c>
       <c r="C118" s="20" t="s">
@@ -13513,32 +13498,32 @@
       <c r="D118" s="20" t="s">
         <v>827</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E118" s="0" t="s">
         <v>827</v>
       </c>
       <c r="F118" s="67" t="s">
         <v>828</v>
       </c>
-      <c r="G118" t="s">
+      <c r="G118" s="0" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="15.5">
+    <row r="119" ht="15.5">
       <c r="A119" s="19">
         <v>118</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="0" t="s">
         <v>830</v>
       </c>
       <c r="C119" s="38" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="120" spans="1:12">
+    <row r="120">
       <c r="A120" s="19">
         <v>119</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="0" t="s">
         <v>831</v>
       </c>
       <c r="C120" s="20" t="s">
@@ -13547,21 +13532,21 @@
       <c r="D120" s="20" t="s">
         <v>832</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E120" s="0" t="s">
         <v>832</v>
       </c>
       <c r="F120" s="67" t="s">
         <v>833</v>
       </c>
-      <c r="G120" t="s">
+      <c r="G120" s="0" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="121" spans="1:12">
+    <row r="121">
       <c r="A121" s="19">
         <v>120</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="0" t="s">
         <v>835</v>
       </c>
       <c r="C121" s="20" t="s">
@@ -13576,15 +13561,15 @@
       <c r="F121" s="67" t="s">
         <v>837</v>
       </c>
-      <c r="G121" t="s">
+      <c r="G121" s="0" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="122" spans="1:12">
+    <row r="122">
       <c r="A122" s="19">
         <v>121</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="0" t="s">
         <v>839</v>
       </c>
       <c r="C122" s="20" t="s">
@@ -13599,15 +13584,15 @@
       <c r="F122" s="67" t="s">
         <v>841</v>
       </c>
-      <c r="G122" t="s">
+      <c r="G122" s="0" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="123" spans="1:12">
+    <row r="123">
       <c r="A123" s="19">
         <v>122</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="0" t="s">
         <v>843</v>
       </c>
       <c r="C123" s="20" t="s">
@@ -13622,15 +13607,15 @@
       <c r="F123" s="67" t="s">
         <v>845</v>
       </c>
-      <c r="G123" t="s">
+      <c r="G123" s="0" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="124" spans="1:12">
+    <row r="124">
       <c r="A124" s="19">
         <v>123</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="0" t="s">
         <v>847</v>
       </c>
       <c r="C124" s="20" t="s">
@@ -13645,15 +13630,15 @@
       <c r="F124" s="67" t="s">
         <v>849</v>
       </c>
-      <c r="G124" t="s">
+      <c r="G124" s="0" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="125" spans="1:12">
+    <row r="125">
       <c r="A125" s="19">
         <v>124</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="0" t="s">
         <v>851</v>
       </c>
       <c r="C125" s="20" t="s">
@@ -13668,15 +13653,15 @@
       <c r="F125" s="67" t="s">
         <v>853</v>
       </c>
-      <c r="G125" t="s">
+      <c r="G125" s="0" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="126" spans="1:12">
+    <row r="126">
       <c r="A126" s="19">
         <v>125</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="0" t="s">
         <v>854</v>
       </c>
       <c r="C126" s="20" t="s">
@@ -13691,18 +13676,18 @@
       <c r="F126" s="67" t="s">
         <v>856</v>
       </c>
-      <c r="G126" t="s">
+      <c r="G126" s="0" t="s">
         <v>857</v>
       </c>
       <c r="H126" s="68" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="127" spans="1:12">
+    <row r="127">
       <c r="A127" s="19">
         <v>126</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="0" t="s">
         <v>859</v>
       </c>
       <c r="C127" s="20" t="s">
@@ -13714,18 +13699,18 @@
       <c r="E127" s="67" t="s">
         <v>860</v>
       </c>
-      <c r="F127" t="s">
+      <c r="F127" s="0" t="s">
         <v>861</v>
       </c>
-      <c r="G127" t="s">
+      <c r="G127" s="0" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="128" spans="1:12">
+    <row r="128">
       <c r="A128" s="19">
         <v>127</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="0" t="s">
         <v>862</v>
       </c>
       <c r="C128" s="20" t="s">
@@ -13737,21 +13722,21 @@
       <c r="E128" s="67" t="s">
         <v>863</v>
       </c>
-      <c r="F128" t="s">
+      <c r="F128" s="0" t="s">
         <v>864</v>
       </c>
-      <c r="G128" t="s">
+      <c r="G128" s="0" t="s">
         <v>865</v>
       </c>
       <c r="L128" s="20">
         <v>13908033153</v>
       </c>
     </row>
-    <row r="129" spans="1:12">
+    <row r="129">
       <c r="A129" s="19">
         <v>128</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="0" t="s">
         <v>866</v>
       </c>
       <c r="C129" s="20" t="s">
@@ -13766,18 +13751,18 @@
       <c r="F129" s="67" t="s">
         <v>868</v>
       </c>
-      <c r="G129" t="s">
+      <c r="G129" s="0" t="s">
         <v>869</v>
       </c>
       <c r="L129" s="20">
         <v>13882183189</v>
       </c>
     </row>
-    <row r="130" spans="1:12">
+    <row r="130">
       <c r="A130" s="19">
         <v>129</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="0" t="s">
         <v>870</v>
       </c>
       <c r="C130" s="20" t="s">
@@ -13789,21 +13774,21 @@
       <c r="E130" s="67" t="s">
         <v>871</v>
       </c>
-      <c r="F130" t="s">
+      <c r="F130" s="0" t="s">
         <v>872</v>
       </c>
-      <c r="G130" t="s">
+      <c r="G130" s="0" t="s">
         <v>873</v>
       </c>
       <c r="L130" s="20">
         <v>18681695840</v>
       </c>
     </row>
-    <row r="131" spans="1:12">
+    <row r="131">
       <c r="A131" s="19">
         <v>130</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="0" t="s">
         <v>874</v>
       </c>
       <c r="C131" s="20" t="s">
@@ -13815,21 +13800,21 @@
       <c r="E131" s="67" t="s">
         <v>875</v>
       </c>
-      <c r="F131" t="s">
+      <c r="F131" s="0" t="s">
         <v>876</v>
       </c>
-      <c r="G131" t="s">
+      <c r="G131" s="0" t="s">
         <v>877</v>
       </c>
       <c r="L131" s="20">
         <v>13684011028</v>
       </c>
     </row>
-    <row r="132" spans="1:12">
+    <row r="132">
       <c r="A132" s="19">
         <v>131</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="0" t="s">
         <v>878</v>
       </c>
       <c r="C132" s="20" t="s">
@@ -13841,21 +13826,21 @@
       <c r="E132" s="67" t="s">
         <v>879</v>
       </c>
-      <c r="F132" t="s">
+      <c r="F132" s="0" t="s">
         <v>880</v>
       </c>
-      <c r="G132" t="s">
+      <c r="G132" s="0" t="s">
         <v>881</v>
       </c>
       <c r="L132" s="20">
         <v>13980967180</v>
       </c>
     </row>
-    <row r="133" spans="1:12">
+    <row r="133">
       <c r="A133" s="19">
         <v>132</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="0" t="s">
         <v>782</v>
       </c>
       <c r="C133" s="20" t="s">
@@ -13864,24 +13849,24 @@
       <c r="D133" s="20" t="s">
         <v>882</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E133" s="0" t="s">
         <v>882</v>
       </c>
-      <c r="F133" t="s">
+      <c r="F133" s="0" t="s">
         <v>883</v>
       </c>
-      <c r="G133" t="s">
+      <c r="G133" s="0" t="s">
         <v>884</v>
       </c>
       <c r="L133" s="20">
         <v>15908180960</v>
       </c>
     </row>
-    <row r="134" spans="1:12">
+    <row r="134">
       <c r="A134" s="19">
         <v>133</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="0" t="s">
         <v>885</v>
       </c>
       <c r="C134" s="20" t="s">
@@ -13893,21 +13878,21 @@
       <c r="E134" s="67" t="s">
         <v>886</v>
       </c>
-      <c r="F134" t="s">
+      <c r="F134" s="0" t="s">
         <v>887</v>
       </c>
-      <c r="G134" t="s">
+      <c r="G134" s="0" t="s">
         <v>888</v>
       </c>
       <c r="L134" s="20">
         <v>18618193010</v>
       </c>
     </row>
-    <row r="135" spans="1:12">
+    <row r="135">
       <c r="A135" s="19">
         <v>134</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="0" t="s">
         <v>889</v>
       </c>
       <c r="C135" s="26" t="s">
@@ -13916,13 +13901,13 @@
       <c r="D135" s="68" t="s">
         <v>890</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E135" s="0" t="s">
         <v>891</v>
       </c>
-      <c r="F135" t="s">
+      <c r="F135" s="0" t="s">
         <v>892</v>
       </c>
-      <c r="G135" t="s">
+      <c r="G135" s="0" t="s">
         <v>888</v>
       </c>
       <c r="K135" s="68" t="s">
@@ -13932,11 +13917,11 @@
         <v>13908013979</v>
       </c>
     </row>
-    <row r="136" spans="1:12">
+    <row r="136">
       <c r="A136" s="19">
         <v>135</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="0" t="s">
         <v>893</v>
       </c>
       <c r="C136" s="20" t="s">
@@ -13945,21 +13930,21 @@
       <c r="D136" s="67" t="s">
         <v>894</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E136" s="0" t="s">
         <v>895</v>
       </c>
       <c r="F136" s="67" t="s">
         <v>894</v>
       </c>
-      <c r="G136" t="s">
+      <c r="G136" s="0" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="137" spans="1:12">
+    <row r="137">
       <c r="A137" s="19">
         <v>136</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="0" t="s">
         <v>897</v>
       </c>
       <c r="C137" s="20" t="s">
@@ -13974,18 +13959,18 @@
       <c r="F137" s="67" t="s">
         <v>899</v>
       </c>
-      <c r="G137" t="s">
+      <c r="G137" s="0" t="s">
         <v>900</v>
       </c>
       <c r="L137" s="20">
         <v>15883506572</v>
       </c>
     </row>
-    <row r="138" spans="1:12">
+    <row r="138">
       <c r="A138" s="19">
         <v>137</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="0" t="s">
         <v>901</v>
       </c>
       <c r="C138" s="26" t="s">
@@ -14001,11 +13986,11 @@
         <v>18349139474</v>
       </c>
     </row>
-    <row r="139" spans="1:12">
+    <row r="139">
       <c r="A139" s="19">
         <v>138</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="0" t="s">
         <v>903</v>
       </c>
       <c r="C139" s="26" t="s">
@@ -14018,11 +14003,11 @@
         <v>904</v>
       </c>
     </row>
-    <row r="140" spans="1:12">
+    <row r="140">
       <c r="A140" s="19">
         <v>139</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="0" t="s">
         <v>905</v>
       </c>
       <c r="C140" s="26" t="s">
@@ -14035,11 +14020,11 @@
         <v>906</v>
       </c>
     </row>
-    <row r="141" spans="1:12">
+    <row r="141">
       <c r="A141" s="19">
         <v>140</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="0" t="s">
         <v>907</v>
       </c>
       <c r="C141" s="26" t="s">
@@ -14051,18 +14036,18 @@
       <c r="F141" s="67" t="s">
         <v>909</v>
       </c>
-      <c r="G141" t="s">
+      <c r="G141" s="0" t="s">
         <v>910</v>
       </c>
       <c r="K141" s="68" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="142" spans="1:12">
+    <row r="142">
       <c r="A142" s="19">
         <v>141</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="0" t="s">
         <v>911</v>
       </c>
       <c r="C142" s="26" t="s">
@@ -14074,18 +14059,18 @@
       <c r="F142" s="67" t="s">
         <v>913</v>
       </c>
-      <c r="G142" t="s">
+      <c r="G142" s="0" t="s">
         <v>914</v>
       </c>
       <c r="K142" s="68" t="s">
         <v>912</v>
       </c>
     </row>
-    <row r="143" spans="1:12">
+    <row r="143">
       <c r="A143" s="19">
         <v>142</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="0" t="s">
         <v>915</v>
       </c>
       <c r="C143" s="26" t="s">
@@ -14097,7 +14082,7 @@
       <c r="F143" s="67" t="s">
         <v>917</v>
       </c>
-      <c r="G143" t="s">
+      <c r="G143" s="0" t="s">
         <v>918</v>
       </c>
       <c r="K143" s="68" t="s">
@@ -14107,11 +14092,11 @@
         <v>13880985377</v>
       </c>
     </row>
-    <row r="144" spans="1:12">
+    <row r="144">
       <c r="A144" s="19">
         <v>143</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="0" t="s">
         <v>919</v>
       </c>
       <c r="C144" s="26" t="s">
@@ -14123,7 +14108,7 @@
       <c r="F144" s="67" t="s">
         <v>921</v>
       </c>
-      <c r="G144" t="s">
+      <c r="G144" s="0" t="s">
         <v>922</v>
       </c>
       <c r="K144" s="68" t="s">
@@ -14133,11 +14118,11 @@
         <v>19829705092</v>
       </c>
     </row>
-    <row r="145" spans="1:12">
+    <row r="145">
       <c r="A145" s="19">
         <v>144</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="0" t="s">
         <v>923</v>
       </c>
       <c r="C145" s="26" t="s">
@@ -14149,18 +14134,18 @@
       <c r="F145" s="67" t="s">
         <v>925</v>
       </c>
-      <c r="G145" t="s">
+      <c r="G145" s="0" t="s">
         <v>926</v>
       </c>
       <c r="K145" s="68" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="146" spans="1:12">
+    <row r="146">
       <c r="A146" s="19">
         <v>145</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="0" t="s">
         <v>927</v>
       </c>
       <c r="C146" s="26" t="s">
@@ -14172,18 +14157,18 @@
       <c r="F146" s="67" t="s">
         <v>929</v>
       </c>
-      <c r="G146" t="s">
+      <c r="G146" s="0" t="s">
         <v>930</v>
       </c>
       <c r="K146" s="68" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="147" spans="1:12">
+    <row r="147">
       <c r="A147" s="19">
         <v>146</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="0" t="s">
         <v>931</v>
       </c>
       <c r="C147" s="26" t="s">
@@ -14195,7 +14180,7 @@
       <c r="F147" s="67" t="s">
         <v>933</v>
       </c>
-      <c r="G147" t="s">
+      <c r="G147" s="0" t="s">
         <v>934</v>
       </c>
       <c r="K147" s="68" t="s">
@@ -14205,11 +14190,11 @@
         <v>13881103012</v>
       </c>
     </row>
-    <row r="148" spans="1:12">
+    <row r="148">
       <c r="A148" s="19">
         <v>147</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="0" t="s">
         <v>935</v>
       </c>
       <c r="C148" s="26" t="s">
@@ -14228,11 +14213,11 @@
         <v>13281117026</v>
       </c>
     </row>
-    <row r="149" spans="1:12">
+    <row r="149">
       <c r="A149" s="19">
         <v>148</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="0" t="s">
         <v>938</v>
       </c>
       <c r="C149" s="20" t="s">
@@ -14247,15 +14232,15 @@
       <c r="F149" s="67" t="s">
         <v>940</v>
       </c>
-      <c r="G149" t="s">
+      <c r="G149" s="0" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="150" spans="1:12">
+    <row r="150">
       <c r="A150" s="19">
         <v>149</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="0" t="s">
         <v>942</v>
       </c>
       <c r="C150" s="26" t="s">
@@ -14268,11 +14253,11 @@
         <v>943</v>
       </c>
     </row>
-    <row r="151" spans="1:12">
+    <row r="151">
       <c r="A151" s="19">
         <v>150</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="0" t="s">
         <v>944</v>
       </c>
       <c r="C151" s="20" t="s">
@@ -14284,15 +14269,15 @@
       <c r="F151" s="67" t="s">
         <v>945</v>
       </c>
-      <c r="G151" t="s">
+      <c r="G151" s="0" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="152" spans="1:12">
+    <row r="152">
       <c r="A152" s="19">
         <v>151</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="0" t="s">
         <v>947</v>
       </c>
       <c r="C152" s="26" t="s">
@@ -14308,7 +14293,7 @@
         <v>6240022</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="28">
+    <row r="153" ht="28">
       <c r="A153" s="19">
         <v>152</v>
       </c>
@@ -14319,7 +14304,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="154" spans="1:12">
+    <row r="154">
       <c r="A154" s="19">
         <v>153</v>
       </c>
@@ -14335,18 +14320,18 @@
       <c r="F154" s="67" t="s">
         <v>952</v>
       </c>
-      <c r="G154" t="s">
+      <c r="G154" s="0" t="s">
         <v>530</v>
       </c>
       <c r="K154" s="68" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="155" spans="1:12">
+    <row r="155">
       <c r="A155" s="19">
         <v>154</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="0" t="s">
         <v>953</v>
       </c>
       <c r="C155" s="20" t="s">
@@ -14355,24 +14340,24 @@
       <c r="D155" s="20" t="s">
         <v>954</v>
       </c>
-      <c r="E155" t="s">
+      <c r="E155" s="0" t="s">
         <v>954</v>
       </c>
       <c r="F155" s="67" t="s">
         <v>955</v>
       </c>
-      <c r="G155" t="s">
+      <c r="G155" s="0" t="s">
         <v>956</v>
       </c>
       <c r="K155" s="20">
         <v>18382957777</v>
       </c>
     </row>
-    <row r="156" spans="1:12">
+    <row r="156">
       <c r="A156" s="19">
         <v>155</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="0" t="s">
         <v>957</v>
       </c>
       <c r="C156" s="20" t="s">
@@ -14387,18 +14372,18 @@
       <c r="F156" s="67" t="s">
         <v>959</v>
       </c>
-      <c r="G156" t="s">
+      <c r="G156" s="0" t="s">
         <v>960</v>
       </c>
       <c r="K156" s="20">
         <v>17381890296</v>
       </c>
     </row>
-    <row r="157" spans="1:12">
+    <row r="157">
       <c r="A157" s="19">
         <v>156</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="0" t="s">
         <v>961</v>
       </c>
       <c r="C157" s="20" t="s">
@@ -14413,7 +14398,7 @@
       <c r="F157" s="67" t="s">
         <v>963</v>
       </c>
-      <c r="G157" t="s">
+      <c r="G157" s="0" t="s">
         <v>964</v>
       </c>
       <c r="K157" s="20">
@@ -14423,11 +14408,11 @@
         <v>947</v>
       </c>
     </row>
-    <row r="158" spans="1:12">
+    <row r="158">
       <c r="A158" s="19">
         <v>157</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="0" t="s">
         <v>965</v>
       </c>
       <c r="C158" s="20" t="s">
@@ -14436,21 +14421,21 @@
       <c r="D158" s="20" t="s">
         <v>966</v>
       </c>
-      <c r="E158" t="s">
+      <c r="E158" s="0" t="s">
         <v>966</v>
       </c>
       <c r="F158" s="67" t="s">
         <v>967</v>
       </c>
-      <c r="G158" t="s">
+      <c r="G158" s="0" t="s">
         <v>968</v>
       </c>
     </row>
-    <row r="159" spans="1:12">
+    <row r="159">
       <c r="A159" s="19">
         <v>158</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="0" t="s">
         <v>969</v>
       </c>
       <c r="C159" s="20" t="s">
@@ -14465,18 +14450,18 @@
       <c r="F159" s="67" t="s">
         <v>971</v>
       </c>
-      <c r="G159" t="s">
+      <c r="G159" s="0" t="s">
         <v>972</v>
       </c>
       <c r="K159" s="20">
         <v>18349260951</v>
       </c>
     </row>
-    <row r="160" spans="1:12">
+    <row r="160">
       <c r="A160" s="19">
         <v>159</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="0" t="s">
         <v>973</v>
       </c>
       <c r="C160" s="20" t="s">
@@ -14485,24 +14470,24 @@
       <c r="D160" s="20" t="s">
         <v>974</v>
       </c>
-      <c r="E160" t="s">
+      <c r="E160" s="0" t="s">
         <v>974</v>
       </c>
       <c r="F160" s="67" t="s">
         <v>975</v>
       </c>
-      <c r="G160" t="s">
+      <c r="G160" s="0" t="s">
         <v>972</v>
       </c>
       <c r="K160" s="20">
         <v>13688479908</v>
       </c>
     </row>
-    <row r="161" spans="1:13">
+    <row r="161">
       <c r="A161" s="19">
         <v>160</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" s="0" t="s">
         <v>976</v>
       </c>
       <c r="C161" s="20" t="s">
@@ -14517,21 +14502,21 @@
       <c r="F161" s="67" t="s">
         <v>978</v>
       </c>
-      <c r="G161" t="s">
+      <c r="G161" s="0" t="s">
         <v>972</v>
       </c>
       <c r="K161" s="20">
         <v>18030512239</v>
       </c>
-      <c r="M161" t="s">
+      <c r="M161" s="0" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="162" spans="1:13">
+    <row r="162">
       <c r="A162" s="19">
         <v>161</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" s="0" t="s">
         <v>980</v>
       </c>
       <c r="C162" s="20" t="s">
@@ -14546,15 +14531,15 @@
       <c r="F162" s="67" t="s">
         <v>982</v>
       </c>
-      <c r="G162" t="s">
+      <c r="G162" s="0" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="163" spans="1:13">
+    <row r="163">
       <c r="A163" s="19">
         <v>162</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B163" s="0" t="s">
         <v>984</v>
       </c>
       <c r="C163" s="20" t="s">
@@ -14566,15 +14551,15 @@
       <c r="F163" s="67" t="s">
         <v>985</v>
       </c>
-      <c r="G163" t="s">
+      <c r="G163" s="0" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="164" spans="1:13">
+    <row r="164">
       <c r="A164" s="19">
         <v>163</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" s="0" t="s">
         <v>986</v>
       </c>
       <c r="C164" s="20" t="s">
@@ -14587,11 +14572,11 @@
         <v>987</v>
       </c>
     </row>
-    <row r="165" spans="1:13">
+    <row r="165">
       <c r="A165" s="19">
         <v>164</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" s="0" t="s">
         <v>988</v>
       </c>
       <c r="C165" s="20" t="s">
@@ -14606,18 +14591,18 @@
       <c r="F165" s="67" t="s">
         <v>990</v>
       </c>
-      <c r="G165" t="s">
+      <c r="G165" s="0" t="s">
         <v>991</v>
       </c>
       <c r="L165" s="20">
         <v>13548110233</v>
       </c>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166">
       <c r="A166" s="19">
         <v>165</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166" s="0" t="s">
         <v>992</v>
       </c>
       <c r="C166" s="20" t="s">
@@ -14630,11 +14615,11 @@
         <v>993</v>
       </c>
     </row>
-    <row r="167" spans="1:13">
+    <row r="167">
       <c r="A167" s="19">
         <v>166</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="0" t="s">
         <v>994</v>
       </c>
       <c r="C167" s="20" t="s">
@@ -14647,11 +14632,11 @@
         <v>995</v>
       </c>
     </row>
-    <row r="168" spans="1:13">
+    <row r="168">
       <c r="A168" s="19">
         <v>167</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="0" t="s">
         <v>996</v>
       </c>
       <c r="C168" s="20" t="s">
@@ -14664,11 +14649,11 @@
         <v>997</v>
       </c>
     </row>
-    <row r="169" spans="1:13">
+    <row r="169">
       <c r="A169" s="19">
         <v>168</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169" s="0" t="s">
         <v>998</v>
       </c>
       <c r="C169" s="20" t="s">
@@ -14681,11 +14666,11 @@
         <v>999</v>
       </c>
     </row>
-    <row r="170" spans="1:13">
+    <row r="170">
       <c r="A170" s="19">
         <v>169</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170" s="0" t="s">
         <v>1000</v>
       </c>
       <c r="C170" s="20" t="s">
@@ -14700,18 +14685,18 @@
       <c r="F170" s="67" t="s">
         <v>1002</v>
       </c>
-      <c r="G170" t="s">
+      <c r="G170" s="0" t="s">
         <v>641</v>
       </c>
       <c r="L170" s="20">
         <v>13881939276</v>
       </c>
     </row>
-    <row r="171" spans="1:13">
+    <row r="171">
       <c r="A171" s="19">
         <v>170</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171" s="0" t="s">
         <v>1003</v>
       </c>
       <c r="C171" s="20" t="s">
@@ -14720,24 +14705,24 @@
       <c r="D171" s="20" t="s">
         <v>1004</v>
       </c>
-      <c r="E171" t="s">
+      <c r="E171" s="0" t="s">
         <v>1004</v>
       </c>
       <c r="F171" s="67" t="s">
         <v>1005</v>
       </c>
-      <c r="G171" t="s">
+      <c r="G171" s="0" t="s">
         <v>972</v>
       </c>
       <c r="L171" s="20">
         <v>13980555007</v>
       </c>
     </row>
-    <row r="172" spans="1:13">
+    <row r="172">
       <c r="A172" s="19">
         <v>171</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B172" s="0" t="s">
         <v>1006</v>
       </c>
       <c r="C172" s="20" t="s">
@@ -14752,18 +14737,18 @@
       <c r="F172" s="67" t="s">
         <v>1008</v>
       </c>
-      <c r="G172" t="s">
+      <c r="G172" s="0" t="s">
         <v>1009</v>
       </c>
       <c r="L172" s="20">
         <v>13808186159</v>
       </c>
     </row>
-    <row r="173" spans="1:13">
+    <row r="173">
       <c r="A173" s="19">
         <v>172</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B173" s="0" t="s">
         <v>1010</v>
       </c>
       <c r="C173" s="20" t="s">
@@ -14778,21 +14763,21 @@
       <c r="F173" s="67" t="s">
         <v>1012</v>
       </c>
-      <c r="G173" t="s">
+      <c r="G173" s="0" t="s">
         <v>1013</v>
       </c>
       <c r="L173" s="20">
         <v>13438192391</v>
       </c>
-      <c r="M173" t="s">
+      <c r="M173" s="0" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="174" spans="1:13">
+    <row r="174">
       <c r="A174" s="19">
         <v>173</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174" s="0" t="s">
         <v>1015</v>
       </c>
       <c r="C174" s="20" t="s">
@@ -14807,18 +14792,18 @@
       <c r="F174" s="67" t="s">
         <v>1017</v>
       </c>
-      <c r="G174" t="s">
+      <c r="G174" s="0" t="s">
         <v>1018</v>
       </c>
       <c r="L174" s="20">
         <v>13540600883</v>
       </c>
     </row>
-    <row r="175" spans="1:13">
+    <row r="175">
       <c r="A175" s="19">
         <v>174</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B175" s="0" t="s">
         <v>1019</v>
       </c>
       <c r="C175" s="20" t="s">
@@ -14833,18 +14818,18 @@
       <c r="F175" s="67" t="s">
         <v>1021</v>
       </c>
-      <c r="G175" t="s">
+      <c r="G175" s="0" t="s">
         <v>972</v>
       </c>
       <c r="L175" s="20">
         <v>13881986933</v>
       </c>
     </row>
-    <row r="176" spans="1:13">
+    <row r="176">
       <c r="A176" s="19">
         <v>175</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="0" t="s">
         <v>1022</v>
       </c>
       <c r="C176" s="20" t="s">
@@ -14859,15 +14844,15 @@
       <c r="F176" s="67" t="s">
         <v>1023</v>
       </c>
-      <c r="G176" t="s">
+      <c r="G176" s="0" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="177" spans="1:13">
+    <row r="177">
       <c r="A177" s="19">
         <v>176</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B177" s="0" t="s">
         <v>1025</v>
       </c>
       <c r="C177" s="20" t="s">
@@ -14876,13 +14861,13 @@
       <c r="D177" s="68" t="s">
         <v>1026</v>
       </c>
-      <c r="E177">
+      <c r="E177" s="0">
         <v>0</v>
       </c>
-      <c r="F177">
+      <c r="F177" s="0">
         <v>0</v>
       </c>
-      <c r="G177">
+      <c r="G177" s="0">
         <v>0</v>
       </c>
       <c r="K177" s="68" t="s">
@@ -14892,11 +14877,11 @@
         <v>18088744160</v>
       </c>
     </row>
-    <row r="178" spans="1:13">
+    <row r="178">
       <c r="A178" s="19">
         <v>177</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B178" s="0" t="s">
         <v>1027</v>
       </c>
       <c r="C178" s="20" t="s">
@@ -14911,18 +14896,18 @@
       <c r="F178" s="67" t="s">
         <v>1029</v>
       </c>
-      <c r="G178" t="s">
+      <c r="G178" s="0" t="s">
         <v>1030</v>
       </c>
       <c r="L178" s="20">
         <v>17381897976</v>
       </c>
     </row>
-    <row r="179" spans="1:13">
+    <row r="179">
       <c r="A179" s="19">
         <v>178</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B179" s="0" t="s">
         <v>1031</v>
       </c>
       <c r="C179" s="20" t="s">
@@ -14937,18 +14922,18 @@
       <c r="F179" s="67" t="s">
         <v>1033</v>
       </c>
-      <c r="G179" t="s">
+      <c r="G179" s="0" t="s">
         <v>1034</v>
       </c>
       <c r="L179" s="20">
         <v>18511881577</v>
       </c>
     </row>
-    <row r="180" spans="1:13">
+    <row r="180">
       <c r="A180" s="19">
         <v>179</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B180" s="0" t="s">
         <v>1035</v>
       </c>
       <c r="C180" s="20" t="s">
@@ -14963,18 +14948,18 @@
       <c r="F180" s="67" t="s">
         <v>1037</v>
       </c>
-      <c r="G180" t="s">
+      <c r="G180" s="0" t="s">
         <v>1038</v>
       </c>
       <c r="L180" s="20">
         <v>13709485953</v>
       </c>
     </row>
-    <row r="181" spans="1:13">
+    <row r="181">
       <c r="A181" s="19">
         <v>180</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B181" s="0" t="s">
         <v>1039</v>
       </c>
       <c r="C181" s="20" t="s">
@@ -14989,18 +14974,18 @@
       <c r="F181" s="67" t="s">
         <v>1041</v>
       </c>
-      <c r="G181" t="s">
+      <c r="G181" s="0" t="s">
         <v>1042</v>
       </c>
       <c r="L181" s="20">
         <v>13720184932</v>
       </c>
     </row>
-    <row r="182" spans="1:13">
+    <row r="182">
       <c r="A182" s="19">
         <v>181</v>
       </c>
-      <c r="B182" t="s">
+      <c r="B182" s="0" t="s">
         <v>1043</v>
       </c>
       <c r="C182" s="20" t="s">
@@ -15009,21 +14994,21 @@
       <c r="D182" s="67" t="s">
         <v>1044</v>
       </c>
-      <c r="E182" t="s">
+      <c r="E182" s="0" t="s">
         <v>1045</v>
       </c>
       <c r="F182" s="67" t="s">
         <v>1044</v>
       </c>
-      <c r="G182" t="s">
+      <c r="G182" s="0" t="s">
         <v>1046</v>
       </c>
     </row>
-    <row r="183" spans="1:13">
+    <row r="183">
       <c r="A183" s="19">
         <v>182</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B183" s="0" t="s">
         <v>1047</v>
       </c>
       <c r="C183" s="20" t="s">
@@ -15038,7 +15023,7 @@
       <c r="F183" s="67" t="s">
         <v>1049</v>
       </c>
-      <c r="G183" t="s">
+      <c r="G183" s="0" t="s">
         <v>881</v>
       </c>
       <c r="H183" s="68" t="s">
@@ -15048,11 +15033,11 @@
         <v>13072883388</v>
       </c>
     </row>
-    <row r="184" spans="1:13">
+    <row r="184">
       <c r="A184" s="19">
         <v>183</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B184" s="0" t="s">
         <v>1051</v>
       </c>
       <c r="C184" s="20" t="s">
@@ -15067,7 +15052,7 @@
       <c r="F184" s="67" t="s">
         <v>1053</v>
       </c>
-      <c r="G184" t="s">
+      <c r="G184" s="0" t="s">
         <v>1054</v>
       </c>
       <c r="H184" s="68" t="s">
@@ -15077,11 +15062,11 @@
         <v>13880384547</v>
       </c>
     </row>
-    <row r="185" spans="1:13">
+    <row r="185">
       <c r="A185" s="19">
         <v>184</v>
       </c>
-      <c r="B185" t="s">
+      <c r="B185" s="0" t="s">
         <v>1056</v>
       </c>
       <c r="C185" s="20" t="s">
@@ -15096,7 +15081,7 @@
       <c r="F185" s="67" t="s">
         <v>1058</v>
       </c>
-      <c r="G185" t="s">
+      <c r="G185" s="0" t="s">
         <v>1059</v>
       </c>
       <c r="H185" s="33" t="s">
@@ -15106,11 +15091,11 @@
         <v>13551109316</v>
       </c>
     </row>
-    <row r="186" spans="1:13">
+    <row r="186">
       <c r="A186" s="19">
         <v>185</v>
       </c>
-      <c r="B186" t="s">
+      <c r="B186" s="0" t="s">
         <v>1061</v>
       </c>
       <c r="C186" s="20" t="s">
@@ -15125,7 +15110,7 @@
       <c r="F186" s="67" t="s">
         <v>1063</v>
       </c>
-      <c r="G186" t="s">
+      <c r="G186" s="0" t="s">
         <v>1064</v>
       </c>
       <c r="H186" s="68" t="s">
@@ -15135,11 +15120,11 @@
         <v>18982291559</v>
       </c>
     </row>
-    <row r="187" spans="1:13">
+    <row r="187">
       <c r="A187" s="19">
         <v>186</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B187" s="0" t="s">
         <v>1066</v>
       </c>
       <c r="C187" s="20" t="s">
@@ -15154,7 +15139,7 @@
       <c r="F187" s="67" t="s">
         <v>1068</v>
       </c>
-      <c r="G187" t="s">
+      <c r="G187" s="0" t="s">
         <v>1069</v>
       </c>
       <c r="H187" s="68" t="s">
@@ -15164,11 +15149,11 @@
         <v>13881834239</v>
       </c>
     </row>
-    <row r="188" spans="1:13">
+    <row r="188">
       <c r="A188" s="19">
         <v>187</v>
       </c>
-      <c r="B188" t="s">
+      <c r="B188" s="0" t="s">
         <v>1071</v>
       </c>
       <c r="C188" s="20" t="s">
@@ -15181,11 +15166,11 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="189" spans="1:13">
+    <row r="189">
       <c r="A189" s="19">
         <v>188</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B189" s="0" t="s">
         <v>1074</v>
       </c>
       <c r="C189" s="20" t="s">
@@ -15198,11 +15183,11 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="190" spans="1:13">
+    <row r="190">
       <c r="A190" s="19">
         <v>189</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B190" s="0" t="s">
         <v>1076</v>
       </c>
       <c r="C190" s="20" t="s">
@@ -15217,21 +15202,21 @@
       <c r="F190" s="67" t="s">
         <v>1078</v>
       </c>
-      <c r="G190" t="s">
+      <c r="G190" s="0" t="s">
         <v>1079</v>
       </c>
       <c r="L190" s="20">
         <v>18911990856</v>
       </c>
-      <c r="M190" t="s">
+      <c r="M190" s="0" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="191" spans="1:13">
+    <row r="191">
       <c r="A191" s="19">
         <v>190</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B191" s="0" t="s">
         <v>1080</v>
       </c>
       <c r="C191" s="20" t="s">
@@ -15246,21 +15231,21 @@
       <c r="F191" s="67" t="s">
         <v>1082</v>
       </c>
-      <c r="G191" t="s">
+      <c r="G191" s="0" t="s">
         <v>1083</v>
       </c>
       <c r="L191" s="20">
         <v>18911990414</v>
       </c>
-      <c r="M191" t="s">
+      <c r="M191" s="0" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="192" spans="1:13">
+    <row r="192">
       <c r="A192" s="19">
         <v>191</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B192" s="0" t="s">
         <v>1084</v>
       </c>
       <c r="C192" s="20" t="s">
@@ -15275,21 +15260,21 @@
       <c r="F192" s="67" t="s">
         <v>1086</v>
       </c>
-      <c r="G192" t="s">
+      <c r="G192" s="0" t="s">
         <v>1083</v>
       </c>
       <c r="L192" s="20">
         <v>18911990473</v>
       </c>
-      <c r="M192" t="s">
+      <c r="M192" s="0" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="193" spans="1:13">
+    <row r="193">
       <c r="A193" s="19">
         <v>192</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B193" s="0" t="s">
         <v>1087</v>
       </c>
       <c r="C193" s="20" t="s">
@@ -15304,21 +15289,21 @@
       <c r="F193" s="67" t="s">
         <v>1089</v>
       </c>
-      <c r="G193" t="s">
+      <c r="G193" s="0" t="s">
         <v>1090</v>
       </c>
       <c r="L193" s="20">
         <v>18911990641</v>
       </c>
-      <c r="M193" t="s">
+      <c r="M193" s="0" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="194" spans="1:13">
+    <row r="194">
       <c r="A194" s="19">
         <v>193</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B194" s="0" t="s">
         <v>1091</v>
       </c>
       <c r="C194" s="20" t="s">
@@ -15327,27 +15312,27 @@
       <c r="D194" s="20" t="s">
         <v>1092</v>
       </c>
-      <c r="E194" t="s">
+      <c r="E194" s="0" t="s">
         <v>1092</v>
       </c>
       <c r="F194" s="67" t="s">
         <v>1093</v>
       </c>
-      <c r="G194" t="s">
+      <c r="G194" s="0" t="s">
         <v>1094</v>
       </c>
       <c r="L194" s="20">
         <v>18911990655</v>
       </c>
-      <c r="M194" t="s">
+      <c r="M194" s="0" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="195" spans="1:13">
+    <row r="195">
       <c r="A195" s="19">
         <v>194</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B195" s="0" t="s">
         <v>1095</v>
       </c>
       <c r="C195" s="20" t="s">
@@ -15362,21 +15347,21 @@
       <c r="F195" s="67" t="s">
         <v>1097</v>
       </c>
-      <c r="G195" t="s">
+      <c r="G195" s="0" t="s">
         <v>1098</v>
       </c>
       <c r="L195" s="20">
         <v>18911990605</v>
       </c>
-      <c r="M195" t="s">
+      <c r="M195" s="0" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="196" spans="1:13">
+    <row r="196">
       <c r="A196" s="19">
         <v>195</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B196" s="0" t="s">
         <v>1099</v>
       </c>
       <c r="C196" s="20" t="s">
@@ -15391,21 +15376,21 @@
       <c r="F196" s="67" t="s">
         <v>1101</v>
       </c>
-      <c r="G196" t="s">
+      <c r="G196" s="0" t="s">
         <v>1102</v>
       </c>
       <c r="L196" s="20">
         <v>18911990484</v>
       </c>
-      <c r="M196" t="s">
+      <c r="M196" s="0" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="197" spans="1:13">
+    <row r="197">
       <c r="A197" s="19">
         <v>196</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B197" s="0" t="s">
         <v>1103</v>
       </c>
       <c r="C197" s="20" t="s">
@@ -15420,21 +15405,21 @@
       <c r="F197" s="67" t="s">
         <v>1105</v>
       </c>
-      <c r="G197" t="s">
+      <c r="G197" s="0" t="s">
         <v>1106</v>
       </c>
       <c r="L197" s="20">
         <v>18110078468</v>
       </c>
-      <c r="M197" t="s">
+      <c r="M197" s="0" t="s">
         <v>1107</v>
       </c>
     </row>
-    <row r="198" spans="1:13">
+    <row r="198">
       <c r="A198" s="19">
         <v>197</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B198" s="0" t="s">
         <v>1108</v>
       </c>
       <c r="C198" s="20" t="s">
@@ -15443,27 +15428,27 @@
       <c r="D198" s="20" t="s">
         <v>1109</v>
       </c>
-      <c r="E198" t="s">
+      <c r="E198" s="0" t="s">
         <v>1109</v>
       </c>
       <c r="F198" s="67" t="s">
         <v>1110</v>
       </c>
-      <c r="G198" t="s">
+      <c r="G198" s="0" t="s">
         <v>1111</v>
       </c>
       <c r="L198" s="20">
         <v>18110071878</v>
       </c>
-      <c r="M198" t="s">
+      <c r="M198" s="0" t="s">
         <v>1107</v>
       </c>
     </row>
-    <row r="199" spans="1:13">
+    <row r="199">
       <c r="A199" s="19">
         <v>198</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B199" s="0" t="s">
         <v>1112</v>
       </c>
       <c r="C199" s="20" t="s">
@@ -15472,27 +15457,27 @@
       <c r="D199" s="20" t="s">
         <v>1113</v>
       </c>
-      <c r="E199" t="s">
+      <c r="E199" s="0" t="s">
         <v>1113</v>
       </c>
       <c r="F199" s="67" t="s">
         <v>1114</v>
       </c>
-      <c r="G199" t="s">
+      <c r="G199" s="0" t="s">
         <v>1115</v>
       </c>
       <c r="L199" s="20">
         <v>18110070838</v>
       </c>
-      <c r="M199" t="s">
+      <c r="M199" s="0" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200">
       <c r="A200" s="19">
         <v>199</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B200" s="0" t="s">
         <v>1116</v>
       </c>
       <c r="C200" s="20" t="s">
@@ -15507,7 +15492,7 @@
       <c r="F200" s="67" t="s">
         <v>1119</v>
       </c>
-      <c r="G200" t="s">
+      <c r="G200" s="0" t="s">
         <v>1120</v>
       </c>
       <c r="K200" s="68" t="s">
@@ -15517,11 +15502,11 @@
         <v>18575780914</v>
       </c>
     </row>
-    <row r="201" spans="1:13">
+    <row r="201">
       <c r="A201" s="19">
         <v>200</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B201" s="0" t="s">
         <v>1121</v>
       </c>
       <c r="C201" s="20" t="s">
@@ -15540,11 +15525,11 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="202" spans="1:13">
+    <row r="202">
       <c r="A202" s="19">
         <v>201</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B202" s="0" t="s">
         <v>1125</v>
       </c>
       <c r="C202" s="20" t="s">
@@ -15559,7 +15544,7 @@
       <c r="F202" s="67" t="s">
         <v>1127</v>
       </c>
-      <c r="G202" t="s">
+      <c r="G202" s="0" t="s">
         <v>1128</v>
       </c>
       <c r="L202" s="20">
@@ -15569,11 +15554,11 @@
         <v>979</v>
       </c>
     </row>
-    <row r="203" spans="1:13">
+    <row r="203">
       <c r="A203" s="19">
         <v>202</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B203" s="0" t="s">
         <v>1129</v>
       </c>
       <c r="C203" s="20" t="s">
@@ -15588,7 +15573,7 @@
       <c r="F203" s="67" t="s">
         <v>1131</v>
       </c>
-      <c r="G203" t="s">
+      <c r="G203" s="0" t="s">
         <v>1128</v>
       </c>
       <c r="L203" s="20">
@@ -15598,11 +15583,11 @@
         <v>979</v>
       </c>
     </row>
-    <row r="204" spans="1:13">
+    <row r="204">
       <c r="A204" s="19">
         <v>203</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B204" s="0" t="s">
         <v>1132</v>
       </c>
       <c r="C204" s="26" t="s">
@@ -15617,7 +15602,7 @@
       <c r="F204" s="67" t="s">
         <v>1134</v>
       </c>
-      <c r="G204" t="s">
+      <c r="G204" s="0" t="s">
         <v>1135</v>
       </c>
       <c r="K204" s="20">
@@ -15630,11 +15615,11 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="205" spans="1:13">
+    <row r="205">
       <c r="A205" s="19">
         <v>204</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B205" s="0" t="s">
         <v>1137</v>
       </c>
       <c r="C205" s="26" t="s">
@@ -15656,11 +15641,11 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="206" spans="1:13">
+    <row r="206">
       <c r="A206" s="19">
         <v>205</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B206" s="0" t="s">
         <v>1140</v>
       </c>
       <c r="C206" s="26" t="s">
@@ -15682,11 +15667,11 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="207" spans="1:13">
+    <row r="207">
       <c r="A207" s="19">
         <v>206</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B207" s="0" t="s">
         <v>1142</v>
       </c>
       <c r="C207" s="20" t="s">
@@ -15695,15 +15680,15 @@
       <c r="D207" s="20" t="s">
         <v>1143</v>
       </c>
-      <c r="E207" t="s">
+      <c r="E207" s="0" t="s">
         <v>1143</v>
       </c>
     </row>
-    <row r="208" spans="1:13">
+    <row r="208">
       <c r="A208" s="19">
         <v>207</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B208" s="0" t="s">
         <v>1144</v>
       </c>
       <c r="C208" s="20" t="s">
@@ -15718,7 +15703,7 @@
       <c r="F208" s="67" t="s">
         <v>1146</v>
       </c>
-      <c r="G208" t="s">
+      <c r="G208" s="0" t="s">
         <v>1147</v>
       </c>
       <c r="L208" s="20">
@@ -15728,11 +15713,11 @@
         <v>979</v>
       </c>
     </row>
-    <row r="209" spans="1:13">
+    <row r="209">
       <c r="A209" s="19">
         <v>208</v>
       </c>
-      <c r="B209" t="s">
+      <c r="B209" s="0" t="s">
         <v>1148</v>
       </c>
       <c r="C209" s="20" t="s">
@@ -15747,7 +15732,7 @@
       <c r="F209" s="67" t="s">
         <v>1150</v>
       </c>
-      <c r="G209" t="s">
+      <c r="G209" s="0" t="s">
         <v>1151</v>
       </c>
       <c r="L209" s="20">
@@ -15757,11 +15742,11 @@
         <v>979</v>
       </c>
     </row>
-    <row r="210" spans="1:13">
+    <row r="210">
       <c r="A210" s="19">
         <v>209</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B210" s="0" t="s">
         <v>1152</v>
       </c>
       <c r="C210" s="20" t="s">
@@ -15776,18 +15761,18 @@
       <c r="F210" s="67" t="s">
         <v>1154</v>
       </c>
-      <c r="G210" t="s">
+      <c r="G210" s="0" t="s">
         <v>1155</v>
       </c>
       <c r="M210" s="20" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="211" spans="1:13">
+    <row r="211">
       <c r="A211" s="19">
         <v>210</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B211" s="0" t="s">
         <v>1156</v>
       </c>
       <c r="C211" s="20" t="s">
@@ -15802,15 +15787,15 @@
       <c r="F211" s="67" t="s">
         <v>1158</v>
       </c>
-      <c r="G211" t="s">
+      <c r="G211" s="0" t="s">
         <v>1159</v>
       </c>
     </row>
-    <row r="212" spans="1:13">
+    <row r="212">
       <c r="A212" s="19">
         <v>211</v>
       </c>
-      <c r="B212" t="s">
+      <c r="B212" s="0" t="s">
         <v>1160</v>
       </c>
       <c r="C212" s="20" t="s">
@@ -15819,21 +15804,21 @@
       <c r="D212" s="20" t="s">
         <v>1161</v>
       </c>
-      <c r="E212" t="s">
+      <c r="E212" s="0" t="s">
         <v>1161</v>
       </c>
       <c r="F212" s="67" t="s">
         <v>1162</v>
       </c>
-      <c r="G212" t="s">
+      <c r="G212" s="0" t="s">
         <v>1163</v>
       </c>
     </row>
-    <row r="213" spans="1:13">
+    <row r="213">
       <c r="A213" s="19">
         <v>212</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B213" s="0" t="s">
         <v>1164</v>
       </c>
       <c r="C213" s="20" t="s">
@@ -15846,11 +15831,11 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="214" spans="1:13">
+    <row r="214">
       <c r="A214" s="19">
         <v>213</v>
       </c>
-      <c r="B214" t="s">
+      <c r="B214" s="0" t="s">
         <v>1166</v>
       </c>
       <c r="C214" s="20" t="s">
@@ -15863,11 +15848,11 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="215" spans="1:13">
+    <row r="215">
       <c r="A215" s="19">
         <v>214</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B215" s="0" t="s">
         <v>1168</v>
       </c>
       <c r="C215" s="20" t="s">
@@ -15882,18 +15867,18 @@
       <c r="F215" s="67" t="s">
         <v>1170</v>
       </c>
-      <c r="G215" t="s">
+      <c r="G215" s="0" t="s">
         <v>1171</v>
       </c>
       <c r="L215" s="20">
         <v>13350060662</v>
       </c>
     </row>
-    <row r="216" spans="1:13">
+    <row r="216">
       <c r="A216" s="19">
         <v>215</v>
       </c>
-      <c r="B216" t="s">
+      <c r="B216" s="0" t="s">
         <v>1172</v>
       </c>
       <c r="C216" s="20" t="s">
@@ -15906,11 +15891,11 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="217" spans="1:13">
+    <row r="217">
       <c r="A217" s="19">
         <v>216</v>
       </c>
-      <c r="B217" t="s">
+      <c r="B217" s="0" t="s">
         <v>1174</v>
       </c>
       <c r="C217" s="20" t="s">
@@ -15925,18 +15910,18 @@
       <c r="F217" s="67" t="s">
         <v>1176</v>
       </c>
-      <c r="G217" t="s">
+      <c r="G217" s="0" t="s">
         <v>1177</v>
       </c>
       <c r="L217" s="20">
         <v>15507702646</v>
       </c>
     </row>
-    <row r="218" spans="1:13">
+    <row r="218">
       <c r="A218" s="19">
         <v>217</v>
       </c>
-      <c r="B218" t="s">
+      <c r="B218" s="0" t="s">
         <v>1178</v>
       </c>
       <c r="C218" s="20" t="s">
@@ -15951,18 +15936,18 @@
       <c r="F218" s="67" t="s">
         <v>1180</v>
       </c>
-      <c r="G218" t="s">
+      <c r="G218" s="0" t="s">
         <v>1181</v>
       </c>
       <c r="L218" s="20">
         <v>15184444781</v>
       </c>
     </row>
-    <row r="219" spans="1:13">
+    <row r="219">
       <c r="A219" s="19">
         <v>218</v>
       </c>
-      <c r="B219" t="s">
+      <c r="B219" s="0" t="s">
         <v>1182</v>
       </c>
       <c r="C219" s="20" t="s">
@@ -15977,18 +15962,18 @@
       <c r="F219" s="67" t="s">
         <v>1184</v>
       </c>
-      <c r="G219" t="s">
+      <c r="G219" s="0" t="s">
         <v>1185</v>
       </c>
       <c r="L219" s="20">
         <v>13880012488</v>
       </c>
     </row>
-    <row r="220" spans="1:13">
+    <row r="220">
       <c r="A220" s="19">
         <v>219</v>
       </c>
-      <c r="B220" t="s">
+      <c r="B220" s="0" t="s">
         <v>1186</v>
       </c>
       <c r="C220" s="20" t="s">
@@ -16003,21 +15988,21 @@
       <c r="F220" s="67" t="s">
         <v>1188</v>
       </c>
-      <c r="G220" t="s">
+      <c r="G220" s="0" t="s">
         <v>1189</v>
       </c>
       <c r="L220" s="20">
         <v>13258218888</v>
       </c>
-      <c r="M220" t="s">
+      <c r="M220" s="0" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="221" spans="1:13">
+    <row r="221">
       <c r="A221" s="19">
         <v>220</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B221" s="0" t="s">
         <v>1190</v>
       </c>
       <c r="C221" s="20" t="s">
@@ -16032,21 +16017,21 @@
       <c r="F221" s="67" t="s">
         <v>1192</v>
       </c>
-      <c r="G221" t="s">
+      <c r="G221" s="0" t="s">
         <v>1193</v>
       </c>
       <c r="L221" s="20">
         <v>13981819638</v>
       </c>
-      <c r="M221" t="s">
+      <c r="M221" s="0" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="222" spans="1:13">
+    <row r="222">
       <c r="A222" s="19">
         <v>221</v>
       </c>
-      <c r="B222" t="s">
+      <c r="B222" s="0" t="s">
         <v>1194</v>
       </c>
       <c r="C222" s="20" t="s">
@@ -16061,21 +16046,21 @@
       <c r="F222" s="67" t="s">
         <v>1196</v>
       </c>
-      <c r="G222" t="s">
+      <c r="G222" s="0" t="s">
         <v>544</v>
       </c>
       <c r="L222" s="20">
         <v>18683618560</v>
       </c>
-      <c r="M222" t="s">
+      <c r="M222" s="0" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="223" spans="1:13">
+    <row r="223">
       <c r="A223" s="19">
         <v>222</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B223" s="0" t="s">
         <v>1197</v>
       </c>
       <c r="C223" s="20" t="s">
@@ -16090,21 +16075,21 @@
       <c r="F223" s="67" t="s">
         <v>1199</v>
       </c>
-      <c r="G223" t="s">
+      <c r="G223" s="0" t="s">
         <v>1200</v>
       </c>
       <c r="L223" s="20">
         <v>13880417337</v>
       </c>
-      <c r="M223" t="s">
+      <c r="M223" s="0" t="s">
         <v>1201</v>
       </c>
     </row>
-    <row r="224" spans="1:13">
+    <row r="224">
       <c r="A224" s="19">
         <v>223</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B224" s="0" t="s">
         <v>1202</v>
       </c>
       <c r="C224" s="20" t="s">
@@ -16119,21 +16104,21 @@
       <c r="F224" s="67" t="s">
         <v>1204</v>
       </c>
-      <c r="G224" t="s">
+      <c r="G224" s="0" t="s">
         <v>1205</v>
       </c>
       <c r="L224" s="20">
         <v>13982254477</v>
       </c>
-      <c r="M224" t="s">
+      <c r="M224" s="0" t="s">
         <v>1201</v>
       </c>
     </row>
-    <row r="225" spans="1:13">
+    <row r="225">
       <c r="A225" s="19">
         <v>224</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B225" s="0" t="s">
         <v>1206</v>
       </c>
       <c r="C225" s="20" t="s">
@@ -16149,11 +16134,11 @@
         <v>17835601430</v>
       </c>
     </row>
-    <row r="226" spans="1:13">
+    <row r="226">
       <c r="A226" s="19">
         <v>225</v>
       </c>
-      <c r="B226" t="s">
+      <c r="B226" s="0" t="s">
         <v>1208</v>
       </c>
       <c r="C226" s="20" t="s">
@@ -16162,24 +16147,24 @@
       <c r="D226" s="20" t="s">
         <v>1209</v>
       </c>
-      <c r="E226" t="s">
+      <c r="E226" s="0" t="s">
         <v>1209</v>
       </c>
       <c r="F226" s="67" t="s">
         <v>1210</v>
       </c>
-      <c r="G226" t="s">
+      <c r="G226" s="0" t="s">
         <v>1211</v>
       </c>
       <c r="L226" s="20">
         <v>18375939215</v>
       </c>
     </row>
-    <row r="227" spans="1:13">
+    <row r="227">
       <c r="A227" s="19">
         <v>226</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B227" s="0" t="s">
         <v>1212</v>
       </c>
       <c r="C227" s="20" t="s">
@@ -16191,7 +16176,7 @@
       <c r="F227" s="67" t="s">
         <v>1214</v>
       </c>
-      <c r="G227" t="s">
+      <c r="G227" s="0" t="s">
         <v>647</v>
       </c>
       <c r="K227" s="68" t="s">
@@ -16201,11 +16186,11 @@
         <v>13518306314</v>
       </c>
     </row>
-    <row r="228" spans="1:13">
+    <row r="228">
       <c r="A228" s="19">
         <v>227</v>
       </c>
-      <c r="B228" t="s">
+      <c r="B228" s="0" t="s">
         <v>1215</v>
       </c>
       <c r="C228" s="20" t="s">
@@ -16218,11 +16203,11 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="229" spans="1:13">
+    <row r="229">
       <c r="A229" s="19">
         <v>228</v>
       </c>
-      <c r="B229" t="s">
+      <c r="B229" s="0" t="s">
         <v>1217</v>
       </c>
       <c r="C229" s="20" t="s">
@@ -16231,27 +16216,27 @@
       <c r="D229" s="20" t="s">
         <v>1218</v>
       </c>
-      <c r="E229" t="s">
+      <c r="E229" s="0" t="s">
         <v>1218</v>
       </c>
       <c r="F229" s="67" t="s">
         <v>1219</v>
       </c>
-      <c r="G229" t="s">
+      <c r="G229" s="0" t="s">
         <v>1013</v>
       </c>
       <c r="L229" s="20">
         <v>13882226385</v>
       </c>
-      <c r="M229" t="s">
+      <c r="M229" s="0" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="230" spans="1:13">
+    <row r="230">
       <c r="A230" s="19">
         <v>229</v>
       </c>
-      <c r="B230" t="s">
+      <c r="B230" s="0" t="s">
         <v>1220</v>
       </c>
       <c r="C230" s="20" t="s">
@@ -16266,21 +16251,21 @@
       <c r="F230" s="67" t="s">
         <v>1222</v>
       </c>
-      <c r="G230" t="s">
+      <c r="G230" s="0" t="s">
         <v>1223</v>
       </c>
       <c r="L230" s="20">
         <v>13908061512</v>
       </c>
-      <c r="M230" t="s">
+      <c r="M230" s="0" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="231" spans="1:13">
+    <row r="231">
       <c r="A231" s="19">
         <v>230</v>
       </c>
-      <c r="B231" t="s">
+      <c r="B231" s="0" t="s">
         <v>1224</v>
       </c>
       <c r="C231" s="20" t="s">
@@ -16289,27 +16274,27 @@
       <c r="D231" s="20" t="s">
         <v>1225</v>
       </c>
-      <c r="E231" t="s">
+      <c r="E231" s="0" t="s">
         <v>1225</v>
       </c>
       <c r="F231" s="67" t="s">
         <v>1226</v>
       </c>
-      <c r="G231" t="s">
+      <c r="G231" s="0" t="s">
         <v>1227</v>
       </c>
       <c r="L231" s="20">
         <v>13550226561</v>
       </c>
-      <c r="M231" t="s">
+      <c r="M231" s="0" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="232" spans="1:13">
+    <row r="232">
       <c r="A232" s="19">
         <v>231</v>
       </c>
-      <c r="B232" t="s">
+      <c r="B232" s="0" t="s">
         <v>1228</v>
       </c>
       <c r="C232" s="20" t="s">
@@ -16324,21 +16309,21 @@
       <c r="F232" s="67" t="s">
         <v>1230</v>
       </c>
-      <c r="G232" t="s">
+      <c r="G232" s="0" t="s">
         <v>1231</v>
       </c>
       <c r="L232" s="20">
         <v>18010678960</v>
       </c>
-      <c r="M232" t="s">
+      <c r="M232" s="0" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="233" spans="1:13">
+    <row r="233">
       <c r="A233" s="19">
         <v>232</v>
       </c>
-      <c r="B233" t="s">
+      <c r="B233" s="0" t="s">
         <v>1232</v>
       </c>
       <c r="C233" s="20" t="s">
@@ -16353,21 +16338,21 @@
       <c r="F233" s="67" t="s">
         <v>1234</v>
       </c>
-      <c r="G233" t="s">
+      <c r="G233" s="0" t="s">
         <v>1235</v>
       </c>
       <c r="L233" s="20">
         <v>13709020198</v>
       </c>
-      <c r="M233" t="s">
+      <c r="M233" s="0" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="234" spans="1:13">
+    <row r="234">
       <c r="A234" s="19">
         <v>233</v>
       </c>
-      <c r="B234" t="s">
+      <c r="B234" s="0" t="s">
         <v>1236</v>
       </c>
       <c r="C234" s="20" t="s">
@@ -16376,24 +16361,24 @@
       <c r="D234" s="20" t="s">
         <v>1237</v>
       </c>
-      <c r="E234" t="s">
+      <c r="E234" s="0" t="s">
         <v>1237</v>
       </c>
       <c r="F234" s="67" t="s">
         <v>1238</v>
       </c>
-      <c r="G234" t="s">
+      <c r="G234" s="0" t="s">
         <v>1239</v>
       </c>
       <c r="L234" s="20">
         <v>18033950999</v>
       </c>
     </row>
-    <row r="235" spans="1:13">
+    <row r="235">
       <c r="A235" s="19">
         <v>234</v>
       </c>
-      <c r="B235" t="s">
+      <c r="B235" s="0" t="s">
         <v>1240</v>
       </c>
       <c r="C235" s="20" t="s">
@@ -16408,7 +16393,7 @@
       <c r="F235" s="67" t="s">
         <v>1242</v>
       </c>
-      <c r="G235" t="s">
+      <c r="G235" s="0" t="s">
         <v>467</v>
       </c>
       <c r="K235" s="20">
@@ -16418,11 +16403,11 @@
         <v>13547285749</v>
       </c>
     </row>
-    <row r="236" spans="1:13">
+    <row r="236">
       <c r="A236" s="19">
         <v>235</v>
       </c>
-      <c r="B236" t="s">
+      <c r="B236" s="0" t="s">
         <v>1243</v>
       </c>
       <c r="C236" s="20" t="s">
@@ -16434,15 +16419,15 @@
       <c r="F236" s="67" t="s">
         <v>1244</v>
       </c>
-      <c r="G236" t="s">
+      <c r="G236" s="0" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="237" spans="1:13">
+    <row r="237">
       <c r="A237" s="19">
         <v>236</v>
       </c>
-      <c r="B237" t="s">
+      <c r="B237" s="0" t="s">
         <v>1246</v>
       </c>
       <c r="C237" s="20" t="s">
@@ -16457,18 +16442,18 @@
       <c r="F237" s="76" t="s">
         <v>1248</v>
       </c>
-      <c r="G237" t="s">
+      <c r="G237" s="0" t="s">
         <v>1249</v>
       </c>
       <c r="L237" s="20">
         <v>15202871402</v>
       </c>
     </row>
-    <row r="238" spans="1:13">
+    <row r="238">
       <c r="A238" s="19">
         <v>237</v>
       </c>
-      <c r="B238" t="s">
+      <c r="B238" s="0" t="s">
         <v>1243</v>
       </c>
       <c r="C238" s="20" t="s">
@@ -16484,11 +16469,11 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="239" spans="1:13">
+    <row r="239">
       <c r="A239" s="19">
         <v>238</v>
       </c>
-      <c r="B239" t="s">
+      <c r="B239" s="0" t="s">
         <v>1250</v>
       </c>
       <c r="C239" s="20" t="s">
@@ -16500,7 +16485,7 @@
       <c r="F239" s="67" t="s">
         <v>1251</v>
       </c>
-      <c r="G239" t="s">
+      <c r="G239" s="0" t="s">
         <v>467</v>
       </c>
       <c r="K239" s="20">
@@ -16510,11 +16495,11 @@
         <v>15008489824</v>
       </c>
     </row>
-    <row r="240" spans="1:13">
+    <row r="240">
       <c r="A240" s="19">
         <v>239</v>
       </c>
-      <c r="B240" t="s">
+      <c r="B240" s="0" t="s">
         <v>1252</v>
       </c>
       <c r="C240" s="20" t="s">
@@ -16530,11 +16515,11 @@
         <v>13730885415</v>
       </c>
     </row>
-    <row r="241" spans="1:12">
+    <row r="241">
       <c r="A241" s="19">
         <v>240</v>
       </c>
-      <c r="B241" t="s">
+      <c r="B241" s="0" t="s">
         <v>1253</v>
       </c>
       <c r="C241" s="20" t="s">
@@ -16547,11 +16532,11 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="242" spans="1:12">
+    <row r="242">
       <c r="A242" s="19">
         <v>241</v>
       </c>
-      <c r="B242" t="s">
+      <c r="B242" s="0" t="s">
         <v>1255</v>
       </c>
       <c r="C242" s="20" t="s">
@@ -16564,11 +16549,11 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="243" spans="1:12">
+    <row r="243">
       <c r="A243" s="19">
         <v>242</v>
       </c>
-      <c r="B243" t="s">
+      <c r="B243" s="0" t="s">
         <v>1257</v>
       </c>
       <c r="C243" s="20" t="s">
@@ -16593,11 +16578,11 @@
         <v>13281811416</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="14.15" customHeight="1">
+    <row r="244" ht="14.15" customHeight="1">
       <c r="A244" s="19">
         <v>243</v>
       </c>
-      <c r="B244" t="s">
+      <c r="B244" s="0" t="s">
         <v>1262</v>
       </c>
       <c r="C244" s="20" t="s">
@@ -16612,18 +16597,18 @@
       <c r="F244" s="67" t="s">
         <v>1264</v>
       </c>
-      <c r="G244" t="s">
+      <c r="G244" s="0" t="s">
         <v>1265</v>
       </c>
       <c r="L244" s="20">
         <v>13008141065</v>
       </c>
     </row>
-    <row r="245" spans="1:12">
+    <row r="245">
       <c r="A245" s="19">
         <v>244</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B245" s="0" t="s">
         <v>1266</v>
       </c>
       <c r="C245" s="20" t="s">
@@ -16638,7 +16623,7 @@
       <c r="F245" s="76" t="s">
         <v>1270</v>
       </c>
-      <c r="G245" t="s">
+      <c r="G245" s="0" t="s">
         <v>1271</v>
       </c>
       <c r="K245" s="68" t="s">
@@ -16648,11 +16633,11 @@
         <v>19828415638</v>
       </c>
     </row>
-    <row r="246" spans="1:12">
+    <row r="246">
       <c r="A246" s="19">
         <v>245</v>
       </c>
-      <c r="B246" t="s">
+      <c r="B246" s="0" t="s">
         <v>1272</v>
       </c>
       <c r="C246" s="20" t="s">
@@ -16665,11 +16650,11 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="247" spans="1:12">
+    <row r="247">
       <c r="A247" s="19">
         <v>246</v>
       </c>
-      <c r="B247" t="s">
+      <c r="B247" s="0" t="s">
         <v>1274</v>
       </c>
       <c r="C247" s="20" t="s">
@@ -16682,11 +16667,11 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="248" spans="1:12">
+    <row r="248">
       <c r="A248" s="19">
         <v>247</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B248" s="0" t="s">
         <v>1276</v>
       </c>
       <c r="C248" s="20" t="s">
@@ -16695,21 +16680,21 @@
       <c r="D248" s="20" t="s">
         <v>1277</v>
       </c>
-      <c r="E248" t="s">
+      <c r="E248" s="0" t="s">
         <v>1277</v>
       </c>
       <c r="F248" s="67" t="s">
         <v>1278</v>
       </c>
-      <c r="G248" t="s">
+      <c r="G248" s="0" t="s">
         <v>1279</v>
       </c>
     </row>
-    <row r="249" spans="1:12">
+    <row r="249">
       <c r="A249" s="19">
         <v>248</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B249" s="0" t="s">
         <v>1280</v>
       </c>
       <c r="C249" s="20" t="s">
@@ -16724,15 +16709,15 @@
       <c r="F249" s="67" t="s">
         <v>1282</v>
       </c>
-      <c r="G249" t="s">
+      <c r="G249" s="0" t="s">
         <v>1283</v>
       </c>
     </row>
-    <row r="250" spans="1:12">
+    <row r="250">
       <c r="A250" s="19">
         <v>249</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B250" s="0" t="s">
         <v>1284</v>
       </c>
       <c r="C250" s="20" t="s">
@@ -16747,7 +16732,7 @@
       <c r="F250" s="67" t="s">
         <v>1287</v>
       </c>
-      <c r="G250" t="s">
+      <c r="G250" s="0" t="s">
         <v>1288</v>
       </c>
       <c r="K250" s="68" t="s">
@@ -16757,11 +16742,11 @@
         <v>13408470814</v>
       </c>
     </row>
-    <row r="251" spans="1:12">
+    <row r="251">
       <c r="A251" s="19">
         <v>250</v>
       </c>
-      <c r="B251" t="s">
+      <c r="B251" s="0" t="s">
         <v>1289</v>
       </c>
       <c r="C251" s="20" t="s">
@@ -16770,21 +16755,21 @@
       <c r="D251" s="45">
         <v>4240503</v>
       </c>
-      <c r="F251" t="s">
+      <c r="F251" s="0" t="s">
         <v>1290</v>
       </c>
-      <c r="G251" t="s">
+      <c r="G251" s="0" t="s">
         <v>467</v>
       </c>
       <c r="K251" s="45">
         <v>4240503</v>
       </c>
     </row>
-    <row r="252" spans="1:12">
+    <row r="252">
       <c r="A252" s="19">
         <v>251</v>
       </c>
-      <c r="B252" t="s">
+      <c r="B252" s="0" t="s">
         <v>1291</v>
       </c>
       <c r="C252" s="20" t="s">
@@ -16796,21 +16781,21 @@
       <c r="E252" s="67" t="s">
         <v>1292</v>
       </c>
-      <c r="F252" t="s">
+      <c r="F252" s="0" t="s">
         <v>1293</v>
       </c>
-      <c r="G252" t="s">
+      <c r="G252" s="0" t="s">
         <v>467</v>
       </c>
       <c r="K252" s="45">
         <v>4240504</v>
       </c>
     </row>
-    <row r="253" spans="1:12">
+    <row r="253">
       <c r="A253" s="19">
         <v>252</v>
       </c>
-      <c r="B253" t="s">
+      <c r="B253" s="0" t="s">
         <v>1294</v>
       </c>
       <c r="C253" s="20" t="s">
@@ -16825,18 +16810,18 @@
       <c r="F253" s="67" t="s">
         <v>1296</v>
       </c>
-      <c r="G253" t="s">
+      <c r="G253" s="0" t="s">
         <v>1297</v>
       </c>
       <c r="L253" s="20">
         <v>13301372866</v>
       </c>
     </row>
-    <row r="254" spans="1:12">
+    <row r="254">
       <c r="A254" s="19">
         <v>253</v>
       </c>
-      <c r="B254" t="s">
+      <c r="B254" s="0" t="s">
         <v>1298</v>
       </c>
       <c r="C254" s="20" t="s">
@@ -16851,18 +16836,18 @@
       <c r="F254" s="67" t="s">
         <v>1300</v>
       </c>
-      <c r="G254" t="s">
+      <c r="G254" s="0" t="s">
         <v>1301</v>
       </c>
       <c r="L254" s="20">
         <v>13898800176</v>
       </c>
     </row>
-    <row r="255" spans="1:12">
+    <row r="255">
       <c r="A255" s="19">
         <v>254</v>
       </c>
-      <c r="B255" t="s">
+      <c r="B255" s="0" t="s">
         <v>1302</v>
       </c>
       <c r="C255" s="20" t="s">
@@ -16877,18 +16862,18 @@
       <c r="F255" s="67" t="s">
         <v>1304</v>
       </c>
-      <c r="G255" t="s">
+      <c r="G255" s="0" t="s">
         <v>1305</v>
       </c>
       <c r="L255" s="20">
         <v>18818272538</v>
       </c>
     </row>
-    <row r="256" spans="1:12">
+    <row r="256">
       <c r="A256" s="19">
         <v>255</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B256" s="0" t="s">
         <v>1306</v>
       </c>
       <c r="C256" s="20" t="s">
@@ -16903,18 +16888,18 @@
       <c r="F256" s="67" t="s">
         <v>1308</v>
       </c>
-      <c r="G256" t="s">
+      <c r="G256" s="0" t="s">
         <v>972</v>
       </c>
       <c r="L256" s="20">
         <v>18113135523</v>
       </c>
     </row>
-    <row r="257" spans="1:13">
+    <row r="257">
       <c r="A257" s="19">
         <v>256</v>
       </c>
-      <c r="B257" t="s">
+      <c r="B257" s="0" t="s">
         <v>1309</v>
       </c>
       <c r="C257" s="20" t="s">
@@ -16929,18 +16914,18 @@
       <c r="F257" s="67" t="s">
         <v>1311</v>
       </c>
-      <c r="G257" t="s">
+      <c r="G257" s="0" t="s">
         <v>1301</v>
       </c>
       <c r="L257" s="20">
         <v>13940534749</v>
       </c>
     </row>
-    <row r="258" spans="1:13">
+    <row r="258">
       <c r="A258" s="19">
         <v>257</v>
       </c>
-      <c r="B258" t="s">
+      <c r="B258" s="0" t="s">
         <v>1312</v>
       </c>
       <c r="C258" s="20" t="s">
@@ -16956,11 +16941,11 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="259" spans="1:13">
+    <row r="259">
       <c r="A259" s="19">
         <v>258</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B259" s="0" t="s">
         <v>1315</v>
       </c>
       <c r="C259" s="20" t="s">
@@ -16976,11 +16961,11 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="260" spans="1:13">
+    <row r="260">
       <c r="A260" s="19">
         <v>259</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B260" s="0" t="s">
         <v>1318</v>
       </c>
       <c r="C260" s="20" t="s">
@@ -16996,11 +16981,11 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="261" spans="1:13">
+    <row r="261">
       <c r="A261" s="19">
         <v>260</v>
       </c>
-      <c r="B261" t="s">
+      <c r="B261" s="0" t="s">
         <v>1321</v>
       </c>
       <c r="C261" s="20" t="s">
@@ -17016,11 +17001,11 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="262" spans="1:13">
+    <row r="262">
       <c r="A262" s="19">
         <v>261</v>
       </c>
-      <c r="B262" t="s">
+      <c r="B262" s="0" t="s">
         <v>1324</v>
       </c>
       <c r="C262" s="20" t="s">
@@ -17036,11 +17021,11 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="263" spans="1:13">
+    <row r="263">
       <c r="A263" s="19">
         <v>262</v>
       </c>
-      <c r="B263" t="s">
+      <c r="B263" s="0" t="s">
         <v>1327</v>
       </c>
       <c r="C263" s="20" t="s">
@@ -17053,11 +17038,11 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="264" spans="1:13">
+    <row r="264">
       <c r="A264" s="19">
         <v>263</v>
       </c>
-      <c r="B264" t="s">
+      <c r="B264" s="0" t="s">
         <v>1329</v>
       </c>
       <c r="C264" s="20" t="s">
@@ -17072,18 +17057,18 @@
       <c r="F264" s="67" t="s">
         <v>1331</v>
       </c>
-      <c r="G264" t="s">
+      <c r="G264" s="0" t="s">
         <v>1332</v>
       </c>
       <c r="L264" s="20">
         <v>13432240262</v>
       </c>
     </row>
-    <row r="265" spans="1:13">
+    <row r="265">
       <c r="A265" s="19">
         <v>264</v>
       </c>
-      <c r="B265" t="s">
+      <c r="B265" s="0" t="s">
         <v>1333</v>
       </c>
       <c r="C265" s="20" t="s">
@@ -17096,11 +17081,11 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="266" spans="1:13">
+    <row r="266">
       <c r="A266" s="19">
         <v>265</v>
       </c>
-      <c r="B266" t="s">
+      <c r="B266" s="0" t="s">
         <v>1335</v>
       </c>
       <c r="C266" s="20" t="s">
@@ -17115,18 +17100,18 @@
       <c r="F266" s="67" t="s">
         <v>1337</v>
       </c>
-      <c r="G266" t="s">
+      <c r="G266" s="0" t="s">
         <v>1338</v>
       </c>
-      <c r="M266" t="s">
+      <c r="M266" s="0" t="s">
         <v>1339</v>
       </c>
     </row>
-    <row r="267" spans="1:13">
+    <row r="267">
       <c r="A267" s="19">
         <v>266</v>
       </c>
-      <c r="B267" t="s">
+      <c r="B267" s="0" t="s">
         <v>1340</v>
       </c>
       <c r="C267" s="20" t="s">
@@ -17135,21 +17120,21 @@
       <c r="D267" s="20" t="s">
         <v>1341</v>
       </c>
-      <c r="E267" t="s">
+      <c r="E267" s="0" t="s">
         <v>1341</v>
       </c>
       <c r="F267" s="67" t="s">
         <v>1342</v>
       </c>
-      <c r="G267" t="s">
+      <c r="G267" s="0" t="s">
         <v>1343</v>
       </c>
     </row>
-    <row r="268" spans="1:13">
+    <row r="268">
       <c r="A268" s="19">
         <v>267</v>
       </c>
-      <c r="B268" t="s">
+      <c r="B268" s="0" t="s">
         <v>1344</v>
       </c>
       <c r="C268" s="20" t="s">
@@ -17164,7 +17149,7 @@
       <c r="F268" s="67" t="s">
         <v>1346</v>
       </c>
-      <c r="G268" t="s">
+      <c r="G268" s="0" t="s">
         <v>1347</v>
       </c>
       <c r="K268" s="20">
@@ -17174,11 +17159,11 @@
         <v>18227623393</v>
       </c>
     </row>
-    <row r="269" spans="1:13">
+    <row r="269">
       <c r="A269" s="19">
         <v>268</v>
       </c>
-      <c r="B269" t="s">
+      <c r="B269" s="0" t="s">
         <v>1348</v>
       </c>
       <c r="C269" s="20" t="s">
@@ -17187,13 +17172,13 @@
       <c r="D269" s="20">
         <v>4250136</v>
       </c>
-      <c r="E269" t="s">
+      <c r="E269" s="0" t="s">
         <v>1349</v>
       </c>
       <c r="F269" s="67" t="s">
         <v>1350</v>
       </c>
-      <c r="G269" t="s">
+      <c r="G269" s="0" t="s">
         <v>467</v>
       </c>
       <c r="K269" s="20">
@@ -17203,11 +17188,11 @@
         <v>18784992511</v>
       </c>
     </row>
-    <row r="270" spans="1:13">
+    <row r="270">
       <c r="A270" s="19">
         <v>269</v>
       </c>
-      <c r="B270" t="s">
+      <c r="B270" s="0" t="s">
         <v>1351</v>
       </c>
       <c r="C270" s="20" t="s">
@@ -17222,7 +17207,7 @@
       <c r="F270" s="67" t="s">
         <v>1353</v>
       </c>
-      <c r="G270" t="s">
+      <c r="G270" s="0" t="s">
         <v>1354</v>
       </c>
       <c r="K270" s="20">
@@ -17232,11 +17217,11 @@
         <v>18882027754</v>
       </c>
     </row>
-    <row r="271" spans="1:13">
+    <row r="271">
       <c r="A271" s="19">
         <v>270</v>
       </c>
-      <c r="B271" t="s">
+      <c r="B271" s="0" t="s">
         <v>1355</v>
       </c>
       <c r="C271" s="20" t="s">
@@ -17249,11 +17234,11 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="272" spans="1:13">
+    <row r="272">
       <c r="A272" s="19">
         <v>271</v>
       </c>
-      <c r="B272" t="s">
+      <c r="B272" s="0" t="s">
         <v>1357</v>
       </c>
       <c r="C272" s="20" t="s">
@@ -17266,11 +17251,11 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="273" spans="1:12">
+    <row r="273">
       <c r="A273" s="19">
         <v>272</v>
       </c>
-      <c r="B273" t="s">
+      <c r="B273" s="0" t="s">
         <v>1359</v>
       </c>
       <c r="C273" s="20" t="s">
@@ -17279,24 +17264,24 @@
       <c r="D273" s="20" t="s">
         <v>1360</v>
       </c>
-      <c r="E273" t="s">
+      <c r="E273" s="0" t="s">
         <v>1360</v>
       </c>
       <c r="F273" s="67" t="s">
         <v>1361</v>
       </c>
-      <c r="G273" t="s">
+      <c r="G273" s="0" t="s">
         <v>1362</v>
       </c>
       <c r="L273" s="20" t="s">
         <v>1363</v>
       </c>
     </row>
-    <row r="274" spans="1:12">
+    <row r="274">
       <c r="A274" s="19">
         <v>273</v>
       </c>
-      <c r="B274" t="s">
+      <c r="B274" s="0" t="s">
         <v>1364</v>
       </c>
       <c r="D274" s="68" t="s">
@@ -17306,11 +17291,11 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="275" spans="1:12">
+    <row r="275">
       <c r="A275" s="19">
         <v>274</v>
       </c>
-      <c r="B275" t="s">
+      <c r="B275" s="0" t="s">
         <v>1366</v>
       </c>
       <c r="C275" s="20" t="s">
@@ -17325,18 +17310,18 @@
       <c r="F275" s="67" t="s">
         <v>1368</v>
       </c>
-      <c r="G275" t="s">
+      <c r="G275" s="0" t="s">
         <v>1369</v>
       </c>
       <c r="L275" s="44">
         <v>13869207670</v>
       </c>
     </row>
-    <row r="276" spans="1:12">
+    <row r="276">
       <c r="A276" s="19">
         <v>275</v>
       </c>
-      <c r="B276" t="s">
+      <c r="B276" s="0" t="s">
         <v>1370</v>
       </c>
       <c r="C276" s="20" t="s">
@@ -17345,21 +17330,21 @@
       <c r="D276" s="20" t="s">
         <v>1371</v>
       </c>
-      <c r="E276" t="s">
+      <c r="E276" s="0" t="s">
         <v>1371</v>
       </c>
       <c r="F276" s="19">
         <v>153654564</v>
       </c>
-      <c r="G276" t="s">
+      <c r="G276" s="0" t="s">
         <v>1372</v>
       </c>
     </row>
-    <row r="277" spans="1:12">
+    <row r="277">
       <c r="A277" s="19">
         <v>276</v>
       </c>
-      <c r="B277" t="s">
+      <c r="B277" s="0" t="s">
         <v>1373</v>
       </c>
       <c r="C277" s="20" t="s">
@@ -17374,18 +17359,18 @@
       <c r="F277" s="67" t="s">
         <v>1375</v>
       </c>
-      <c r="G277" t="s">
+      <c r="G277" s="0" t="s">
         <v>1376</v>
       </c>
       <c r="L277" s="20">
         <v>15734900293</v>
       </c>
     </row>
-    <row r="278" spans="1:12">
+    <row r="278">
       <c r="A278" s="19">
         <v>277</v>
       </c>
-      <c r="B278" t="s">
+      <c r="B278" s="0" t="s">
         <v>1377</v>
       </c>
       <c r="C278" s="20" t="s">
@@ -17400,7 +17385,7 @@
       <c r="F278" s="67" t="s">
         <v>1380</v>
       </c>
-      <c r="G278" t="s">
+      <c r="G278" s="0" t="s">
         <v>1381</v>
       </c>
       <c r="K278" s="68" t="s">
@@ -17410,11 +17395,11 @@
         <v>18980343526</v>
       </c>
     </row>
-    <row r="279" spans="1:12">
+    <row r="279">
       <c r="A279" s="19">
         <v>278</v>
       </c>
-      <c r="B279" t="s">
+      <c r="B279" s="0" t="s">
         <v>1382</v>
       </c>
       <c r="C279" s="20" t="s">
@@ -17426,21 +17411,21 @@
       <c r="E279" s="67" t="s">
         <v>1383</v>
       </c>
-      <c r="F279" t="s">
+      <c r="F279" s="0" t="s">
         <v>1384</v>
       </c>
-      <c r="G279" t="s">
+      <c r="G279" s="0" t="s">
         <v>1385</v>
       </c>
       <c r="L279" s="20">
         <v>18008210260</v>
       </c>
     </row>
-    <row r="280" spans="1:12">
+    <row r="280">
       <c r="A280" s="19">
         <v>279</v>
       </c>
-      <c r="B280" t="s">
+      <c r="B280" s="0" t="s">
         <v>1386</v>
       </c>
       <c r="C280" s="20" t="s">
@@ -17455,18 +17440,18 @@
       <c r="F280" s="67" t="s">
         <v>1388</v>
       </c>
-      <c r="G280" t="s">
+      <c r="G280" s="0" t="s">
         <v>1389</v>
       </c>
       <c r="L280" s="20">
         <v>17763464579</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="14.15" customHeight="1">
+    <row r="281" ht="14.15" customHeight="1">
       <c r="A281" s="19">
         <v>280</v>
       </c>
-      <c r="B281" t="s">
+      <c r="B281" s="0" t="s">
         <v>1390</v>
       </c>
       <c r="C281" s="20" t="s">
@@ -17481,18 +17466,18 @@
       <c r="F281" s="67" t="s">
         <v>1392</v>
       </c>
-      <c r="G281" t="s">
+      <c r="G281" s="0" t="s">
         <v>1393</v>
       </c>
       <c r="L281" s="20">
         <v>18080502583</v>
       </c>
     </row>
-    <row r="282" spans="1:12">
+    <row r="282">
       <c r="A282" s="19">
         <v>281</v>
       </c>
-      <c r="B282" t="s">
+      <c r="B282" s="0" t="s">
         <v>1394</v>
       </c>
       <c r="C282" s="20" t="s">
@@ -17501,7 +17486,7 @@
       <c r="D282" s="20" t="s">
         <v>1395</v>
       </c>
-      <c r="E282" t="s">
+      <c r="E282" s="0" t="s">
         <v>1395</v>
       </c>
       <c r="F282" s="67" t="s">
@@ -17511,11 +17496,11 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="283" spans="1:12">
+    <row r="283">
       <c r="A283" s="19">
         <v>282</v>
       </c>
-      <c r="B283" t="s">
+      <c r="B283" s="0" t="s">
         <v>1398</v>
       </c>
       <c r="C283" s="20" t="s">
@@ -17524,13 +17509,13 @@
       <c r="D283" s="20" t="s">
         <v>1399</v>
       </c>
-      <c r="E283" t="s">
+      <c r="E283" s="0" t="s">
         <v>1399</v>
       </c>
       <c r="F283" s="67" t="s">
         <v>1400</v>
       </c>
-      <c r="G283" t="s">
+      <c r="G283" s="0" t="s">
         <v>1401</v>
       </c>
       <c r="H283" s="68" t="s">
@@ -17540,11 +17525,11 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="284" spans="1:12">
+    <row r="284">
       <c r="A284" s="19">
         <v>283</v>
       </c>
-      <c r="B284" t="s">
+      <c r="B284" s="0" t="s">
         <v>1404</v>
       </c>
       <c r="C284" s="20" t="s">
@@ -17553,21 +17538,21 @@
       <c r="D284" s="20" t="s">
         <v>1405</v>
       </c>
-      <c r="E284" t="s">
+      <c r="E284" s="0" t="s">
         <v>1405</v>
       </c>
       <c r="F284" s="67" t="s">
         <v>1406</v>
       </c>
-      <c r="G284" t="s">
+      <c r="G284" s="0" t="s">
         <v>1401</v>
       </c>
     </row>
-    <row r="285" spans="1:12">
+    <row r="285">
       <c r="A285" s="19">
         <v>284</v>
       </c>
-      <c r="B285" t="s">
+      <c r="B285" s="0" t="s">
         <v>1407</v>
       </c>
       <c r="C285" s="20" t="s">
@@ -17580,11 +17565,11 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="286" spans="1:12">
+    <row r="286">
       <c r="A286" s="19">
         <v>285</v>
       </c>
-      <c r="B286" t="s">
+      <c r="B286" s="0" t="s">
         <v>1409</v>
       </c>
       <c r="C286" s="20" t="s">
@@ -17593,21 +17578,21 @@
       <c r="D286" s="20" t="s">
         <v>1410</v>
       </c>
-      <c r="E286" t="s">
+      <c r="E286" s="0" t="s">
         <v>1410</v>
       </c>
       <c r="F286" s="67" t="s">
         <v>1411</v>
       </c>
-      <c r="G286" t="s">
+      <c r="G286" s="0" t="s">
         <v>1401</v>
       </c>
     </row>
-    <row r="287" spans="1:12">
+    <row r="287">
       <c r="A287" s="19">
         <v>286</v>
       </c>
-      <c r="B287" t="s">
+      <c r="B287" s="0" t="s">
         <v>1412</v>
       </c>
       <c r="C287" s="20" t="s">
@@ -17616,21 +17601,21 @@
       <c r="D287" s="20" t="s">
         <v>1413</v>
       </c>
-      <c r="E287" t="s">
+      <c r="E287" s="0" t="s">
         <v>1413</v>
       </c>
       <c r="F287" s="67" t="s">
         <v>1414</v>
       </c>
-      <c r="G287" t="s">
+      <c r="G287" s="0" t="s">
         <v>1401</v>
       </c>
     </row>
-    <row r="288" spans="1:12">
+    <row r="288">
       <c r="A288" s="19">
         <v>287</v>
       </c>
-      <c r="B288" t="s">
+      <c r="B288" s="0" t="s">
         <v>1415</v>
       </c>
       <c r="C288" s="20" t="s">
@@ -17643,11 +17628,11 @@
         <v>3210049</v>
       </c>
     </row>
-    <row r="289" spans="1:13">
+    <row r="289">
       <c r="A289" s="19">
         <v>288</v>
       </c>
-      <c r="B289" t="s">
+      <c r="B289" s="0" t="s">
         <v>1416</v>
       </c>
       <c r="C289" s="20" t="s">
@@ -17662,21 +17647,21 @@
       <c r="F289" s="67" t="s">
         <v>1418</v>
       </c>
-      <c r="G289" t="s">
+      <c r="G289" s="0" t="s">
         <v>972</v>
       </c>
       <c r="L289" s="20">
         <v>13689068809</v>
       </c>
-      <c r="M289" t="s">
+      <c r="M289" s="0" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="290" spans="1:13">
+    <row r="290">
       <c r="A290" s="19">
         <v>289</v>
       </c>
-      <c r="B290" t="s">
+      <c r="B290" s="0" t="s">
         <v>1419</v>
       </c>
       <c r="C290" s="20" t="s">
@@ -17691,21 +17676,21 @@
       <c r="F290" s="67" t="s">
         <v>1421</v>
       </c>
-      <c r="G290" t="s">
+      <c r="G290" s="0" t="s">
         <v>1422</v>
       </c>
       <c r="L290" s="20">
         <v>13397191921</v>
       </c>
-      <c r="M290" t="s">
+      <c r="M290" s="0" t="s">
         <v>1423</v>
       </c>
     </row>
-    <row r="291" spans="1:13">
+    <row r="291">
       <c r="A291" s="19">
         <v>290</v>
       </c>
-      <c r="B291" t="s">
+      <c r="B291" s="0" t="s">
         <v>1424</v>
       </c>
       <c r="C291" s="20" t="s">
@@ -17720,7 +17705,7 @@
       <c r="F291" s="67" t="s">
         <v>1426</v>
       </c>
-      <c r="G291" t="s">
+      <c r="G291" s="0" t="s">
         <v>1427</v>
       </c>
       <c r="H291" s="68" t="s">
@@ -17730,11 +17715,11 @@
         <v>15775883745</v>
       </c>
     </row>
-    <row r="292" spans="1:13">
+    <row r="292">
       <c r="A292" s="19">
         <v>291</v>
       </c>
-      <c r="B292" t="s">
+      <c r="B292" s="0" t="s">
         <v>1429</v>
       </c>
       <c r="C292" s="20" t="s">
@@ -17746,21 +17731,21 @@
       <c r="E292" s="67" t="s">
         <v>1430</v>
       </c>
-      <c r="F292" t="s">
+      <c r="F292" s="0" t="s">
         <v>1431</v>
       </c>
-      <c r="G292" t="s">
+      <c r="G292" s="0" t="s">
         <v>1432</v>
       </c>
       <c r="L292" s="20">
         <v>18030588167</v>
       </c>
     </row>
-    <row r="293" spans="1:13">
+    <row r="293">
       <c r="A293" s="19">
         <v>292</v>
       </c>
-      <c r="B293" t="s">
+      <c r="B293" s="0" t="s">
         <v>1433</v>
       </c>
       <c r="C293" s="20" t="s">
@@ -17775,14 +17760,14 @@
       <c r="F293" s="67" t="s">
         <v>1435</v>
       </c>
-      <c r="G293" t="s">
+      <c r="G293" s="0" t="s">
         <v>1436</v>
       </c>
       <c r="H293" s="68" t="s">
         <v>1437</v>
       </c>
     </row>
-    <row r="294" spans="1:13" ht="15.5">
+    <row r="294" ht="15.5">
       <c r="A294" s="19">
         <v>293</v>
       </c>
@@ -17793,17 +17778,18 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -17812,14 +17798,14 @@
   <dimension ref="A1:R3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="20.25" style="9" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="9.83203125" style="10" customWidth="1"/>
-    <col min="4" max="7" width="16" style="10" customWidth="1"/>
-    <col min="8" max="8" width="21.08203125" style="11" customWidth="1"/>
-    <col min="9" max="9" width="19.58203125" style="11" customWidth="1"/>
-    <col min="10" max="10" width="21.25" style="11" customWidth="1"/>
-    <col min="11" max="11" width="20.5" style="11" customWidth="1"/>
+    <col min="1" max="1" width="20.25" customWidth="1" style="9"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1" style="10"/>
+    <col min="3" max="3" width="9.83203125" customWidth="1" style="10"/>
+    <col min="4" max="7" width="16" customWidth="1" style="10"/>
+    <col min="8" max="8" width="21.08203125" customWidth="1" style="11"/>
+    <col min="9" max="9" width="19.58203125" customWidth="1" style="11"/>
+    <col min="10" max="10" width="21.25" customWidth="1" style="11"/>
+    <col min="11" max="11" width="20.5" customWidth="1" style="11"/>
     <col min="12" max="12" width="22.58203125" customWidth="1"/>
     <col min="13" max="13" width="14.75" customWidth="1"/>
     <col min="14" max="14" width="17.58203125" customWidth="1"/>
@@ -17827,7 +17813,7 @@
     <col min="16" max="16" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="8" customFormat="1" ht="107">
+    <row r="1" ht="107" s="8" customFormat="1">
       <c r="A1" s="12" t="s">
         <v>1439</v>
       </c>
@@ -17883,49 +17869,49 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2">
       <c r="B2" s="15"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3">
       <c r="B3" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AM4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="5" max="5" width="73.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" bestFit="1" width="73.6640625" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="14.58203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
     <col min="10" max="10" width="9" customWidth="1"/>
     <col min="11" max="11" width="18.25" customWidth="1"/>
-    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="18.25" customWidth="1"/>
-    <col min="15" max="15" width="11.08203125" customWidth="1"/>
-    <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="19" max="19" width="13.25" customWidth="1"/>
-    <col min="20" max="20" width="8" customWidth="1"/>
-    <col min="22" max="22" width="13.83203125" customWidth="1"/>
-    <col min="26" max="26" width="13.4140625" style="84" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.33203125" customWidth="1"/>
-    <col min="32" max="32" width="11.5" customWidth="1"/>
-    <col min="34" max="34" width="9.33203125" customWidth="1"/>
-    <col min="35" max="35" width="16" customWidth="1"/>
-    <col min="36" max="36" width="14.33203125" customWidth="1"/>
-    <col min="37" max="37" width="73.6640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="18.25" customWidth="1"/>
+    <col min="14" max="14" width="11.08203125" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="18" max="18" width="13.25" customWidth="1"/>
+    <col min="19" max="19" width="8" customWidth="1"/>
+    <col min="21" max="21" width="13.83203125" customWidth="1"/>
+    <col min="25" max="25" bestFit="1" width="13.4140625" customWidth="1" style="84"/>
+    <col min="27" max="27" width="13.33203125" customWidth="1"/>
+    <col min="31" max="31" width="11.5" customWidth="1"/>
+    <col min="33" max="33" width="9.33203125" customWidth="1"/>
+    <col min="34" max="34" width="16" customWidth="1"/>
+    <col min="35" max="35" width="14.33203125" customWidth="1"/>
+    <col min="36" max="36" bestFit="1" width="73.6640625" customWidth="1"/>
+    <col min="39" max="39" bestFit="1" width="7.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="1" customFormat="1" ht="42">
+    <row r="1" ht="42" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>1457</v>
       </c>
@@ -17965,89 +17951,86 @@
       <c r="M1" s="4" t="s">
         <v>1468</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>1467</v>
+      <c r="N1" s="5" t="s">
+        <v>1469</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>1478</v>
-      </c>
-      <c r="Y1" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>1480</v>
       </c>
+      <c r="Z1" s="5" t="s">
+        <v>1481</v>
+      </c>
       <c r="AA1" s="5" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="AB1" s="5" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="AC1" s="5" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="AD1" s="5" t="s">
-        <v>1484</v>
-      </c>
-      <c r="AE1" s="5" t="s">
         <v>1485</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>1486</v>
       </c>
+      <c r="AF1" s="5" t="s">
+        <v>1487</v>
+      </c>
       <c r="AG1" s="5" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="AH1" s="5" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="AI1" s="5" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="AJ1" s="5" t="s">
-        <v>1490</v>
-      </c>
-      <c r="AK1" s="5" t="s">
         <v>1491</v>
       </c>
+      <c r="AK1" s="79" t="s">
+        <v>1492</v>
+      </c>
       <c r="AL1" s="79" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="AM1" s="79" t="s">
-        <v>1493</v>
-      </c>
-      <c r="AN1" s="79" t="s">
         <v>1494</v>
       </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -18070,58 +18053,55 @@
         <v>1496</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>1516</v>
+        <v>1496</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>1496</v>
       </c>
       <c r="N2" s="3" t="s">
+        <v>1497</v>
+      </c>
+      <c r="O2" s="78" t="s">
+        <v>361</v>
+      </c>
+      <c r="P2" s="78">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="P2" s="78" t="s">
-        <v>361</v>
-      </c>
-      <c r="Q2" s="78">
-        <v>2</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>1498</v>
-      </c>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
       <c r="U2" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="V2" s="3">
+        <v>3600</v>
+      </c>
+      <c r="W2" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="V2" s="3" t="s">
-        <v>1499</v>
-      </c>
-      <c r="W2" s="3">
-        <v>3600</v>
-      </c>
       <c r="X2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y2" s="7">
+        <v>5070016</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AB2" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="Y2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z2" s="7">
-        <v>5070016</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>1500</v>
-      </c>
-      <c r="AB2" s="3">
-        <v>3500</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>1496</v>
-      </c>
-      <c r="AD2" s="3"/>
-    </row>
-    <row r="3" spans="1:40">
+      <c r="AC2" s="3"/>
+    </row>
+    <row r="3">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -18138,9 +18118,9 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
+      <c r="O3" s="78"/>
       <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
+      <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
@@ -18148,42 +18128,41 @@
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="7" t="s">
+      <c r="Y3" s="7" t="s">
         <v>993</v>
       </c>
-      <c r="AA3" s="3" t="s">
+      <c r="Z3" s="3" t="s">
         <v>1501</v>
       </c>
-      <c r="AB3" s="3">
+      <c r="AA3" s="3">
         <v>100</v>
       </c>
+      <c r="AB3" s="3" t="s">
+        <v>1496</v>
+      </c>
       <c r="AC3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD3" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="AD3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AE3" s="7" t="s">
+        <v>1502</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>1503</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AH3" s="3" t="s">
         <v>1496</v>
-      </c>
-      <c r="AF3" s="7" t="s">
-        <v>1502</v>
-      </c>
-      <c r="AG3" s="3" t="s">
-        <v>1503</v>
-      </c>
-      <c r="AH3" s="3" t="s">
-        <v>1504</v>
       </c>
       <c r="AI3" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="AJ3" s="3" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="4" spans="1:40">
+    </row>
+    <row r="4">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -18206,80 +18185,78 @@
         <v>1496</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>1516</v>
+        <v>1496</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>1496</v>
       </c>
       <c r="N4" s="3" t="s">
+        <v>1497</v>
+      </c>
+      <c r="O4" s="78" t="s">
+        <v>386</v>
+      </c>
+      <c r="P4" s="78">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="O4" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="P4" s="78" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q4" s="78">
-        <v>5</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>1498</v>
-      </c>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="V4" s="3">
+        <v>560</v>
+      </c>
+      <c r="W4" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="V4" s="3" t="s">
-        <v>1505</v>
-      </c>
-      <c r="W4" s="3">
+      <c r="X4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y4" s="83">
+        <v>5110016</v>
+      </c>
+      <c r="Z4" s="78" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA4" s="3">
         <v>560</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="AB4" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="AC4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Z4" s="83">
-        <v>5110016</v>
-      </c>
-      <c r="AA4" s="78" t="s">
-        <v>1506</v>
-      </c>
-      <c r="AB4" s="3">
-        <v>560</v>
-      </c>
-      <c r="AC4" s="3" t="s">
+      <c r="AD4" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="AD4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE4" s="3" t="s">
+      <c r="AE4" s="7" t="s">
+        <v>1502</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>1503</v>
+      </c>
+      <c r="AG4" s="3" t="s">
+        <v>1504</v>
+      </c>
+      <c r="AH4" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="AF4" s="7" t="s">
-        <v>1502</v>
-      </c>
-      <c r="AG4" s="3" t="s">
-        <v>1503</v>
-      </c>
-      <c r="AH4" s="3" t="s">
-        <v>1504</v>
-      </c>
       <c r="AI4" s="3" t="s">
-        <v>1496</v>
-      </c>
-      <c r="AJ4" s="3" t="s">
         <v>1496</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18288,10 +18265,10 @@
   <dimension ref="A1:AN3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="28" max="28" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" bestFit="1" width="13.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="42">
+    <row r="1" ht="42">
       <c r="A1" s="2" t="s">
         <v>1457</v>
       </c>
@@ -18332,10 +18309,10 @@
         <v>1507</v>
       </c>
       <c r="N1" s="85" t="s">
+        <v>1467</v>
+      </c>
+      <c r="O1" s="85" t="s">
         <v>1468</v>
-      </c>
-      <c r="O1" s="85" t="s">
-        <v>1467</v>
       </c>
       <c r="P1" s="86" t="s">
         <v>1507</v>
@@ -18413,68 +18390,68 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="2" spans="1:40">
-      <c r="G2">
+    <row r="2">
+      <c r="G2" s="0">
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <v>5130008</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="0" t="s">
         <v>1510</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="0" t="s">
         <v>1496</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="0">
         <v>5</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="0" t="s">
         <v>1496</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="0">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="0" t="s">
         <v>1496</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="0" t="s">
         <v>1496</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="0">
         <v>0</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="0" t="s">
         <v>1497</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" s="0" t="s">
         <v>250</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="0">
         <v>2</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="0" t="s">
         <v>1498</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" s="0" t="s">
         <v>1511</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" s="0" t="s">
         <v>1512</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="0" t="s">
         <v>1496</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" s="0" t="s">
         <v>1513</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="0">
         <v>100</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="Z2" s="0" t="s">
         <v>1496</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" s="0" t="s">
         <v>22</v>
       </c>
       <c r="AB2" s="88">
@@ -18483,22 +18460,22 @@
       <c r="AC2" s="88">
         <v>3</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AD2" s="0" t="s">
         <v>1514</v>
       </c>
-      <c r="AE2">
+      <c r="AE2" s="0">
         <v>50</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF2" s="0" t="s">
         <v>1496</v>
       </c>
-      <c r="AG2">
+      <c r="AG2" s="0">
         <v>3</v>
       </c>
       <c r="AJ2" s="84"/>
     </row>
-    <row r="3" spans="1:40">
-      <c r="G3">
+    <row r="3">
+      <c r="G3" s="0">
         <v>1</v>
       </c>
       <c r="AB3" s="88">
@@ -18507,22 +18484,22 @@
       <c r="AC3" s="88">
         <v>3</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AD3" s="0" t="s">
         <v>1501</v>
       </c>
-      <c r="AE3">
+      <c r="AE3" s="0">
         <v>50</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AF3" s="0" t="s">
         <v>1496</v>
       </c>
-      <c r="AG3">
+      <c r="AG3" s="0">
         <v>3</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AH3" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AI3" s="0" t="s">
         <v>1496</v>
       </c>
       <c r="AJ3" s="84" t="s">
@@ -18531,13 +18508,13 @@
       <c r="AK3" s="20" t="s">
         <v>1503</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AL3" s="0" t="s">
         <v>1504</v>
       </c>
-      <c r="AM3">
+      <c r="AM3" s="0">
         <v>5</v>
       </c>
-      <c r="AN3" t="s">
+      <c r="AN3" s="0" t="s">
         <v>1496</v>
       </c>
     </row>
@@ -18545,36 +18522,37 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Auto Finan/420财务050823.xlsx
+++ b/Auto Finan/420财务050823.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FH\source\repos\Auto Finan\Auto Finan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D11B1A-1325-498A-8B1B-14616A8068DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122F1E8E-E0CE-4298-A07A-62E6254EDE04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0-Proj信息" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="1516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="1521">
   <si>
     <t>教研室内部项目序号</t>
   </si>
@@ -5042,6 +5042,9 @@
     <t>?预约单状态</t>
   </si>
   <si>
+    <t>操作失败: K2</t>
+  </si>
+  <si>
     <t>Kp5070016</t>
   </si>
   <si>
@@ -5054,7 +5057,7 @@
     <t>个人转卡</t>
   </si>
   <si>
-    <t>#G专用材料费</t>
+    <t>#H专用材料</t>
   </si>
   <si>
     <t>*2818</t>
@@ -5070,6 +5073,18 @@
   </si>
   <si>
     <t>$预约</t>
+  </si>
+  <si>
+    <t>560.00</t>
+  </si>
+  <si>
+    <t>6834251</t>
+  </si>
+  <si>
+    <t>已预约</t>
+  </si>
+  <si>
+    <t>C:\Users\FH\source\repos\Auto Finan\prints\6834251-560.00-20250907_142624.pdf</t>
   </si>
   <si>
     <t>#M专用材料费</t>
@@ -5896,8 +5911,8 @@
     <col min="13" max="13" width="35.33203125" customWidth="1" style="47"/>
     <col min="14" max="15" width="14.25" customWidth="1" style="47"/>
     <col min="16" max="16" width="27" customWidth="1" style="47"/>
-    <col min="17" max="28" width="8.75" customWidth="1" style="47"/>
-    <col min="29" max="16384" width="8.75" customWidth="1" style="47"/>
+    <col min="17" max="33" width="8.75" customWidth="1" style="47"/>
+    <col min="34" max="16384" width="8.75" customWidth="1" style="47"/>
   </cols>
   <sheetData>
     <row r="1" ht="32.5" customHeight="1" s="46" customFormat="1">
@@ -17888,6 +17903,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
+    <col min="4" max="4" bestFit="1" width="12.1640625" customWidth="1"/>
     <col min="5" max="5" bestFit="1" width="73.6640625" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="14.58203125" customWidth="1"/>
@@ -18034,7 +18050,9 @@
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>1495</v>
+      </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3">
@@ -18044,22 +18062,22 @@
         <v>5070016</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="O2" s="78" t="s">
         <v>361</v>
@@ -18068,21 +18086,21 @@
         <v>2</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="V2" s="3">
         <v>3600</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="X2" s="3" t="s">
         <v>22</v>
@@ -18091,13 +18109,13 @@
         <v>5070016</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="AA2" s="3">
         <v>3500</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="AC2" s="3"/>
     </row>
@@ -18132,42 +18150,50 @@
         <v>993</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="AA3" s="3">
         <v>100</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="AC3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="AE3" s="7" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1509</v>
+      </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
         <v>2</v>
@@ -18176,22 +18202,22 @@
         <v>5070016</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="O4" s="78" t="s">
         <v>386</v>
@@ -18200,21 +18226,21 @@
         <v>5</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>1505</v>
+        <v>1510</v>
       </c>
       <c r="V4" s="3">
         <v>560</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="X4" s="3" t="s">
         <v>22</v>
@@ -18223,39 +18249,40 @@
         <v>5110016</v>
       </c>
       <c r="Z4" s="78" t="s">
-        <v>1506</v>
+        <v>1511</v>
       </c>
       <c r="AA4" s="3">
         <v>560</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="AC4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="AE4" s="7" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="AG4" s="3" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="AH4" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="AI4" s="3" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -18300,13 +18327,13 @@
         <v>1465</v>
       </c>
       <c r="K1" s="85" t="s">
-        <v>1507</v>
+        <v>1512</v>
       </c>
       <c r="L1" s="85" t="s">
         <v>1466</v>
       </c>
       <c r="M1" s="85" t="s">
-        <v>1507</v>
+        <v>1512</v>
       </c>
       <c r="N1" s="85" t="s">
         <v>1467</v>
@@ -18315,10 +18342,10 @@
         <v>1468</v>
       </c>
       <c r="P1" s="86" t="s">
-        <v>1507</v>
+        <v>1512</v>
       </c>
       <c r="Q1" s="86" t="s">
-        <v>1508</v>
+        <v>1513</v>
       </c>
       <c r="R1" s="86" t="s">
         <v>1470</v>
@@ -18354,7 +18381,7 @@
         <v>1480</v>
       </c>
       <c r="AC1" s="86" t="s">
-        <v>1507</v>
+        <v>1512</v>
       </c>
       <c r="AD1" s="86" t="s">
         <v>1481</v>
@@ -18366,7 +18393,7 @@
         <v>1483</v>
       </c>
       <c r="AG1" s="86" t="s">
-        <v>1507</v>
+        <v>1512</v>
       </c>
       <c r="AH1" s="86" t="s">
         <v>1484</v>
@@ -18384,10 +18411,10 @@
         <v>1488</v>
       </c>
       <c r="AM1" s="86" t="s">
-        <v>1507</v>
+        <v>1512</v>
       </c>
       <c r="AN1" s="86" t="s">
-        <v>1509</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="2">
@@ -18398,31 +18425,31 @@
         <v>5130008</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>1510</v>
+        <v>1515</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="K2" s="0">
         <v>5</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="M2" s="0">
         <v>0</v>
       </c>
       <c r="N2" s="0" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="O2" s="0" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="P2" s="0">
         <v>0</v>
       </c>
       <c r="Q2" s="0" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="R2" s="0" t="s">
         <v>250</v>
@@ -18431,25 +18458,25 @@
         <v>2</v>
       </c>
       <c r="T2" s="0" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="U2" s="0" t="s">
-        <v>1511</v>
+        <v>1516</v>
       </c>
       <c r="V2" s="0" t="s">
-        <v>1512</v>
+        <v>1517</v>
       </c>
       <c r="W2" s="0" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="X2" s="0" t="s">
-        <v>1513</v>
+        <v>1518</v>
       </c>
       <c r="Y2" s="0">
         <v>100</v>
       </c>
       <c r="Z2" s="0" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="AA2" s="0" t="s">
         <v>22</v>
@@ -18461,13 +18488,13 @@
         <v>3</v>
       </c>
       <c r="AD2" s="0" t="s">
-        <v>1514</v>
+        <v>1519</v>
       </c>
       <c r="AE2" s="0">
         <v>50</v>
       </c>
       <c r="AF2" s="0" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="AG2" s="0">
         <v>3</v>
@@ -18485,13 +18512,13 @@
         <v>3</v>
       </c>
       <c r="AD3" s="0" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="AE3" s="0">
         <v>50</v>
       </c>
       <c r="AF3" s="0" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="AG3" s="0">
         <v>3</v>
@@ -18500,22 +18527,22 @@
         <v>22</v>
       </c>
       <c r="AI3" s="0" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="AJ3" s="84" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="AK3" s="20" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="AL3" s="0" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="AM3" s="0">
         <v>5</v>
       </c>
       <c r="AN3" s="0" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
   </sheetData>

--- a/Auto Finan/420财务050823.xlsx
+++ b/Auto Finan/420财务050823.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FH\source\repos\Auto Finan\Auto Finan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122F1E8E-E0CE-4298-A07A-62E6254EDE04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F271A8-6571-4766-8BC7-5CB1F95718A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0-Proj信息" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="2-助研" sheetId="8" r:id="rId8"/>
     <sheet name="2-工资" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="1521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2702" uniqueCount="1524">
   <si>
     <t>教研室内部项目序号</t>
   </si>
@@ -147,7 +147,7 @@
     <t>是</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 10.151726; 
+    <t>项目余额: 10.151726; 
 收入: 450; 
 支出: 10.151726; 
 （一）直接费用: 10.151726; 
@@ -202,7 +202,7 @@
     <t>省-成果转化</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 0.0017; 
+    <t>项目余额: 0.0017; 
 收入: 45; 
 支出: 0.0017; 
 （一）直接费用: 0.0017; 
@@ -252,7 +252,7 @@
     <t>科瑞</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 1.650842; 
+    <t>项目余额: 1.650842; 
 收入: 110; 
 支出: 1.650842; 
 （一）直接费用: 1.650842; 
@@ -275,7 +275,7 @@
     <t>省-重大专项</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 2.669907; 
+    <t>项目余额: 2.669907; 
 收入: 300; 
 支出: 2.669907; 
 （一）直接费用: 2.669907; 
@@ -323,7 +323,7 @@
     <t>九州</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 1.106867; 
+    <t>项目余额: 1.106867; 
 收入: 30; 
 支出: 1.106867; 
 （一）直接费用: 1.106867; 
@@ -350,7 +350,7 @@
     <t>云智</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 0.01; 
+    <t>项目余额: 0.01; 
 收入: 20; 
 支出: 0.01; 
 （一）直接费用: 0.01; 
@@ -370,7 +370,7 @@
     <t>客如云</t>
   </si>
   <si>
-    <t xml:space="preserve">收入: 100; 
+    <t>收入: 100; 
 2.材料费: -1.328864; 
 3.测试化验加工费: 0.2; 
 5.差旅费: -0.147726; 
@@ -418,7 +418,7 @@
     <t>万维图新</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 2.361425; 
+    <t>项目余额: 2.361425; 
 收入: 60; 
 支出: 2.361425; 
 （一）直接费用: 2.361425; 
@@ -459,7 +459,7 @@
     <t>文轩教育</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 6.774598; 
+    <t>项目余额: 6.774598; 
 收入: 100; 
 支出: 6.774598; 
 （一）直接费用: 6.774598; 
@@ -499,7 +499,7 @@
     <t>教育融媒体统一内容生成服务平台成果转化及示范</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 0.823078; 
+    <t>项目余额: 0.823078; 
 收入: 50; 
 支出: 0.823078; 
 （一）直接费用: 0.823078; 
@@ -521,7 +521,7 @@
     <t>苗子工程</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 0.009808; 
+    <t>项目余额: 0.009808; 
 收入: 10; 
 支出: 0.009808; 
 （一）直接费用: 0.009808; 
@@ -556,7 +556,7 @@
     <t>省-科普类</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 0.002458; 
+    <t>项目余额: 0.002458; 
 收入: 20; 
 支出: 0.002458; 
 （一）直接费用: 0.002458; 
@@ -574,7 +574,7 @@
     <t>面向可穿戴设备的神经网络优实现及优化</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 1.052523; 
+    <t>项目余额: 1.052523; 
 收入: 8; 
 支出: 1.052523; 
 （一）直接费用: 1.052523; 
@@ -603,7 +603,7 @@
     <t>咪咕音乐</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 5.654086; 
+    <t>项目余额: 5.654086; 
 收入: 80; 
 支出: 5.654086; 
 （一）直接费用: 5.654086; 
@@ -626,7 +626,7 @@
     <t>新华文轩</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 8.706049; 
+    <t>项目余额: 8.706049; 
 收入: 100; 
 支出: 8.706049; 
 （一）直接费用: 8.706049; 
@@ -720,7 +720,7 @@
     <t>智能协同下轨道交通运维检修系统研发及其在供电设备运检中的实践</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 4.768043; 
+    <t>项目余额: 4.768043; 
 收入: 50; 
 支出: 4.768043; 
 （一）直接费用: 4.768043; 
@@ -763,7 +763,7 @@
     <t>横向</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 5.975; 
+    <t>项目余额: 5.975; 
 收入: 25; 
 支出: 5.975; 
 材料费: 3.375; 
@@ -781,7 +781,7 @@
     <t>四川省博物院</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 0.01001; 
+    <t>项目余额: 0.01001; 
 收入: 13; 
 支出: 0.01001; 
 1.项目业务费: 0.10951; 
@@ -799,7 +799,7 @@
     <t>完美时空</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 3.235642; 
+    <t>项目余额: 3.235642; 
 收入: 48; 
 支出: 3.235642; 
 1.项目业务费: 0.030642; 
@@ -819,7 +819,7 @@
     <t>东方电气</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 10.767764; 
+    <t>项目余额: 10.767764; 
 收入: 19.223301; 
 支出: 11.344463; 
 1.项目业务费: 10.869607; 
@@ -839,7 +839,7 @@
     <t>航天三院</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 31.490104; 
+    <t>项目余额: 31.490104; 
 收入: 39; 
 支出: 122.490104; 
 1.项目业务费: 33.135657; 
@@ -858,7 +858,7 @@
     <t>质量缺陷分析关键技术研究与工具开发服务</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 8.329888; 
+    <t>项目余额: 8.329888; 
 收入: 28.15534; 
 支出: 9.174548; 
 1.项目业务费: 8.644598; 
@@ -875,7 +875,7 @@
     <t>战术决策自动执行与反馈技术研究</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 13.410537; 
+    <t>项目余额: 13.410537; 
 收入: 101.941748; 
 支出: 16.468789; 
 1.项目业务费: 1.2642; 
@@ -902,7 +902,7 @@
     <t>面向虚拟战场的全局态势生成与PVI设计</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 75.68481; 
+    <t>项目余额: 75.68481; 
 收入: 91.262136; 
 支出: 78.422674; 
 1.项目业务费: 35.656396; 
@@ -920,7 +920,7 @@
     <t>基于任务互操作的分布式封控作战空基指控集成仿真验证环境</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 0.711514; 
+    <t>项目余额: 0.711514; 
 收入: 187.378641; 
 支出: 6.332873; 
 3.人员费: 6.332873; 
@@ -937,7 +937,7 @@
     <t>成都九洲电子信息系统股份有限公司</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 15.420918; 
+    <t>项目余额: 15.420918; 
 收入: 20.38835; 
 支出: 16.032568; 
 1.项目业务费: 7.062267; 
@@ -1107,7 +1107,7 @@
     <t>东方电气集团科学技术研究院</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 5.856465; 
+    <t>项目余额: 5.856465; 
 收入: 35; 
 支出: 5.856465; 
 一、直接费用: 5.856465; 
@@ -1140,7 +1140,7 @@
     <t>省-中央引导发展专项</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 17.183228; 
+    <t>项目余额: 17.183228; 
 收入: 30; 
 支出: 17.183228; 
 一、直接费用: 17.183228; 
@@ -1174,7 +1174,7 @@
     <t>四川省人民政府国防动员办公室</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 6.906731; 
+    <t>项目余额: 6.906731; 
 收入: 7.23301; 
 支出: 7.123721; 
 1.项目业务费: 7.152; 
@@ -1211,7 +1211,7 @@
     <t>军口-课题二</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 0.154824; 
+    <t>项目余额: 0.154824; 
 收入: 46; 
 支出: 4.154824; 
 （一）直接费用: 3.264424; 
@@ -1249,7 +1249,7 @@
     <t>面向虚拟场景的图像自动标注技术研究</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 0.034168; 
+    <t>项目余额: 0.034168; 
 收入: 3; 
 支出: 0.034168; 
 一、直接费用: 0.034168; 
@@ -1268,7 +1268,7 @@
     <t>中国船舶集团有限公司系统工程研究院</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 8.312066; 
+    <t>项目余额: 8.312066; 
 收入: 183.495146; 
 支出: 13.81692; 
 1.项目业务费: 4.713955; 
@@ -1298,7 +1298,7 @@
     <t>军口</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 13.905458; 
+    <t>项目余额: 13.905458; 
 收入: 25.242718; 
 支出: 54.38274; 
 外协费: 24; 
@@ -1372,7 +1372,7 @@
     <t>****飞机快速座舱工效评估POP驱动模型开发</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 80.748593; 
+    <t>项目余额: 80.748593; 
 收入: 91.262136; 
 支出: 83.486457; 
 1.项目业务费: 54; 
@@ -1392,7 +1392,7 @@
     <t>中铁二院工程集团有限责任公司</t>
   </si>
   <si>
-    <t xml:space="preserve">收入: 7; 
+    <t>收入: 7; 
 其中：1.绩效支出: 1.5; 
 2.其他: -1.5; 
 收入(不计项目余额): 5.5; 
@@ -1408,7 +1408,7 @@
     <t>四川科瑞软件有限责任公司</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 8.170787; 
+    <t>项目余额: 8.170787; 
 收入: 9.708738; 
 支出: 8.462049; 
 1.项目业务费: 6.8; 
@@ -1479,7 +1479,7 @@
     <t>中国航发四川燃气涡轮研究院</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 11.725266; 
+    <t>项目余额: 11.725266; 
 收入: 14.271845; 
 支出: 46.453421; 
 1.项目业务费: 17.3984; 
@@ -1503,7 +1503,7 @@
     <t>动态测试数字化管理技术研究</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 4.714275; 
+    <t>项目余额: 4.714275; 
 收入: 6.116505; 
 支出: 19.59777; 
 1.项目业务费: 11.6; 
@@ -1533,7 +1533,7 @@
     <t>市-重点研发支撑计划</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 1.9341; 
+    <t>项目余额: 1.9341; 
 收入: 10; 
 支出: 1.9341; 
 （一）直接费用: 1.9341; 
@@ -1558,7 +1558,7 @@
     <t>省-科技计划“揭榜挂帅”</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 31.64416; 
+    <t>项目余额: 31.64416; 
 收入: 40; 
 支出: 91.64416; 
 一、直接费用: 45.64416; 
@@ -1591,7 +1591,7 @@
     <t>省-经信后补助</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 62.475728; 
+    <t>项目余额: 62.475728; 
 收入: 77.475728; 
 支出: 64.8; 
 （一）直接费用: 64.8; 
@@ -1622,7 +1622,7 @@
     <t>四川百嘉数字科技有限公司</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 21.986144; 
+    <t>项目余额: 21.986144; 
 收入: 60; 
 支出: 21.986144; 
 一、直接费用: 21.986144; 
@@ -1650,7 +1650,7 @@
     <t>舆情态势感知智能分析算法技术服务采购项目</t>
   </si>
   <si>
-    <t xml:space="preserve">项目余额: 19.849231; 
+    <t>项目余额: 19.849231; 
 收入: 22.23301; 
 支出: 43.416221; 
 1.项目业务费: 21.02; 
@@ -4788,35 +4788,35 @@
     <t>侯超凡</t>
   </si>
   <si>
-    <t xml:space="preserve">一、
+    <t>一、
 教研室内部报销编号</t>
   </si>
   <si>
-    <t xml:space="preserve">二、
+    <t>二、
 提出时间</t>
   </si>
   <si>
-    <t xml:space="preserve">二、
+    <t>二、
 新事由？</t>
   </si>
   <si>
-    <t xml:space="preserve">二、
+    <t>二、
 历史报销编号</t>
   </si>
   <si>
-    <t xml:space="preserve">二、
+    <t>二、
 报销事由</t>
   </si>
   <si>
-    <t xml:space="preserve">二、
+    <t>二、
 涉及人/单位</t>
   </si>
   <si>
-    <t xml:space="preserve">二、
+    <t>二、
 涉及总金额</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <b/>
         <sz val="18"/>
@@ -4829,7 +4829,7 @@
       <t>三、
 报销审查意见</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -4843,11 +4843,11 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">三、
+    <t>三、
 具体意见</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <b/>
         <sz val="18"/>
@@ -4861,7 +4861,7 @@
 执行反馈
 </t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
@@ -4874,7 +4874,7 @@
     </r>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <b/>
         <sz val="18"/>
@@ -4888,7 +4888,7 @@
 执行情况说明
 </t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
@@ -4901,30 +4901,30 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">四、内部所需-
+    <t>四、内部所需-
 教研室内部项目序号</t>
   </si>
   <si>
-    <t xml:space="preserve">四、内部所需-
+    <t>四、内部所需-
 项目编号</t>
   </si>
   <si>
     <t>四、内部所需-项目名称</t>
   </si>
   <si>
-    <t xml:space="preserve">四、
+    <t>四、
 收/支</t>
   </si>
   <si>
-    <t xml:space="preserve">四、
+    <t>四、
 实际支出科目</t>
   </si>
   <si>
-    <t xml:space="preserve">四、
+    <t>四、
 人/单位</t>
   </si>
   <si>
-    <t xml:space="preserve">四、
+    <t>四、
 金额</t>
   </si>
   <si>
@@ -5042,9 +5042,6 @@
     <t>?预约单状态</t>
   </si>
   <si>
-    <t>操作失败: K2</t>
-  </si>
-  <si>
     <t>Kp5070016</t>
   </si>
   <si>
@@ -5057,9 +5054,6 @@
     <t>个人转卡</t>
   </si>
   <si>
-    <t>#H专用材料</t>
-  </si>
-  <si>
     <t>*2818</t>
   </si>
   <si>
@@ -5075,18 +5069,6 @@
     <t>$预约</t>
   </si>
   <si>
-    <t>560.00</t>
-  </si>
-  <si>
-    <t>6834251</t>
-  </si>
-  <si>
-    <t>已预约</t>
-  </si>
-  <si>
-    <t>C:\Users\FH\source\repos\Auto Finan\prints\6834251-560.00-20250907_142624.pdf</t>
-  </si>
-  <si>
     <t>#M专用材料费</t>
   </si>
   <si>
@@ -5118,14 +5100,49 @@
   </si>
   <si>
     <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>登录界面工号</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Uestc418</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>$$报销业务</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>M112023ZHCG0006</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>个人转卡</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我是一条备注</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我是特殊事项</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>$点击</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>#M电费</t>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5253,6 +5270,26 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -5375,50 +5412,50 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" applyFont="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" applyFill="1" borderId="3" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="3" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyFont="1" fillId="4" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" applyNumberFormat="1" fontId="0" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="4" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -5427,57 +5464,57 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -5489,73 +5526,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="12" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="5" applyFill="1" borderId="3" applyBorder="1" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="5" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="4" applyBorder="1" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="5" applyFill="1" borderId="4" applyBorder="1" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="3" applyBorder="1" xfId="0">
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="5" applyBorder="1" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
@@ -5568,55 +5605,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyFont="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" applyFont="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="14" applyFont="1" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" applyFont="1" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" applyFont="1" fillId="0" borderId="6" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="16" applyFont="1" fillId="0" borderId="6" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5896,26 +5933,26 @@
   <dimension ref="A1:P119"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.58203125" customWidth="1" style="47"/>
-    <col min="2" max="2" width="29.25" customWidth="1" style="47"/>
-    <col min="3" max="3" width="42.5" customWidth="1" style="47"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1" style="47"/>
-    <col min="5" max="5" width="16.25" customWidth="1" style="47"/>
-    <col min="6" max="6" width="16.5" customWidth="1" style="47"/>
-    <col min="7" max="7" width="16" customWidth="1" style="47"/>
-    <col min="8" max="8" width="16.58203125" customWidth="1" style="47"/>
-    <col min="9" max="9" width="23.83203125" customWidth="1" style="47"/>
-    <col min="10" max="10" width="20.75" customWidth="1" style="47"/>
-    <col min="11" max="11" width="27.08203125" customWidth="1" style="47"/>
-    <col min="12" max="12" bestFit="1" width="17.9140625" customWidth="1" style="47"/>
-    <col min="13" max="13" width="35.33203125" customWidth="1" style="47"/>
-    <col min="14" max="15" width="14.25" customWidth="1" style="47"/>
-    <col min="16" max="16" width="27" customWidth="1" style="47"/>
-    <col min="17" max="33" width="8.75" customWidth="1" style="47"/>
-    <col min="34" max="16384" width="8.75" customWidth="1" style="47"/>
+    <col min="1" max="1" width="13.58203125" style="47" customWidth="1"/>
+    <col min="2" max="2" width="29.25" style="47" customWidth="1"/>
+    <col min="3" max="3" width="42.5" style="47" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" style="47" customWidth="1"/>
+    <col min="5" max="5" width="16.25" style="47" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="47" customWidth="1"/>
+    <col min="7" max="7" width="16" style="47" customWidth="1"/>
+    <col min="8" max="8" width="16.58203125" style="47" customWidth="1"/>
+    <col min="9" max="9" width="23.83203125" style="47" customWidth="1"/>
+    <col min="10" max="10" width="20.75" style="47" customWidth="1"/>
+    <col min="11" max="11" width="27.08203125" style="47" customWidth="1"/>
+    <col min="12" max="12" width="17.9140625" style="47" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="35.33203125" style="47" customWidth="1"/>
+    <col min="14" max="15" width="14.25" style="47" customWidth="1"/>
+    <col min="16" max="16" width="27" style="47" customWidth="1"/>
+    <col min="17" max="34" width="8.75" style="47" customWidth="1"/>
+    <col min="35" max="16384" width="8.75" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.5" customHeight="1" s="46" customFormat="1">
+    <row r="1" spans="1:16" s="46" customFormat="1" ht="32.5" customHeight="1">
       <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
@@ -5965,7 +6002,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" ht="252.5">
+    <row r="2" spans="1:16" ht="252.5">
       <c r="A2" s="50">
         <v>2025001</v>
       </c>
@@ -6009,7 +6046,7 @@
         <v>10.151726</v>
       </c>
     </row>
-    <row r="3" ht="31">
+    <row r="3" spans="1:16" ht="31">
       <c r="A3" s="50">
         <v>2025002</v>
       </c>
@@ -6047,7 +6084,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="15.5">
+    <row r="4" spans="1:16" ht="15.5">
       <c r="A4" s="54">
         <v>2025003</v>
       </c>
@@ -6085,7 +6122,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" ht="98.5">
+    <row r="5" spans="1:16" ht="98.5">
       <c r="A5" s="54">
         <v>2025004</v>
       </c>
@@ -6126,10 +6163,10 @@
         <v>36</v>
       </c>
       <c r="N5" s="47">
-        <v>0.0017</v>
-      </c>
-    </row>
-    <row r="6" ht="15.5">
+        <v>1.6999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15.5">
       <c r="A6" s="54">
         <v>2025005</v>
       </c>
@@ -6167,7 +6204,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" ht="28.5">
+    <row r="7" spans="1:16" ht="28.5">
       <c r="A7" s="54">
         <v>2025006</v>
       </c>
@@ -6205,7 +6242,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" ht="28.5">
+    <row r="8" spans="1:16" ht="28.5">
       <c r="A8" s="54">
         <v>2025007</v>
       </c>
@@ -6243,7 +6280,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" ht="168.5">
+    <row r="9" spans="1:16" ht="168.5">
       <c r="A9" s="54">
         <v>2025008</v>
       </c>
@@ -6284,10 +6321,10 @@
         <v>51</v>
       </c>
       <c r="N9" s="47">
-        <v>1.650842</v>
-      </c>
-    </row>
-    <row r="10" ht="238.5">
+        <v>1.6508419999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="238.5">
       <c r="A10" s="54">
         <v>2025009</v>
       </c>
@@ -6328,10 +6365,10 @@
         <v>55</v>
       </c>
       <c r="N10" s="47">
-        <v>2.669907</v>
-      </c>
-    </row>
-    <row r="11" ht="15.5">
+        <v>2.6699069999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15.5">
       <c r="A11" s="54">
         <v>2025010</v>
       </c>
@@ -6369,7 +6406,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="15.5">
+    <row r="12" spans="1:16" ht="15.5">
       <c r="A12" s="54">
         <v>2025011</v>
       </c>
@@ -6407,7 +6444,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" ht="154.5">
+    <row r="13" spans="1:16" ht="154.5">
       <c r="A13" s="54">
         <v>2025012</v>
       </c>
@@ -6451,7 +6488,7 @@
         <v>1.106867</v>
       </c>
     </row>
-    <row r="14" ht="28.5">
+    <row r="14" spans="1:16" ht="28.5">
       <c r="A14" s="54">
         <v>2025013</v>
       </c>
@@ -6489,7 +6526,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="126.5">
+    <row r="15" spans="1:16" ht="126.5">
       <c r="A15" s="54">
         <v>2025014</v>
       </c>
@@ -6533,7 +6570,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" ht="140.5">
+    <row r="16" spans="1:16" ht="140.5">
       <c r="A16" s="54">
         <v>2025015</v>
       </c>
@@ -6577,7 +6614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="15.5">
+    <row r="17" spans="1:14" ht="15.5">
       <c r="A17" s="54">
         <v>2025016</v>
       </c>
@@ -6615,7 +6652,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" ht="15.5">
+    <row r="18" spans="1:14" ht="15.5">
       <c r="A18" s="54">
         <v>2025017</v>
       </c>
@@ -6653,7 +6690,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" ht="15.5">
+    <row r="19" spans="1:14" ht="15.5">
       <c r="A19" s="54">
         <v>2025018</v>
       </c>
@@ -6691,7 +6728,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" ht="182.5">
+    <row r="20" spans="1:14" ht="182.5">
       <c r="A20" s="54">
         <v>2025019</v>
       </c>
@@ -6732,10 +6769,10 @@
         <v>89</v>
       </c>
       <c r="N20" s="47">
-        <v>2.361425</v>
-      </c>
-    </row>
-    <row r="21" ht="15.5">
+        <v>2.3614250000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15.5">
       <c r="A21" s="54">
         <v>2025020</v>
       </c>
@@ -6773,7 +6810,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" ht="15.5">
+    <row r="22" spans="1:14" ht="15.5">
       <c r="A22" s="54">
         <v>2025021</v>
       </c>
@@ -6811,7 +6848,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" ht="196.5">
+    <row r="23" spans="1:14" ht="196.5">
       <c r="A23" s="54">
         <v>2025022</v>
       </c>
@@ -6852,10 +6889,10 @@
         <v>99</v>
       </c>
       <c r="N23" s="47">
-        <v>6.774598</v>
-      </c>
-    </row>
-    <row r="24" ht="15.5">
+        <v>6.7745980000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15.5">
       <c r="A24" s="54">
         <v>2025023</v>
       </c>
@@ -6893,7 +6930,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" ht="28.5">
+    <row r="25" spans="1:14" ht="28.5">
       <c r="A25" s="54">
         <v>2025024</v>
       </c>
@@ -6931,7 +6968,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" ht="154.5">
+    <row r="26" spans="1:14" ht="154.5">
       <c r="A26" s="54">
         <v>2025025</v>
       </c>
@@ -6972,10 +7009,10 @@
         <v>108</v>
       </c>
       <c r="N26" s="47">
-        <v>0.823078</v>
-      </c>
-    </row>
-    <row r="27" ht="182.5">
+        <v>0.82307799999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="182.5">
       <c r="A27" s="54">
         <v>2025026</v>
       </c>
@@ -7016,10 +7053,10 @@
         <v>112</v>
       </c>
       <c r="N27" s="47">
-        <v>0.009808</v>
-      </c>
-    </row>
-    <row r="28" ht="15.5">
+        <v>9.8080000000000007E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="15.5">
       <c r="A28" s="54">
         <v>2025027</v>
       </c>
@@ -7057,7 +7094,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" ht="140.5">
+    <row r="29" spans="1:14" ht="140.5">
       <c r="A29" s="54">
         <v>2025028</v>
       </c>
@@ -7098,10 +7135,10 @@
         <v>120</v>
       </c>
       <c r="N29" s="47">
-        <v>0.002458</v>
-      </c>
-    </row>
-    <row r="30" ht="126.5">
+        <v>2.4580000000000001E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="126.5">
       <c r="A30" s="54">
         <v>2025029</v>
       </c>
@@ -7142,10 +7179,10 @@
         <v>123</v>
       </c>
       <c r="N30" s="47">
-        <v>1.052523</v>
-      </c>
-    </row>
-    <row r="31" ht="15.5">
+        <v>1.0525230000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15.5">
       <c r="A31" s="54">
         <v>2025030</v>
       </c>
@@ -7183,7 +7220,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" ht="168.5">
+    <row r="32" spans="1:14" ht="168.5">
       <c r="A32" s="54">
         <v>2025031</v>
       </c>
@@ -7224,10 +7261,10 @@
         <v>130</v>
       </c>
       <c r="N32" s="47">
-        <v>5.654086</v>
-      </c>
-    </row>
-    <row r="33" ht="154.5">
+        <v>5.6540860000000004</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="154.5">
       <c r="A33" s="54">
         <v>2025032</v>
       </c>
@@ -7268,10 +7305,10 @@
         <v>134</v>
       </c>
       <c r="N33" s="47">
-        <v>8.706049</v>
-      </c>
-    </row>
-    <row r="34" ht="15.5">
+        <v>8.7060490000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="15.5">
       <c r="A34" s="54">
         <v>2025033</v>
       </c>
@@ -7309,7 +7346,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" ht="15.5">
+    <row r="35" spans="1:14" ht="15.5">
       <c r="A35" s="54">
         <v>2025034</v>
       </c>
@@ -7347,7 +7384,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" ht="15.5">
+    <row r="36" spans="1:14" ht="15.5">
       <c r="A36" s="54">
         <v>2025035</v>
       </c>
@@ -7385,7 +7422,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" ht="15.5">
+    <row r="37" spans="1:14" ht="15.5">
       <c r="A37" s="54">
         <v>2025036</v>
       </c>
@@ -7423,7 +7460,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" ht="15.5">
+    <row r="38" spans="1:14" ht="15.5">
       <c r="A38" s="54">
         <v>2025037</v>
       </c>
@@ -7461,7 +7498,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" ht="15.5">
+    <row r="39" spans="1:14" ht="15.5">
       <c r="A39" s="54">
         <v>2025038</v>
       </c>
@@ -7499,7 +7536,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" ht="15.5">
+    <row r="40" spans="1:14" ht="15.5">
       <c r="A40" s="54">
         <v>2025039</v>
       </c>
@@ -7537,7 +7574,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" ht="15.5">
+    <row r="41" spans="1:14" ht="15.5">
       <c r="A41" s="54">
         <v>2025040</v>
       </c>
@@ -7575,7 +7612,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" ht="252.5">
+    <row r="42" spans="1:14" ht="252.5">
       <c r="A42" s="54">
         <v>2025041</v>
       </c>
@@ -7616,10 +7653,10 @@
         <v>162</v>
       </c>
       <c r="N42" s="47">
-        <v>4.768043</v>
-      </c>
-    </row>
-    <row r="43" ht="15.5">
+        <v>4.7680429999999996</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="15.5">
       <c r="A43" s="54">
         <v>2025042</v>
       </c>
@@ -7657,7 +7694,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" ht="15.5">
+    <row r="44" spans="1:14" ht="15.5">
       <c r="A44" s="54">
         <v>2025043</v>
       </c>
@@ -7695,7 +7732,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" ht="51" customHeight="1">
+    <row r="45" spans="1:14" ht="51" customHeight="1">
       <c r="A45" s="54">
         <v>2025044</v>
       </c>
@@ -7736,10 +7773,10 @@
         <v>171</v>
       </c>
       <c r="N45" s="47">
-        <v>5.975</v>
-      </c>
-    </row>
-    <row r="46" ht="98.5">
+        <v>5.9749999999999996</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="98.5">
       <c r="A46" s="54">
         <v>2025045</v>
       </c>
@@ -7780,10 +7817,10 @@
         <v>175</v>
       </c>
       <c r="N46" s="47">
-        <v>0.01001</v>
-      </c>
-    </row>
-    <row r="47" ht="126.5">
+        <v>1.001E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="126.5">
       <c r="A47" s="54">
         <v>2025046</v>
       </c>
@@ -7824,10 +7861,10 @@
         <v>179</v>
       </c>
       <c r="N47" s="47">
-        <v>3.235642</v>
-      </c>
-    </row>
-    <row r="48" ht="126.5">
+        <v>3.2356419999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="126.5">
       <c r="A48" s="54">
         <v>2025047</v>
       </c>
@@ -7871,7 +7908,7 @@
         <v>10.767764</v>
       </c>
     </row>
-    <row r="49" ht="154.5">
+    <row r="49" spans="1:14" ht="154.5">
       <c r="A49" s="54">
         <v>2025048</v>
       </c>
@@ -7912,10 +7949,10 @@
         <v>187</v>
       </c>
       <c r="N49" s="47">
-        <v>31.490104</v>
-      </c>
-    </row>
-    <row r="50" ht="126.5">
+        <v>31.490103999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="126.5">
       <c r="A50" s="54">
         <v>2025049</v>
       </c>
@@ -7956,10 +7993,10 @@
         <v>190</v>
       </c>
       <c r="N50" s="47">
-        <v>8.329888</v>
-      </c>
-    </row>
-    <row r="51" ht="140.5">
+        <v>8.3298880000000004</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="140.5">
       <c r="A51" s="54">
         <v>2025050</v>
       </c>
@@ -8003,7 +8040,7 @@
         <v>13.410537</v>
       </c>
     </row>
-    <row r="52" ht="28.5">
+    <row r="52" spans="1:14" ht="28.5">
       <c r="A52" s="54">
         <v>2025051</v>
       </c>
@@ -8041,7 +8078,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" ht="140.5">
+    <row r="53" spans="1:14" ht="140.5">
       <c r="A53" s="54">
         <v>2025052</v>
       </c>
@@ -8082,10 +8119,10 @@
         <v>199</v>
       </c>
       <c r="N53" s="47">
-        <v>75.68481</v>
-      </c>
-    </row>
-    <row r="54" ht="84.5">
+        <v>75.684809999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="84.5">
       <c r="A54" s="54">
         <v>2025053</v>
       </c>
@@ -8126,10 +8163,10 @@
         <v>202</v>
       </c>
       <c r="N54" s="47">
-        <v>0.711514</v>
-      </c>
-    </row>
-    <row r="55" ht="126.5">
+        <v>0.71151399999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="126.5">
       <c r="A55" s="54">
         <v>2025054</v>
       </c>
@@ -8173,7 +8210,7 @@
         <v>15.420918</v>
       </c>
     </row>
-    <row r="56" ht="28.5">
+    <row r="56" spans="1:14" ht="28.5">
       <c r="A56" s="54">
         <v>2025055</v>
       </c>
@@ -8211,7 +8248,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" ht="15.5">
+    <row r="57" spans="1:14" ht="15.5">
       <c r="A57" s="54">
         <v>2025056</v>
       </c>
@@ -8241,7 +8278,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" ht="15.5">
+    <row r="58" spans="1:14" ht="15.5">
       <c r="A58" s="54">
         <v>2025057</v>
       </c>
@@ -8271,7 +8308,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" ht="15.5">
+    <row r="59" spans="1:14" ht="15.5">
       <c r="A59" s="54">
         <v>2025058</v>
       </c>
@@ -8301,7 +8338,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="60" ht="15.5">
+    <row r="60" spans="1:14" ht="15.5">
       <c r="A60" s="54">
         <v>2025059</v>
       </c>
@@ -8331,7 +8368,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" ht="15.5">
+    <row r="61" spans="1:14" ht="15.5">
       <c r="A61" s="54">
         <v>2025060</v>
       </c>
@@ -8361,7 +8398,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" ht="15.5">
+    <row r="62" spans="1:14" ht="15.5">
       <c r="A62" s="54">
         <v>2025061</v>
       </c>
@@ -8391,7 +8428,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" ht="28.5">
+    <row r="63" spans="1:14" ht="28.5">
       <c r="A63" s="54">
         <v>2025062</v>
       </c>
@@ -8429,7 +8466,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" ht="15.5">
+    <row r="64" spans="1:14" ht="15.5">
       <c r="A64" s="54">
         <v>2025063</v>
       </c>
@@ -8463,7 +8500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="65" ht="15.5">
+    <row r="65" spans="1:14" ht="15.5">
       <c r="A65" s="54">
         <v>2025064</v>
       </c>
@@ -8493,7 +8530,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" ht="15.5">
+    <row r="66" spans="1:14" ht="15.5">
       <c r="A66" s="54">
         <v>2025065</v>
       </c>
@@ -8527,7 +8564,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" ht="68.5" customHeight="1">
+    <row r="67" spans="1:14" ht="68.5" customHeight="1">
       <c r="A67" s="54">
         <v>2025066</v>
       </c>
@@ -8561,7 +8598,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" ht="28.5">
+    <row r="68" spans="1:14" ht="28.5">
       <c r="A68" s="54">
         <v>2025067</v>
       </c>
@@ -8599,7 +8636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" ht="16">
+    <row r="69" spans="1:14" ht="16">
       <c r="A69" s="54">
         <v>2025068</v>
       </c>
@@ -8637,7 +8674,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" ht="28.5">
+    <row r="70" spans="1:14" ht="28.5">
       <c r="A70" s="54">
         <v>2025069</v>
       </c>
@@ -8675,7 +8712,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" ht="28.5">
+    <row r="71" spans="1:14" ht="28.5">
       <c r="A71" s="54">
         <v>2025070</v>
       </c>
@@ -8713,7 +8750,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72" ht="15.5">
+    <row r="72" spans="1:14" ht="15.5">
       <c r="A72" s="54">
         <v>2025071</v>
       </c>
@@ -8743,7 +8780,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" ht="28.5">
+    <row r="73" spans="1:14" ht="28.5">
       <c r="A73" s="54">
         <v>2025072</v>
       </c>
@@ -8781,7 +8818,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" ht="140.5">
+    <row r="74" spans="1:14" ht="140.5">
       <c r="A74" s="54">
         <v>2025073</v>
       </c>
@@ -8825,7 +8862,7 @@
         <v>5.856465</v>
       </c>
     </row>
-    <row r="75" ht="28.5">
+    <row r="75" spans="1:14" ht="28.5">
       <c r="A75" s="54">
         <v>2025074</v>
       </c>
@@ -8863,7 +8900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" ht="112.5">
+    <row r="76" spans="1:14" ht="112.5">
       <c r="A76" s="54">
         <v>2025075</v>
       </c>
@@ -8907,7 +8944,7 @@
         <v>17.183228</v>
       </c>
     </row>
-    <row r="77" ht="28">
+    <row r="77" spans="1:14" ht="28">
       <c r="A77" s="54">
         <v>2025076</v>
       </c>
@@ -8945,7 +8982,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78" ht="15.5">
+    <row r="78" spans="1:14" ht="15.5">
       <c r="A78" s="54">
         <v>2025077</v>
       </c>
@@ -8983,7 +9020,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79" ht="112.5">
+    <row r="79" spans="1:14" ht="112.5">
       <c r="A79" s="54">
         <v>2025078</v>
       </c>
@@ -9024,10 +9061,10 @@
         <v>277</v>
       </c>
       <c r="N79" s="47">
-        <v>6.906731</v>
-      </c>
-    </row>
-    <row r="80" ht="28.5">
+        <v>6.9067309999999997</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" ht="28.5">
       <c r="A80" s="54">
         <v>2025079</v>
       </c>
@@ -9053,10 +9090,10 @@
         <v>280</v>
       </c>
       <c r="I80" s="65">
-        <v>9.8</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="J80" s="65">
-        <v>9.8</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="K80" s="56" t="s">
         <v>170</v>
@@ -9065,7 +9102,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" ht="28.5">
+    <row r="81" spans="1:14" ht="28.5">
       <c r="A81" s="54">
         <v>2025080</v>
       </c>
@@ -9093,7 +9130,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="82" ht="168.5">
+    <row r="82" spans="1:14" ht="168.5">
       <c r="A82" s="54">
         <v>2025081</v>
       </c>
@@ -9130,10 +9167,10 @@
         <v>287</v>
       </c>
       <c r="N82" s="47">
-        <v>0.154824</v>
-      </c>
-    </row>
-    <row r="83" ht="168.5">
+        <v>0.15482399999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" ht="168.5">
       <c r="A83" s="54">
         <v>2025082</v>
       </c>
@@ -9170,10 +9207,10 @@
         <v>287</v>
       </c>
       <c r="N83" s="47">
-        <v>0.154824</v>
-      </c>
-    </row>
-    <row r="84" ht="15.5">
+        <v>0.15482399999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" ht="15.5">
       <c r="A84" s="54">
         <v>2025083</v>
       </c>
@@ -9209,7 +9246,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85" ht="126.5">
+    <row r="85" spans="1:14" ht="126.5">
       <c r="A85" s="54">
         <v>2025084</v>
       </c>
@@ -9248,10 +9285,10 @@
         <v>296</v>
       </c>
       <c r="N85" s="47">
-        <v>0.034168</v>
-      </c>
-    </row>
-    <row r="86" ht="140.5">
+        <v>3.4167999999999997E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" ht="140.5">
       <c r="A86" s="54">
         <v>2025085</v>
       </c>
@@ -9288,10 +9325,10 @@
         <v>300</v>
       </c>
       <c r="N86" s="47">
-        <v>8.312066</v>
-      </c>
-    </row>
-    <row r="87" ht="15.5">
+        <v>8.3120659999999997</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" ht="15.5">
       <c r="A87" s="54">
         <v>2025086</v>
       </c>
@@ -9319,7 +9356,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="88" ht="126.5">
+    <row r="88" spans="1:14" ht="126.5">
       <c r="A88" s="54">
         <v>2025087</v>
       </c>
@@ -9356,10 +9393,10 @@
         <v>307</v>
       </c>
       <c r="N88" s="47">
-        <v>13.905458</v>
-      </c>
-    </row>
-    <row r="89" ht="42.5">
+        <v>13.905457999999999</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" ht="42.5">
       <c r="A89" s="54">
         <v>2025088</v>
       </c>
@@ -9397,7 +9434,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" ht="39.65" customHeight="1">
+    <row r="90" spans="1:14" ht="39.65" customHeight="1">
       <c r="A90" s="54">
         <v>2025089</v>
       </c>
@@ -9419,10 +9456,10 @@
         <v>313</v>
       </c>
       <c r="I90" s="52">
-        <v>26.993477</v>
+        <v>26.993476999999999</v>
       </c>
       <c r="J90" s="52">
-        <v>26.993477</v>
+        <v>26.993476999999999</v>
       </c>
       <c r="K90" s="52" t="s">
         <v>170</v>
@@ -9431,7 +9468,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" ht="28.5">
+    <row r="91" spans="1:14" ht="28.5">
       <c r="A91" s="54">
         <v>2025090</v>
       </c>
@@ -9471,7 +9508,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="92" ht="28.5">
+    <row r="92" spans="1:14" ht="28.5">
       <c r="A92" s="54">
         <v>2025091</v>
       </c>
@@ -9510,7 +9547,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="93" ht="28.5">
+    <row r="93" spans="1:14" ht="28.5">
       <c r="A93" s="54">
         <v>2025092</v>
       </c>
@@ -9549,7 +9586,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="94" ht="15.5">
+    <row r="94" spans="1:14" ht="15.5">
       <c r="A94" s="54">
         <v>2025093</v>
       </c>
@@ -9575,7 +9612,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" ht="15.5">
+    <row r="95" spans="1:14" ht="15.5">
       <c r="A95" s="54">
         <v>2025094</v>
       </c>
@@ -9605,7 +9642,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="96" ht="126.5">
+    <row r="96" spans="1:14" ht="126.5">
       <c r="A96" s="54">
         <v>2025095</v>
       </c>
@@ -9649,7 +9686,7 @@
         <v>80.748593</v>
       </c>
     </row>
-    <row r="97" ht="70.5">
+    <row r="97" spans="1:14" ht="70.5">
       <c r="A97" s="54">
         <v>2025096</v>
       </c>
@@ -9691,7 +9728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" ht="126.5">
+    <row r="98" spans="1:14" ht="126.5">
       <c r="A98" s="54">
         <v>2025097</v>
       </c>
@@ -9732,10 +9769,10 @@
         <v>337</v>
       </c>
       <c r="N98" s="47">
-        <v>8.170787</v>
-      </c>
-    </row>
-    <row r="99" ht="28.5">
+        <v>8.1707870000000007</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" ht="28.5">
       <c r="A99" s="54">
         <v>2025098</v>
       </c>
@@ -9765,7 +9802,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="100" ht="28.5">
+    <row r="100" spans="1:14" ht="28.5">
       <c r="A100" s="54">
         <v>2025099</v>
       </c>
@@ -9795,7 +9832,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="101" ht="28.5">
+    <row r="101" spans="1:14" ht="28.5">
       <c r="A101" s="54">
         <v>2025100</v>
       </c>
@@ -9825,7 +9862,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" ht="57.65" customHeight="1">
+    <row r="102" spans="1:14" ht="57.65" customHeight="1">
       <c r="A102" s="54">
         <v>2025101</v>
       </c>
@@ -9855,7 +9892,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="103" ht="15.5">
+    <row r="103" spans="1:14" ht="15.5">
       <c r="A103" s="54">
         <v>2025102</v>
       </c>
@@ -9873,10 +9910,10 @@
         <v>350</v>
       </c>
       <c r="I103" s="52">
-        <v>9.46</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="J103" s="52">
-        <v>9.46</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="K103" s="52" t="s">
         <v>234</v>
@@ -9885,7 +9922,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="104" ht="15.5">
+    <row r="104" spans="1:14" ht="15.5">
       <c r="A104" s="54">
         <v>2025103</v>
       </c>
@@ -9915,7 +9952,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="105" ht="140.5">
+    <row r="105" spans="1:14" ht="140.5">
       <c r="A105" s="54">
         <v>2025104</v>
       </c>
@@ -9959,7 +9996,7 @@
         <v>11.725266</v>
       </c>
     </row>
-    <row r="106" ht="42.5">
+    <row r="106" spans="1:14" ht="42.5">
       <c r="A106" s="54">
         <v>2025105</v>
       </c>
@@ -9985,7 +10022,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" ht="140.5">
+    <row r="107" spans="1:14" ht="140.5">
       <c r="A107" s="54">
         <v>2025106</v>
       </c>
@@ -10026,10 +10063,10 @@
         <v>363</v>
       </c>
       <c r="N107" s="47">
-        <v>4.714275</v>
-      </c>
-    </row>
-    <row r="108" ht="28.5">
+        <v>4.7142749999999998</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" ht="28.5">
       <c r="A108" s="54">
         <v>2025107</v>
       </c>
@@ -10055,7 +10092,7 @@
         <v>366</v>
       </c>
       <c r="I108" s="52">
-        <v>70.4</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="J108" s="52"/>
       <c r="K108" s="52" t="s">
@@ -10065,7 +10102,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" ht="210.5">
+    <row r="109" spans="1:14" ht="210.5">
       <c r="A109" s="54">
         <v>2025108</v>
       </c>
@@ -10104,10 +10141,10 @@
         <v>370</v>
       </c>
       <c r="N109" s="47">
-        <v>1.9341</v>
-      </c>
-    </row>
-    <row r="110" ht="140.5">
+        <v>1.9340999999999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" ht="140.5">
       <c r="A110" s="54">
         <v>2025109</v>
       </c>
@@ -10148,10 +10185,10 @@
         <v>374</v>
       </c>
       <c r="N110" s="47">
-        <v>31.64416</v>
-      </c>
-    </row>
-    <row r="111" ht="15.5">
+        <v>31.644159999999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" ht="15.5">
       <c r="A111" s="54">
         <v>2025110</v>
       </c>
@@ -10187,7 +10224,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="112" ht="154.5">
+    <row r="112" spans="1:14" ht="154.5">
       <c r="A112" s="54">
         <v>2025111</v>
       </c>
@@ -10228,10 +10265,10 @@
         <v>382</v>
       </c>
       <c r="N112" s="47">
-        <v>62.475728</v>
-      </c>
-    </row>
-    <row r="113" ht="28.5">
+        <v>62.475727999999997</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" ht="28.5">
       <c r="A113" s="54">
         <v>2025112</v>
       </c>
@@ -10267,7 +10304,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="114" ht="112.5">
+    <row r="114" spans="1:14" ht="112.5">
       <c r="A114" s="54">
         <v>2025113</v>
       </c>
@@ -10308,10 +10345,10 @@
         <v>389</v>
       </c>
       <c r="N114" s="47">
-        <v>21.986144</v>
-      </c>
-    </row>
-    <row r="115" ht="31">
+        <v>21.986143999999999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" ht="31">
       <c r="A115" s="54">
         <v>2025114</v>
       </c>
@@ -10347,7 +10384,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="116" ht="140.5">
+    <row r="116" spans="1:14" ht="140.5">
       <c r="A116" s="54">
         <v>2025115</v>
       </c>
@@ -10391,7 +10428,7 @@
         <v>19.849231</v>
       </c>
     </row>
-    <row r="117" ht="15.5">
+    <row r="117" spans="1:14" ht="15.5">
       <c r="A117" s="54">
         <v>2025116</v>
       </c>
@@ -10421,7 +10458,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" ht="15.5">
+    <row r="118" spans="1:14" ht="15.5">
       <c r="A118" s="54">
         <v>2025117</v>
       </c>
@@ -10459,14 +10496,13 @@
         <v>22</v>
       </c>
     </row>
-    <row r="119" ht="15.5">
+    <row r="119" spans="1:14" ht="15.5">
       <c r="A119" s="62"/>
       <c r="C119" s="62"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -10477,18 +10513,18 @@
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="32.08203125" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1" style="20"/>
-    <col min="4" max="4" width="23.83203125" customWidth="1" style="20"/>
+    <col min="3" max="3" width="14.33203125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="23.83203125" style="20" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="24.25" customWidth="1"/>
     <col min="7" max="7" width="44.33203125" customWidth="1"/>
-    <col min="8" max="8" width="14.08203125" customWidth="1" style="20"/>
-    <col min="11" max="11" width="21.25" customWidth="1" style="20"/>
-    <col min="12" max="12" width="18.5" customWidth="1" style="20"/>
+    <col min="8" max="8" width="14.08203125" style="20" customWidth="1"/>
+    <col min="11" max="11" width="21.25" style="20" customWidth="1"/>
+    <col min="12" max="12" width="18.5" style="20" customWidth="1"/>
     <col min="13" max="13" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5">
+    <row r="1" spans="1:12" ht="15.5">
       <c r="A1" s="21" t="s">
         <v>403</v>
       </c>
@@ -10520,7 +10556,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="2" s="19" customFormat="1">
+    <row r="2" spans="1:12" s="19" customFormat="1">
       <c r="A2" s="19">
         <v>1</v>
       </c>
@@ -10546,7 +10582,7 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
     </row>
-    <row r="3" s="19" customFormat="1">
+    <row r="3" spans="1:12" s="19" customFormat="1">
       <c r="A3" s="19">
         <v>2</v>
       </c>
@@ -10572,7 +10608,7 @@
       <c r="K3" s="20"/>
       <c r="L3" s="20"/>
     </row>
-    <row r="4" ht="15.5" s="19" customFormat="1">
+    <row r="4" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A4" s="19">
         <v>3</v>
       </c>
@@ -10598,7 +10634,7 @@
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
     </row>
-    <row r="5" s="19" customFormat="1">
+    <row r="5" spans="1:12" s="19" customFormat="1">
       <c r="A5" s="19">
         <v>4</v>
       </c>
@@ -10624,7 +10660,7 @@
       <c r="K5" s="20"/>
       <c r="L5" s="20"/>
     </row>
-    <row r="6" s="19" customFormat="1">
+    <row r="6" spans="1:12" s="19" customFormat="1">
       <c r="A6" s="19">
         <v>5</v>
       </c>
@@ -10650,7 +10686,7 @@
       <c r="K6" s="20"/>
       <c r="L6" s="20"/>
     </row>
-    <row r="7" s="19" customFormat="1">
+    <row r="7" spans="1:12" s="19" customFormat="1">
       <c r="A7" s="19">
         <v>6</v>
       </c>
@@ -10676,7 +10712,7 @@
       </c>
       <c r="L7" s="20"/>
     </row>
-    <row r="8" s="19" customFormat="1">
+    <row r="8" spans="1:12" s="19" customFormat="1">
       <c r="A8" s="19">
         <v>7</v>
       </c>
@@ -10702,7 +10738,7 @@
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
     </row>
-    <row r="9" s="19" customFormat="1">
+    <row r="9" spans="1:12" s="19" customFormat="1">
       <c r="A9" s="19">
         <v>8</v>
       </c>
@@ -10728,7 +10764,7 @@
       </c>
       <c r="L9" s="20"/>
     </row>
-    <row r="10" s="19" customFormat="1">
+    <row r="10" spans="1:12" s="19" customFormat="1">
       <c r="A10" s="19">
         <v>9</v>
       </c>
@@ -10754,7 +10790,7 @@
       </c>
       <c r="L10" s="20"/>
     </row>
-    <row r="11" s="19" customFormat="1">
+    <row r="11" spans="1:12" s="19" customFormat="1">
       <c r="A11" s="19">
         <v>10</v>
       </c>
@@ -10780,7 +10816,7 @@
       </c>
       <c r="L11" s="20"/>
     </row>
-    <row r="12" s="19" customFormat="1">
+    <row r="12" spans="1:12" s="19" customFormat="1">
       <c r="A12" s="19">
         <v>11</v>
       </c>
@@ -10806,7 +10842,7 @@
       </c>
       <c r="L12" s="20"/>
     </row>
-    <row r="13" s="19" customFormat="1">
+    <row r="13" spans="1:12" s="19" customFormat="1">
       <c r="A13" s="19">
         <v>12</v>
       </c>
@@ -10832,7 +10868,7 @@
       </c>
       <c r="L13" s="20"/>
     </row>
-    <row r="14" s="19" customFormat="1">
+    <row r="14" spans="1:12" s="19" customFormat="1">
       <c r="A14" s="19">
         <v>13</v>
       </c>
@@ -10854,11 +10890,11 @@
       </c>
       <c r="L14" s="20"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:12">
       <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" t="s">
         <v>46</v>
       </c>
       <c r="C15" s="26" t="s">
@@ -10871,11 +10907,11 @@
         <v>5110016</v>
       </c>
     </row>
-    <row r="16" ht="15.5">
+    <row r="16" spans="1:12" ht="15.5">
       <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" t="s">
         <v>209</v>
       </c>
       <c r="C16" s="26" t="s">
@@ -10887,7 +10923,7 @@
       <c r="F16" s="67" t="s">
         <v>457</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="G16" t="s">
         <v>446</v>
       </c>
       <c r="H16" s="68" t="s">
@@ -10900,11 +10936,11 @@
         <v>15828154009</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:12">
       <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" t="s">
         <v>459</v>
       </c>
       <c r="C17" s="26" t="s">
@@ -10917,7 +10953,7 @@
         <v>5090235</v>
       </c>
     </row>
-    <row r="18" s="19" customFormat="1">
+    <row r="18" spans="1:12" s="19" customFormat="1">
       <c r="A18" s="19">
         <v>17</v>
       </c>
@@ -10936,7 +10972,7 @@
       </c>
       <c r="L18" s="20"/>
     </row>
-    <row r="19" s="19" customFormat="1">
+    <row r="19" spans="1:12" s="19" customFormat="1">
       <c r="A19" s="19">
         <v>18</v>
       </c>
@@ -10955,7 +10991,7 @@
       </c>
       <c r="L19" s="20"/>
     </row>
-    <row r="20" s="19" customFormat="1">
+    <row r="20" spans="1:12" s="19" customFormat="1">
       <c r="A20" s="19">
         <v>19</v>
       </c>
@@ -10983,7 +11019,7 @@
       </c>
       <c r="L20" s="20"/>
     </row>
-    <row r="21" s="19" customFormat="1">
+    <row r="21" spans="1:12" s="19" customFormat="1">
       <c r="A21" s="19">
         <v>20</v>
       </c>
@@ -11010,7 +11046,7 @@
         <v>15828085356</v>
       </c>
     </row>
-    <row r="22" s="19" customFormat="1">
+    <row r="22" spans="1:12" s="19" customFormat="1">
       <c r="A22" s="19">
         <v>21</v>
       </c>
@@ -11034,11 +11070,11 @@
       <c r="K22" s="20"/>
       <c r="L22" s="20"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:12">
       <c r="A23" s="19">
         <v>22</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" t="s">
         <v>474</v>
       </c>
       <c r="C23" s="20" t="s">
@@ -11050,18 +11086,18 @@
       <c r="F23" s="67" t="s">
         <v>476</v>
       </c>
-      <c r="G23" s="0" t="s">
+      <c r="G23" t="s">
         <v>477</v>
       </c>
       <c r="K23" s="20">
         <v>4230032</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:12">
       <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" t="s">
         <v>478</v>
       </c>
       <c r="C24" s="20" t="s">
@@ -11076,18 +11112,18 @@
       <c r="F24" s="67" t="s">
         <v>480</v>
       </c>
-      <c r="G24" s="0" t="s">
+      <c r="G24" t="s">
         <v>467</v>
       </c>
       <c r="K24" s="20">
         <v>4230036</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:12">
       <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" t="s">
         <v>481</v>
       </c>
       <c r="C25" s="20" t="s">
@@ -11106,11 +11142,11 @@
         <v>15828139278</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:12">
       <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" t="s">
         <v>484</v>
       </c>
       <c r="C26" s="20" t="s">
@@ -11126,7 +11162,7 @@
         <v>4230437</v>
       </c>
     </row>
-    <row r="27" ht="15.5" s="19" customFormat="1">
+    <row r="27" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A27" s="19">
         <v>26</v>
       </c>
@@ -11152,7 +11188,7 @@
       </c>
       <c r="L27" s="20"/>
     </row>
-    <row r="28" s="19" customFormat="1">
+    <row r="28" spans="1:12" s="19" customFormat="1">
       <c r="A28" s="19">
         <v>27</v>
       </c>
@@ -11178,7 +11214,7 @@
       </c>
       <c r="L28" s="20"/>
     </row>
-    <row r="29" s="19" customFormat="1">
+    <row r="29" spans="1:12" s="19" customFormat="1">
       <c r="A29" s="19">
         <v>28</v>
       </c>
@@ -11204,7 +11240,7 @@
       </c>
       <c r="L29" s="20"/>
     </row>
-    <row r="30" s="19" customFormat="1">
+    <row r="30" spans="1:12" s="19" customFormat="1">
       <c r="A30" s="19">
         <v>29</v>
       </c>
@@ -11230,7 +11266,7 @@
       </c>
       <c r="L30" s="20"/>
     </row>
-    <row r="31" s="19" customFormat="1">
+    <row r="31" spans="1:12" s="19" customFormat="1">
       <c r="A31" s="19">
         <v>30</v>
       </c>
@@ -11256,7 +11292,7 @@
       </c>
       <c r="L31" s="20"/>
     </row>
-    <row r="32" s="19" customFormat="1">
+    <row r="32" spans="1:12" s="19" customFormat="1">
       <c r="A32" s="19">
         <v>31</v>
       </c>
@@ -11282,7 +11318,7 @@
       </c>
       <c r="L32" s="20"/>
     </row>
-    <row r="33" s="19" customFormat="1">
+    <row r="33" spans="1:12" s="19" customFormat="1">
       <c r="A33" s="19">
         <v>32</v>
       </c>
@@ -11308,7 +11344,7 @@
       </c>
       <c r="L33" s="20"/>
     </row>
-    <row r="34" s="19" customFormat="1">
+    <row r="34" spans="1:12" s="19" customFormat="1">
       <c r="A34" s="19">
         <v>33</v>
       </c>
@@ -11334,7 +11370,7 @@
       </c>
       <c r="L34" s="20"/>
     </row>
-    <row r="35" ht="15.5" s="19" customFormat="1">
+    <row r="35" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A35" s="19">
         <v>34</v>
       </c>
@@ -11360,7 +11396,7 @@
       </c>
       <c r="L35" s="20"/>
     </row>
-    <row r="36" s="19" customFormat="1">
+    <row r="36" spans="1:12" s="19" customFormat="1">
       <c r="A36" s="19">
         <v>35</v>
       </c>
@@ -11386,7 +11422,7 @@
       </c>
       <c r="L36" s="20"/>
     </row>
-    <row r="37" s="19" customFormat="1">
+    <row r="37" spans="1:12" s="19" customFormat="1">
       <c r="A37" s="19">
         <v>36</v>
       </c>
@@ -11412,7 +11448,7 @@
       </c>
       <c r="L37" s="20"/>
     </row>
-    <row r="38" s="19" customFormat="1">
+    <row r="38" spans="1:12" s="19" customFormat="1">
       <c r="A38" s="19">
         <v>37</v>
       </c>
@@ -11438,7 +11474,7 @@
       </c>
       <c r="L38" s="20"/>
     </row>
-    <row r="39" s="19" customFormat="1">
+    <row r="39" spans="1:12" s="19" customFormat="1">
       <c r="A39" s="19">
         <v>38</v>
       </c>
@@ -11464,7 +11500,7 @@
       </c>
       <c r="L39" s="20"/>
     </row>
-    <row r="40" ht="15.5" s="19" customFormat="1">
+    <row r="40" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A40" s="19">
         <v>39</v>
       </c>
@@ -11490,7 +11526,7 @@
       </c>
       <c r="L40" s="20"/>
     </row>
-    <row r="41" ht="15.5" s="19" customFormat="1">
+    <row r="41" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A41" s="19">
         <v>40</v>
       </c>
@@ -11516,7 +11552,7 @@
       </c>
       <c r="L41" s="20"/>
     </row>
-    <row r="42" ht="15.5" s="19" customFormat="1">
+    <row r="42" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A42" s="19">
         <v>41</v>
       </c>
@@ -11542,7 +11578,7 @@
       </c>
       <c r="L42" s="20"/>
     </row>
-    <row r="43" ht="15.5" s="19" customFormat="1">
+    <row r="43" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A43" s="19">
         <v>42</v>
       </c>
@@ -11568,7 +11604,7 @@
       </c>
       <c r="L43" s="20"/>
     </row>
-    <row r="44" s="19" customFormat="1">
+    <row r="44" spans="1:12" s="19" customFormat="1">
       <c r="A44" s="19">
         <v>43</v>
       </c>
@@ -11594,7 +11630,7 @@
       </c>
       <c r="L44" s="20"/>
     </row>
-    <row r="45" s="19" customFormat="1">
+    <row r="45" spans="1:12" s="19" customFormat="1">
       <c r="A45" s="19">
         <v>44</v>
       </c>
@@ -11620,7 +11656,7 @@
       </c>
       <c r="L45" s="20"/>
     </row>
-    <row r="46" ht="15.5" s="19" customFormat="1">
+    <row r="46" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A46" s="19">
         <v>45</v>
       </c>
@@ -11646,7 +11682,7 @@
       </c>
       <c r="L46" s="20"/>
     </row>
-    <row r="47" s="19" customFormat="1">
+    <row r="47" spans="1:12" s="19" customFormat="1">
       <c r="A47" s="19">
         <v>46</v>
       </c>
@@ -11672,7 +11708,7 @@
       </c>
       <c r="L47" s="20"/>
     </row>
-    <row r="48" s="19" customFormat="1">
+    <row r="48" spans="1:12" s="19" customFormat="1">
       <c r="A48" s="19">
         <v>47</v>
       </c>
@@ -11698,7 +11734,7 @@
       <c r="K48" s="20"/>
       <c r="L48" s="20"/>
     </row>
-    <row r="49" s="19" customFormat="1">
+    <row r="49" spans="1:15" s="19" customFormat="1">
       <c r="A49" s="19">
         <v>48</v>
       </c>
@@ -11725,7 +11761,7 @@
         <v>13880828042</v>
       </c>
     </row>
-    <row r="50" s="19" customFormat="1">
+    <row r="50" spans="1:15" s="19" customFormat="1">
       <c r="A50" s="19">
         <v>49</v>
       </c>
@@ -11760,7 +11796,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="51" s="19" customFormat="1">
+    <row r="51" spans="1:15" s="19" customFormat="1">
       <c r="A51" s="19">
         <v>50</v>
       </c>
@@ -11795,7 +11831,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="52" s="19" customFormat="1">
+    <row r="52" spans="1:15" s="19" customFormat="1">
       <c r="A52" s="19">
         <v>51</v>
       </c>
@@ -11830,7 +11866,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="53" s="19" customFormat="1">
+    <row r="53" spans="1:15" s="19" customFormat="1">
       <c r="A53" s="19">
         <v>52</v>
       </c>
@@ -11865,7 +11901,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="54" s="19" customFormat="1">
+    <row r="54" spans="1:15" s="19" customFormat="1">
       <c r="A54" s="19">
         <v>53</v>
       </c>
@@ -11900,7 +11936,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="55" s="19" customFormat="1">
+    <row r="55" spans="1:15" s="19" customFormat="1">
       <c r="A55" s="19">
         <v>54</v>
       </c>
@@ -11935,7 +11971,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="56" s="19" customFormat="1">
+    <row r="56" spans="1:15" s="19" customFormat="1">
       <c r="A56" s="19">
         <v>55</v>
       </c>
@@ -11961,7 +11997,7 @@
       <c r="K56" s="24"/>
       <c r="L56" s="24"/>
     </row>
-    <row r="57" s="19" customFormat="1">
+    <row r="57" spans="1:15" s="19" customFormat="1">
       <c r="A57" s="19">
         <v>56</v>
       </c>
@@ -11987,7 +12023,7 @@
       <c r="K57" s="24"/>
       <c r="L57" s="24"/>
     </row>
-    <row r="58" s="19" customFormat="1">
+    <row r="58" spans="1:15" s="19" customFormat="1">
       <c r="A58" s="19">
         <v>57</v>
       </c>
@@ -12013,7 +12049,7 @@
       <c r="K58" s="24"/>
       <c r="L58" s="24"/>
     </row>
-    <row r="59" s="19" customFormat="1">
+    <row r="59" spans="1:15" s="19" customFormat="1">
       <c r="A59" s="19">
         <v>58</v>
       </c>
@@ -12038,7 +12074,7 @@
       </c>
       <c r="L59" s="20"/>
     </row>
-    <row r="60" s="19" customFormat="1">
+    <row r="60" spans="1:15" s="19" customFormat="1">
       <c r="A60" s="19">
         <v>59</v>
       </c>
@@ -12069,7 +12105,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="61" ht="17.15" customHeight="1" s="19" customFormat="1">
+    <row r="61" spans="1:15" s="19" customFormat="1" ht="17.149999999999999" customHeight="1">
       <c r="A61" s="19">
         <v>60</v>
       </c>
@@ -12104,7 +12140,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="62" ht="28" s="19" customFormat="1">
+    <row r="62" spans="1:15" s="19" customFormat="1" ht="28">
       <c r="A62" s="19">
         <v>61</v>
       </c>
@@ -12130,7 +12166,7 @@
       <c r="K62" s="20"/>
       <c r="L62" s="20"/>
     </row>
-    <row r="63" s="19" customFormat="1">
+    <row r="63" spans="1:15" s="19" customFormat="1">
       <c r="A63" s="19">
         <v>62</v>
       </c>
@@ -12156,7 +12192,7 @@
       <c r="K63" s="26"/>
       <c r="L63" s="20"/>
     </row>
-    <row r="64" ht="15.5" s="19" customFormat="1">
+    <row r="64" spans="1:15" s="19" customFormat="1" ht="15.5">
       <c r="A64" s="19">
         <v>63</v>
       </c>
@@ -12181,7 +12217,7 @@
       </c>
       <c r="L64" s="20"/>
     </row>
-    <row r="65" s="19" customFormat="1">
+    <row r="65" spans="1:12" s="19" customFormat="1">
       <c r="A65" s="19">
         <v>64</v>
       </c>
@@ -12209,7 +12245,7 @@
       </c>
       <c r="L65" s="20"/>
     </row>
-    <row r="66" s="19" customFormat="1">
+    <row r="66" spans="1:12" s="19" customFormat="1">
       <c r="A66" s="19">
         <v>65</v>
       </c>
@@ -12228,7 +12264,7 @@
       </c>
       <c r="L66" s="20"/>
     </row>
-    <row r="67" s="19" customFormat="1">
+    <row r="67" spans="1:12" s="19" customFormat="1">
       <c r="A67" s="19">
         <v>66</v>
       </c>
@@ -12253,7 +12289,7 @@
       </c>
       <c r="L67" s="20"/>
     </row>
-    <row r="68" s="19" customFormat="1">
+    <row r="68" spans="1:12" s="19" customFormat="1">
       <c r="A68" s="19">
         <v>67</v>
       </c>
@@ -12272,7 +12308,7 @@
       </c>
       <c r="L68" s="20"/>
     </row>
-    <row r="69" ht="15.5" s="19" customFormat="1">
+    <row r="69" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A69" s="19">
         <v>68</v>
       </c>
@@ -12291,7 +12327,7 @@
       </c>
       <c r="L69" s="20"/>
     </row>
-    <row r="70" ht="15.5" s="19" customFormat="1">
+    <row r="70" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A70" s="19">
         <v>69</v>
       </c>
@@ -12316,7 +12352,7 @@
       </c>
       <c r="L70" s="20"/>
     </row>
-    <row r="71" ht="15.5" s="19" customFormat="1">
+    <row r="71" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A71" s="19">
         <v>70</v>
       </c>
@@ -12335,7 +12371,7 @@
       </c>
       <c r="L71" s="20"/>
     </row>
-    <row r="72" ht="15.5" s="19" customFormat="1">
+    <row r="72" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A72" s="19">
         <v>71</v>
       </c>
@@ -12360,7 +12396,7 @@
       </c>
       <c r="L72" s="20"/>
     </row>
-    <row r="73" ht="15.5" s="19" customFormat="1">
+    <row r="73" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A73" s="19">
         <v>72</v>
       </c>
@@ -12388,7 +12424,7 @@
       </c>
       <c r="L73" s="20"/>
     </row>
-    <row r="74" s="19" customFormat="1">
+    <row r="74" spans="1:12" s="19" customFormat="1">
       <c r="A74" s="19">
         <v>73</v>
       </c>
@@ -12414,7 +12450,7 @@
       <c r="K74" s="20"/>
       <c r="L74" s="20"/>
     </row>
-    <row r="75" s="19" customFormat="1">
+    <row r="75" spans="1:12" s="19" customFormat="1">
       <c r="A75" s="19">
         <v>74</v>
       </c>
@@ -12440,7 +12476,7 @@
       <c r="K75" s="20"/>
       <c r="L75" s="20"/>
     </row>
-    <row r="76" s="19" customFormat="1">
+    <row r="76" spans="1:12" s="19" customFormat="1">
       <c r="A76" s="19">
         <v>75</v>
       </c>
@@ -12466,7 +12502,7 @@
       <c r="K76" s="20"/>
       <c r="L76" s="20"/>
     </row>
-    <row r="77" s="19" customFormat="1">
+    <row r="77" spans="1:12" s="19" customFormat="1">
       <c r="A77" s="19">
         <v>76</v>
       </c>
@@ -12492,7 +12528,7 @@
       <c r="K77" s="20"/>
       <c r="L77" s="20"/>
     </row>
-    <row r="78" s="19" customFormat="1">
+    <row r="78" spans="1:12" s="19" customFormat="1">
       <c r="A78" s="19">
         <v>77</v>
       </c>
@@ -12518,7 +12554,7 @@
       <c r="K78" s="20"/>
       <c r="L78" s="20"/>
     </row>
-    <row r="79" s="19" customFormat="1">
+    <row r="79" spans="1:12" s="19" customFormat="1">
       <c r="A79" s="19">
         <v>78</v>
       </c>
@@ -12533,7 +12569,7 @@
       <c r="K79" s="20"/>
       <c r="L79" s="20"/>
     </row>
-    <row r="80" s="19" customFormat="1">
+    <row r="80" spans="1:12" s="19" customFormat="1">
       <c r="A80" s="19">
         <v>79</v>
       </c>
@@ -12561,7 +12597,7 @@
         <v>13550296530</v>
       </c>
     </row>
-    <row r="81" s="19" customFormat="1">
+    <row r="81" spans="1:12" s="19" customFormat="1">
       <c r="A81" s="19">
         <v>80</v>
       </c>
@@ -12589,7 +12625,7 @@
         <v>18380557907</v>
       </c>
     </row>
-    <row r="82" s="19" customFormat="1">
+    <row r="82" spans="1:12" s="19" customFormat="1">
       <c r="A82" s="19">
         <v>81</v>
       </c>
@@ -12617,7 +12653,7 @@
         <v>18980596322</v>
       </c>
     </row>
-    <row r="83" s="19" customFormat="1">
+    <row r="83" spans="1:12" s="19" customFormat="1">
       <c r="A83" s="19">
         <v>82</v>
       </c>
@@ -12645,7 +12681,7 @@
       </c>
       <c r="L83" s="20"/>
     </row>
-    <row r="84" ht="15.5" s="19" customFormat="1">
+    <row r="84" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A84" s="19">
         <v>83</v>
       </c>
@@ -12671,7 +12707,7 @@
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
     </row>
-    <row r="85" s="19" customFormat="1">
+    <row r="85" spans="1:12" s="19" customFormat="1">
       <c r="A85" s="19">
         <v>84</v>
       </c>
@@ -12699,7 +12735,7 @@
         <v>13980664852</v>
       </c>
     </row>
-    <row r="86" s="19" customFormat="1">
+    <row r="86" spans="1:12" s="19" customFormat="1">
       <c r="A86" s="19">
         <v>85</v>
       </c>
@@ -12727,7 +12763,7 @@
         <v>13808086286</v>
       </c>
     </row>
-    <row r="87" s="19" customFormat="1">
+    <row r="87" spans="1:12" s="19" customFormat="1">
       <c r="A87" s="19">
         <v>86</v>
       </c>
@@ -12755,7 +12791,7 @@
         <v>13608196859</v>
       </c>
     </row>
-    <row r="88" s="19" customFormat="1">
+    <row r="88" spans="1:12" s="19" customFormat="1">
       <c r="A88" s="19">
         <v>87</v>
       </c>
@@ -12783,7 +12819,7 @@
         <v>13658013287</v>
       </c>
     </row>
-    <row r="89" ht="15.5" s="19" customFormat="1">
+    <row r="89" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A89" s="19">
         <v>88</v>
       </c>
@@ -12811,7 +12847,7 @@
         <v>13648032216</v>
       </c>
     </row>
-    <row r="90" ht="15.5" s="19" customFormat="1">
+    <row r="90" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A90" s="19">
         <v>89</v>
       </c>
@@ -12839,7 +12875,7 @@
         <v>18108257155</v>
       </c>
     </row>
-    <row r="91" ht="15.5" s="19" customFormat="1">
+    <row r="91" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A91" s="19">
         <v>90</v>
       </c>
@@ -12867,7 +12903,7 @@
         <v>13908237000</v>
       </c>
     </row>
-    <row r="92" ht="15.5" s="19" customFormat="1">
+    <row r="92" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A92" s="19">
         <v>91</v>
       </c>
@@ -12895,7 +12931,7 @@
         <v>13801116402</v>
       </c>
     </row>
-    <row r="93" s="19" customFormat="1">
+    <row r="93" spans="1:12" s="19" customFormat="1">
       <c r="A93" s="19">
         <v>92</v>
       </c>
@@ -12921,7 +12957,7 @@
       <c r="K93" s="20"/>
       <c r="L93" s="20"/>
     </row>
-    <row r="94" s="19" customFormat="1">
+    <row r="94" spans="1:12" s="19" customFormat="1">
       <c r="A94" s="19">
         <v>93</v>
       </c>
@@ -12947,7 +12983,7 @@
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
     </row>
-    <row r="95" s="19" customFormat="1">
+    <row r="95" spans="1:12" s="19" customFormat="1">
       <c r="A95" s="19">
         <v>94</v>
       </c>
@@ -12973,7 +13009,7 @@
       <c r="K95" s="20"/>
       <c r="L95" s="20"/>
     </row>
-    <row r="96" s="19" customFormat="1">
+    <row r="96" spans="1:12" s="19" customFormat="1">
       <c r="A96" s="19">
         <v>95</v>
       </c>
@@ -12999,7 +13035,7 @@
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
     </row>
-    <row r="97" s="19" customFormat="1">
+    <row r="97" spans="1:12" s="19" customFormat="1">
       <c r="A97" s="19">
         <v>96</v>
       </c>
@@ -13025,7 +13061,7 @@
       <c r="K97" s="20"/>
       <c r="L97" s="20"/>
     </row>
-    <row r="98" s="19" customFormat="1">
+    <row r="98" spans="1:12" s="19" customFormat="1">
       <c r="A98" s="19">
         <v>97</v>
       </c>
@@ -13051,11 +13087,11 @@
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:12">
       <c r="A99" s="19">
         <v>98</v>
       </c>
-      <c r="B99" s="0" t="s">
+      <c r="B99" t="s">
         <v>760</v>
       </c>
       <c r="C99" s="20" t="s">
@@ -13064,24 +13100,24 @@
       <c r="D99" s="20">
         <v>4230116</v>
       </c>
-      <c r="E99" s="0" t="s">
+      <c r="E99" t="s">
         <v>761</v>
       </c>
       <c r="F99" s="67" t="s">
         <v>762</v>
       </c>
-      <c r="G99" s="0" t="s">
+      <c r="G99" t="s">
         <v>467</v>
       </c>
       <c r="K99" s="20">
         <v>4230116</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:12">
       <c r="A100" s="19">
         <v>99</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="B100" t="s">
         <v>763</v>
       </c>
       <c r="C100" s="20" t="s">
@@ -13096,7 +13132,7 @@
       <c r="F100" s="67" t="s">
         <v>765</v>
       </c>
-      <c r="G100" s="0" t="s">
+      <c r="G100" t="s">
         <v>467</v>
       </c>
       <c r="K100" s="20">
@@ -13106,11 +13142,11 @@
         <v>18980092808</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:12">
       <c r="A101" s="19">
         <v>100</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="B101" t="s">
         <v>766</v>
       </c>
       <c r="C101" s="20" t="s">
@@ -13122,26 +13158,26 @@
       <c r="F101" s="67" t="s">
         <v>767</v>
       </c>
-      <c r="G101" s="0" t="s">
+      <c r="G101" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="102" ht="15.5">
+    <row r="102" spans="1:12" ht="15.5">
       <c r="A102" s="19">
         <v>101</v>
       </c>
-      <c r="B102" s="0" t="s">
+      <c r="B102" t="s">
         <v>769</v>
       </c>
       <c r="C102" s="38" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:12">
       <c r="A103" s="19">
         <v>102</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="B103" t="s">
         <v>771</v>
       </c>
       <c r="C103" s="20" t="s">
@@ -13150,21 +13186,21 @@
       <c r="D103" s="19">
         <v>638391245</v>
       </c>
-      <c r="E103" s="0" t="s">
+      <c r="E103" t="s">
         <v>772</v>
       </c>
       <c r="F103" s="19">
         <v>638391245</v>
       </c>
-      <c r="G103" s="0" t="s">
+      <c r="G103" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:12">
       <c r="A104" s="19">
         <v>103</v>
       </c>
-      <c r="B104" s="0" t="s">
+      <c r="B104" t="s">
         <v>774</v>
       </c>
       <c r="C104" s="20" t="s">
@@ -13173,24 +13209,24 @@
       <c r="D104" s="20" t="s">
         <v>775</v>
       </c>
-      <c r="E104" s="0" t="s">
+      <c r="E104" t="s">
         <v>775</v>
       </c>
       <c r="F104" s="67" t="s">
         <v>776</v>
       </c>
-      <c r="G104" s="0" t="s">
+      <c r="G104" t="s">
         <v>777</v>
       </c>
       <c r="L104" s="20">
         <v>18328325926</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:12">
       <c r="A105" s="19">
         <v>104</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="B105" t="s">
         <v>778</v>
       </c>
       <c r="C105" s="20" t="s">
@@ -13205,15 +13241,15 @@
       <c r="F105" s="67" t="s">
         <v>780</v>
       </c>
-      <c r="G105" s="0" t="s">
+      <c r="G105" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:12">
       <c r="A106" s="19">
         <v>105</v>
       </c>
-      <c r="B106" s="0" t="s">
+      <c r="B106" t="s">
         <v>782</v>
       </c>
       <c r="C106" s="20" t="s">
@@ -13228,15 +13264,15 @@
       <c r="F106" s="67" t="s">
         <v>784</v>
       </c>
-      <c r="G106" s="0" t="s">
+      <c r="G106" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:12">
       <c r="A107" s="19">
         <v>106</v>
       </c>
-      <c r="B107" s="0" t="s">
+      <c r="B107" t="s">
         <v>785</v>
       </c>
       <c r="C107" s="20" t="s">
@@ -13251,15 +13287,15 @@
       <c r="F107" s="67" t="s">
         <v>787</v>
       </c>
-      <c r="G107" s="0" t="s">
+      <c r="G107" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:12">
       <c r="A108" s="19">
         <v>107</v>
       </c>
-      <c r="B108" s="0" t="s">
+      <c r="B108" t="s">
         <v>788</v>
       </c>
       <c r="C108" s="20" t="s">
@@ -13274,15 +13310,15 @@
       <c r="F108" s="67" t="s">
         <v>790</v>
       </c>
-      <c r="G108" s="0" t="s">
+      <c r="G108" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:12">
       <c r="A109" s="19">
         <v>108</v>
       </c>
-      <c r="B109" s="0" t="s">
+      <c r="B109" t="s">
         <v>791</v>
       </c>
       <c r="C109" s="20" t="s">
@@ -13297,11 +13333,11 @@
       <c r="F109" s="67" t="s">
         <v>793</v>
       </c>
-      <c r="G109" s="0" t="s">
+      <c r="G109" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="110" ht="15.5" s="19" customFormat="1">
+    <row r="110" spans="1:12" s="19" customFormat="1" ht="15.5">
       <c r="A110" s="19">
         <v>109</v>
       </c>
@@ -13327,11 +13363,11 @@
       </c>
       <c r="L110" s="20"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:12">
       <c r="A111" s="19">
         <v>110</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="B111" t="s">
         <v>797</v>
       </c>
       <c r="C111" s="20" t="s">
@@ -13343,18 +13379,18 @@
       <c r="F111" s="67" t="s">
         <v>798</v>
       </c>
-      <c r="G111" s="0" t="s">
+      <c r="G111" t="s">
         <v>799</v>
       </c>
       <c r="H111" s="68" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:12">
       <c r="A112" s="19">
         <v>111</v>
       </c>
-      <c r="B112" s="0" t="s">
+      <c r="B112" t="s">
         <v>801</v>
       </c>
       <c r="C112" s="20" t="s">
@@ -13366,15 +13402,15 @@
       <c r="F112" s="67" t="s">
         <v>802</v>
       </c>
-      <c r="G112" s="0" t="s">
+      <c r="G112" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:12">
       <c r="A113" s="19">
         <v>112</v>
       </c>
-      <c r="B113" s="0" t="s">
+      <c r="B113" t="s">
         <v>804</v>
       </c>
       <c r="C113" s="26" t="s">
@@ -13389,7 +13425,7 @@
       <c r="F113" s="67" t="s">
         <v>807</v>
       </c>
-      <c r="G113" s="0" t="s">
+      <c r="G113" t="s">
         <v>808</v>
       </c>
       <c r="K113" s="68" t="s">
@@ -13399,11 +13435,11 @@
         <v>17852935846</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:12">
       <c r="A114" s="19">
         <v>113</v>
       </c>
-      <c r="B114" s="0" t="s">
+      <c r="B114" t="s">
         <v>809</v>
       </c>
       <c r="C114" s="26" t="s">
@@ -13418,18 +13454,18 @@
       <c r="F114" s="67" t="s">
         <v>812</v>
       </c>
-      <c r="G114" s="0" t="s">
+      <c r="G114" t="s">
         <v>813</v>
       </c>
       <c r="K114" s="68" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:12">
       <c r="A115" s="19">
         <v>114</v>
       </c>
-      <c r="B115" s="0" t="s">
+      <c r="B115" t="s">
         <v>814</v>
       </c>
       <c r="C115" s="26" t="s">
@@ -13444,7 +13480,7 @@
       <c r="F115" s="67" t="s">
         <v>817</v>
       </c>
-      <c r="G115" s="0" t="s">
+      <c r="G115" t="s">
         <v>537</v>
       </c>
       <c r="K115" s="68" t="s">
@@ -13454,11 +13490,11 @@
         <v>18380269853</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:12">
       <c r="A116" s="19">
         <v>115</v>
       </c>
-      <c r="B116" s="0" t="s">
+      <c r="B116" t="s">
         <v>818</v>
       </c>
       <c r="C116" s="20" t="s">
@@ -13473,15 +13509,15 @@
       <c r="F116" s="67" t="s">
         <v>820</v>
       </c>
-      <c r="G116" s="0" t="s">
+      <c r="G116" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="117" ht="15.5">
+    <row r="117" spans="1:12" ht="15.5">
       <c r="A117" s="19">
         <v>116</v>
       </c>
-      <c r="B117" s="0" t="s">
+      <c r="B117" t="s">
         <v>822</v>
       </c>
       <c r="C117" s="26" t="s">
@@ -13493,18 +13529,18 @@
       <c r="F117" s="67" t="s">
         <v>824</v>
       </c>
-      <c r="G117" s="0" t="s">
+      <c r="G117" t="s">
         <v>825</v>
       </c>
       <c r="K117" s="28" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:12">
       <c r="A118" s="19">
         <v>117</v>
       </c>
-      <c r="B118" s="0" t="s">
+      <c r="B118" t="s">
         <v>826</v>
       </c>
       <c r="C118" s="20" t="s">
@@ -13513,32 +13549,32 @@
       <c r="D118" s="20" t="s">
         <v>827</v>
       </c>
-      <c r="E118" s="0" t="s">
+      <c r="E118" t="s">
         <v>827</v>
       </c>
       <c r="F118" s="67" t="s">
         <v>828</v>
       </c>
-      <c r="G118" s="0" t="s">
+      <c r="G118" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="119" ht="15.5">
+    <row r="119" spans="1:12" ht="15.5">
       <c r="A119" s="19">
         <v>118</v>
       </c>
-      <c r="B119" s="0" t="s">
+      <c r="B119" t="s">
         <v>830</v>
       </c>
       <c r="C119" s="38" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:12">
       <c r="A120" s="19">
         <v>119</v>
       </c>
-      <c r="B120" s="0" t="s">
+      <c r="B120" t="s">
         <v>831</v>
       </c>
       <c r="C120" s="20" t="s">
@@ -13547,21 +13583,21 @@
       <c r="D120" s="20" t="s">
         <v>832</v>
       </c>
-      <c r="E120" s="0" t="s">
+      <c r="E120" t="s">
         <v>832</v>
       </c>
       <c r="F120" s="67" t="s">
         <v>833</v>
       </c>
-      <c r="G120" s="0" t="s">
+      <c r="G120" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:12">
       <c r="A121" s="19">
         <v>120</v>
       </c>
-      <c r="B121" s="0" t="s">
+      <c r="B121" t="s">
         <v>835</v>
       </c>
       <c r="C121" s="20" t="s">
@@ -13576,15 +13612,15 @@
       <c r="F121" s="67" t="s">
         <v>837</v>
       </c>
-      <c r="G121" s="0" t="s">
+      <c r="G121" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:12">
       <c r="A122" s="19">
         <v>121</v>
       </c>
-      <c r="B122" s="0" t="s">
+      <c r="B122" t="s">
         <v>839</v>
       </c>
       <c r="C122" s="20" t="s">
@@ -13599,15 +13635,15 @@
       <c r="F122" s="67" t="s">
         <v>841</v>
       </c>
-      <c r="G122" s="0" t="s">
+      <c r="G122" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:12">
       <c r="A123" s="19">
         <v>122</v>
       </c>
-      <c r="B123" s="0" t="s">
+      <c r="B123" t="s">
         <v>843</v>
       </c>
       <c r="C123" s="20" t="s">
@@ -13622,15 +13658,15 @@
       <c r="F123" s="67" t="s">
         <v>845</v>
       </c>
-      <c r="G123" s="0" t="s">
+      <c r="G123" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:12">
       <c r="A124" s="19">
         <v>123</v>
       </c>
-      <c r="B124" s="0" t="s">
+      <c r="B124" t="s">
         <v>847</v>
       </c>
       <c r="C124" s="20" t="s">
@@ -13645,15 +13681,15 @@
       <c r="F124" s="67" t="s">
         <v>849</v>
       </c>
-      <c r="G124" s="0" t="s">
+      <c r="G124" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:12">
       <c r="A125" s="19">
         <v>124</v>
       </c>
-      <c r="B125" s="0" t="s">
+      <c r="B125" t="s">
         <v>851</v>
       </c>
       <c r="C125" s="20" t="s">
@@ -13668,15 +13704,15 @@
       <c r="F125" s="67" t="s">
         <v>853</v>
       </c>
-      <c r="G125" s="0" t="s">
+      <c r="G125" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:12">
       <c r="A126" s="19">
         <v>125</v>
       </c>
-      <c r="B126" s="0" t="s">
+      <c r="B126" t="s">
         <v>854</v>
       </c>
       <c r="C126" s="20" t="s">
@@ -13691,18 +13727,18 @@
       <c r="F126" s="67" t="s">
         <v>856</v>
       </c>
-      <c r="G126" s="0" t="s">
+      <c r="G126" t="s">
         <v>857</v>
       </c>
       <c r="H126" s="68" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:12">
       <c r="A127" s="19">
         <v>126</v>
       </c>
-      <c r="B127" s="0" t="s">
+      <c r="B127" t="s">
         <v>859</v>
       </c>
       <c r="C127" s="20" t="s">
@@ -13714,18 +13750,18 @@
       <c r="E127" s="67" t="s">
         <v>860</v>
       </c>
-      <c r="F127" s="0" t="s">
+      <c r="F127" t="s">
         <v>861</v>
       </c>
-      <c r="G127" s="0" t="s">
+      <c r="G127" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:12">
       <c r="A128" s="19">
         <v>127</v>
       </c>
-      <c r="B128" s="0" t="s">
+      <c r="B128" t="s">
         <v>862</v>
       </c>
       <c r="C128" s="20" t="s">
@@ -13737,21 +13773,21 @@
       <c r="E128" s="67" t="s">
         <v>863</v>
       </c>
-      <c r="F128" s="0" t="s">
+      <c r="F128" t="s">
         <v>864</v>
       </c>
-      <c r="G128" s="0" t="s">
+      <c r="G128" t="s">
         <v>865</v>
       </c>
       <c r="L128" s="20">
         <v>13908033153</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:12">
       <c r="A129" s="19">
         <v>128</v>
       </c>
-      <c r="B129" s="0" t="s">
+      <c r="B129" t="s">
         <v>866</v>
       </c>
       <c r="C129" s="20" t="s">
@@ -13766,18 +13802,18 @@
       <c r="F129" s="67" t="s">
         <v>868</v>
       </c>
-      <c r="G129" s="0" t="s">
+      <c r="G129" t="s">
         <v>869</v>
       </c>
       <c r="L129" s="20">
         <v>13882183189</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:12">
       <c r="A130" s="19">
         <v>129</v>
       </c>
-      <c r="B130" s="0" t="s">
+      <c r="B130" t="s">
         <v>870</v>
       </c>
       <c r="C130" s="20" t="s">
@@ -13789,21 +13825,21 @@
       <c r="E130" s="67" t="s">
         <v>871</v>
       </c>
-      <c r="F130" s="0" t="s">
+      <c r="F130" t="s">
         <v>872</v>
       </c>
-      <c r="G130" s="0" t="s">
+      <c r="G130" t="s">
         <v>873</v>
       </c>
       <c r="L130" s="20">
         <v>18681695840</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:12">
       <c r="A131" s="19">
         <v>130</v>
       </c>
-      <c r="B131" s="0" t="s">
+      <c r="B131" t="s">
         <v>874</v>
       </c>
       <c r="C131" s="20" t="s">
@@ -13815,21 +13851,21 @@
       <c r="E131" s="67" t="s">
         <v>875</v>
       </c>
-      <c r="F131" s="0" t="s">
+      <c r="F131" t="s">
         <v>876</v>
       </c>
-      <c r="G131" s="0" t="s">
+      <c r="G131" t="s">
         <v>877</v>
       </c>
       <c r="L131" s="20">
         <v>13684011028</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:12">
       <c r="A132" s="19">
         <v>131</v>
       </c>
-      <c r="B132" s="0" t="s">
+      <c r="B132" t="s">
         <v>878</v>
       </c>
       <c r="C132" s="20" t="s">
@@ -13841,21 +13877,21 @@
       <c r="E132" s="67" t="s">
         <v>879</v>
       </c>
-      <c r="F132" s="0" t="s">
+      <c r="F132" t="s">
         <v>880</v>
       </c>
-      <c r="G132" s="0" t="s">
+      <c r="G132" t="s">
         <v>881</v>
       </c>
       <c r="L132" s="20">
         <v>13980967180</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:12">
       <c r="A133" s="19">
         <v>132</v>
       </c>
-      <c r="B133" s="0" t="s">
+      <c r="B133" t="s">
         <v>782</v>
       </c>
       <c r="C133" s="20" t="s">
@@ -13864,24 +13900,24 @@
       <c r="D133" s="20" t="s">
         <v>882</v>
       </c>
-      <c r="E133" s="0" t="s">
+      <c r="E133" t="s">
         <v>882</v>
       </c>
-      <c r="F133" s="0" t="s">
+      <c r="F133" t="s">
         <v>883</v>
       </c>
-      <c r="G133" s="0" t="s">
+      <c r="G133" t="s">
         <v>884</v>
       </c>
       <c r="L133" s="20">
         <v>15908180960</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:12">
       <c r="A134" s="19">
         <v>133</v>
       </c>
-      <c r="B134" s="0" t="s">
+      <c r="B134" t="s">
         <v>885</v>
       </c>
       <c r="C134" s="20" t="s">
@@ -13893,21 +13929,21 @@
       <c r="E134" s="67" t="s">
         <v>886</v>
       </c>
-      <c r="F134" s="0" t="s">
+      <c r="F134" t="s">
         <v>887</v>
       </c>
-      <c r="G134" s="0" t="s">
+      <c r="G134" t="s">
         <v>888</v>
       </c>
       <c r="L134" s="20">
         <v>18618193010</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:12">
       <c r="A135" s="19">
         <v>134</v>
       </c>
-      <c r="B135" s="0" t="s">
+      <c r="B135" t="s">
         <v>889</v>
       </c>
       <c r="C135" s="26" t="s">
@@ -13916,13 +13952,13 @@
       <c r="D135" s="68" t="s">
         <v>890</v>
       </c>
-      <c r="E135" s="0" t="s">
+      <c r="E135" t="s">
         <v>891</v>
       </c>
-      <c r="F135" s="0" t="s">
+      <c r="F135" t="s">
         <v>892</v>
       </c>
-      <c r="G135" s="0" t="s">
+      <c r="G135" t="s">
         <v>888</v>
       </c>
       <c r="K135" s="68" t="s">
@@ -13932,11 +13968,11 @@
         <v>13908013979</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:12">
       <c r="A136" s="19">
         <v>135</v>
       </c>
-      <c r="B136" s="0" t="s">
+      <c r="B136" t="s">
         <v>893</v>
       </c>
       <c r="C136" s="20" t="s">
@@ -13945,21 +13981,21 @@
       <c r="D136" s="67" t="s">
         <v>894</v>
       </c>
-      <c r="E136" s="0" t="s">
+      <c r="E136" t="s">
         <v>895</v>
       </c>
       <c r="F136" s="67" t="s">
         <v>894</v>
       </c>
-      <c r="G136" s="0" t="s">
+      <c r="G136" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:12">
       <c r="A137" s="19">
         <v>136</v>
       </c>
-      <c r="B137" s="0" t="s">
+      <c r="B137" t="s">
         <v>897</v>
       </c>
       <c r="C137" s="20" t="s">
@@ -13974,18 +14010,18 @@
       <c r="F137" s="67" t="s">
         <v>899</v>
       </c>
-      <c r="G137" s="0" t="s">
+      <c r="G137" t="s">
         <v>900</v>
       </c>
       <c r="L137" s="20">
         <v>15883506572</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:12">
       <c r="A138" s="19">
         <v>137</v>
       </c>
-      <c r="B138" s="0" t="s">
+      <c r="B138" t="s">
         <v>901</v>
       </c>
       <c r="C138" s="26" t="s">
@@ -14001,11 +14037,11 @@
         <v>18349139474</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:12">
       <c r="A139" s="19">
         <v>138</v>
       </c>
-      <c r="B139" s="0" t="s">
+      <c r="B139" t="s">
         <v>903</v>
       </c>
       <c r="C139" s="26" t="s">
@@ -14018,11 +14054,11 @@
         <v>904</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:12">
       <c r="A140" s="19">
         <v>139</v>
       </c>
-      <c r="B140" s="0" t="s">
+      <c r="B140" t="s">
         <v>905</v>
       </c>
       <c r="C140" s="26" t="s">
@@ -14035,11 +14071,11 @@
         <v>906</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:12">
       <c r="A141" s="19">
         <v>140</v>
       </c>
-      <c r="B141" s="0" t="s">
+      <c r="B141" t="s">
         <v>907</v>
       </c>
       <c r="C141" s="26" t="s">
@@ -14051,18 +14087,18 @@
       <c r="F141" s="67" t="s">
         <v>909</v>
       </c>
-      <c r="G141" s="0" t="s">
+      <c r="G141" t="s">
         <v>910</v>
       </c>
       <c r="K141" s="68" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:12">
       <c r="A142" s="19">
         <v>141</v>
       </c>
-      <c r="B142" s="0" t="s">
+      <c r="B142" t="s">
         <v>911</v>
       </c>
       <c r="C142" s="26" t="s">
@@ -14074,18 +14110,18 @@
       <c r="F142" s="67" t="s">
         <v>913</v>
       </c>
-      <c r="G142" s="0" t="s">
+      <c r="G142" t="s">
         <v>914</v>
       </c>
       <c r="K142" s="68" t="s">
         <v>912</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:12">
       <c r="A143" s="19">
         <v>142</v>
       </c>
-      <c r="B143" s="0" t="s">
+      <c r="B143" t="s">
         <v>915</v>
       </c>
       <c r="C143" s="26" t="s">
@@ -14097,7 +14133,7 @@
       <c r="F143" s="67" t="s">
         <v>917</v>
       </c>
-      <c r="G143" s="0" t="s">
+      <c r="G143" t="s">
         <v>918</v>
       </c>
       <c r="K143" s="68" t="s">
@@ -14107,11 +14143,11 @@
         <v>13880985377</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:12">
       <c r="A144" s="19">
         <v>143</v>
       </c>
-      <c r="B144" s="0" t="s">
+      <c r="B144" t="s">
         <v>919</v>
       </c>
       <c r="C144" s="26" t="s">
@@ -14123,7 +14159,7 @@
       <c r="F144" s="67" t="s">
         <v>921</v>
       </c>
-      <c r="G144" s="0" t="s">
+      <c r="G144" t="s">
         <v>922</v>
       </c>
       <c r="K144" s="68" t="s">
@@ -14133,11 +14169,11 @@
         <v>19829705092</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:12">
       <c r="A145" s="19">
         <v>144</v>
       </c>
-      <c r="B145" s="0" t="s">
+      <c r="B145" t="s">
         <v>923</v>
       </c>
       <c r="C145" s="26" t="s">
@@ -14149,18 +14185,18 @@
       <c r="F145" s="67" t="s">
         <v>925</v>
       </c>
-      <c r="G145" s="0" t="s">
+      <c r="G145" t="s">
         <v>926</v>
       </c>
       <c r="K145" s="68" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:12">
       <c r="A146" s="19">
         <v>145</v>
       </c>
-      <c r="B146" s="0" t="s">
+      <c r="B146" t="s">
         <v>927</v>
       </c>
       <c r="C146" s="26" t="s">
@@ -14172,18 +14208,18 @@
       <c r="F146" s="67" t="s">
         <v>929</v>
       </c>
-      <c r="G146" s="0" t="s">
+      <c r="G146" t="s">
         <v>930</v>
       </c>
       <c r="K146" s="68" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:12">
       <c r="A147" s="19">
         <v>146</v>
       </c>
-      <c r="B147" s="0" t="s">
+      <c r="B147" t="s">
         <v>931</v>
       </c>
       <c r="C147" s="26" t="s">
@@ -14195,7 +14231,7 @@
       <c r="F147" s="67" t="s">
         <v>933</v>
       </c>
-      <c r="G147" s="0" t="s">
+      <c r="G147" t="s">
         <v>934</v>
       </c>
       <c r="K147" s="68" t="s">
@@ -14205,11 +14241,11 @@
         <v>13881103012</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:12">
       <c r="A148" s="19">
         <v>147</v>
       </c>
-      <c r="B148" s="0" t="s">
+      <c r="B148" t="s">
         <v>935</v>
       </c>
       <c r="C148" s="26" t="s">
@@ -14228,11 +14264,11 @@
         <v>13281117026</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:12">
       <c r="A149" s="19">
         <v>148</v>
       </c>
-      <c r="B149" s="0" t="s">
+      <c r="B149" t="s">
         <v>938</v>
       </c>
       <c r="C149" s="20" t="s">
@@ -14247,15 +14283,15 @@
       <c r="F149" s="67" t="s">
         <v>940</v>
       </c>
-      <c r="G149" s="0" t="s">
+      <c r="G149" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:12">
       <c r="A150" s="19">
         <v>149</v>
       </c>
-      <c r="B150" s="0" t="s">
+      <c r="B150" t="s">
         <v>942</v>
       </c>
       <c r="C150" s="26" t="s">
@@ -14268,11 +14304,11 @@
         <v>943</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:12">
       <c r="A151" s="19">
         <v>150</v>
       </c>
-      <c r="B151" s="0" t="s">
+      <c r="B151" t="s">
         <v>944</v>
       </c>
       <c r="C151" s="20" t="s">
@@ -14284,15 +14320,15 @@
       <c r="F151" s="67" t="s">
         <v>945</v>
       </c>
-      <c r="G151" s="0" t="s">
+      <c r="G151" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:12">
       <c r="A152" s="19">
         <v>151</v>
       </c>
-      <c r="B152" s="0" t="s">
+      <c r="B152" t="s">
         <v>947</v>
       </c>
       <c r="C152" s="26" t="s">
@@ -14308,7 +14344,7 @@
         <v>6240022</v>
       </c>
     </row>
-    <row r="153" ht="28">
+    <row r="153" spans="1:12" ht="28">
       <c r="A153" s="19">
         <v>152</v>
       </c>
@@ -14319,7 +14355,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:12">
       <c r="A154" s="19">
         <v>153</v>
       </c>
@@ -14335,18 +14371,18 @@
       <c r="F154" s="67" t="s">
         <v>952</v>
       </c>
-      <c r="G154" s="0" t="s">
+      <c r="G154" t="s">
         <v>530</v>
       </c>
       <c r="K154" s="68" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:12">
       <c r="A155" s="19">
         <v>154</v>
       </c>
-      <c r="B155" s="0" t="s">
+      <c r="B155" t="s">
         <v>953</v>
       </c>
       <c r="C155" s="20" t="s">
@@ -14355,24 +14391,24 @@
       <c r="D155" s="20" t="s">
         <v>954</v>
       </c>
-      <c r="E155" s="0" t="s">
+      <c r="E155" t="s">
         <v>954</v>
       </c>
       <c r="F155" s="67" t="s">
         <v>955</v>
       </c>
-      <c r="G155" s="0" t="s">
+      <c r="G155" t="s">
         <v>956</v>
       </c>
       <c r="K155" s="20">
         <v>18382957777</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:12">
       <c r="A156" s="19">
         <v>155</v>
       </c>
-      <c r="B156" s="0" t="s">
+      <c r="B156" t="s">
         <v>957</v>
       </c>
       <c r="C156" s="20" t="s">
@@ -14387,18 +14423,18 @@
       <c r="F156" s="67" t="s">
         <v>959</v>
       </c>
-      <c r="G156" s="0" t="s">
+      <c r="G156" t="s">
         <v>960</v>
       </c>
       <c r="K156" s="20">
         <v>17381890296</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:12">
       <c r="A157" s="19">
         <v>156</v>
       </c>
-      <c r="B157" s="0" t="s">
+      <c r="B157" t="s">
         <v>961</v>
       </c>
       <c r="C157" s="20" t="s">
@@ -14413,7 +14449,7 @@
       <c r="F157" s="67" t="s">
         <v>963</v>
       </c>
-      <c r="G157" s="0" t="s">
+      <c r="G157" t="s">
         <v>964</v>
       </c>
       <c r="K157" s="20">
@@ -14423,11 +14459,11 @@
         <v>947</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:12">
       <c r="A158" s="19">
         <v>157</v>
       </c>
-      <c r="B158" s="0" t="s">
+      <c r="B158" t="s">
         <v>965</v>
       </c>
       <c r="C158" s="20" t="s">
@@ -14436,21 +14472,21 @@
       <c r="D158" s="20" t="s">
         <v>966</v>
       </c>
-      <c r="E158" s="0" t="s">
+      <c r="E158" t="s">
         <v>966</v>
       </c>
       <c r="F158" s="67" t="s">
         <v>967</v>
       </c>
-      <c r="G158" s="0" t="s">
+      <c r="G158" t="s">
         <v>968</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:12">
       <c r="A159" s="19">
         <v>158</v>
       </c>
-      <c r="B159" s="0" t="s">
+      <c r="B159" t="s">
         <v>969</v>
       </c>
       <c r="C159" s="20" t="s">
@@ -14465,18 +14501,18 @@
       <c r="F159" s="67" t="s">
         <v>971</v>
       </c>
-      <c r="G159" s="0" t="s">
+      <c r="G159" t="s">
         <v>972</v>
       </c>
       <c r="K159" s="20">
         <v>18349260951</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:12">
       <c r="A160" s="19">
         <v>159</v>
       </c>
-      <c r="B160" s="0" t="s">
+      <c r="B160" t="s">
         <v>973</v>
       </c>
       <c r="C160" s="20" t="s">
@@ -14485,24 +14521,24 @@
       <c r="D160" s="20" t="s">
         <v>974</v>
       </c>
-      <c r="E160" s="0" t="s">
+      <c r="E160" t="s">
         <v>974</v>
       </c>
       <c r="F160" s="67" t="s">
         <v>975</v>
       </c>
-      <c r="G160" s="0" t="s">
+      <c r="G160" t="s">
         <v>972</v>
       </c>
       <c r="K160" s="20">
         <v>13688479908</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:13">
       <c r="A161" s="19">
         <v>160</v>
       </c>
-      <c r="B161" s="0" t="s">
+      <c r="B161" t="s">
         <v>976</v>
       </c>
       <c r="C161" s="20" t="s">
@@ -14517,21 +14553,21 @@
       <c r="F161" s="67" t="s">
         <v>978</v>
       </c>
-      <c r="G161" s="0" t="s">
+      <c r="G161" t="s">
         <v>972</v>
       </c>
       <c r="K161" s="20">
         <v>18030512239</v>
       </c>
-      <c r="M161" s="0" t="s">
+      <c r="M161" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:13">
       <c r="A162" s="19">
         <v>161</v>
       </c>
-      <c r="B162" s="0" t="s">
+      <c r="B162" t="s">
         <v>980</v>
       </c>
       <c r="C162" s="20" t="s">
@@ -14546,15 +14582,15 @@
       <c r="F162" s="67" t="s">
         <v>982</v>
       </c>
-      <c r="G162" s="0" t="s">
+      <c r="G162" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:13">
       <c r="A163" s="19">
         <v>162</v>
       </c>
-      <c r="B163" s="0" t="s">
+      <c r="B163" t="s">
         <v>984</v>
       </c>
       <c r="C163" s="20" t="s">
@@ -14566,15 +14602,15 @@
       <c r="F163" s="67" t="s">
         <v>985</v>
       </c>
-      <c r="G163" s="0" t="s">
+      <c r="G163" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:13">
       <c r="A164" s="19">
         <v>163</v>
       </c>
-      <c r="B164" s="0" t="s">
+      <c r="B164" t="s">
         <v>986</v>
       </c>
       <c r="C164" s="20" t="s">
@@ -14587,11 +14623,11 @@
         <v>987</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:13">
       <c r="A165" s="19">
         <v>164</v>
       </c>
-      <c r="B165" s="0" t="s">
+      <c r="B165" t="s">
         <v>988</v>
       </c>
       <c r="C165" s="20" t="s">
@@ -14606,18 +14642,18 @@
       <c r="F165" s="67" t="s">
         <v>990</v>
       </c>
-      <c r="G165" s="0" t="s">
+      <c r="G165" t="s">
         <v>991</v>
       </c>
       <c r="L165" s="20">
         <v>13548110233</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:13">
       <c r="A166" s="19">
         <v>165</v>
       </c>
-      <c r="B166" s="0" t="s">
+      <c r="B166" t="s">
         <v>992</v>
       </c>
       <c r="C166" s="20" t="s">
@@ -14630,11 +14666,11 @@
         <v>993</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:13">
       <c r="A167" s="19">
         <v>166</v>
       </c>
-      <c r="B167" s="0" t="s">
+      <c r="B167" t="s">
         <v>994</v>
       </c>
       <c r="C167" s="20" t="s">
@@ -14647,11 +14683,11 @@
         <v>995</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:13">
       <c r="A168" s="19">
         <v>167</v>
       </c>
-      <c r="B168" s="0" t="s">
+      <c r="B168" t="s">
         <v>996</v>
       </c>
       <c r="C168" s="20" t="s">
@@ -14664,11 +14700,11 @@
         <v>997</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:13">
       <c r="A169" s="19">
         <v>168</v>
       </c>
-      <c r="B169" s="0" t="s">
+      <c r="B169" t="s">
         <v>998</v>
       </c>
       <c r="C169" s="20" t="s">
@@ -14681,11 +14717,11 @@
         <v>999</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:13">
       <c r="A170" s="19">
         <v>169</v>
       </c>
-      <c r="B170" s="0" t="s">
+      <c r="B170" t="s">
         <v>1000</v>
       </c>
       <c r="C170" s="20" t="s">
@@ -14700,18 +14736,18 @@
       <c r="F170" s="67" t="s">
         <v>1002</v>
       </c>
-      <c r="G170" s="0" t="s">
+      <c r="G170" t="s">
         <v>641</v>
       </c>
       <c r="L170" s="20">
         <v>13881939276</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:13">
       <c r="A171" s="19">
         <v>170</v>
       </c>
-      <c r="B171" s="0" t="s">
+      <c r="B171" t="s">
         <v>1003</v>
       </c>
       <c r="C171" s="20" t="s">
@@ -14720,24 +14756,24 @@
       <c r="D171" s="20" t="s">
         <v>1004</v>
       </c>
-      <c r="E171" s="0" t="s">
+      <c r="E171" t="s">
         <v>1004</v>
       </c>
       <c r="F171" s="67" t="s">
         <v>1005</v>
       </c>
-      <c r="G171" s="0" t="s">
+      <c r="G171" t="s">
         <v>972</v>
       </c>
       <c r="L171" s="20">
         <v>13980555007</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:13">
       <c r="A172" s="19">
         <v>171</v>
       </c>
-      <c r="B172" s="0" t="s">
+      <c r="B172" t="s">
         <v>1006</v>
       </c>
       <c r="C172" s="20" t="s">
@@ -14752,18 +14788,18 @@
       <c r="F172" s="67" t="s">
         <v>1008</v>
       </c>
-      <c r="G172" s="0" t="s">
+      <c r="G172" t="s">
         <v>1009</v>
       </c>
       <c r="L172" s="20">
         <v>13808186159</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:13">
       <c r="A173" s="19">
         <v>172</v>
       </c>
-      <c r="B173" s="0" t="s">
+      <c r="B173" t="s">
         <v>1010</v>
       </c>
       <c r="C173" s="20" t="s">
@@ -14778,21 +14814,21 @@
       <c r="F173" s="67" t="s">
         <v>1012</v>
       </c>
-      <c r="G173" s="0" t="s">
+      <c r="G173" t="s">
         <v>1013</v>
       </c>
       <c r="L173" s="20">
         <v>13438192391</v>
       </c>
-      <c r="M173" s="0" t="s">
+      <c r="M173" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:13">
       <c r="A174" s="19">
         <v>173</v>
       </c>
-      <c r="B174" s="0" t="s">
+      <c r="B174" t="s">
         <v>1015</v>
       </c>
       <c r="C174" s="20" t="s">
@@ -14807,18 +14843,18 @@
       <c r="F174" s="67" t="s">
         <v>1017</v>
       </c>
-      <c r="G174" s="0" t="s">
+      <c r="G174" t="s">
         <v>1018</v>
       </c>
       <c r="L174" s="20">
         <v>13540600883</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:13">
       <c r="A175" s="19">
         <v>174</v>
       </c>
-      <c r="B175" s="0" t="s">
+      <c r="B175" t="s">
         <v>1019</v>
       </c>
       <c r="C175" s="20" t="s">
@@ -14833,18 +14869,18 @@
       <c r="F175" s="67" t="s">
         <v>1021</v>
       </c>
-      <c r="G175" s="0" t="s">
+      <c r="G175" t="s">
         <v>972</v>
       </c>
       <c r="L175" s="20">
         <v>13881986933</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:13">
       <c r="A176" s="19">
         <v>175</v>
       </c>
-      <c r="B176" s="0" t="s">
+      <c r="B176" t="s">
         <v>1022</v>
       </c>
       <c r="C176" s="20" t="s">
@@ -14859,15 +14895,15 @@
       <c r="F176" s="67" t="s">
         <v>1023</v>
       </c>
-      <c r="G176" s="0" t="s">
+      <c r="G176" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:13">
       <c r="A177" s="19">
         <v>176</v>
       </c>
-      <c r="B177" s="0" t="s">
+      <c r="B177" t="s">
         <v>1025</v>
       </c>
       <c r="C177" s="20" t="s">
@@ -14876,13 +14912,13 @@
       <c r="D177" s="68" t="s">
         <v>1026</v>
       </c>
-      <c r="E177" s="0">
+      <c r="E177">
         <v>0</v>
       </c>
-      <c r="F177" s="0">
+      <c r="F177">
         <v>0</v>
       </c>
-      <c r="G177" s="0">
+      <c r="G177">
         <v>0</v>
       </c>
       <c r="K177" s="68" t="s">
@@ -14892,11 +14928,11 @@
         <v>18088744160</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:13">
       <c r="A178" s="19">
         <v>177</v>
       </c>
-      <c r="B178" s="0" t="s">
+      <c r="B178" t="s">
         <v>1027</v>
       </c>
       <c r="C178" s="20" t="s">
@@ -14911,18 +14947,18 @@
       <c r="F178" s="67" t="s">
         <v>1029</v>
       </c>
-      <c r="G178" s="0" t="s">
+      <c r="G178" t="s">
         <v>1030</v>
       </c>
       <c r="L178" s="20">
         <v>17381897976</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:13">
       <c r="A179" s="19">
         <v>178</v>
       </c>
-      <c r="B179" s="0" t="s">
+      <c r="B179" t="s">
         <v>1031</v>
       </c>
       <c r="C179" s="20" t="s">
@@ -14937,18 +14973,18 @@
       <c r="F179" s="67" t="s">
         <v>1033</v>
       </c>
-      <c r="G179" s="0" t="s">
+      <c r="G179" t="s">
         <v>1034</v>
       </c>
       <c r="L179" s="20">
         <v>18511881577</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:13">
       <c r="A180" s="19">
         <v>179</v>
       </c>
-      <c r="B180" s="0" t="s">
+      <c r="B180" t="s">
         <v>1035</v>
       </c>
       <c r="C180" s="20" t="s">
@@ -14963,18 +14999,18 @@
       <c r="F180" s="67" t="s">
         <v>1037</v>
       </c>
-      <c r="G180" s="0" t="s">
+      <c r="G180" t="s">
         <v>1038</v>
       </c>
       <c r="L180" s="20">
         <v>13709485953</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:13">
       <c r="A181" s="19">
         <v>180</v>
       </c>
-      <c r="B181" s="0" t="s">
+      <c r="B181" t="s">
         <v>1039</v>
       </c>
       <c r="C181" s="20" t="s">
@@ -14989,18 +15025,18 @@
       <c r="F181" s="67" t="s">
         <v>1041</v>
       </c>
-      <c r="G181" s="0" t="s">
+      <c r="G181" t="s">
         <v>1042</v>
       </c>
       <c r="L181" s="20">
         <v>13720184932</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:13">
       <c r="A182" s="19">
         <v>181</v>
       </c>
-      <c r="B182" s="0" t="s">
+      <c r="B182" t="s">
         <v>1043</v>
       </c>
       <c r="C182" s="20" t="s">
@@ -15009,21 +15045,21 @@
       <c r="D182" s="67" t="s">
         <v>1044</v>
       </c>
-      <c r="E182" s="0" t="s">
+      <c r="E182" t="s">
         <v>1045</v>
       </c>
       <c r="F182" s="67" t="s">
         <v>1044</v>
       </c>
-      <c r="G182" s="0" t="s">
+      <c r="G182" t="s">
         <v>1046</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:13">
       <c r="A183" s="19">
         <v>182</v>
       </c>
-      <c r="B183" s="0" t="s">
+      <c r="B183" t="s">
         <v>1047</v>
       </c>
       <c r="C183" s="20" t="s">
@@ -15038,7 +15074,7 @@
       <c r="F183" s="67" t="s">
         <v>1049</v>
       </c>
-      <c r="G183" s="0" t="s">
+      <c r="G183" t="s">
         <v>881</v>
       </c>
       <c r="H183" s="68" t="s">
@@ -15048,11 +15084,11 @@
         <v>13072883388</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:13">
       <c r="A184" s="19">
         <v>183</v>
       </c>
-      <c r="B184" s="0" t="s">
+      <c r="B184" t="s">
         <v>1051</v>
       </c>
       <c r="C184" s="20" t="s">
@@ -15067,7 +15103,7 @@
       <c r="F184" s="67" t="s">
         <v>1053</v>
       </c>
-      <c r="G184" s="0" t="s">
+      <c r="G184" t="s">
         <v>1054</v>
       </c>
       <c r="H184" s="68" t="s">
@@ -15077,11 +15113,11 @@
         <v>13880384547</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:13">
       <c r="A185" s="19">
         <v>184</v>
       </c>
-      <c r="B185" s="0" t="s">
+      <c r="B185" t="s">
         <v>1056</v>
       </c>
       <c r="C185" s="20" t="s">
@@ -15096,7 +15132,7 @@
       <c r="F185" s="67" t="s">
         <v>1058</v>
       </c>
-      <c r="G185" s="0" t="s">
+      <c r="G185" t="s">
         <v>1059</v>
       </c>
       <c r="H185" s="33" t="s">
@@ -15106,11 +15142,11 @@
         <v>13551109316</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:13">
       <c r="A186" s="19">
         <v>185</v>
       </c>
-      <c r="B186" s="0" t="s">
+      <c r="B186" t="s">
         <v>1061</v>
       </c>
       <c r="C186" s="20" t="s">
@@ -15125,7 +15161,7 @@
       <c r="F186" s="67" t="s">
         <v>1063</v>
       </c>
-      <c r="G186" s="0" t="s">
+      <c r="G186" t="s">
         <v>1064</v>
       </c>
       <c r="H186" s="68" t="s">
@@ -15135,11 +15171,11 @@
         <v>18982291559</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:13">
       <c r="A187" s="19">
         <v>186</v>
       </c>
-      <c r="B187" s="0" t="s">
+      <c r="B187" t="s">
         <v>1066</v>
       </c>
       <c r="C187" s="20" t="s">
@@ -15154,7 +15190,7 @@
       <c r="F187" s="67" t="s">
         <v>1068</v>
       </c>
-      <c r="G187" s="0" t="s">
+      <c r="G187" t="s">
         <v>1069</v>
       </c>
       <c r="H187" s="68" t="s">
@@ -15164,11 +15200,11 @@
         <v>13881834239</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:13">
       <c r="A188" s="19">
         <v>187</v>
       </c>
-      <c r="B188" s="0" t="s">
+      <c r="B188" t="s">
         <v>1071</v>
       </c>
       <c r="C188" s="20" t="s">
@@ -15181,11 +15217,11 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:13">
       <c r="A189" s="19">
         <v>188</v>
       </c>
-      <c r="B189" s="0" t="s">
+      <c r="B189" t="s">
         <v>1074</v>
       </c>
       <c r="C189" s="20" t="s">
@@ -15198,11 +15234,11 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:13">
       <c r="A190" s="19">
         <v>189</v>
       </c>
-      <c r="B190" s="0" t="s">
+      <c r="B190" t="s">
         <v>1076</v>
       </c>
       <c r="C190" s="20" t="s">
@@ -15217,21 +15253,21 @@
       <c r="F190" s="67" t="s">
         <v>1078</v>
       </c>
-      <c r="G190" s="0" t="s">
+      <c r="G190" t="s">
         <v>1079</v>
       </c>
       <c r="L190" s="20">
         <v>18911990856</v>
       </c>
-      <c r="M190" s="0" t="s">
+      <c r="M190" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:13">
       <c r="A191" s="19">
         <v>190</v>
       </c>
-      <c r="B191" s="0" t="s">
+      <c r="B191" t="s">
         <v>1080</v>
       </c>
       <c r="C191" s="20" t="s">
@@ -15246,21 +15282,21 @@
       <c r="F191" s="67" t="s">
         <v>1082</v>
       </c>
-      <c r="G191" s="0" t="s">
+      <c r="G191" t="s">
         <v>1083</v>
       </c>
       <c r="L191" s="20">
         <v>18911990414</v>
       </c>
-      <c r="M191" s="0" t="s">
+      <c r="M191" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:13">
       <c r="A192" s="19">
         <v>191</v>
       </c>
-      <c r="B192" s="0" t="s">
+      <c r="B192" t="s">
         <v>1084</v>
       </c>
       <c r="C192" s="20" t="s">
@@ -15275,21 +15311,21 @@
       <c r="F192" s="67" t="s">
         <v>1086</v>
       </c>
-      <c r="G192" s="0" t="s">
+      <c r="G192" t="s">
         <v>1083</v>
       </c>
       <c r="L192" s="20">
         <v>18911990473</v>
       </c>
-      <c r="M192" s="0" t="s">
+      <c r="M192" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:13">
       <c r="A193" s="19">
         <v>192</v>
       </c>
-      <c r="B193" s="0" t="s">
+      <c r="B193" t="s">
         <v>1087</v>
       </c>
       <c r="C193" s="20" t="s">
@@ -15304,21 +15340,21 @@
       <c r="F193" s="67" t="s">
         <v>1089</v>
       </c>
-      <c r="G193" s="0" t="s">
+      <c r="G193" t="s">
         <v>1090</v>
       </c>
       <c r="L193" s="20">
         <v>18911990641</v>
       </c>
-      <c r="M193" s="0" t="s">
+      <c r="M193" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:13">
       <c r="A194" s="19">
         <v>193</v>
       </c>
-      <c r="B194" s="0" t="s">
+      <c r="B194" t="s">
         <v>1091</v>
       </c>
       <c r="C194" s="20" t="s">
@@ -15327,27 +15363,27 @@
       <c r="D194" s="20" t="s">
         <v>1092</v>
       </c>
-      <c r="E194" s="0" t="s">
+      <c r="E194" t="s">
         <v>1092</v>
       </c>
       <c r="F194" s="67" t="s">
         <v>1093</v>
       </c>
-      <c r="G194" s="0" t="s">
+      <c r="G194" t="s">
         <v>1094</v>
       </c>
       <c r="L194" s="20">
         <v>18911990655</v>
       </c>
-      <c r="M194" s="0" t="s">
+      <c r="M194" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:13">
       <c r="A195" s="19">
         <v>194</v>
       </c>
-      <c r="B195" s="0" t="s">
+      <c r="B195" t="s">
         <v>1095</v>
       </c>
       <c r="C195" s="20" t="s">
@@ -15362,21 +15398,21 @@
       <c r="F195" s="67" t="s">
         <v>1097</v>
       </c>
-      <c r="G195" s="0" t="s">
+      <c r="G195" t="s">
         <v>1098</v>
       </c>
       <c r="L195" s="20">
         <v>18911990605</v>
       </c>
-      <c r="M195" s="0" t="s">
+      <c r="M195" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:13">
       <c r="A196" s="19">
         <v>195</v>
       </c>
-      <c r="B196" s="0" t="s">
+      <c r="B196" t="s">
         <v>1099</v>
       </c>
       <c r="C196" s="20" t="s">
@@ -15391,21 +15427,21 @@
       <c r="F196" s="67" t="s">
         <v>1101</v>
       </c>
-      <c r="G196" s="0" t="s">
+      <c r="G196" t="s">
         <v>1102</v>
       </c>
       <c r="L196" s="20">
         <v>18911990484</v>
       </c>
-      <c r="M196" s="0" t="s">
+      <c r="M196" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:13">
       <c r="A197" s="19">
         <v>196</v>
       </c>
-      <c r="B197" s="0" t="s">
+      <c r="B197" t="s">
         <v>1103</v>
       </c>
       <c r="C197" s="20" t="s">
@@ -15420,21 +15456,21 @@
       <c r="F197" s="67" t="s">
         <v>1105</v>
       </c>
-      <c r="G197" s="0" t="s">
+      <c r="G197" t="s">
         <v>1106</v>
       </c>
       <c r="L197" s="20">
         <v>18110078468</v>
       </c>
-      <c r="M197" s="0" t="s">
+      <c r="M197" t="s">
         <v>1107</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:13">
       <c r="A198" s="19">
         <v>197</v>
       </c>
-      <c r="B198" s="0" t="s">
+      <c r="B198" t="s">
         <v>1108</v>
       </c>
       <c r="C198" s="20" t="s">
@@ -15443,27 +15479,27 @@
       <c r="D198" s="20" t="s">
         <v>1109</v>
       </c>
-      <c r="E198" s="0" t="s">
+      <c r="E198" t="s">
         <v>1109</v>
       </c>
       <c r="F198" s="67" t="s">
         <v>1110</v>
       </c>
-      <c r="G198" s="0" t="s">
+      <c r="G198" t="s">
         <v>1111</v>
       </c>
       <c r="L198" s="20">
         <v>18110071878</v>
       </c>
-      <c r="M198" s="0" t="s">
+      <c r="M198" t="s">
         <v>1107</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:13">
       <c r="A199" s="19">
         <v>198</v>
       </c>
-      <c r="B199" s="0" t="s">
+      <c r="B199" t="s">
         <v>1112</v>
       </c>
       <c r="C199" s="20" t="s">
@@ -15472,27 +15508,27 @@
       <c r="D199" s="20" t="s">
         <v>1113</v>
       </c>
-      <c r="E199" s="0" t="s">
+      <c r="E199" t="s">
         <v>1113</v>
       </c>
       <c r="F199" s="67" t="s">
         <v>1114</v>
       </c>
-      <c r="G199" s="0" t="s">
+      <c r="G199" t="s">
         <v>1115</v>
       </c>
       <c r="L199" s="20">
         <v>18110070838</v>
       </c>
-      <c r="M199" s="0" t="s">
+      <c r="M199" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:13">
       <c r="A200" s="19">
         <v>199</v>
       </c>
-      <c r="B200" s="0" t="s">
+      <c r="B200" t="s">
         <v>1116</v>
       </c>
       <c r="C200" s="20" t="s">
@@ -15507,7 +15543,7 @@
       <c r="F200" s="67" t="s">
         <v>1119</v>
       </c>
-      <c r="G200" s="0" t="s">
+      <c r="G200" t="s">
         <v>1120</v>
       </c>
       <c r="K200" s="68" t="s">
@@ -15517,11 +15553,11 @@
         <v>18575780914</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:13">
       <c r="A201" s="19">
         <v>200</v>
       </c>
-      <c r="B201" s="0" t="s">
+      <c r="B201" t="s">
         <v>1121</v>
       </c>
       <c r="C201" s="20" t="s">
@@ -15540,11 +15576,11 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:13">
       <c r="A202" s="19">
         <v>201</v>
       </c>
-      <c r="B202" s="0" t="s">
+      <c r="B202" t="s">
         <v>1125</v>
       </c>
       <c r="C202" s="20" t="s">
@@ -15559,7 +15595,7 @@
       <c r="F202" s="67" t="s">
         <v>1127</v>
       </c>
-      <c r="G202" s="0" t="s">
+      <c r="G202" t="s">
         <v>1128</v>
       </c>
       <c r="L202" s="20">
@@ -15569,11 +15605,11 @@
         <v>979</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:13">
       <c r="A203" s="19">
         <v>202</v>
       </c>
-      <c r="B203" s="0" t="s">
+      <c r="B203" t="s">
         <v>1129</v>
       </c>
       <c r="C203" s="20" t="s">
@@ -15588,7 +15624,7 @@
       <c r="F203" s="67" t="s">
         <v>1131</v>
       </c>
-      <c r="G203" s="0" t="s">
+      <c r="G203" t="s">
         <v>1128</v>
       </c>
       <c r="L203" s="20">
@@ -15598,11 +15634,11 @@
         <v>979</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:13">
       <c r="A204" s="19">
         <v>203</v>
       </c>
-      <c r="B204" s="0" t="s">
+      <c r="B204" t="s">
         <v>1132</v>
       </c>
       <c r="C204" s="26" t="s">
@@ -15617,7 +15653,7 @@
       <c r="F204" s="67" t="s">
         <v>1134</v>
       </c>
-      <c r="G204" s="0" t="s">
+      <c r="G204" t="s">
         <v>1135</v>
       </c>
       <c r="K204" s="20">
@@ -15630,11 +15666,11 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:13">
       <c r="A205" s="19">
         <v>204</v>
       </c>
-      <c r="B205" s="0" t="s">
+      <c r="B205" t="s">
         <v>1137</v>
       </c>
       <c r="C205" s="26" t="s">
@@ -15656,11 +15692,11 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:13">
       <c r="A206" s="19">
         <v>205</v>
       </c>
-      <c r="B206" s="0" t="s">
+      <c r="B206" t="s">
         <v>1140</v>
       </c>
       <c r="C206" s="26" t="s">
@@ -15682,11 +15718,11 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:13">
       <c r="A207" s="19">
         <v>206</v>
       </c>
-      <c r="B207" s="0" t="s">
+      <c r="B207" t="s">
         <v>1142</v>
       </c>
       <c r="C207" s="20" t="s">
@@ -15695,15 +15731,15 @@
       <c r="D207" s="20" t="s">
         <v>1143</v>
       </c>
-      <c r="E207" s="0" t="s">
+      <c r="E207" t="s">
         <v>1143</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:13">
       <c r="A208" s="19">
         <v>207</v>
       </c>
-      <c r="B208" s="0" t="s">
+      <c r="B208" t="s">
         <v>1144</v>
       </c>
       <c r="C208" s="20" t="s">
@@ -15718,7 +15754,7 @@
       <c r="F208" s="67" t="s">
         <v>1146</v>
       </c>
-      <c r="G208" s="0" t="s">
+      <c r="G208" t="s">
         <v>1147</v>
       </c>
       <c r="L208" s="20">
@@ -15728,11 +15764,11 @@
         <v>979</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:13">
       <c r="A209" s="19">
         <v>208</v>
       </c>
-      <c r="B209" s="0" t="s">
+      <c r="B209" t="s">
         <v>1148</v>
       </c>
       <c r="C209" s="20" t="s">
@@ -15747,7 +15783,7 @@
       <c r="F209" s="67" t="s">
         <v>1150</v>
       </c>
-      <c r="G209" s="0" t="s">
+      <c r="G209" t="s">
         <v>1151</v>
       </c>
       <c r="L209" s="20">
@@ -15757,11 +15793,11 @@
         <v>979</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:13">
       <c r="A210" s="19">
         <v>209</v>
       </c>
-      <c r="B210" s="0" t="s">
+      <c r="B210" t="s">
         <v>1152</v>
       </c>
       <c r="C210" s="20" t="s">
@@ -15776,18 +15812,18 @@
       <c r="F210" s="67" t="s">
         <v>1154</v>
       </c>
-      <c r="G210" s="0" t="s">
+      <c r="G210" t="s">
         <v>1155</v>
       </c>
       <c r="M210" s="20" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:13">
       <c r="A211" s="19">
         <v>210</v>
       </c>
-      <c r="B211" s="0" t="s">
+      <c r="B211" t="s">
         <v>1156</v>
       </c>
       <c r="C211" s="20" t="s">
@@ -15802,15 +15838,15 @@
       <c r="F211" s="67" t="s">
         <v>1158</v>
       </c>
-      <c r="G211" s="0" t="s">
+      <c r="G211" t="s">
         <v>1159</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:13">
       <c r="A212" s="19">
         <v>211</v>
       </c>
-      <c r="B212" s="0" t="s">
+      <c r="B212" t="s">
         <v>1160</v>
       </c>
       <c r="C212" s="20" t="s">
@@ -15819,21 +15855,21 @@
       <c r="D212" s="20" t="s">
         <v>1161</v>
       </c>
-      <c r="E212" s="0" t="s">
+      <c r="E212" t="s">
         <v>1161</v>
       </c>
       <c r="F212" s="67" t="s">
         <v>1162</v>
       </c>
-      <c r="G212" s="0" t="s">
+      <c r="G212" t="s">
         <v>1163</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:13">
       <c r="A213" s="19">
         <v>212</v>
       </c>
-      <c r="B213" s="0" t="s">
+      <c r="B213" t="s">
         <v>1164</v>
       </c>
       <c r="C213" s="20" t="s">
@@ -15846,11 +15882,11 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:13">
       <c r="A214" s="19">
         <v>213</v>
       </c>
-      <c r="B214" s="0" t="s">
+      <c r="B214" t="s">
         <v>1166</v>
       </c>
       <c r="C214" s="20" t="s">
@@ -15863,11 +15899,11 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:13">
       <c r="A215" s="19">
         <v>214</v>
       </c>
-      <c r="B215" s="0" t="s">
+      <c r="B215" t="s">
         <v>1168</v>
       </c>
       <c r="C215" s="20" t="s">
@@ -15882,18 +15918,18 @@
       <c r="F215" s="67" t="s">
         <v>1170</v>
       </c>
-      <c r="G215" s="0" t="s">
+      <c r="G215" t="s">
         <v>1171</v>
       </c>
       <c r="L215" s="20">
         <v>13350060662</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="1:13">
       <c r="A216" s="19">
         <v>215</v>
       </c>
-      <c r="B216" s="0" t="s">
+      <c r="B216" t="s">
         <v>1172</v>
       </c>
       <c r="C216" s="20" t="s">
@@ -15906,11 +15942,11 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:13">
       <c r="A217" s="19">
         <v>216</v>
       </c>
-      <c r="B217" s="0" t="s">
+      <c r="B217" t="s">
         <v>1174</v>
       </c>
       <c r="C217" s="20" t="s">
@@ -15925,18 +15961,18 @@
       <c r="F217" s="67" t="s">
         <v>1176</v>
       </c>
-      <c r="G217" s="0" t="s">
+      <c r="G217" t="s">
         <v>1177</v>
       </c>
       <c r="L217" s="20">
         <v>15507702646</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="1:13">
       <c r="A218" s="19">
         <v>217</v>
       </c>
-      <c r="B218" s="0" t="s">
+      <c r="B218" t="s">
         <v>1178</v>
       </c>
       <c r="C218" s="20" t="s">
@@ -15951,18 +15987,18 @@
       <c r="F218" s="67" t="s">
         <v>1180</v>
       </c>
-      <c r="G218" s="0" t="s">
+      <c r="G218" t="s">
         <v>1181</v>
       </c>
       <c r="L218" s="20">
         <v>15184444781</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:13">
       <c r="A219" s="19">
         <v>218</v>
       </c>
-      <c r="B219" s="0" t="s">
+      <c r="B219" t="s">
         <v>1182</v>
       </c>
       <c r="C219" s="20" t="s">
@@ -15977,18 +16013,18 @@
       <c r="F219" s="67" t="s">
         <v>1184</v>
       </c>
-      <c r="G219" s="0" t="s">
+      <c r="G219" t="s">
         <v>1185</v>
       </c>
       <c r="L219" s="20">
         <v>13880012488</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="1:13">
       <c r="A220" s="19">
         <v>219</v>
       </c>
-      <c r="B220" s="0" t="s">
+      <c r="B220" t="s">
         <v>1186</v>
       </c>
       <c r="C220" s="20" t="s">
@@ -16003,21 +16039,21 @@
       <c r="F220" s="67" t="s">
         <v>1188</v>
       </c>
-      <c r="G220" s="0" t="s">
+      <c r="G220" t="s">
         <v>1189</v>
       </c>
       <c r="L220" s="20">
         <v>13258218888</v>
       </c>
-      <c r="M220" s="0" t="s">
+      <c r="M220" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" spans="1:13">
       <c r="A221" s="19">
         <v>220</v>
       </c>
-      <c r="B221" s="0" t="s">
+      <c r="B221" t="s">
         <v>1190</v>
       </c>
       <c r="C221" s="20" t="s">
@@ -16032,21 +16068,21 @@
       <c r="F221" s="67" t="s">
         <v>1192</v>
       </c>
-      <c r="G221" s="0" t="s">
+      <c r="G221" t="s">
         <v>1193</v>
       </c>
       <c r="L221" s="20">
         <v>13981819638</v>
       </c>
-      <c r="M221" s="0" t="s">
+      <c r="M221" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="1:13">
       <c r="A222" s="19">
         <v>221</v>
       </c>
-      <c r="B222" s="0" t="s">
+      <c r="B222" t="s">
         <v>1194</v>
       </c>
       <c r="C222" s="20" t="s">
@@ -16061,21 +16097,21 @@
       <c r="F222" s="67" t="s">
         <v>1196</v>
       </c>
-      <c r="G222" s="0" t="s">
+      <c r="G222" t="s">
         <v>544</v>
       </c>
       <c r="L222" s="20">
         <v>18683618560</v>
       </c>
-      <c r="M222" s="0" t="s">
+      <c r="M222" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="1:13">
       <c r="A223" s="19">
         <v>222</v>
       </c>
-      <c r="B223" s="0" t="s">
+      <c r="B223" t="s">
         <v>1197</v>
       </c>
       <c r="C223" s="20" t="s">
@@ -16090,21 +16126,21 @@
       <c r="F223" s="67" t="s">
         <v>1199</v>
       </c>
-      <c r="G223" s="0" t="s">
+      <c r="G223" t="s">
         <v>1200</v>
       </c>
       <c r="L223" s="20">
         <v>13880417337</v>
       </c>
-      <c r="M223" s="0" t="s">
+      <c r="M223" t="s">
         <v>1201</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="1:13">
       <c r="A224" s="19">
         <v>223</v>
       </c>
-      <c r="B224" s="0" t="s">
+      <c r="B224" t="s">
         <v>1202</v>
       </c>
       <c r="C224" s="20" t="s">
@@ -16119,21 +16155,21 @@
       <c r="F224" s="67" t="s">
         <v>1204</v>
       </c>
-      <c r="G224" s="0" t="s">
+      <c r="G224" t="s">
         <v>1205</v>
       </c>
       <c r="L224" s="20">
         <v>13982254477</v>
       </c>
-      <c r="M224" s="0" t="s">
+      <c r="M224" t="s">
         <v>1201</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="1:13">
       <c r="A225" s="19">
         <v>224</v>
       </c>
-      <c r="B225" s="0" t="s">
+      <c r="B225" t="s">
         <v>1206</v>
       </c>
       <c r="C225" s="20" t="s">
@@ -16149,11 +16185,11 @@
         <v>17835601430</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" spans="1:13">
       <c r="A226" s="19">
         <v>225</v>
       </c>
-      <c r="B226" s="0" t="s">
+      <c r="B226" t="s">
         <v>1208</v>
       </c>
       <c r="C226" s="20" t="s">
@@ -16162,24 +16198,24 @@
       <c r="D226" s="20" t="s">
         <v>1209</v>
       </c>
-      <c r="E226" s="0" t="s">
+      <c r="E226" t="s">
         <v>1209</v>
       </c>
       <c r="F226" s="67" t="s">
         <v>1210</v>
       </c>
-      <c r="G226" s="0" t="s">
+      <c r="G226" t="s">
         <v>1211</v>
       </c>
       <c r="L226" s="20">
         <v>18375939215</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="1:13">
       <c r="A227" s="19">
         <v>226</v>
       </c>
-      <c r="B227" s="0" t="s">
+      <c r="B227" t="s">
         <v>1212</v>
       </c>
       <c r="C227" s="20" t="s">
@@ -16191,7 +16227,7 @@
       <c r="F227" s="67" t="s">
         <v>1214</v>
       </c>
-      <c r="G227" s="0" t="s">
+      <c r="G227" t="s">
         <v>647</v>
       </c>
       <c r="K227" s="68" t="s">
@@ -16201,11 +16237,11 @@
         <v>13518306314</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="1:13">
       <c r="A228" s="19">
         <v>227</v>
       </c>
-      <c r="B228" s="0" t="s">
+      <c r="B228" t="s">
         <v>1215</v>
       </c>
       <c r="C228" s="20" t="s">
@@ -16218,11 +16254,11 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="1:13">
       <c r="A229" s="19">
         <v>228</v>
       </c>
-      <c r="B229" s="0" t="s">
+      <c r="B229" t="s">
         <v>1217</v>
       </c>
       <c r="C229" s="20" t="s">
@@ -16231,27 +16267,27 @@
       <c r="D229" s="20" t="s">
         <v>1218</v>
       </c>
-      <c r="E229" s="0" t="s">
+      <c r="E229" t="s">
         <v>1218</v>
       </c>
       <c r="F229" s="67" t="s">
         <v>1219</v>
       </c>
-      <c r="G229" s="0" t="s">
+      <c r="G229" t="s">
         <v>1013</v>
       </c>
       <c r="L229" s="20">
         <v>13882226385</v>
       </c>
-      <c r="M229" s="0" t="s">
+      <c r="M229" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="1:13">
       <c r="A230" s="19">
         <v>229</v>
       </c>
-      <c r="B230" s="0" t="s">
+      <c r="B230" t="s">
         <v>1220</v>
       </c>
       <c r="C230" s="20" t="s">
@@ -16266,21 +16302,21 @@
       <c r="F230" s="67" t="s">
         <v>1222</v>
       </c>
-      <c r="G230" s="0" t="s">
+      <c r="G230" t="s">
         <v>1223</v>
       </c>
       <c r="L230" s="20">
         <v>13908061512</v>
       </c>
-      <c r="M230" s="0" t="s">
+      <c r="M230" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="1:13">
       <c r="A231" s="19">
         <v>230</v>
       </c>
-      <c r="B231" s="0" t="s">
+      <c r="B231" t="s">
         <v>1224</v>
       </c>
       <c r="C231" s="20" t="s">
@@ -16289,27 +16325,27 @@
       <c r="D231" s="20" t="s">
         <v>1225</v>
       </c>
-      <c r="E231" s="0" t="s">
+      <c r="E231" t="s">
         <v>1225</v>
       </c>
       <c r="F231" s="67" t="s">
         <v>1226</v>
       </c>
-      <c r="G231" s="0" t="s">
+      <c r="G231" t="s">
         <v>1227</v>
       </c>
       <c r="L231" s="20">
         <v>13550226561</v>
       </c>
-      <c r="M231" s="0" t="s">
+      <c r="M231" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="1:13">
       <c r="A232" s="19">
         <v>231</v>
       </c>
-      <c r="B232" s="0" t="s">
+      <c r="B232" t="s">
         <v>1228</v>
       </c>
       <c r="C232" s="20" t="s">
@@ -16324,21 +16360,21 @@
       <c r="F232" s="67" t="s">
         <v>1230</v>
       </c>
-      <c r="G232" s="0" t="s">
+      <c r="G232" t="s">
         <v>1231</v>
       </c>
       <c r="L232" s="20">
         <v>18010678960</v>
       </c>
-      <c r="M232" s="0" t="s">
+      <c r="M232" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="1:13">
       <c r="A233" s="19">
         <v>232</v>
       </c>
-      <c r="B233" s="0" t="s">
+      <c r="B233" t="s">
         <v>1232</v>
       </c>
       <c r="C233" s="20" t="s">
@@ -16353,21 +16389,21 @@
       <c r="F233" s="67" t="s">
         <v>1234</v>
       </c>
-      <c r="G233" s="0" t="s">
+      <c r="G233" t="s">
         <v>1235</v>
       </c>
       <c r="L233" s="20">
         <v>13709020198</v>
       </c>
-      <c r="M233" s="0" t="s">
+      <c r="M233" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="1:13">
       <c r="A234" s="19">
         <v>233</v>
       </c>
-      <c r="B234" s="0" t="s">
+      <c r="B234" t="s">
         <v>1236</v>
       </c>
       <c r="C234" s="20" t="s">
@@ -16376,24 +16412,24 @@
       <c r="D234" s="20" t="s">
         <v>1237</v>
       </c>
-      <c r="E234" s="0" t="s">
+      <c r="E234" t="s">
         <v>1237</v>
       </c>
       <c r="F234" s="67" t="s">
         <v>1238</v>
       </c>
-      <c r="G234" s="0" t="s">
+      <c r="G234" t="s">
         <v>1239</v>
       </c>
       <c r="L234" s="20">
         <v>18033950999</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="1:13">
       <c r="A235" s="19">
         <v>234</v>
       </c>
-      <c r="B235" s="0" t="s">
+      <c r="B235" t="s">
         <v>1240</v>
       </c>
       <c r="C235" s="20" t="s">
@@ -16408,7 +16444,7 @@
       <c r="F235" s="67" t="s">
         <v>1242</v>
       </c>
-      <c r="G235" s="0" t="s">
+      <c r="G235" t="s">
         <v>467</v>
       </c>
       <c r="K235" s="20">
@@ -16418,11 +16454,11 @@
         <v>13547285749</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="1:13">
       <c r="A236" s="19">
         <v>235</v>
       </c>
-      <c r="B236" s="0" t="s">
+      <c r="B236" t="s">
         <v>1243</v>
       </c>
       <c r="C236" s="20" t="s">
@@ -16434,15 +16470,15 @@
       <c r="F236" s="67" t="s">
         <v>1244</v>
       </c>
-      <c r="G236" s="0" t="s">
+      <c r="G236" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="1:13">
       <c r="A237" s="19">
         <v>236</v>
       </c>
-      <c r="B237" s="0" t="s">
+      <c r="B237" t="s">
         <v>1246</v>
       </c>
       <c r="C237" s="20" t="s">
@@ -16457,18 +16493,18 @@
       <c r="F237" s="76" t="s">
         <v>1248</v>
       </c>
-      <c r="G237" s="0" t="s">
+      <c r="G237" t="s">
         <v>1249</v>
       </c>
       <c r="L237" s="20">
         <v>15202871402</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="1:13">
       <c r="A238" s="19">
         <v>237</v>
       </c>
-      <c r="B238" s="0" t="s">
+      <c r="B238" t="s">
         <v>1243</v>
       </c>
       <c r="C238" s="20" t="s">
@@ -16484,11 +16520,11 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="1:13">
       <c r="A239" s="19">
         <v>238</v>
       </c>
-      <c r="B239" s="0" t="s">
+      <c r="B239" t="s">
         <v>1250</v>
       </c>
       <c r="C239" s="20" t="s">
@@ -16500,7 +16536,7 @@
       <c r="F239" s="67" t="s">
         <v>1251</v>
       </c>
-      <c r="G239" s="0" t="s">
+      <c r="G239" t="s">
         <v>467</v>
       </c>
       <c r="K239" s="20">
@@ -16510,11 +16546,11 @@
         <v>15008489824</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="1:13">
       <c r="A240" s="19">
         <v>239</v>
       </c>
-      <c r="B240" s="0" t="s">
+      <c r="B240" t="s">
         <v>1252</v>
       </c>
       <c r="C240" s="20" t="s">
@@ -16530,11 +16566,11 @@
         <v>13730885415</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="1:12">
       <c r="A241" s="19">
         <v>240</v>
       </c>
-      <c r="B241" s="0" t="s">
+      <c r="B241" t="s">
         <v>1253</v>
       </c>
       <c r="C241" s="20" t="s">
@@ -16547,11 +16583,11 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="1:12">
       <c r="A242" s="19">
         <v>241</v>
       </c>
-      <c r="B242" s="0" t="s">
+      <c r="B242" t="s">
         <v>1255</v>
       </c>
       <c r="C242" s="20" t="s">
@@ -16564,11 +16600,11 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="1:12">
       <c r="A243" s="19">
         <v>242</v>
       </c>
-      <c r="B243" s="0" t="s">
+      <c r="B243" t="s">
         <v>1257</v>
       </c>
       <c r="C243" s="20" t="s">
@@ -16593,11 +16629,11 @@
         <v>13281811416</v>
       </c>
     </row>
-    <row r="244" ht="14.15" customHeight="1">
+    <row r="244" spans="1:12" ht="14.15" customHeight="1">
       <c r="A244" s="19">
         <v>243</v>
       </c>
-      <c r="B244" s="0" t="s">
+      <c r="B244" t="s">
         <v>1262</v>
       </c>
       <c r="C244" s="20" t="s">
@@ -16612,18 +16648,18 @@
       <c r="F244" s="67" t="s">
         <v>1264</v>
       </c>
-      <c r="G244" s="0" t="s">
+      <c r="G244" t="s">
         <v>1265</v>
       </c>
       <c r="L244" s="20">
         <v>13008141065</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="1:12">
       <c r="A245" s="19">
         <v>244</v>
       </c>
-      <c r="B245" s="0" t="s">
+      <c r="B245" t="s">
         <v>1266</v>
       </c>
       <c r="C245" s="20" t="s">
@@ -16638,7 +16674,7 @@
       <c r="F245" s="76" t="s">
         <v>1270</v>
       </c>
-      <c r="G245" s="0" t="s">
+      <c r="G245" t="s">
         <v>1271</v>
       </c>
       <c r="K245" s="68" t="s">
@@ -16648,11 +16684,11 @@
         <v>19828415638</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="1:12">
       <c r="A246" s="19">
         <v>245</v>
       </c>
-      <c r="B246" s="0" t="s">
+      <c r="B246" t="s">
         <v>1272</v>
       </c>
       <c r="C246" s="20" t="s">
@@ -16665,11 +16701,11 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" spans="1:12">
       <c r="A247" s="19">
         <v>246</v>
       </c>
-      <c r="B247" s="0" t="s">
+      <c r="B247" t="s">
         <v>1274</v>
       </c>
       <c r="C247" s="20" t="s">
@@ -16682,11 +16718,11 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="1:12">
       <c r="A248" s="19">
         <v>247</v>
       </c>
-      <c r="B248" s="0" t="s">
+      <c r="B248" t="s">
         <v>1276</v>
       </c>
       <c r="C248" s="20" t="s">
@@ -16695,21 +16731,21 @@
       <c r="D248" s="20" t="s">
         <v>1277</v>
       </c>
-      <c r="E248" s="0" t="s">
+      <c r="E248" t="s">
         <v>1277</v>
       </c>
       <c r="F248" s="67" t="s">
         <v>1278</v>
       </c>
-      <c r="G248" s="0" t="s">
+      <c r="G248" t="s">
         <v>1279</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="1:12">
       <c r="A249" s="19">
         <v>248</v>
       </c>
-      <c r="B249" s="0" t="s">
+      <c r="B249" t="s">
         <v>1280</v>
       </c>
       <c r="C249" s="20" t="s">
@@ -16724,15 +16760,15 @@
       <c r="F249" s="67" t="s">
         <v>1282</v>
       </c>
-      <c r="G249" s="0" t="s">
+      <c r="G249" t="s">
         <v>1283</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="1:12">
       <c r="A250" s="19">
         <v>249</v>
       </c>
-      <c r="B250" s="0" t="s">
+      <c r="B250" t="s">
         <v>1284</v>
       </c>
       <c r="C250" s="20" t="s">
@@ -16747,7 +16783,7 @@
       <c r="F250" s="67" t="s">
         <v>1287</v>
       </c>
-      <c r="G250" s="0" t="s">
+      <c r="G250" t="s">
         <v>1288</v>
       </c>
       <c r="K250" s="68" t="s">
@@ -16757,11 +16793,11 @@
         <v>13408470814</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="1:12">
       <c r="A251" s="19">
         <v>250</v>
       </c>
-      <c r="B251" s="0" t="s">
+      <c r="B251" t="s">
         <v>1289</v>
       </c>
       <c r="C251" s="20" t="s">
@@ -16770,21 +16806,21 @@
       <c r="D251" s="45">
         <v>4240503</v>
       </c>
-      <c r="F251" s="0" t="s">
+      <c r="F251" t="s">
         <v>1290</v>
       </c>
-      <c r="G251" s="0" t="s">
+      <c r="G251" t="s">
         <v>467</v>
       </c>
       <c r="K251" s="45">
         <v>4240503</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" spans="1:12">
       <c r="A252" s="19">
         <v>251</v>
       </c>
-      <c r="B252" s="0" t="s">
+      <c r="B252" t="s">
         <v>1291</v>
       </c>
       <c r="C252" s="20" t="s">
@@ -16796,21 +16832,21 @@
       <c r="E252" s="67" t="s">
         <v>1292</v>
       </c>
-      <c r="F252" s="0" t="s">
+      <c r="F252" t="s">
         <v>1293</v>
       </c>
-      <c r="G252" s="0" t="s">
+      <c r="G252" t="s">
         <v>467</v>
       </c>
       <c r="K252" s="45">
         <v>4240504</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" spans="1:12">
       <c r="A253" s="19">
         <v>252</v>
       </c>
-      <c r="B253" s="0" t="s">
+      <c r="B253" t="s">
         <v>1294</v>
       </c>
       <c r="C253" s="20" t="s">
@@ -16825,18 +16861,18 @@
       <c r="F253" s="67" t="s">
         <v>1296</v>
       </c>
-      <c r="G253" s="0" t="s">
+      <c r="G253" t="s">
         <v>1297</v>
       </c>
       <c r="L253" s="20">
         <v>13301372866</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" spans="1:12">
       <c r="A254" s="19">
         <v>253</v>
       </c>
-      <c r="B254" s="0" t="s">
+      <c r="B254" t="s">
         <v>1298</v>
       </c>
       <c r="C254" s="20" t="s">
@@ -16851,18 +16887,18 @@
       <c r="F254" s="67" t="s">
         <v>1300</v>
       </c>
-      <c r="G254" s="0" t="s">
+      <c r="G254" t="s">
         <v>1301</v>
       </c>
       <c r="L254" s="20">
         <v>13898800176</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="1:12">
       <c r="A255" s="19">
         <v>254</v>
       </c>
-      <c r="B255" s="0" t="s">
+      <c r="B255" t="s">
         <v>1302</v>
       </c>
       <c r="C255" s="20" t="s">
@@ -16877,18 +16913,18 @@
       <c r="F255" s="67" t="s">
         <v>1304</v>
       </c>
-      <c r="G255" s="0" t="s">
+      <c r="G255" t="s">
         <v>1305</v>
       </c>
       <c r="L255" s="20">
         <v>18818272538</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="1:12">
       <c r="A256" s="19">
         <v>255</v>
       </c>
-      <c r="B256" s="0" t="s">
+      <c r="B256" t="s">
         <v>1306</v>
       </c>
       <c r="C256" s="20" t="s">
@@ -16903,18 +16939,18 @@
       <c r="F256" s="67" t="s">
         <v>1308</v>
       </c>
-      <c r="G256" s="0" t="s">
+      <c r="G256" t="s">
         <v>972</v>
       </c>
       <c r="L256" s="20">
         <v>18113135523</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="1:13">
       <c r="A257" s="19">
         <v>256</v>
       </c>
-      <c r="B257" s="0" t="s">
+      <c r="B257" t="s">
         <v>1309</v>
       </c>
       <c r="C257" s="20" t="s">
@@ -16929,18 +16965,18 @@
       <c r="F257" s="67" t="s">
         <v>1311</v>
       </c>
-      <c r="G257" s="0" t="s">
+      <c r="G257" t="s">
         <v>1301</v>
       </c>
       <c r="L257" s="20">
         <v>13940534749</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="1:13">
       <c r="A258" s="19">
         <v>257</v>
       </c>
-      <c r="B258" s="0" t="s">
+      <c r="B258" t="s">
         <v>1312</v>
       </c>
       <c r="C258" s="20" t="s">
@@ -16956,11 +16992,11 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" spans="1:13">
       <c r="A259" s="19">
         <v>258</v>
       </c>
-      <c r="B259" s="0" t="s">
+      <c r="B259" t="s">
         <v>1315</v>
       </c>
       <c r="C259" s="20" t="s">
@@ -16976,11 +17012,11 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="1:13">
       <c r="A260" s="19">
         <v>259</v>
       </c>
-      <c r="B260" s="0" t="s">
+      <c r="B260" t="s">
         <v>1318</v>
       </c>
       <c r="C260" s="20" t="s">
@@ -16996,11 +17032,11 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="1:13">
       <c r="A261" s="19">
         <v>260</v>
       </c>
-      <c r="B261" s="0" t="s">
+      <c r="B261" t="s">
         <v>1321</v>
       </c>
       <c r="C261" s="20" t="s">
@@ -17016,11 +17052,11 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" spans="1:13">
       <c r="A262" s="19">
         <v>261</v>
       </c>
-      <c r="B262" s="0" t="s">
+      <c r="B262" t="s">
         <v>1324</v>
       </c>
       <c r="C262" s="20" t="s">
@@ -17036,11 +17072,11 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="1:13">
       <c r="A263" s="19">
         <v>262</v>
       </c>
-      <c r="B263" s="0" t="s">
+      <c r="B263" t="s">
         <v>1327</v>
       </c>
       <c r="C263" s="20" t="s">
@@ -17053,11 +17089,11 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" spans="1:13">
       <c r="A264" s="19">
         <v>263</v>
       </c>
-      <c r="B264" s="0" t="s">
+      <c r="B264" t="s">
         <v>1329</v>
       </c>
       <c r="C264" s="20" t="s">
@@ -17072,18 +17108,18 @@
       <c r="F264" s="67" t="s">
         <v>1331</v>
       </c>
-      <c r="G264" s="0" t="s">
+      <c r="G264" t="s">
         <v>1332</v>
       </c>
       <c r="L264" s="20">
         <v>13432240262</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" spans="1:13">
       <c r="A265" s="19">
         <v>264</v>
       </c>
-      <c r="B265" s="0" t="s">
+      <c r="B265" t="s">
         <v>1333</v>
       </c>
       <c r="C265" s="20" t="s">
@@ -17096,11 +17132,11 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="1:13">
       <c r="A266" s="19">
         <v>265</v>
       </c>
-      <c r="B266" s="0" t="s">
+      <c r="B266" t="s">
         <v>1335</v>
       </c>
       <c r="C266" s="20" t="s">
@@ -17115,18 +17151,18 @@
       <c r="F266" s="67" t="s">
         <v>1337</v>
       </c>
-      <c r="G266" s="0" t="s">
+      <c r="G266" t="s">
         <v>1338</v>
       </c>
-      <c r="M266" s="0" t="s">
+      <c r="M266" t="s">
         <v>1339</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="1:13">
       <c r="A267" s="19">
         <v>266</v>
       </c>
-      <c r="B267" s="0" t="s">
+      <c r="B267" t="s">
         <v>1340</v>
       </c>
       <c r="C267" s="20" t="s">
@@ -17135,21 +17171,21 @@
       <c r="D267" s="20" t="s">
         <v>1341</v>
       </c>
-      <c r="E267" s="0" t="s">
+      <c r="E267" t="s">
         <v>1341</v>
       </c>
       <c r="F267" s="67" t="s">
         <v>1342</v>
       </c>
-      <c r="G267" s="0" t="s">
+      <c r="G267" t="s">
         <v>1343</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" spans="1:13">
       <c r="A268" s="19">
         <v>267</v>
       </c>
-      <c r="B268" s="0" t="s">
+      <c r="B268" t="s">
         <v>1344</v>
       </c>
       <c r="C268" s="20" t="s">
@@ -17164,7 +17200,7 @@
       <c r="F268" s="67" t="s">
         <v>1346</v>
       </c>
-      <c r="G268" s="0" t="s">
+      <c r="G268" t="s">
         <v>1347</v>
       </c>
       <c r="K268" s="20">
@@ -17174,11 +17210,11 @@
         <v>18227623393</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" spans="1:13">
       <c r="A269" s="19">
         <v>268</v>
       </c>
-      <c r="B269" s="0" t="s">
+      <c r="B269" t="s">
         <v>1348</v>
       </c>
       <c r="C269" s="20" t="s">
@@ -17187,13 +17223,13 @@
       <c r="D269" s="20">
         <v>4250136</v>
       </c>
-      <c r="E269" s="0" t="s">
+      <c r="E269" t="s">
         <v>1349</v>
       </c>
       <c r="F269" s="67" t="s">
         <v>1350</v>
       </c>
-      <c r="G269" s="0" t="s">
+      <c r="G269" t="s">
         <v>467</v>
       </c>
       <c r="K269" s="20">
@@ -17203,11 +17239,11 @@
         <v>18784992511</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="1:13">
       <c r="A270" s="19">
         <v>269</v>
       </c>
-      <c r="B270" s="0" t="s">
+      <c r="B270" t="s">
         <v>1351</v>
       </c>
       <c r="C270" s="20" t="s">
@@ -17222,7 +17258,7 @@
       <c r="F270" s="67" t="s">
         <v>1353</v>
       </c>
-      <c r="G270" s="0" t="s">
+      <c r="G270" t="s">
         <v>1354</v>
       </c>
       <c r="K270" s="20">
@@ -17232,11 +17268,11 @@
         <v>18882027754</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="1:13">
       <c r="A271" s="19">
         <v>270</v>
       </c>
-      <c r="B271" s="0" t="s">
+      <c r="B271" t="s">
         <v>1355</v>
       </c>
       <c r="C271" s="20" t="s">
@@ -17249,11 +17285,11 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="1:13">
       <c r="A272" s="19">
         <v>271</v>
       </c>
-      <c r="B272" s="0" t="s">
+      <c r="B272" t="s">
         <v>1357</v>
       </c>
       <c r="C272" s="20" t="s">
@@ -17266,11 +17302,11 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" spans="1:12">
       <c r="A273" s="19">
         <v>272</v>
       </c>
-      <c r="B273" s="0" t="s">
+      <c r="B273" t="s">
         <v>1359</v>
       </c>
       <c r="C273" s="20" t="s">
@@ -17279,24 +17315,24 @@
       <c r="D273" s="20" t="s">
         <v>1360</v>
       </c>
-      <c r="E273" s="0" t="s">
+      <c r="E273" t="s">
         <v>1360</v>
       </c>
       <c r="F273" s="67" t="s">
         <v>1361</v>
       </c>
-      <c r="G273" s="0" t="s">
+      <c r="G273" t="s">
         <v>1362</v>
       </c>
       <c r="L273" s="20" t="s">
         <v>1363</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" spans="1:12">
       <c r="A274" s="19">
         <v>273</v>
       </c>
-      <c r="B274" s="0" t="s">
+      <c r="B274" t="s">
         <v>1364</v>
       </c>
       <c r="D274" s="68" t="s">
@@ -17306,11 +17342,11 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" spans="1:12">
       <c r="A275" s="19">
         <v>274</v>
       </c>
-      <c r="B275" s="0" t="s">
+      <c r="B275" t="s">
         <v>1366</v>
       </c>
       <c r="C275" s="20" t="s">
@@ -17325,18 +17361,18 @@
       <c r="F275" s="67" t="s">
         <v>1368</v>
       </c>
-      <c r="G275" s="0" t="s">
+      <c r="G275" t="s">
         <v>1369</v>
       </c>
       <c r="L275" s="44">
         <v>13869207670</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" spans="1:12">
       <c r="A276" s="19">
         <v>275</v>
       </c>
-      <c r="B276" s="0" t="s">
+      <c r="B276" t="s">
         <v>1370</v>
       </c>
       <c r="C276" s="20" t="s">
@@ -17345,21 +17381,21 @@
       <c r="D276" s="20" t="s">
         <v>1371</v>
       </c>
-      <c r="E276" s="0" t="s">
+      <c r="E276" t="s">
         <v>1371</v>
       </c>
       <c r="F276" s="19">
         <v>153654564</v>
       </c>
-      <c r="G276" s="0" t="s">
+      <c r="G276" t="s">
         <v>1372</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" spans="1:12">
       <c r="A277" s="19">
         <v>276</v>
       </c>
-      <c r="B277" s="0" t="s">
+      <c r="B277" t="s">
         <v>1373</v>
       </c>
       <c r="C277" s="20" t="s">
@@ -17374,18 +17410,18 @@
       <c r="F277" s="67" t="s">
         <v>1375</v>
       </c>
-      <c r="G277" s="0" t="s">
+      <c r="G277" t="s">
         <v>1376</v>
       </c>
       <c r="L277" s="20">
         <v>15734900293</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" spans="1:12">
       <c r="A278" s="19">
         <v>277</v>
       </c>
-      <c r="B278" s="0" t="s">
+      <c r="B278" t="s">
         <v>1377</v>
       </c>
       <c r="C278" s="20" t="s">
@@ -17400,7 +17436,7 @@
       <c r="F278" s="67" t="s">
         <v>1380</v>
       </c>
-      <c r="G278" s="0" t="s">
+      <c r="G278" t="s">
         <v>1381</v>
       </c>
       <c r="K278" s="68" t="s">
@@ -17410,11 +17446,11 @@
         <v>18980343526</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" spans="1:12">
       <c r="A279" s="19">
         <v>278</v>
       </c>
-      <c r="B279" s="0" t="s">
+      <c r="B279" t="s">
         <v>1382</v>
       </c>
       <c r="C279" s="20" t="s">
@@ -17426,21 +17462,21 @@
       <c r="E279" s="67" t="s">
         <v>1383</v>
       </c>
-      <c r="F279" s="0" t="s">
+      <c r="F279" t="s">
         <v>1384</v>
       </c>
-      <c r="G279" s="0" t="s">
+      <c r="G279" t="s">
         <v>1385</v>
       </c>
       <c r="L279" s="20">
         <v>18008210260</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" spans="1:12">
       <c r="A280" s="19">
         <v>279</v>
       </c>
-      <c r="B280" s="0" t="s">
+      <c r="B280" t="s">
         <v>1386</v>
       </c>
       <c r="C280" s="20" t="s">
@@ -17455,18 +17491,18 @@
       <c r="F280" s="67" t="s">
         <v>1388</v>
       </c>
-      <c r="G280" s="0" t="s">
+      <c r="G280" t="s">
         <v>1389</v>
       </c>
       <c r="L280" s="20">
         <v>17763464579</v>
       </c>
     </row>
-    <row r="281" ht="14.15" customHeight="1">
+    <row r="281" spans="1:12" ht="14.15" customHeight="1">
       <c r="A281" s="19">
         <v>280</v>
       </c>
-      <c r="B281" s="0" t="s">
+      <c r="B281" t="s">
         <v>1390</v>
       </c>
       <c r="C281" s="20" t="s">
@@ -17481,18 +17517,18 @@
       <c r="F281" s="67" t="s">
         <v>1392</v>
       </c>
-      <c r="G281" s="0" t="s">
+      <c r="G281" t="s">
         <v>1393</v>
       </c>
       <c r="L281" s="20">
         <v>18080502583</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" spans="1:12">
       <c r="A282" s="19">
         <v>281</v>
       </c>
-      <c r="B282" s="0" t="s">
+      <c r="B282" t="s">
         <v>1394</v>
       </c>
       <c r="C282" s="20" t="s">
@@ -17501,7 +17537,7 @@
       <c r="D282" s="20" t="s">
         <v>1395</v>
       </c>
-      <c r="E282" s="0" t="s">
+      <c r="E282" t="s">
         <v>1395</v>
       </c>
       <c r="F282" s="67" t="s">
@@ -17511,11 +17547,11 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" spans="1:12">
       <c r="A283" s="19">
         <v>282</v>
       </c>
-      <c r="B283" s="0" t="s">
+      <c r="B283" t="s">
         <v>1398</v>
       </c>
       <c r="C283" s="20" t="s">
@@ -17524,13 +17560,13 @@
       <c r="D283" s="20" t="s">
         <v>1399</v>
       </c>
-      <c r="E283" s="0" t="s">
+      <c r="E283" t="s">
         <v>1399</v>
       </c>
       <c r="F283" s="67" t="s">
         <v>1400</v>
       </c>
-      <c r="G283" s="0" t="s">
+      <c r="G283" t="s">
         <v>1401</v>
       </c>
       <c r="H283" s="68" t="s">
@@ -17540,11 +17576,11 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" spans="1:12">
       <c r="A284" s="19">
         <v>283</v>
       </c>
-      <c r="B284" s="0" t="s">
+      <c r="B284" t="s">
         <v>1404</v>
       </c>
       <c r="C284" s="20" t="s">
@@ -17553,21 +17589,21 @@
       <c r="D284" s="20" t="s">
         <v>1405</v>
       </c>
-      <c r="E284" s="0" t="s">
+      <c r="E284" t="s">
         <v>1405</v>
       </c>
       <c r="F284" s="67" t="s">
         <v>1406</v>
       </c>
-      <c r="G284" s="0" t="s">
+      <c r="G284" t="s">
         <v>1401</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" spans="1:12">
       <c r="A285" s="19">
         <v>284</v>
       </c>
-      <c r="B285" s="0" t="s">
+      <c r="B285" t="s">
         <v>1407</v>
       </c>
       <c r="C285" s="20" t="s">
@@ -17580,11 +17616,11 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" spans="1:12">
       <c r="A286" s="19">
         <v>285</v>
       </c>
-      <c r="B286" s="0" t="s">
+      <c r="B286" t="s">
         <v>1409</v>
       </c>
       <c r="C286" s="20" t="s">
@@ -17593,21 +17629,21 @@
       <c r="D286" s="20" t="s">
         <v>1410</v>
       </c>
-      <c r="E286" s="0" t="s">
+      <c r="E286" t="s">
         <v>1410</v>
       </c>
       <c r="F286" s="67" t="s">
         <v>1411</v>
       </c>
-      <c r="G286" s="0" t="s">
+      <c r="G286" t="s">
         <v>1401</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" spans="1:12">
       <c r="A287" s="19">
         <v>286</v>
       </c>
-      <c r="B287" s="0" t="s">
+      <c r="B287" t="s">
         <v>1412</v>
       </c>
       <c r="C287" s="20" t="s">
@@ -17616,21 +17652,21 @@
       <c r="D287" s="20" t="s">
         <v>1413</v>
       </c>
-      <c r="E287" s="0" t="s">
+      <c r="E287" t="s">
         <v>1413</v>
       </c>
       <c r="F287" s="67" t="s">
         <v>1414</v>
       </c>
-      <c r="G287" s="0" t="s">
+      <c r="G287" t="s">
         <v>1401</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" spans="1:12">
       <c r="A288" s="19">
         <v>287</v>
       </c>
-      <c r="B288" s="0" t="s">
+      <c r="B288" t="s">
         <v>1415</v>
       </c>
       <c r="C288" s="20" t="s">
@@ -17643,11 +17679,11 @@
         <v>3210049</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" spans="1:13">
       <c r="A289" s="19">
         <v>288</v>
       </c>
-      <c r="B289" s="0" t="s">
+      <c r="B289" t="s">
         <v>1416</v>
       </c>
       <c r="C289" s="20" t="s">
@@ -17662,21 +17698,21 @@
       <c r="F289" s="67" t="s">
         <v>1418</v>
       </c>
-      <c r="G289" s="0" t="s">
+      <c r="G289" t="s">
         <v>972</v>
       </c>
       <c r="L289" s="20">
         <v>13689068809</v>
       </c>
-      <c r="M289" s="0" t="s">
+      <c r="M289" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" spans="1:13">
       <c r="A290" s="19">
         <v>289</v>
       </c>
-      <c r="B290" s="0" t="s">
+      <c r="B290" t="s">
         <v>1419</v>
       </c>
       <c r="C290" s="20" t="s">
@@ -17691,21 +17727,21 @@
       <c r="F290" s="67" t="s">
         <v>1421</v>
       </c>
-      <c r="G290" s="0" t="s">
+      <c r="G290" t="s">
         <v>1422</v>
       </c>
       <c r="L290" s="20">
         <v>13397191921</v>
       </c>
-      <c r="M290" s="0" t="s">
+      <c r="M290" t="s">
         <v>1423</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" spans="1:13">
       <c r="A291" s="19">
         <v>290</v>
       </c>
-      <c r="B291" s="0" t="s">
+      <c r="B291" t="s">
         <v>1424</v>
       </c>
       <c r="C291" s="20" t="s">
@@ -17720,7 +17756,7 @@
       <c r="F291" s="67" t="s">
         <v>1426</v>
       </c>
-      <c r="G291" s="0" t="s">
+      <c r="G291" t="s">
         <v>1427</v>
       </c>
       <c r="H291" s="68" t="s">
@@ -17730,11 +17766,11 @@
         <v>15775883745</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" spans="1:13">
       <c r="A292" s="19">
         <v>291</v>
       </c>
-      <c r="B292" s="0" t="s">
+      <c r="B292" t="s">
         <v>1429</v>
       </c>
       <c r="C292" s="20" t="s">
@@ -17746,21 +17782,21 @@
       <c r="E292" s="67" t="s">
         <v>1430</v>
       </c>
-      <c r="F292" s="0" t="s">
+      <c r="F292" t="s">
         <v>1431</v>
       </c>
-      <c r="G292" s="0" t="s">
+      <c r="G292" t="s">
         <v>1432</v>
       </c>
       <c r="L292" s="20">
         <v>18030588167</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" spans="1:13">
       <c r="A293" s="19">
         <v>292</v>
       </c>
-      <c r="B293" s="0" t="s">
+      <c r="B293" t="s">
         <v>1433</v>
       </c>
       <c r="C293" s="20" t="s">
@@ -17775,14 +17811,14 @@
       <c r="F293" s="67" t="s">
         <v>1435</v>
       </c>
-      <c r="G293" s="0" t="s">
+      <c r="G293" t="s">
         <v>1436</v>
       </c>
       <c r="H293" s="68" t="s">
         <v>1437</v>
       </c>
     </row>
-    <row r="294" ht="15.5">
+    <row r="294" spans="1:13" ht="15.5">
       <c r="A294" s="19">
         <v>293</v>
       </c>
@@ -17793,18 +17829,17 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -17813,14 +17848,14 @@
   <dimension ref="A1:R3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="20.25" customWidth="1" style="9"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1" style="10"/>
-    <col min="3" max="3" width="9.83203125" customWidth="1" style="10"/>
-    <col min="4" max="7" width="16" customWidth="1" style="10"/>
-    <col min="8" max="8" width="21.08203125" customWidth="1" style="11"/>
-    <col min="9" max="9" width="19.58203125" customWidth="1" style="11"/>
-    <col min="10" max="10" width="21.25" customWidth="1" style="11"/>
-    <col min="11" max="11" width="20.5" customWidth="1" style="11"/>
+    <col min="1" max="1" width="20.25" style="9" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" style="10" customWidth="1"/>
+    <col min="4" max="7" width="16" style="10" customWidth="1"/>
+    <col min="8" max="8" width="21.08203125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="19.58203125" style="11" customWidth="1"/>
+    <col min="10" max="10" width="21.25" style="11" customWidth="1"/>
+    <col min="11" max="11" width="20.5" style="11" customWidth="1"/>
     <col min="12" max="12" width="22.58203125" customWidth="1"/>
     <col min="13" max="13" width="14.75" customWidth="1"/>
     <col min="14" max="14" width="17.58203125" customWidth="1"/>
@@ -17828,7 +17863,7 @@
     <col min="16" max="16" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="107" s="8" customFormat="1">
+    <row r="1" spans="1:18" s="8" customFormat="1" ht="107">
       <c r="A1" s="12" t="s">
         <v>1439</v>
       </c>
@@ -17884,27 +17919,26 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:18">
       <c r="B2" s="15"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:18">
       <c r="B3" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AM4"/>
+  <dimension ref="A1:AM30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="4" max="4" bestFit="1" width="12.1640625" customWidth="1"/>
-    <col min="5" max="5" bestFit="1" width="73.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="73.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="14.58203125" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
@@ -17915,19 +17949,19 @@
     <col min="14" max="14" width="11.08203125" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
     <col min="18" max="18" width="13.25" customWidth="1"/>
-    <col min="19" max="19" width="8" customWidth="1"/>
+    <col min="19" max="19" width="13.4140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13.83203125" customWidth="1"/>
-    <col min="25" max="25" bestFit="1" width="13.4140625" customWidth="1" style="84"/>
+    <col min="25" max="25" width="13.4140625" style="84" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="13.33203125" customWidth="1"/>
     <col min="31" max="31" width="11.5" customWidth="1"/>
     <col min="33" max="33" width="9.33203125" customWidth="1"/>
     <col min="34" max="34" width="16" customWidth="1"/>
     <col min="35" max="35" width="14.33203125" customWidth="1"/>
-    <col min="36" max="36" bestFit="1" width="73.6640625" customWidth="1"/>
-    <col min="39" max="39" bestFit="1" width="7.5" customWidth="1"/>
+    <col min="36" max="36" width="73.6640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" s="1" customFormat="1">
+    <row r="1" spans="1:39" s="1" customFormat="1" ht="42">
       <c r="A1" s="2" t="s">
         <v>1457</v>
       </c>
@@ -17950,7 +17984,7 @@
         <v>403</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>1463</v>
+        <v>1515</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>1464</v>
@@ -18046,61 +18080,63 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:39">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
-        <v>1495</v>
-      </c>
+      <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3">
         <v>1</v>
       </c>
-      <c r="H2" s="3">
-        <v>5070016</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="H2">
+        <v>5130008</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1516</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>1497</v>
-      </c>
       <c r="K2" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>1498</v>
-      </c>
-      <c r="O2" s="78" t="s">
-        <v>361</v>
-      </c>
-      <c r="P2" s="78">
+        <v>1496</v>
+      </c>
+      <c r="N2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1518</v>
+      </c>
+      <c r="P2">
         <v>2</v>
       </c>
-      <c r="Q2" s="3" t="s">
-        <v>1499</v>
-      </c>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>1500</v>
-      </c>
-      <c r="V2" s="3">
-        <v>3600</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>1497</v>
+      <c r="Q2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="R2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="S2" t="s">
+        <v>1521</v>
+      </c>
+      <c r="T2" t="s">
+        <v>1522</v>
+      </c>
+      <c r="U2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="V2">
+        <v>100</v>
+      </c>
+      <c r="W2" t="s">
+        <v>1522</v>
       </c>
       <c r="X2" s="3" t="s">
         <v>22</v>
@@ -18109,17 +18145,17 @@
         <v>5070016</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="AA2" s="3">
-        <v>3500</v>
+        <v>50</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="AC2" s="3"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:39">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -18150,74 +18186,66 @@
         <v>993</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="AA3" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="AC3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="AE3" s="7" t="s">
+        <v>1501</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="AG3" s="3" t="s">
         <v>1503</v>
       </c>
-      <c r="AF3" s="3" t="s">
-        <v>1504</v>
-      </c>
-      <c r="AG3" s="3" t="s">
-        <v>1505</v>
-      </c>
       <c r="AH3" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>1497</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39">
       <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
-        <v>1506</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>1507</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1508</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1509</v>
-      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
         <v>2</v>
       </c>
       <c r="H4" s="3">
-        <v>5070016</v>
+        <v>123445</v>
       </c>
       <c r="I4" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>1496</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>1497</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>1498</v>
       </c>
       <c r="O4" s="78" t="s">
         <v>386</v>
@@ -18226,21 +18254,21 @@
         <v>5</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>1510</v>
+        <v>1504</v>
       </c>
       <c r="V4" s="3">
         <v>560</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="X4" s="3" t="s">
         <v>22</v>
@@ -18249,41 +18277,170 @@
         <v>5110016</v>
       </c>
       <c r="Z4" s="78" t="s">
-        <v>1511</v>
+        <v>1505</v>
       </c>
       <c r="AA4" s="3">
         <v>560</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="AC4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="AE4" s="7" t="s">
+        <v>1501</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="AG4" s="3" t="s">
         <v>1503</v>
       </c>
-      <c r="AF4" s="3" t="s">
-        <v>1504</v>
-      </c>
-      <c r="AG4" s="3" t="s">
-        <v>1505</v>
-      </c>
       <c r="AH4" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="AI4" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39">
+      <c r="J5" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39">
+      <c r="J6" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39">
+      <c r="J7" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39">
+      <c r="J8" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39">
+      <c r="J9" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39">
+      <c r="J10" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39">
+      <c r="J11" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39">
+      <c r="J12" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39">
+      <c r="J13" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39">
+      <c r="J14" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39">
+      <c r="J15" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39">
+      <c r="J16" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="17" spans="10:10">
+      <c r="J17" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="18" spans="10:10">
+      <c r="J18" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="19" spans="10:10">
+      <c r="J19" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="20" spans="10:10">
+      <c r="J20" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="21" spans="10:10">
+      <c r="J21" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="22" spans="10:10">
+      <c r="J22" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="23" spans="10:10">
+      <c r="J23" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="24" spans="10:10">
+      <c r="J24" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="25" spans="10:10">
+      <c r="J25" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="26" spans="10:10">
+      <c r="J26" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="27" spans="10:10">
+      <c r="J27" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="28" spans="10:10">
+      <c r="J28" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="29" spans="10:10">
+      <c r="J29" s="3" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="30" spans="10:10">
+      <c r="J30" s="3" t="s">
+        <v>1496</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18292,10 +18449,10 @@
   <dimension ref="A1:AN3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="28" max="28" bestFit="1" width="13.4140625" customWidth="1"/>
+    <col min="28" max="28" width="13.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42">
+    <row r="1" spans="1:40" ht="42">
       <c r="A1" s="2" t="s">
         <v>1457</v>
       </c>
@@ -18327,13 +18484,13 @@
         <v>1465</v>
       </c>
       <c r="K1" s="85" t="s">
-        <v>1512</v>
+        <v>1506</v>
       </c>
       <c r="L1" s="85" t="s">
         <v>1466</v>
       </c>
       <c r="M1" s="85" t="s">
-        <v>1512</v>
+        <v>1506</v>
       </c>
       <c r="N1" s="85" t="s">
         <v>1467</v>
@@ -18342,10 +18499,10 @@
         <v>1468</v>
       </c>
       <c r="P1" s="86" t="s">
-        <v>1512</v>
+        <v>1506</v>
       </c>
       <c r="Q1" s="86" t="s">
-        <v>1513</v>
+        <v>1507</v>
       </c>
       <c r="R1" s="86" t="s">
         <v>1470</v>
@@ -18381,7 +18538,7 @@
         <v>1480</v>
       </c>
       <c r="AC1" s="86" t="s">
-        <v>1512</v>
+        <v>1506</v>
       </c>
       <c r="AD1" s="86" t="s">
         <v>1481</v>
@@ -18393,7 +18550,7 @@
         <v>1483</v>
       </c>
       <c r="AG1" s="86" t="s">
-        <v>1512</v>
+        <v>1506</v>
       </c>
       <c r="AH1" s="86" t="s">
         <v>1484</v>
@@ -18411,74 +18568,74 @@
         <v>1488</v>
       </c>
       <c r="AM1" s="86" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AN1" s="86" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>5130008</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="R2" t="s">
+        <v>250</v>
+      </c>
+      <c r="S2">
+        <v>2</v>
+      </c>
+      <c r="T2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="U2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="V2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="W2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="X2" t="s">
         <v>1512</v>
       </c>
-      <c r="AN1" s="86" t="s">
-        <v>1514</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="G2" s="0">
-        <v>1</v>
-      </c>
-      <c r="H2" s="0">
-        <v>5130008</v>
-      </c>
-      <c r="I2" s="0" t="s">
-        <v>1515</v>
-      </c>
-      <c r="J2" s="0" t="s">
-        <v>1497</v>
-      </c>
-      <c r="K2" s="0">
-        <v>5</v>
-      </c>
-      <c r="L2" s="0" t="s">
-        <v>1497</v>
-      </c>
-      <c r="M2" s="0">
-        <v>0</v>
-      </c>
-      <c r="N2" s="0" t="s">
-        <v>1497</v>
-      </c>
-      <c r="O2" s="0" t="s">
-        <v>1497</v>
-      </c>
-      <c r="P2" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="0" t="s">
-        <v>1498</v>
-      </c>
-      <c r="R2" s="0" t="s">
-        <v>250</v>
-      </c>
-      <c r="S2" s="0">
-        <v>2</v>
-      </c>
-      <c r="T2" s="0" t="s">
-        <v>1499</v>
-      </c>
-      <c r="U2" s="0" t="s">
-        <v>1516</v>
-      </c>
-      <c r="V2" s="0" t="s">
-        <v>1517</v>
-      </c>
-      <c r="W2" s="0" t="s">
-        <v>1497</v>
-      </c>
-      <c r="X2" s="0" t="s">
-        <v>1518</v>
-      </c>
-      <c r="Y2" s="0">
+      <c r="Y2">
         <v>100</v>
       </c>
-      <c r="Z2" s="0" t="s">
-        <v>1497</v>
-      </c>
-      <c r="AA2" s="0" t="s">
+      <c r="Z2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AA2" t="s">
         <v>22</v>
       </c>
       <c r="AB2" s="88">
@@ -18487,22 +18644,22 @@
       <c r="AC2" s="88">
         <v>3</v>
       </c>
-      <c r="AD2" s="0" t="s">
-        <v>1519</v>
-      </c>
-      <c r="AE2" s="0">
+      <c r="AD2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="AE2">
         <v>50</v>
       </c>
-      <c r="AF2" s="0" t="s">
-        <v>1497</v>
-      </c>
-      <c r="AG2" s="0">
+      <c r="AF2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AG2">
         <v>3</v>
       </c>
       <c r="AJ2" s="84"/>
     </row>
-    <row r="3">
-      <c r="G3" s="0">
+    <row r="3" spans="1:40">
+      <c r="G3">
         <v>1</v>
       </c>
       <c r="AB3" s="88">
@@ -18511,75 +18668,74 @@
       <c r="AC3" s="88">
         <v>3</v>
       </c>
-      <c r="AD3" s="0" t="s">
+      <c r="AD3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="AE3">
+        <v>50</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AG3">
+        <v>3</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AJ3" s="84" t="s">
+        <v>1514</v>
+      </c>
+      <c r="AK3" s="20" t="s">
         <v>1502</v>
       </c>
-      <c r="AE3" s="0">
-        <v>50</v>
-      </c>
-      <c r="AF3" s="0" t="s">
-        <v>1497</v>
-      </c>
-      <c r="AG3" s="0">
-        <v>3</v>
-      </c>
-      <c r="AH3" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="AI3" s="0" t="s">
-        <v>1497</v>
-      </c>
-      <c r="AJ3" s="84" t="s">
-        <v>1520</v>
-      </c>
-      <c r="AK3" s="20" t="s">
-        <v>1504</v>
-      </c>
-      <c r="AL3" s="0" t="s">
-        <v>1505</v>
-      </c>
-      <c r="AM3" s="0">
+      <c r="AL3" t="s">
+        <v>1503</v>
+      </c>
+      <c r="AM3">
         <v>5</v>
       </c>
-      <c r="AN3" s="0" t="s">
-        <v>1497</v>
+      <c r="AN3" t="s">
+        <v>1496</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Auto Finan/420财务050823.xlsx
+++ b/Auto Finan/420财务050823.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FH\source\repos\Auto Finan\Auto Finan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AFA90A-3ED9-4596-B0B6-C36857EDEE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F615D9-C088-44B2-B69A-D416451E1009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1820" yWindow="7170" windowWidth="17380" windowHeight="4130" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,14 +5255,15 @@
     <t>*3275</t>
   </si>
   <si>
-    <t>2025-09-10</t>
-  </si>
-  <si>
     <t>招商银行股份有限公司杭州海创园小微企业专营支行</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
-    <t>交通补助</t>
+    <t>交通补贴</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-09-28</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -19541,7 +19542,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:BP76"/>
+  <dimension ref="A1:BO76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="13" max="13" width="15.08203125" customWidth="1"/>
@@ -19557,14 +19558,15 @@
     <col min="47" max="47" width="11.9140625" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="19.9140625" bestFit="1" customWidth="1"/>
     <col min="50" max="51" width="12.9140625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.9140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="17.75" style="84" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="45.75" bestFit="1" customWidth="1"/>
-    <col min="56" max="57" width="12.9140625" customWidth="1"/>
-    <col min="58" max="58" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="14.9140625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="17.75" style="84" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="45.75" bestFit="1" customWidth="1"/>
+    <col min="55" max="56" width="12.9140625" customWidth="1"/>
+    <col min="57" max="57" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="11.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="42">
+    <row r="1" spans="1:67" ht="42">
       <c r="A1" s="2" t="s">
         <v>1462</v>
       </c>
@@ -19701,7 +19703,7 @@
         <v>1488</v>
       </c>
       <c r="AT1" s="86" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="AU1" s="86" t="s">
         <v>1532</v>
@@ -19718,56 +19720,56 @@
       <c r="AY1" s="5" t="s">
         <v>1486</v>
       </c>
-      <c r="BA1" s="5" t="s">
+      <c r="AZ1" s="5" t="s">
         <v>1534</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>1535</v>
       </c>
+      <c r="BB1" s="5" t="s">
+        <v>1536</v>
+      </c>
       <c r="BC1" s="5" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
       <c r="BD1" s="5" t="s">
-        <v>1533</v>
-      </c>
-      <c r="BE1" s="5" t="s">
         <v>1487</v>
       </c>
+      <c r="BE1" s="86" t="s">
+        <v>1488</v>
+      </c>
       <c r="BF1" s="86" t="s">
-        <v>1488</v>
-      </c>
-      <c r="BG1" s="86" t="s">
         <v>1537</v>
       </c>
-      <c r="BH1" s="87" t="s">
+      <c r="BG1" s="87" t="s">
         <v>1490</v>
       </c>
+      <c r="BH1" s="86" t="s">
+        <v>1491</v>
+      </c>
       <c r="BI1" s="86" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="BJ1" s="86" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="BK1" s="86" t="s">
-        <v>1493</v>
-      </c>
-      <c r="BL1" s="86" t="s">
         <v>1538</v>
       </c>
-      <c r="BM1" s="5" t="s">
+      <c r="BL1" s="5" t="s">
         <v>1495</v>
       </c>
+      <c r="BM1" s="1" t="s">
+        <v>1496</v>
+      </c>
       <c r="BN1" s="1" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>1497</v>
-      </c>
-      <c r="BP1" s="1" t="s">
         <v>1498</v>
       </c>
     </row>
-    <row r="2" spans="1:68">
+    <row r="2" spans="1:67">
       <c r="C2" t="s">
         <v>1539</v>
       </c>
@@ -19852,14 +19854,14 @@
         <v>1500</v>
       </c>
       <c r="AW2" s="88"/>
+      <c r="BJ2" t="s">
+        <v>1500</v>
+      </c>
       <c r="BK2" t="s">
         <v>1500</v>
       </c>
-      <c r="BL2" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:68">
+    </row>
+    <row r="3" spans="1:67">
       <c r="F3">
         <v>1</v>
       </c>
@@ -19920,14 +19922,14 @@
         <v>1500</v>
       </c>
       <c r="AW3" s="88"/>
+      <c r="BJ3" t="s">
+        <v>1500</v>
+      </c>
       <c r="BK3" t="s">
         <v>1500</v>
       </c>
-      <c r="BL3" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:68">
+    </row>
+    <row r="4" spans="1:67">
       <c r="F4">
         <v>1</v>
       </c>
@@ -19988,26 +19990,26 @@
         <v>1500</v>
       </c>
       <c r="AW4" s="88"/>
-      <c r="BG4" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BH4" s="84" t="s">
+      <c r="BF4" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BG4" s="84" t="s">
         <v>1544</v>
       </c>
-      <c r="BI4" s="20" t="s">
+      <c r="BH4" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI4" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ4" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK4" t="s">
         <v>1500</v>
       </c>
-      <c r="BL4" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:68">
+    </row>
+    <row r="5" spans="1:67">
       <c r="F5">
         <v>1</v>
       </c>
@@ -20068,23 +20070,23 @@
         <v>1500</v>
       </c>
       <c r="AW5" s="88"/>
-      <c r="BG5" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI5" s="20" t="s">
+      <c r="BF5" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH5" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI5" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ5" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK5" t="s">
         <v>1500</v>
       </c>
-      <c r="BL5" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:68">
+    </row>
+    <row r="6" spans="1:67">
       <c r="F6">
         <v>1</v>
       </c>
@@ -20170,23 +20172,23 @@
         <v>1500</v>
       </c>
       <c r="AW6" s="88"/>
-      <c r="BG6" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI6" s="20" t="s">
+      <c r="BF6" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH6" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI6" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ6" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK6" t="s">
         <v>1500</v>
       </c>
-      <c r="BL6" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:68">
+    </row>
+    <row r="7" spans="1:67">
       <c r="F7">
         <v>1</v>
       </c>
@@ -20236,23 +20238,23 @@
         <v>1500</v>
       </c>
       <c r="AW7" s="88"/>
-      <c r="BG7" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI7" s="20" t="s">
+      <c r="BF7" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH7" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI7" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ7" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK7" t="s">
         <v>1500</v>
       </c>
-      <c r="BL7" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:68">
+    </row>
+    <row r="8" spans="1:67">
       <c r="F8">
         <v>1</v>
       </c>
@@ -20302,23 +20304,23 @@
         <v>1500</v>
       </c>
       <c r="AW8" s="88"/>
-      <c r="BG8" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI8" s="20" t="s">
+      <c r="BF8" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH8" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI8" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ8" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK8" t="s">
         <v>1500</v>
       </c>
-      <c r="BL8" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:68">
+    </row>
+    <row r="9" spans="1:67">
       <c r="F9">
         <v>1</v>
       </c>
@@ -20368,23 +20370,23 @@
         <v>1500</v>
       </c>
       <c r="AW9" s="88"/>
-      <c r="BG9" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI9" s="20" t="s">
+      <c r="BF9" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH9" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI9" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ9" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK9" t="s">
         <v>1500</v>
       </c>
-      <c r="BL9" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="10" spans="1:68">
+    </row>
+    <row r="10" spans="1:67">
       <c r="F10">
         <v>1</v>
       </c>
@@ -20451,26 +20453,26 @@
       <c r="AY10">
         <v>942</v>
       </c>
-      <c r="BE10" s="3" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BG10" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI10" s="20" t="s">
+      <c r="BD10" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH10" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI10" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ10" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK10" t="s">
         <v>1500</v>
       </c>
-      <c r="BL10" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:68">
+    </row>
+    <row r="11" spans="1:67">
       <c r="F11">
         <v>1</v>
       </c>
@@ -20506,38 +20508,38 @@
       <c r="AY11">
         <v>700</v>
       </c>
-      <c r="BA11" s="89" t="s">
+      <c r="AZ11" s="89" t="s">
         <v>1555</v>
       </c>
-      <c r="BB11" s="84" t="s">
+      <c r="BA11" s="84" t="s">
         <v>1214</v>
       </c>
+      <c r="BB11" s="89" t="s">
+        <v>1215</v>
+      </c>
       <c r="BC11" s="89" t="s">
-        <v>1215</v>
-      </c>
-      <c r="BD11" s="89" t="s">
         <v>1368</v>
       </c>
-      <c r="BE11" s="3" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BG11" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI11" s="20" t="s">
+      <c r="BD11" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH11" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI11" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ11" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK11" t="s">
         <v>1500</v>
       </c>
-      <c r="BL11" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:68">
+    </row>
+    <row r="12" spans="1:67">
       <c r="F12">
         <v>1</v>
       </c>
@@ -20576,38 +20578,38 @@
       <c r="AY12">
         <v>700</v>
       </c>
-      <c r="BA12" s="89" t="s">
+      <c r="AZ12" s="89" t="s">
         <v>1555</v>
       </c>
-      <c r="BB12" s="91" t="s">
+      <c r="BA12" s="91" t="s">
         <v>1214</v>
       </c>
+      <c r="BB12" s="89" t="s">
+        <v>1557</v>
+      </c>
       <c r="BC12" s="89" t="s">
-        <v>1558</v>
-      </c>
-      <c r="BD12" s="89" t="s">
         <v>1212</v>
       </c>
-      <c r="BE12" s="3" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BG12" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI12" s="20" t="s">
+      <c r="BD12" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH12" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI12" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ12" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK12" t="s">
         <v>1500</v>
       </c>
-      <c r="BL12" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="13" spans="1:68">
+    </row>
+    <row r="13" spans="1:67">
       <c r="F13">
         <v>1</v>
       </c>
@@ -20643,26 +20645,26 @@
       <c r="AY13">
         <v>700</v>
       </c>
-      <c r="BE13" s="3" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BG13" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI13" s="20" t="s">
+      <c r="BD13" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BF13" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH13" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI13" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ13" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK13" t="s">
         <v>1500</v>
       </c>
-      <c r="BL13" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:68">
+    </row>
+    <row r="14" spans="1:67">
       <c r="F14">
         <v>1</v>
       </c>
@@ -20698,32 +20700,32 @@
       <c r="AY14">
         <v>700</v>
       </c>
-      <c r="BE14" s="3" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BF14" s="89" t="s">
+      <c r="BD14" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BE14" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="BG14" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BH14" s="84" t="s">
-        <v>1557</v>
-      </c>
-      <c r="BI14" s="20" t="s">
+      <c r="BF14" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BG14" s="91" t="s">
+        <v>1559</v>
+      </c>
+      <c r="BH14" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI14" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ14" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK14" t="s">
         <v>1500</v>
       </c>
-      <c r="BL14" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:68">
+    </row>
+    <row r="15" spans="1:67">
       <c r="I15" t="s">
         <v>1500</v>
       </c>
@@ -20751,23 +20753,23 @@
         <v>1500</v>
       </c>
       <c r="AW15" s="88"/>
-      <c r="BG15" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI15" s="20" t="s">
+      <c r="BF15" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH15" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI15" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ15" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK15" t="s">
         <v>1500</v>
       </c>
-      <c r="BL15" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:68">
+    </row>
+    <row r="16" spans="1:67">
       <c r="I16" t="s">
         <v>1500</v>
       </c>
@@ -20795,23 +20797,23 @@
         <v>1500</v>
       </c>
       <c r="AW16" s="88"/>
-      <c r="BG16" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI16" s="20" t="s">
+      <c r="BF16" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH16" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI16" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ16" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK16" t="s">
         <v>1500</v>
       </c>
-      <c r="BL16" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="17" spans="9:64">
+    </row>
+    <row r="17" spans="9:63">
       <c r="I17" t="s">
         <v>1500</v>
       </c>
@@ -20839,23 +20841,23 @@
         <v>1500</v>
       </c>
       <c r="AW17" s="88"/>
-      <c r="BG17" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI17" s="20" t="s">
+      <c r="BF17" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH17" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI17" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ17" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK17" t="s">
         <v>1500</v>
       </c>
-      <c r="BL17" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="18" spans="9:64">
+    </row>
+    <row r="18" spans="9:63">
       <c r="I18" t="s">
         <v>1500</v>
       </c>
@@ -20883,23 +20885,23 @@
         <v>1500</v>
       </c>
       <c r="AW18" s="88"/>
-      <c r="BG18" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI18" s="20" t="s">
+      <c r="BF18" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH18" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI18" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ18" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK18" t="s">
         <v>1500</v>
       </c>
-      <c r="BL18" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="19" spans="9:64">
+    </row>
+    <row r="19" spans="9:63">
       <c r="I19" t="s">
         <v>1500</v>
       </c>
@@ -20927,23 +20929,23 @@
         <v>1500</v>
       </c>
       <c r="AW19" s="88"/>
-      <c r="BG19" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI19" s="20" t="s">
+      <c r="BF19" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH19" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI19" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ19" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK19" t="s">
         <v>1500</v>
       </c>
-      <c r="BL19" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="20" spans="9:64">
+    </row>
+    <row r="20" spans="9:63">
       <c r="I20" t="s">
         <v>1500</v>
       </c>
@@ -20971,23 +20973,23 @@
         <v>1500</v>
       </c>
       <c r="AW20" s="88"/>
-      <c r="BG20" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI20" s="20" t="s">
+      <c r="BF20" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH20" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI20" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ20" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK20" t="s">
         <v>1500</v>
       </c>
-      <c r="BL20" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="21" spans="9:64">
+    </row>
+    <row r="21" spans="9:63">
       <c r="I21" t="s">
         <v>1500</v>
       </c>
@@ -21015,23 +21017,23 @@
         <v>1500</v>
       </c>
       <c r="AW21" s="88"/>
-      <c r="BG21" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI21" s="20" t="s">
+      <c r="BF21" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH21" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI21" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ21" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK21" t="s">
         <v>1500</v>
       </c>
-      <c r="BL21" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="22" spans="9:64">
+    </row>
+    <row r="22" spans="9:63">
       <c r="I22" t="s">
         <v>1500</v>
       </c>
@@ -21059,23 +21061,23 @@
         <v>1500</v>
       </c>
       <c r="AW22" s="88"/>
-      <c r="BG22" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI22" s="20" t="s">
+      <c r="BF22" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH22" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI22" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ22" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK22" t="s">
         <v>1500</v>
       </c>
-      <c r="BL22" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="23" spans="9:64">
+    </row>
+    <row r="23" spans="9:63">
       <c r="I23" t="s">
         <v>1500</v>
       </c>
@@ -21103,23 +21105,23 @@
         <v>1500</v>
       </c>
       <c r="AW23" s="88"/>
-      <c r="BG23" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI23" s="20" t="s">
+      <c r="BF23" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH23" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI23" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ23" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK23" t="s">
         <v>1500</v>
       </c>
-      <c r="BL23" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="24" spans="9:64">
+    </row>
+    <row r="24" spans="9:63">
       <c r="I24" t="s">
         <v>1500</v>
       </c>
@@ -21147,23 +21149,23 @@
         <v>1500</v>
       </c>
       <c r="AW24" s="88"/>
-      <c r="BG24" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI24" s="20" t="s">
+      <c r="BF24" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH24" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI24" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ24" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK24" t="s">
         <v>1500</v>
       </c>
-      <c r="BL24" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="25" spans="9:64">
+    </row>
+    <row r="25" spans="9:63">
       <c r="I25" t="s">
         <v>1500</v>
       </c>
@@ -21191,23 +21193,23 @@
         <v>1500</v>
       </c>
       <c r="AW25" s="88"/>
-      <c r="BG25" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI25" s="20" t="s">
+      <c r="BF25" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH25" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI25" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ25" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK25" t="s">
         <v>1500</v>
       </c>
-      <c r="BL25" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="26" spans="9:64">
+    </row>
+    <row r="26" spans="9:63">
       <c r="I26" t="s">
         <v>1500</v>
       </c>
@@ -21235,23 +21237,23 @@
         <v>1500</v>
       </c>
       <c r="AW26" s="88"/>
-      <c r="BG26" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI26" s="20" t="s">
+      <c r="BF26" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH26" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI26" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ26" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK26" t="s">
         <v>1500</v>
       </c>
-      <c r="BL26" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="27" spans="9:64">
+    </row>
+    <row r="27" spans="9:63">
       <c r="I27" t="s">
         <v>1500</v>
       </c>
@@ -21279,23 +21281,23 @@
         <v>1500</v>
       </c>
       <c r="AW27" s="88"/>
-      <c r="BG27" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BI27" s="20" t="s">
+      <c r="BF27" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BH27" s="20" t="s">
         <v>1509</v>
       </c>
+      <c r="BI27" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ27" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="BK27" t="s">
         <v>1500</v>
       </c>
-      <c r="BL27" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="28" spans="9:64">
+    </row>
+    <row r="28" spans="9:63">
       <c r="I28" t="s">
         <v>1500</v>
       </c>
@@ -21320,7 +21322,7 @@
       <c r="AJ28" s="84"/>
       <c r="AK28" s="84"/>
     </row>
-    <row r="29" spans="9:64">
+    <row r="29" spans="9:63">
       <c r="I29" t="s">
         <v>1500</v>
       </c>
@@ -21345,7 +21347,7 @@
       <c r="AJ29" s="84"/>
       <c r="AK29" s="84"/>
     </row>
-    <row r="30" spans="9:64">
+    <row r="30" spans="9:63">
       <c r="I30" t="s">
         <v>1500</v>
       </c>
@@ -21370,7 +21372,7 @@
       <c r="AJ30" s="84"/>
       <c r="AK30" s="84"/>
     </row>
-    <row r="31" spans="9:64">
+    <row r="31" spans="9:63">
       <c r="I31" t="s">
         <v>1500</v>
       </c>
@@ -21392,7 +21394,7 @@
       <c r="AJ31" s="84"/>
       <c r="AK31" s="84"/>
     </row>
-    <row r="32" spans="9:64">
+    <row r="32" spans="9:63">
       <c r="I32" t="s">
         <v>1500</v>
       </c>

--- a/Auto Finan/420财务050823.xlsx
+++ b/Auto Finan/420财务050823.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FH\source\repos\Auto Finan\Auto Finan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E1A01E-6A58-416B-AE0A-81F18035DBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1EBADA-B307-4F8E-8AD1-5A5B841A979E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3509" uniqueCount="1560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3514" uniqueCount="1560">
   <si>
     <t>教研室内部项目序号</t>
   </si>
@@ -19853,12 +19853,63 @@
       <c r="AE2" t="s">
         <v>1545</v>
       </c>
-      <c r="AJ2" s="84"/>
-      <c r="AK2" s="84"/>
+      <c r="AG2">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="AJ2" s="84" t="s">
+        <v>1548</v>
+      </c>
+      <c r="AK2" s="84" t="s">
+        <v>1549</v>
+      </c>
+      <c r="AO2">
+        <v>36</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
       <c r="AU2" t="s">
         <v>1500</v>
       </c>
-      <c r="AW2" s="88"/>
+      <c r="AV2" s="89" t="s">
+        <v>22</v>
+      </c>
+      <c r="AW2" s="88">
+        <v>202512091010</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>1556</v>
+      </c>
+      <c r="AY2">
+        <v>942</v>
+      </c>
+      <c r="BD2" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BG2" s="84" t="s">
+        <v>1546</v>
+      </c>
+      <c r="BH2" s="20" t="s">
+        <v>1509</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>1510</v>
+      </c>
       <c r="BJ2" t="s">
         <v>1500</v>
       </c>
@@ -19921,12 +19972,54 @@
       <c r="AE3" t="s">
         <v>1545</v>
       </c>
-      <c r="AJ3" s="84"/>
-      <c r="AK3" s="84"/>
+      <c r="AH3" t="s">
+        <v>1547</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>1547</v>
+      </c>
+      <c r="AJ3" s="84" t="s">
+        <v>1551</v>
+      </c>
+      <c r="AK3" s="84" t="s">
+        <v>1552</v>
+      </c>
+      <c r="AO3">
+        <v>76</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>1550</v>
+      </c>
       <c r="AU3" t="s">
         <v>1500</v>
       </c>
-      <c r="AW3" s="88"/>
+      <c r="AW3" s="95" t="s">
+        <v>1369</v>
+      </c>
+      <c r="AY3">
+        <v>700</v>
+      </c>
+      <c r="AZ3" s="89" t="s">
+        <v>1557</v>
+      </c>
+      <c r="BA3" s="84" t="s">
+        <v>1214</v>
+      </c>
+      <c r="BB3" s="89" t="s">
+        <v>1215</v>
+      </c>
+      <c r="BC3" s="89" t="s">
+        <v>1368</v>
+      </c>
+      <c r="BD3" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>1500</v>
+      </c>
       <c r="BJ3" t="s">
         <v>1500</v>
       </c>
@@ -19989,12 +20082,54 @@
       <c r="AE4" t="s">
         <v>1545</v>
       </c>
-      <c r="AJ4" s="84"/>
-      <c r="AK4" s="84"/>
+      <c r="AH4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="AJ4" s="84" t="s">
+        <v>1553</v>
+      </c>
+      <c r="AK4" s="84" t="s">
+        <v>1553</v>
+      </c>
+      <c r="AO4">
+        <v>58</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>1550</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>1550</v>
+      </c>
       <c r="AU4" t="s">
         <v>1500</v>
       </c>
-      <c r="AW4" s="88"/>
+      <c r="AW4" s="88" t="s">
+        <v>1213</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>1558</v>
+      </c>
+      <c r="AY4">
+        <v>700</v>
+      </c>
+      <c r="AZ4" s="89" t="s">
+        <v>1557</v>
+      </c>
+      <c r="BA4" s="91" t="s">
+        <v>1214</v>
+      </c>
+      <c r="BB4" s="89" t="s">
+        <v>1215</v>
+      </c>
+      <c r="BC4" s="89" t="s">
+        <v>1212</v>
+      </c>
+      <c r="BD4" s="3" t="s">
+        <v>1500</v>
+      </c>
       <c r="BF4" t="s">
         <v>1500</v>
       </c>
@@ -20069,12 +20204,39 @@
       <c r="AE5" t="s">
         <v>1545</v>
       </c>
-      <c r="AJ5" s="84"/>
-      <c r="AK5" s="84"/>
+      <c r="AH5" t="s">
+        <v>1547</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>1547</v>
+      </c>
+      <c r="AJ5" s="84" t="s">
+        <v>1554</v>
+      </c>
+      <c r="AK5" s="84" t="s">
+        <v>1554</v>
+      </c>
+      <c r="AO5">
+        <v>36</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>1550</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>1550</v>
+      </c>
       <c r="AU5" t="s">
         <v>1500</v>
       </c>
-      <c r="AW5" s="88"/>
+      <c r="AW5" s="92" t="s">
+        <v>1260</v>
+      </c>
+      <c r="AY5">
+        <v>700</v>
+      </c>
+      <c r="BD5" s="3" t="s">
+        <v>1500</v>
+      </c>
       <c r="BF5" t="s">
         <v>1500</v>
       </c>
@@ -20149,9 +20311,6 @@
       <c r="AF6">
         <v>1</v>
       </c>
-      <c r="AG6">
-        <v>1</v>
-      </c>
       <c r="AH6" t="s">
         <v>1547</v>
       </c>
@@ -20159,10 +20318,10 @@
         <v>1547</v>
       </c>
       <c r="AJ6" s="84" t="s">
-        <v>1548</v>
+        <v>1555</v>
       </c>
       <c r="AK6" s="84" t="s">
-        <v>1549</v>
+        <v>1555</v>
       </c>
       <c r="AO6">
         <v>36</v>
@@ -20173,10 +20332,24 @@
       <c r="AR6" t="s">
         <v>1550</v>
       </c>
+      <c r="AS6">
+        <v>1</v>
+      </c>
       <c r="AU6" t="s">
         <v>1500</v>
       </c>
-      <c r="AW6" s="88"/>
+      <c r="AW6" s="92" t="s">
+        <v>1332</v>
+      </c>
+      <c r="AY6">
+        <v>700</v>
+      </c>
+      <c r="BD6" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="BE6" s="89" t="s">
+        <v>22</v>
+      </c>
       <c r="BF6" t="s">
         <v>1500</v>
       </c>
@@ -20218,27 +20391,6 @@
       <c r="T7" s="90">
         <v>10</v>
       </c>
-      <c r="AH7" t="s">
-        <v>1547</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>1547</v>
-      </c>
-      <c r="AJ7" s="84" t="s">
-        <v>1551</v>
-      </c>
-      <c r="AK7" s="84" t="s">
-        <v>1552</v>
-      </c>
-      <c r="AO7">
-        <v>76</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>1550</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>1550</v>
-      </c>
       <c r="AU7" t="s">
         <v>1500</v>
       </c>
@@ -20284,27 +20436,6 @@
       <c r="T8" s="90">
         <v>10</v>
       </c>
-      <c r="AH8" t="s">
-        <v>1547</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>1547</v>
-      </c>
-      <c r="AJ8" s="84" t="s">
-        <v>1553</v>
-      </c>
-      <c r="AK8" s="84" t="s">
-        <v>1553</v>
-      </c>
-      <c r="AO8">
-        <v>58</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>1550</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>1550</v>
-      </c>
       <c r="AU8" t="s">
         <v>1500</v>
       </c>
@@ -20350,27 +20481,6 @@
       <c r="T9" s="90">
         <v>10</v>
       </c>
-      <c r="AH9" t="s">
-        <v>1547</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>1547</v>
-      </c>
-      <c r="AJ9" s="84" t="s">
-        <v>1554</v>
-      </c>
-      <c r="AK9" s="84" t="s">
-        <v>1554</v>
-      </c>
-      <c r="AO9">
-        <v>36</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>1550</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>1550</v>
-      </c>
       <c r="AU9" t="s">
         <v>1500</v>
       </c>
@@ -20416,49 +20526,7 @@
       <c r="T10" s="90">
         <v>10</v>
       </c>
-      <c r="AH10" t="s">
-        <v>1547</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>1547</v>
-      </c>
-      <c r="AJ10" s="84" t="s">
-        <v>1555</v>
-      </c>
-      <c r="AK10" s="84" t="s">
-        <v>1555</v>
-      </c>
-      <c r="AO10">
-        <v>36</v>
-      </c>
-      <c r="AQ10" t="s">
-        <v>1550</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>1550</v>
-      </c>
-      <c r="AS10">
-        <v>1</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
       <c r="AU10" t="s">
-        <v>1500</v>
-      </c>
-      <c r="AV10" s="89" t="s">
-        <v>22</v>
-      </c>
-      <c r="AW10" s="88">
-        <v>202512091010</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>1556</v>
-      </c>
-      <c r="AY10">
-        <v>942</v>
-      </c>
-      <c r="BD10" s="3" t="s">
         <v>1500</v>
       </c>
       <c r="BF10" t="s">
@@ -20507,27 +20575,6 @@
       <c r="AU11" t="s">
         <v>1500</v>
       </c>
-      <c r="AW11" s="95" t="s">
-        <v>1369</v>
-      </c>
-      <c r="AY11">
-        <v>700</v>
-      </c>
-      <c r="AZ11" s="89" t="s">
-        <v>1557</v>
-      </c>
-      <c r="BA11" s="84" t="s">
-        <v>1214</v>
-      </c>
-      <c r="BB11" s="89" t="s">
-        <v>1215</v>
-      </c>
-      <c r="BC11" s="89" t="s">
-        <v>1368</v>
-      </c>
-      <c r="BD11" s="3" t="s">
-        <v>1500</v>
-      </c>
       <c r="BF11" t="s">
         <v>1500</v>
       </c>
@@ -20574,30 +20621,6 @@
       <c r="AU12" t="s">
         <v>1500</v>
       </c>
-      <c r="AW12" s="88" t="s">
-        <v>1213</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>1558</v>
-      </c>
-      <c r="AY12">
-        <v>700</v>
-      </c>
-      <c r="AZ12" s="89" t="s">
-        <v>1557</v>
-      </c>
-      <c r="BA12" s="91" t="s">
-        <v>1214</v>
-      </c>
-      <c r="BB12" s="89" t="s">
-        <v>1215</v>
-      </c>
-      <c r="BC12" s="89" t="s">
-        <v>1212</v>
-      </c>
-      <c r="BD12" s="3" t="s">
-        <v>1500</v>
-      </c>
       <c r="BF12" t="s">
         <v>1500</v>
       </c>
@@ -20644,15 +20667,6 @@
       <c r="AU13" t="s">
         <v>1500</v>
       </c>
-      <c r="AW13" s="92" t="s">
-        <v>1260</v>
-      </c>
-      <c r="AY13">
-        <v>700</v>
-      </c>
-      <c r="BD13" s="3" t="s">
-        <v>1500</v>
-      </c>
       <c r="BF13" t="s">
         <v>1500</v>
       </c>
@@ -20699,18 +20713,6 @@
       <c r="AU14" t="s">
         <v>1500</v>
       </c>
-      <c r="AW14" s="92" t="s">
-        <v>1332</v>
-      </c>
-      <c r="AY14">
-        <v>700</v>
-      </c>
-      <c r="BD14" s="3" t="s">
-        <v>1500</v>
-      </c>
-      <c r="BE14" s="89" t="s">
-        <v>22</v>
-      </c>
       <c r="BF14" t="s">
         <v>1500</v>
       </c>
@@ -22182,7 +22184,7 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Auto Finan/420财务050823.xlsx
+++ b/Auto Finan/420财务050823.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FH\source\repos\Auto Finan\Auto Finan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1EBADA-B307-4F8E-8AD1-5A5B841A979E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE0A69D-DECB-4743-B046-624563D9A46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0-Proj信息" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3514" uniqueCount="1560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3585" uniqueCount="1615">
   <si>
     <t>教研室内部项目序号</t>
   </si>
@@ -5105,9 +5105,6 @@
     <t>*2818</t>
   </si>
   <si>
-    <t>*5054</t>
-  </si>
-  <si>
     <t>2025-09-14</t>
   </si>
   <si>
@@ -5263,6 +5260,229 @@
   <si>
     <t>C:\Users\FH\source\repos\Auto Finan\prints\6848002-3742.00-20250916_143130.pdf</t>
     <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>$点击</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-09-20</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>*5054</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录界面工号</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录界面密码</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录按钮</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>网上预约报账按钮</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>申请报销单按钮</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>已阅读并同意按钮</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择业务大类</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>报销项目号</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>附件张数</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊事项说明</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一步按钮1</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>人员类别</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>酬金性质</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>酬金信息备注</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>劳务费类型</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>发放事由</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>发放标准</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>开始时间</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>结束时间</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一步按钮2</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>单笔录入按钮</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>子序列开始</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>工号/证件号</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>单笔录入金额</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>单笔录入确定按钮</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>子序列结束</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回按钮</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>提交发放清单按钮</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>确定按钮</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>劳务预约时间</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>校区</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>预约按钮</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Uestc418</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>$点击</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>$$酬金业务</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>M112023ZHCG0006</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我是一条备注</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>我是特殊事项</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>学生</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>劳务费</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>事由</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>标准</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-08-01</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-08-30</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>340304200211110418</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>202422090508</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>$$清水河校区</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>$预约</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>$$其他(专项工作酬金)111</t>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5272,7 +5492,7 @@
   <numFmts count="1">
     <numFmt numFmtId="24" formatCode="\$#,##0_);[Red]\(\$#,##0\)"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5413,6 +5633,13 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -5537,7 +5764,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5786,6 +6013,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -19245,9 +19475,27 @@
         <v>50</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>1500</v>
+        <v>1559</v>
       </c>
       <c r="AC2" s="3"/>
+      <c r="AD2" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>1508</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>1509</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>1500</v>
+      </c>
     </row>
     <row r="3" spans="1:39">
       <c r="A3" s="3"/>
@@ -19256,59 +19504,33 @@
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="G3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
       <c r="X3" s="3"/>
-      <c r="Y3" s="7" t="s">
-        <v>997</v>
-      </c>
-      <c r="Z3" s="3" t="s">
-        <v>1507</v>
+      <c r="Y3" s="96">
+        <v>202422090507</v>
+      </c>
+      <c r="Z3" s="89" t="s">
+        <v>1562</v>
       </c>
       <c r="AA3" s="3">
         <v>50</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>1500</v>
+        <v>1559</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD3" s="3" t="s">
-        <v>1500</v>
-      </c>
-      <c r="AE3" s="7" t="s">
-        <v>1508</v>
-      </c>
-      <c r="AF3" s="3" t="s">
-        <v>1509</v>
-      </c>
-      <c r="AG3" s="3" t="s">
-        <v>1510</v>
-      </c>
-      <c r="AH3" s="3" t="s">
-        <v>1500</v>
-      </c>
-      <c r="AI3" s="3" t="s">
-        <v>1500</v>
-      </c>
+        <v>1560</v>
+      </c>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="7"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
     </row>
     <row r="4" spans="1:39">
       <c r="A4" s="3"/>
@@ -19324,7 +19546,7 @@
         <v>123445</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>1500</v>
@@ -19356,7 +19578,7 @@
         <v>1500</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="V4" s="3">
         <v>560</v>
@@ -19371,7 +19593,7 @@
         <v>5110016</v>
       </c>
       <c r="Z4" s="78" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="AA4" s="3">
         <v>560</v>
@@ -19386,13 +19608,13 @@
         <v>1500</v>
       </c>
       <c r="AE4" s="7" t="s">
+        <v>1507</v>
+      </c>
+      <c r="AF4" s="3" t="s">
         <v>1508</v>
       </c>
-      <c r="AF4" s="3" t="s">
+      <c r="AG4" s="3" t="s">
         <v>1509</v>
-      </c>
-      <c r="AG4" s="3" t="s">
-        <v>1510</v>
       </c>
       <c r="AH4" s="3" t="s">
         <v>1500</v>
@@ -19603,7 +19825,7 @@
         <v>1472</v>
       </c>
       <c r="M1" s="86" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="N1" s="86" t="s">
         <v>1474</v>
@@ -19624,40 +19846,40 @@
         <v>1479</v>
       </c>
       <c r="T1" s="86" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="U1" s="85" t="s">
         <v>1483</v>
       </c>
       <c r="V1" s="85" t="s">
+        <v>1515</v>
+      </c>
+      <c r="W1" s="85" t="s">
         <v>1516</v>
       </c>
-      <c r="W1" s="85" t="s">
-        <v>1517</v>
-      </c>
       <c r="X1" s="85" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="Y1" s="85" t="s">
         <v>408</v>
       </c>
       <c r="Z1" s="85" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="AA1" s="85" t="s">
+        <v>1517</v>
+      </c>
+      <c r="AB1" s="85" t="s">
+        <v>1514</v>
+      </c>
+      <c r="AC1" s="85" t="s">
         <v>1518</v>
       </c>
-      <c r="AB1" s="85" t="s">
-        <v>1515</v>
-      </c>
-      <c r="AC1" s="85" t="s">
+      <c r="AD1" s="85" t="s">
+        <v>1514</v>
+      </c>
+      <c r="AE1" s="85" t="s">
         <v>1519</v>
-      </c>
-      <c r="AD1" s="85" t="s">
-        <v>1515</v>
-      </c>
-      <c r="AE1" s="85" t="s">
-        <v>1520</v>
       </c>
       <c r="AF1" s="85" t="s">
         <v>1488</v>
@@ -19666,46 +19888,46 @@
         <v>1483</v>
       </c>
       <c r="AH1" s="86" t="s">
+        <v>1520</v>
+      </c>
+      <c r="AI1" s="86" t="s">
         <v>1521</v>
       </c>
-      <c r="AI1" s="86" t="s">
+      <c r="AJ1" s="87" t="s">
         <v>1522</v>
       </c>
-      <c r="AJ1" s="87" t="s">
+      <c r="AK1" s="87" t="s">
         <v>1523</v>
       </c>
-      <c r="AK1" s="87" t="s">
+      <c r="AL1" s="86" t="s">
         <v>1524</v>
       </c>
-      <c r="AL1" s="86" t="s">
+      <c r="AM1" s="86" t="s">
         <v>1525</v>
       </c>
-      <c r="AM1" s="86" t="s">
+      <c r="AN1" s="86" t="s">
         <v>1526</v>
       </c>
-      <c r="AN1" s="86" t="s">
+      <c r="AO1" s="86" t="s">
         <v>1527</v>
       </c>
-      <c r="AO1" s="86" t="s">
+      <c r="AP1" s="86" t="s">
         <v>1528</v>
       </c>
-      <c r="AP1" s="86" t="s">
+      <c r="AQ1" s="86" t="s">
         <v>1529</v>
       </c>
-      <c r="AQ1" s="86" t="s">
+      <c r="AR1" s="86" t="s">
         <v>1530</v>
-      </c>
-      <c r="AR1" s="86" t="s">
-        <v>1531</v>
       </c>
       <c r="AS1" s="86" t="s">
         <v>1488</v>
       </c>
       <c r="AT1" s="86" t="s">
+        <v>1531</v>
+      </c>
+      <c r="AU1" s="86" t="s">
         <v>1532</v>
-      </c>
-      <c r="AU1" s="86" t="s">
-        <v>1533</v>
       </c>
       <c r="AV1" s="86" t="s">
         <v>1483</v>
@@ -19720,16 +19942,16 @@
         <v>1486</v>
       </c>
       <c r="AZ1" s="5" t="s">
+        <v>1533</v>
+      </c>
+      <c r="BA1" s="6" t="s">
         <v>1534</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BB1" s="5" t="s">
         <v>1535</v>
       </c>
-      <c r="BB1" s="5" t="s">
+      <c r="BC1" s="5" t="s">
         <v>1536</v>
-      </c>
-      <c r="BC1" s="5" t="s">
-        <v>1537</v>
       </c>
       <c r="BD1" s="5" t="s">
         <v>1487</v>
@@ -19738,7 +19960,7 @@
         <v>1488</v>
       </c>
       <c r="BF1" s="86" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="BG1" s="87" t="s">
         <v>1490</v>
@@ -19753,7 +19975,7 @@
         <v>1493</v>
       </c>
       <c r="BK1" s="86" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="BL1" s="5" t="s">
         <v>1495</v>
@@ -19770,13 +19992,13 @@
     </row>
     <row r="2" spans="1:67">
       <c r="A2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B2" t="s">
         <v>1540</v>
       </c>
-      <c r="B2" t="s">
-        <v>1541</v>
-      </c>
       <c r="D2" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -19785,7 +20007,7 @@
         <v>5070016</v>
       </c>
       <c r="H2" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="I2" t="s">
         <v>1500</v>
@@ -19800,7 +20022,7 @@
         <v>1500</v>
       </c>
       <c r="M2" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="N2" t="s">
         <v>327</v>
@@ -19812,7 +20034,7 @@
         <v>1502</v>
       </c>
       <c r="Q2" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="S2" t="s">
         <v>1500</v>
@@ -19839,7 +20061,7 @@
         <v>2</v>
       </c>
       <c r="AA2" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="AB2">
         <v>2</v>
@@ -19851,31 +20073,31 @@
         <v>2</v>
       </c>
       <c r="AE2" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="AG2">
         <v>1</v>
       </c>
       <c r="AH2" t="s">
+        <v>1546</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>1546</v>
+      </c>
+      <c r="AJ2" s="84" t="s">
         <v>1547</v>
       </c>
-      <c r="AI2" t="s">
-        <v>1547</v>
-      </c>
-      <c r="AJ2" s="84" t="s">
+      <c r="AK2" s="84" t="s">
         <v>1548</v>
-      </c>
-      <c r="AK2" s="84" t="s">
-        <v>1549</v>
       </c>
       <c r="AO2">
         <v>36</v>
       </c>
       <c r="AQ2" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="AR2" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="AT2">
         <v>0</v>
@@ -19890,7 +20112,7 @@
         <v>202512091010</v>
       </c>
       <c r="AX2" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="AY2">
         <v>942</v>
@@ -19902,13 +20124,13 @@
         <v>1500</v>
       </c>
       <c r="BG2" s="84" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="BH2" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI2" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ2" t="s">
         <v>1500</v>
@@ -19958,7 +20180,7 @@
         <v>2</v>
       </c>
       <c r="AA3" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="AB3">
         <v>2</v>
@@ -19970,28 +20192,28 @@
         <v>2</v>
       </c>
       <c r="AE3" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="AH3" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="AI3" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="AJ3" s="84" t="s">
+        <v>1550</v>
+      </c>
+      <c r="AK3" s="84" t="s">
         <v>1551</v>
-      </c>
-      <c r="AK3" s="84" t="s">
-        <v>1552</v>
       </c>
       <c r="AO3">
         <v>76</v>
       </c>
       <c r="AQ3" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="AR3" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="AU3" t="s">
         <v>1500</v>
@@ -20003,7 +20225,7 @@
         <v>700</v>
       </c>
       <c r="AZ3" s="89" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="BA3" s="84" t="s">
         <v>1214</v>
@@ -20068,7 +20290,7 @@
         <v>2</v>
       </c>
       <c r="AA4" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="AB4">
         <v>2</v>
@@ -20080,28 +20302,28 @@
         <v>2</v>
       </c>
       <c r="AE4" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="AH4" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="AI4" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="AJ4" s="84" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="AK4" s="84" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="AO4">
         <v>58</v>
       </c>
       <c r="AQ4" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="AR4" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="AU4" t="s">
         <v>1500</v>
@@ -20110,13 +20332,13 @@
         <v>1213</v>
       </c>
       <c r="AX4" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="AY4">
         <v>700</v>
       </c>
       <c r="AZ4" s="89" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="BA4" s="91" t="s">
         <v>1214</v>
@@ -20134,13 +20356,13 @@
         <v>1500</v>
       </c>
       <c r="BG4" s="84" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="BH4" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI4" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI4" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ4" t="s">
         <v>1500</v>
@@ -20190,7 +20412,7 @@
         <v>2</v>
       </c>
       <c r="AA5" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="AB5">
         <v>2</v>
@@ -20202,28 +20424,28 @@
         <v>2</v>
       </c>
       <c r="AE5" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="AH5" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="AI5" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="AJ5" s="84" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="AK5" s="84" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="AO5">
         <v>36</v>
       </c>
       <c r="AQ5" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="AR5" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="AU5" t="s">
         <v>1500</v>
@@ -20241,10 +20463,10 @@
         <v>1500</v>
       </c>
       <c r="BH5" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI5" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ5" t="s">
         <v>1500</v>
@@ -20294,7 +20516,7 @@
         <v>2</v>
       </c>
       <c r="AA6" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="AB6">
         <v>2</v>
@@ -20306,31 +20528,31 @@
         <v>2</v>
       </c>
       <c r="AE6" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="AF6">
         <v>1</v>
       </c>
       <c r="AH6" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="AI6" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="AJ6" s="84" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="AK6" s="84" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="AO6">
         <v>36</v>
       </c>
       <c r="AQ6" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="AR6" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="AS6">
         <v>1</v>
@@ -20354,11 +20576,11 @@
         <v>1500</v>
       </c>
       <c r="BH6" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI6" t="s">
         <v>1509</v>
       </c>
-      <c r="BI6" t="s">
-        <v>1510</v>
-      </c>
       <c r="BJ6" t="s">
         <v>1500</v>
       </c>
@@ -20367,9 +20589,6 @@
       </c>
     </row>
     <row r="7" spans="1:67">
-      <c r="F7">
-        <v>1</v>
-      </c>
       <c r="I7" t="s">
         <v>1500</v>
       </c>
@@ -20399,11 +20618,11 @@
         <v>1500</v>
       </c>
       <c r="BH7" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI7" t="s">
         <v>1509</v>
       </c>
-      <c r="BI7" t="s">
-        <v>1510</v>
-      </c>
       <c r="BJ7" t="s">
         <v>1500</v>
       </c>
@@ -20412,9 +20631,6 @@
       </c>
     </row>
     <row r="8" spans="1:67">
-      <c r="F8">
-        <v>1</v>
-      </c>
       <c r="I8" t="s">
         <v>1500</v>
       </c>
@@ -20444,11 +20660,11 @@
         <v>1500</v>
       </c>
       <c r="BH8" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI8" t="s">
         <v>1509</v>
       </c>
-      <c r="BI8" t="s">
-        <v>1510</v>
-      </c>
       <c r="BJ8" t="s">
         <v>1500</v>
       </c>
@@ -20457,9 +20673,6 @@
       </c>
     </row>
     <row r="9" spans="1:67">
-      <c r="F9">
-        <v>1</v>
-      </c>
       <c r="I9" t="s">
         <v>1500</v>
       </c>
@@ -20489,11 +20702,11 @@
         <v>1500</v>
       </c>
       <c r="BH9" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI9" t="s">
         <v>1509</v>
       </c>
-      <c r="BI9" t="s">
-        <v>1510</v>
-      </c>
       <c r="BJ9" t="s">
         <v>1500</v>
       </c>
@@ -20502,9 +20715,6 @@
       </c>
     </row>
     <row r="10" spans="1:67">
-      <c r="F10">
-        <v>1</v>
-      </c>
       <c r="I10" t="s">
         <v>1500</v>
       </c>
@@ -20533,11 +20743,11 @@
         <v>1500</v>
       </c>
       <c r="BH10" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI10" t="s">
         <v>1509</v>
       </c>
-      <c r="BI10" t="s">
-        <v>1510</v>
-      </c>
       <c r="BJ10" t="s">
         <v>1500</v>
       </c>
@@ -20546,9 +20756,6 @@
       </c>
     </row>
     <row r="11" spans="1:67">
-      <c r="F11">
-        <v>1</v>
-      </c>
       <c r="I11" t="s">
         <v>1500</v>
       </c>
@@ -20579,11 +20786,11 @@
         <v>1500</v>
       </c>
       <c r="BH11" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI11" t="s">
         <v>1509</v>
       </c>
-      <c r="BI11" t="s">
-        <v>1510</v>
-      </c>
       <c r="BJ11" t="s">
         <v>1500</v>
       </c>
@@ -20592,9 +20799,6 @@
       </c>
     </row>
     <row r="12" spans="1:67">
-      <c r="F12">
-        <v>1</v>
-      </c>
       <c r="I12" t="s">
         <v>1500</v>
       </c>
@@ -20625,11 +20829,11 @@
         <v>1500</v>
       </c>
       <c r="BH12" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI12" t="s">
         <v>1509</v>
       </c>
-      <c r="BI12" t="s">
-        <v>1510</v>
-      </c>
       <c r="BJ12" t="s">
         <v>1500</v>
       </c>
@@ -20638,9 +20842,6 @@
       </c>
     </row>
     <row r="13" spans="1:67">
-      <c r="F13">
-        <v>1</v>
-      </c>
       <c r="I13" t="s">
         <v>1500</v>
       </c>
@@ -20671,11 +20872,11 @@
         <v>1500</v>
       </c>
       <c r="BH13" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI13" t="s">
         <v>1509</v>
       </c>
-      <c r="BI13" t="s">
-        <v>1510</v>
-      </c>
       <c r="BJ13" t="s">
         <v>1500</v>
       </c>
@@ -20684,9 +20885,6 @@
       </c>
     </row>
     <row r="14" spans="1:67">
-      <c r="F14">
-        <v>1</v>
-      </c>
       <c r="I14" t="s">
         <v>1500</v>
       </c>
@@ -20717,13 +20915,13 @@
         <v>1500</v>
       </c>
       <c r="BG14" s="91" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="BH14" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI14" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI14" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ14" t="s">
         <v>1500</v>
@@ -20764,10 +20962,10 @@
         <v>1500</v>
       </c>
       <c r="BH15" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI15" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI15" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ15" t="s">
         <v>1500</v>
@@ -20808,10 +21006,10 @@
         <v>1500</v>
       </c>
       <c r="BH16" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI16" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI16" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ16" t="s">
         <v>1500</v>
@@ -20852,10 +21050,10 @@
         <v>1500</v>
       </c>
       <c r="BH17" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI17" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI17" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ17" t="s">
         <v>1500</v>
@@ -20896,10 +21094,10 @@
         <v>1500</v>
       </c>
       <c r="BH18" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI18" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI18" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ18" t="s">
         <v>1500</v>
@@ -20940,10 +21138,10 @@
         <v>1500</v>
       </c>
       <c r="BH19" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI19" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI19" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ19" t="s">
         <v>1500</v>
@@ -20984,10 +21182,10 @@
         <v>1500</v>
       </c>
       <c r="BH20" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI20" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI20" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ20" t="s">
         <v>1500</v>
@@ -21028,10 +21226,10 @@
         <v>1500</v>
       </c>
       <c r="BH21" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI21" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI21" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ21" t="s">
         <v>1500</v>
@@ -21072,10 +21270,10 @@
         <v>1500</v>
       </c>
       <c r="BH22" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI22" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI22" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ22" t="s">
         <v>1500</v>
@@ -21116,10 +21314,10 @@
         <v>1500</v>
       </c>
       <c r="BH23" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI23" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI23" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ23" t="s">
         <v>1500</v>
@@ -21160,10 +21358,10 @@
         <v>1500</v>
       </c>
       <c r="BH24" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI24" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI24" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ24" t="s">
         <v>1500</v>
@@ -21204,10 +21402,10 @@
         <v>1500</v>
       </c>
       <c r="BH25" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI25" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI25" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ25" t="s">
         <v>1500</v>
@@ -21248,10 +21446,10 @@
         <v>1500</v>
       </c>
       <c r="BH26" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI26" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI26" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ26" t="s">
         <v>1500</v>
@@ -21292,10 +21490,10 @@
         <v>1500</v>
       </c>
       <c r="BH27" s="20" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BI27" t="s">
         <v>1509</v>
-      </c>
-      <c r="BI27" t="s">
-        <v>1510</v>
       </c>
       <c r="BJ27" t="s">
         <v>1500</v>
@@ -22190,11 +22388,279 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
+  <dimension ref="A1:AK3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" customWidth="1"/>
+    <col min="5" max="5" width="8.25" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.9140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="16" max="16" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.4140625" style="84" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.08203125" style="84" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.33203125" style="84" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.08203125" customWidth="1"/>
+    <col min="29" max="29" width="10.9140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="8.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37">
+      <c r="A1" s="85" t="s">
+        <v>407</v>
+      </c>
+      <c r="B1" s="85" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C1" s="85" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D1" s="85" t="s">
+        <v>1565</v>
+      </c>
+      <c r="E1" s="85" t="s">
+        <v>1566</v>
+      </c>
+      <c r="F1" s="85" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G1" s="85" t="s">
+        <v>1568</v>
+      </c>
+      <c r="H1" s="86" t="s">
+        <v>1569</v>
+      </c>
+      <c r="I1" s="86" t="s">
+        <v>1570</v>
+      </c>
+      <c r="J1" s="86" t="s">
+        <v>1571</v>
+      </c>
+      <c r="K1" s="86" t="s">
+        <v>1572</v>
+      </c>
+      <c r="L1" s="86" t="s">
+        <v>1573</v>
+      </c>
+      <c r="M1" s="86" t="s">
+        <v>1574</v>
+      </c>
+      <c r="N1" s="86" t="s">
+        <v>1575</v>
+      </c>
+      <c r="O1" s="86" t="s">
+        <v>1576</v>
+      </c>
+      <c r="P1" s="86" t="s">
+        <v>1577</v>
+      </c>
+      <c r="Q1" s="86" t="s">
+        <v>1578</v>
+      </c>
+      <c r="R1" s="86" t="s">
+        <v>1579</v>
+      </c>
+      <c r="S1" s="86" t="s">
+        <v>1580</v>
+      </c>
+      <c r="T1" s="87" t="s">
+        <v>1581</v>
+      </c>
+      <c r="U1" s="87" t="s">
+        <v>1582</v>
+      </c>
+      <c r="V1" s="86" t="s">
+        <v>1583</v>
+      </c>
+      <c r="W1" s="86" t="s">
+        <v>1584</v>
+      </c>
+      <c r="X1" s="86" t="s">
+        <v>1585</v>
+      </c>
+      <c r="Y1" s="87" t="s">
+        <v>1586</v>
+      </c>
+      <c r="Z1" s="86" t="s">
+        <v>1587</v>
+      </c>
+      <c r="AA1" s="86" t="s">
+        <v>1588</v>
+      </c>
+      <c r="AB1" s="86" t="s">
+        <v>1589</v>
+      </c>
+      <c r="AC1" s="86" t="s">
+        <v>1590</v>
+      </c>
+      <c r="AD1" s="86" t="s">
+        <v>1591</v>
+      </c>
+      <c r="AE1" s="86" t="s">
+        <v>1592</v>
+      </c>
+      <c r="AF1" s="86" t="s">
+        <v>1592</v>
+      </c>
+      <c r="AG1" s="87" t="s">
+        <v>1593</v>
+      </c>
+      <c r="AH1" s="86" t="s">
+        <v>1594</v>
+      </c>
+      <c r="AI1" s="86" t="s">
+        <v>1595</v>
+      </c>
+      <c r="AJ1" s="86" t="s">
+        <v>1592</v>
+      </c>
+      <c r="AK1" s="86" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5130008</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="N2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="P2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="Q2" s="89" t="s">
+        <v>1614</v>
+      </c>
+      <c r="R2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="S2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="T2" s="84" t="s">
+        <v>1606</v>
+      </c>
+      <c r="U2" s="84" t="s">
+        <v>1607</v>
+      </c>
+      <c r="V2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="W2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="X2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="Y2" s="84" t="s">
+        <v>1609</v>
+      </c>
+      <c r="Z2">
+        <v>10</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="AG2" s="84" t="s">
+        <v>1611</v>
+      </c>
+      <c r="AH2" s="20" t="s">
+        <v>1612</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37">
+      <c r="Y3" s="84" t="s">
+        <v>1610</v>
+      </c>
+      <c r="Z3">
+        <v>10</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Auto Finan/420财务050823.xlsx
+++ b/Auto Finan/420财务050823.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FH\source\repos\Auto Finan\Auto Finan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE0A69D-DECB-4743-B046-624563D9A46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C718D3-31F7-44FD-8F62-D657C9783F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5481,7 +5481,7 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>$$其他(专项工作酬金)111</t>
+    <t>$$评审费</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -22405,7 +22405,7 @@
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
     <col min="16" max="16" width="12.9140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.75" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.4140625" style="84" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11.08203125" style="84" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="10.83203125" bestFit="1" customWidth="1"/>
